--- a/ejemplos-generados/propuesta-simple.xlsx
+++ b/ejemplos-generados/propuesta-simple.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,16 +33,67 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
+        <bgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF176"/>
+        <bgColor rgb="00FFF176"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB74D"/>
+        <bgColor rgb="00FFB74D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9A9A"/>
+        <bgColor rgb="00EF9A9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5D6A7"/>
+        <bgColor rgb="00A5D6A7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E53935"/>
+        <bgColor rgb="00E53935"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -50,12 +101,191 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thick"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thick"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thick"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thick"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,1702 +701,1742 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Aula 7</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Aula 9</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 1","C111 ","")&amp;IF('C112'!B5="Aula 1","C112 ","")&amp;IF('C113'!B5="Aula 1","C113 ","")&amp;IF('C121'!B5="Aula 1","C121 ","")&amp;IF('C122'!B5="Aula 1","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 2","C111 ","")&amp;IF('C112'!B5="Aula 2","C112 ","")&amp;IF('C113'!B5="Aula 2","C113 ","")&amp;IF('C121'!B5="Aula 2","C121 ","")&amp;IF('C122'!B5="Aula 2","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 3","C111 ","")&amp;IF('C112'!B5="Aula 3","C112 ","")&amp;IF('C113'!B5="Aula 3","C113 ","")&amp;IF('C121'!B5="Aula 3","C121 ","")&amp;IF('C122'!B5="Aula 3","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 4","C111 ","")&amp;IF('C112'!B5="Aula 4","C112 ","")&amp;IF('C113'!B5="Aula 4","C113 ","")&amp;IF('C121'!B5="Aula 4","C121 ","")&amp;IF('C122'!B5="Aula 4","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 5","C111 ","")&amp;IF('C112'!B5="Aula 5","C112 ","")&amp;IF('C113'!B5="Aula 5","C113 ","")&amp;IF('C121'!B5="Aula 5","C121 ","")&amp;IF('C122'!B5="Aula 5","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 6","C111 ","")&amp;IF('C112'!B5="Aula 6","C112 ","")&amp;IF('C113'!B5="Aula 6","C113 ","")&amp;IF('C121'!B5="Aula 6","C121 ","")&amp;IF('C122'!B5="Aula 6","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 7","C111 ","")&amp;IF('C112'!B5="Aula 7","C112 ","")&amp;IF('C113'!B5="Aula 7","C113 ","")&amp;IF('C121'!B5="Aula 7","C121 ","")&amp;IF('C122'!B5="Aula 7","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 8","C111 ","")&amp;IF('C112'!B5="Aula 8","C112 ","")&amp;IF('C113'!B5="Aula 8","C113 ","")&amp;IF('C121'!B5="Aula 8","C121 ","")&amp;IF('C122'!B5="Aula 8","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J2" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Aula 9","C111 ","")&amp;IF('C112'!B5="Aula 9","C112 ","")&amp;IF('C113'!B5="Aula 9","C113 ","")&amp;IF('C121'!B5="Aula 9","C121 ","")&amp;IF('C122'!B5="Aula 9","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K2" s="6">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B5="Lab","C111 ","")&amp;IF('C112'!B5="Lab","C112 ","")&amp;IF('C113'!B5="Lab","C113 ","")&amp;IF('C121'!B5="Lab","C121 ","")&amp;IF('C122'!B5="Lab","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Turno 2</t>
+        </is>
+      </c>
+      <c r="B3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 1","C111 ","")&amp;IF('C112'!B7="Aula 1","C112 ","")&amp;IF('C113'!B7="Aula 1","C113 ","")&amp;IF('C121'!B7="Aula 1","C121 ","")&amp;IF('C122'!B7="Aula 1","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 2","C111 ","")&amp;IF('C112'!B7="Aula 2","C112 ","")&amp;IF('C113'!B7="Aula 2","C113 ","")&amp;IF('C121'!B7="Aula 2","C121 ","")&amp;IF('C122'!B7="Aula 2","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 3","C111 ","")&amp;IF('C112'!B7="Aula 3","C112 ","")&amp;IF('C113'!B7="Aula 3","C113 ","")&amp;IF('C121'!B7="Aula 3","C121 ","")&amp;IF('C122'!B7="Aula 3","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 4","C111 ","")&amp;IF('C112'!B7="Aula 4","C112 ","")&amp;IF('C113'!B7="Aula 4","C113 ","")&amp;IF('C121'!B7="Aula 4","C121 ","")&amp;IF('C122'!B7="Aula 4","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 5","C111 ","")&amp;IF('C112'!B7="Aula 5","C112 ","")&amp;IF('C113'!B7="Aula 5","C113 ","")&amp;IF('C121'!B7="Aula 5","C121 ","")&amp;IF('C122'!B7="Aula 5","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 6","C111 ","")&amp;IF('C112'!B7="Aula 6","C112 ","")&amp;IF('C113'!B7="Aula 6","C113 ","")&amp;IF('C121'!B7="Aula 6","C121 ","")&amp;IF('C122'!B7="Aula 6","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 7","C111 ","")&amp;IF('C112'!B7="Aula 7","C112 ","")&amp;IF('C113'!B7="Aula 7","C113 ","")&amp;IF('C121'!B7="Aula 7","C121 ","")&amp;IF('C122'!B7="Aula 7","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 8","C111 ","")&amp;IF('C112'!B7="Aula 8","C112 ","")&amp;IF('C113'!B7="Aula 8","C113 ","")&amp;IF('C121'!B7="Aula 8","C121 ","")&amp;IF('C122'!B7="Aula 8","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J3" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Aula 9","C111 ","")&amp;IF('C112'!B7="Aula 9","C112 ","")&amp;IF('C113'!B7="Aula 9","C113 ","")&amp;IF('C121'!B7="Aula 9","C121 ","")&amp;IF('C122'!B7="Aula 9","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K3" s="6">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B7="Lab","C111 ","")&amp;IF('C112'!B7="Lab","C112 ","")&amp;IF('C113'!B7="Lab","C113 ","")&amp;IF('C121'!B7="Lab","C121 ","")&amp;IF('C122'!B7="Lab","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Turno 3</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 1","C111 ","")&amp;IF('C112'!B9="Aula 1","C112 ","")&amp;IF('C113'!B9="Aula 1","C113 ","")&amp;IF('C121'!B9="Aula 1","C121 ","")&amp;IF('C122'!B9="Aula 1","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 2","C111 ","")&amp;IF('C112'!B9="Aula 2","C112 ","")&amp;IF('C113'!B9="Aula 2","C113 ","")&amp;IF('C121'!B9="Aula 2","C121 ","")&amp;IF('C122'!B9="Aula 2","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 3","C111 ","")&amp;IF('C112'!B9="Aula 3","C112 ","")&amp;IF('C113'!B9="Aula 3","C113 ","")&amp;IF('C121'!B9="Aula 3","C121 ","")&amp;IF('C122'!B9="Aula 3","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 4","C111 ","")&amp;IF('C112'!B9="Aula 4","C112 ","")&amp;IF('C113'!B9="Aula 4","C113 ","")&amp;IF('C121'!B9="Aula 4","C121 ","")&amp;IF('C122'!B9="Aula 4","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 5","C111 ","")&amp;IF('C112'!B9="Aula 5","C112 ","")&amp;IF('C113'!B9="Aula 5","C113 ","")&amp;IF('C121'!B9="Aula 5","C121 ","")&amp;IF('C122'!B9="Aula 5","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 6","C111 ","")&amp;IF('C112'!B9="Aula 6","C112 ","")&amp;IF('C113'!B9="Aula 6","C113 ","")&amp;IF('C121'!B9="Aula 6","C121 ","")&amp;IF('C122'!B9="Aula 6","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 7","C111 ","")&amp;IF('C112'!B9="Aula 7","C112 ","")&amp;IF('C113'!B9="Aula 7","C113 ","")&amp;IF('C121'!B9="Aula 7","C121 ","")&amp;IF('C122'!B9="Aula 7","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 8","C111 ","")&amp;IF('C112'!B9="Aula 8","C112 ","")&amp;IF('C113'!B9="Aula 8","C113 ","")&amp;IF('C121'!B9="Aula 8","C121 ","")&amp;IF('C122'!B9="Aula 8","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J4" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Aula 9","C111 ","")&amp;IF('C112'!B9="Aula 9","C112 ","")&amp;IF('C113'!B9="Aula 9","C113 ","")&amp;IF('C121'!B9="Aula 9","C121 ","")&amp;IF('C122'!B9="Aula 9","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K4" s="6">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B9="Lab","C111 ","")&amp;IF('C112'!B9="Lab","C112 ","")&amp;IF('C113'!B9="Lab","C113 ","")&amp;IF('C121'!B9="Lab","C121 ","")&amp;IF('C122'!B9="Lab","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Turno 4</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 1","C111 ","")&amp;IF('C112'!B11="Aula 1","C112 ","")&amp;IF('C113'!B11="Aula 1","C113 ","")&amp;IF('C121'!B11="Aula 1","C121 ","")&amp;IF('C122'!B11="Aula 1","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 2","C111 ","")&amp;IF('C112'!B11="Aula 2","C112 ","")&amp;IF('C113'!B11="Aula 2","C113 ","")&amp;IF('C121'!B11="Aula 2","C121 ","")&amp;IF('C122'!B11="Aula 2","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 3","C111 ","")&amp;IF('C112'!B11="Aula 3","C112 ","")&amp;IF('C113'!B11="Aula 3","C113 ","")&amp;IF('C121'!B11="Aula 3","C121 ","")&amp;IF('C122'!B11="Aula 3","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 4","C111 ","")&amp;IF('C112'!B11="Aula 4","C112 ","")&amp;IF('C113'!B11="Aula 4","C113 ","")&amp;IF('C121'!B11="Aula 4","C121 ","")&amp;IF('C122'!B11="Aula 4","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 5","C111 ","")&amp;IF('C112'!B11="Aula 5","C112 ","")&amp;IF('C113'!B11="Aula 5","C113 ","")&amp;IF('C121'!B11="Aula 5","C121 ","")&amp;IF('C122'!B11="Aula 5","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 6","C111 ","")&amp;IF('C112'!B11="Aula 6","C112 ","")&amp;IF('C113'!B11="Aula 6","C113 ","")&amp;IF('C121'!B11="Aula 6","C121 ","")&amp;IF('C122'!B11="Aula 6","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 7","C111 ","")&amp;IF('C112'!B11="Aula 7","C112 ","")&amp;IF('C113'!B11="Aula 7","C113 ","")&amp;IF('C121'!B11="Aula 7","C121 ","")&amp;IF('C122'!B11="Aula 7","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 8","C111 ","")&amp;IF('C112'!B11="Aula 8","C112 ","")&amp;IF('C113'!B11="Aula 8","C113 ","")&amp;IF('C121'!B11="Aula 8","C121 ","")&amp;IF('C122'!B11="Aula 8","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Aula 9","C111 ","")&amp;IF('C112'!B11="Aula 9","C112 ","")&amp;IF('C113'!B11="Aula 9","C113 ","")&amp;IF('C121'!B11="Aula 9","C121 ","")&amp;IF('C122'!B11="Aula 9","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K5" s="6">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B11="Lab","C111 ","")&amp;IF('C112'!B11="Lab","C112 ","")&amp;IF('C113'!B11="Lab","C113 ","")&amp;IF('C121'!B11="Lab","C121 ","")&amp;IF('C122'!B11="Lab","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Turno 5</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 1","C111 ","")&amp;IF('C112'!B13="Aula 1","C112 ","")&amp;IF('C113'!B13="Aula 1","C113 ","")&amp;IF('C121'!B13="Aula 1","C121 ","")&amp;IF('C122'!B13="Aula 1","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 2","C111 ","")&amp;IF('C112'!B13="Aula 2","C112 ","")&amp;IF('C113'!B13="Aula 2","C113 ","")&amp;IF('C121'!B13="Aula 2","C121 ","")&amp;IF('C122'!B13="Aula 2","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 3","C111 ","")&amp;IF('C112'!B13="Aula 3","C112 ","")&amp;IF('C113'!B13="Aula 3","C113 ","")&amp;IF('C121'!B13="Aula 3","C121 ","")&amp;IF('C122'!B13="Aula 3","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 4","C111 ","")&amp;IF('C112'!B13="Aula 4","C112 ","")&amp;IF('C113'!B13="Aula 4","C113 ","")&amp;IF('C121'!B13="Aula 4","C121 ","")&amp;IF('C122'!B13="Aula 4","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 5","C111 ","")&amp;IF('C112'!B13="Aula 5","C112 ","")&amp;IF('C113'!B13="Aula 5","C113 ","")&amp;IF('C121'!B13="Aula 5","C121 ","")&amp;IF('C122'!B13="Aula 5","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 6","C111 ","")&amp;IF('C112'!B13="Aula 6","C112 ","")&amp;IF('C113'!B13="Aula 6","C113 ","")&amp;IF('C121'!B13="Aula 6","C121 ","")&amp;IF('C122'!B13="Aula 6","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 7","C111 ","")&amp;IF('C112'!B13="Aula 7","C112 ","")&amp;IF('C113'!B13="Aula 7","C113 ","")&amp;IF('C121'!B13="Aula 7","C121 ","")&amp;IF('C122'!B13="Aula 7","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 8","C111 ","")&amp;IF('C112'!B13="Aula 8","C112 ","")&amp;IF('C113'!B13="Aula 8","C113 ","")&amp;IF('C121'!B13="Aula 8","C121 ","")&amp;IF('C122'!B13="Aula 8","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J6" s="5">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Aula 9","C111 ","")&amp;IF('C112'!B13="Aula 9","C112 ","")&amp;IF('C113'!B13="Aula 9","C113 ","")&amp;IF('C121'!B13="Aula 9","C121 ","")&amp;IF('C122'!B13="Aula 9","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K6" s="6">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B13="Lab","C111 ","")&amp;IF('C112'!B13="Lab","C112 ","")&amp;IF('C113'!B13="Lab","C113 ","")&amp;IF('C121'!B13="Lab","C121 ","")&amp;IF('C122'!B13="Lab","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Turno 6</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 1","C111 ","")&amp;IF('C112'!B15="Aula 1","C112 ","")&amp;IF('C113'!B15="Aula 1","C113 ","")&amp;IF('C121'!B15="Aula 1","C121 ","")&amp;IF('C122'!B15="Aula 1","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 2","C111 ","")&amp;IF('C112'!B15="Aula 2","C112 ","")&amp;IF('C113'!B15="Aula 2","C113 ","")&amp;IF('C121'!B15="Aula 2","C121 ","")&amp;IF('C122'!B15="Aula 2","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 3","C111 ","")&amp;IF('C112'!B15="Aula 3","C112 ","")&amp;IF('C113'!B15="Aula 3","C113 ","")&amp;IF('C121'!B15="Aula 3","C121 ","")&amp;IF('C122'!B15="Aula 3","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 4","C111 ","")&amp;IF('C112'!B15="Aula 4","C112 ","")&amp;IF('C113'!B15="Aula 4","C113 ","")&amp;IF('C121'!B15="Aula 4","C121 ","")&amp;IF('C122'!B15="Aula 4","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 5","C111 ","")&amp;IF('C112'!B15="Aula 5","C112 ","")&amp;IF('C113'!B15="Aula 5","C113 ","")&amp;IF('C121'!B15="Aula 5","C121 ","")&amp;IF('C122'!B15="Aula 5","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 6","C111 ","")&amp;IF('C112'!B15="Aula 6","C112 ","")&amp;IF('C113'!B15="Aula 6","C113 ","")&amp;IF('C121'!B15="Aula 6","C121 ","")&amp;IF('C122'!B15="Aula 6","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 7","C111 ","")&amp;IF('C112'!B15="Aula 7","C112 ","")&amp;IF('C113'!B15="Aula 7","C113 ","")&amp;IF('C121'!B15="Aula 7","C121 ","")&amp;IF('C122'!B15="Aula 7","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 8","C111 ","")&amp;IF('C112'!B15="Aula 8","C112 ","")&amp;IF('C113'!B15="Aula 8","C113 ","")&amp;IF('C121'!B15="Aula 8","C121 ","")&amp;IF('C122'!B15="Aula 8","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Aula 9","C111 ","")&amp;IF('C112'!B15="Aula 9","C112 ","")&amp;IF('C113'!B15="Aula 9","C113 ","")&amp;IF('C121'!B15="Aula 9","C121 ","")&amp;IF('C122'!B15="Aula 9","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>SUBSTITUTE(TRIM(IF('C111'!B15="Lab","C111 ","")&amp;IF('C112'!B15="Lab","C112 ","")&amp;IF('C113'!B15="Lab","C113 ","")&amp;IF('C121'!B15="Lab","C121 ","")&amp;IF('C122'!B15="Lab","C122 ",""))," ",",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 7</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 8</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Aula 9</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Turno 1</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 1","C111 ","")&amp;IF('C112'!C5="Aula 1","C112 ","")&amp;IF('C113'!C5="Aula 1","C113 ","")&amp;IF('C121'!C5="Aula 1","C121 ","")&amp;IF('C122'!C5="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C2">
+      <c r="C10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 2","C111 ","")&amp;IF('C112'!C5="Aula 2","C112 ","")&amp;IF('C113'!C5="Aula 2","C113 ","")&amp;IF('C121'!C5="Aula 2","C121 ","")&amp;IF('C122'!C5="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D2">
+      <c r="D10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 3","C111 ","")&amp;IF('C112'!C5="Aula 3","C112 ","")&amp;IF('C113'!C5="Aula 3","C113 ","")&amp;IF('C121'!C5="Aula 3","C121 ","")&amp;IF('C122'!C5="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E2">
+      <c r="E10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 4","C111 ","")&amp;IF('C112'!C5="Aula 4","C112 ","")&amp;IF('C113'!C5="Aula 4","C113 ","")&amp;IF('C121'!C5="Aula 4","C121 ","")&amp;IF('C122'!C5="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F2">
+      <c r="F10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 5","C111 ","")&amp;IF('C112'!C5="Aula 5","C112 ","")&amp;IF('C113'!C5="Aula 5","C113 ","")&amp;IF('C121'!C5="Aula 5","C121 ","")&amp;IF('C122'!C5="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G2">
+      <c r="G10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 6","C111 ","")&amp;IF('C112'!C5="Aula 6","C112 ","")&amp;IF('C113'!C5="Aula 6","C113 ","")&amp;IF('C121'!C5="Aula 6","C121 ","")&amp;IF('C122'!C5="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="H10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 7","C111 ","")&amp;IF('C112'!C5="Aula 7","C112 ","")&amp;IF('C113'!C5="Aula 7","C113 ","")&amp;IF('C121'!C5="Aula 7","C121 ","")&amp;IF('C122'!C5="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I2">
+      <c r="I10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 8","C111 ","")&amp;IF('C112'!C5="Aula 8","C112 ","")&amp;IF('C113'!C5="Aula 8","C113 ","")&amp;IF('C121'!C5="Aula 8","C121 ","")&amp;IF('C122'!C5="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J2">
+      <c r="J10" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Aula 9","C111 ","")&amp;IF('C112'!C5="Aula 9","C112 ","")&amp;IF('C113'!C5="Aula 9","C113 ","")&amp;IF('C121'!C5="Aula 9","C121 ","")&amp;IF('C122'!C5="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K2">
+      <c r="K10" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!C5="Lab","C111 ","")&amp;IF('C112'!C5="Lab","C112 ","")&amp;IF('C113'!C5="Lab","C113 ","")&amp;IF('C121'!C5="Lab","C121 ","")&amp;IF('C122'!C5="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 1","C111 ","")&amp;IF('C112'!C7="Aula 1","C112 ","")&amp;IF('C113'!C7="Aula 1","C113 ","")&amp;IF('C121'!C7="Aula 1","C121 ","")&amp;IF('C122'!C7="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C3">
+      <c r="C11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 2","C111 ","")&amp;IF('C112'!C7="Aula 2","C112 ","")&amp;IF('C113'!C7="Aula 2","C113 ","")&amp;IF('C121'!C7="Aula 2","C121 ","")&amp;IF('C122'!C7="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D3">
+      <c r="D11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 3","C111 ","")&amp;IF('C112'!C7="Aula 3","C112 ","")&amp;IF('C113'!C7="Aula 3","C113 ","")&amp;IF('C121'!C7="Aula 3","C121 ","")&amp;IF('C122'!C7="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E3">
+      <c r="E11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 4","C111 ","")&amp;IF('C112'!C7="Aula 4","C112 ","")&amp;IF('C113'!C7="Aula 4","C113 ","")&amp;IF('C121'!C7="Aula 4","C121 ","")&amp;IF('C122'!C7="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F3">
+      <c r="F11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 5","C111 ","")&amp;IF('C112'!C7="Aula 5","C112 ","")&amp;IF('C113'!C7="Aula 5","C113 ","")&amp;IF('C121'!C7="Aula 5","C121 ","")&amp;IF('C122'!C7="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G3">
+      <c r="G11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 6","C111 ","")&amp;IF('C112'!C7="Aula 6","C112 ","")&amp;IF('C113'!C7="Aula 6","C113 ","")&amp;IF('C121'!C7="Aula 6","C121 ","")&amp;IF('C122'!C7="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="H11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 7","C111 ","")&amp;IF('C112'!C7="Aula 7","C112 ","")&amp;IF('C113'!C7="Aula 7","C113 ","")&amp;IF('C121'!C7="Aula 7","C121 ","")&amp;IF('C122'!C7="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I3">
+      <c r="I11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 8","C111 ","")&amp;IF('C112'!C7="Aula 8","C112 ","")&amp;IF('C113'!C7="Aula 8","C113 ","")&amp;IF('C121'!C7="Aula 8","C121 ","")&amp;IF('C122'!C7="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J3">
+      <c r="J11" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Aula 9","C111 ","")&amp;IF('C112'!C7="Aula 9","C112 ","")&amp;IF('C113'!C7="Aula 9","C113 ","")&amp;IF('C121'!C7="Aula 9","C121 ","")&amp;IF('C122'!C7="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K3">
+      <c r="K11" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!C7="Lab","C111 ","")&amp;IF('C112'!C7="Lab","C112 ","")&amp;IF('C113'!C7="Lab","C113 ","")&amp;IF('C121'!C7="Lab","C121 ","")&amp;IF('C122'!C7="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 1","C111 ","")&amp;IF('C112'!C9="Aula 1","C112 ","")&amp;IF('C113'!C9="Aula 1","C113 ","")&amp;IF('C121'!C9="Aula 1","C121 ","")&amp;IF('C122'!C9="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C4">
+      <c r="C12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 2","C111 ","")&amp;IF('C112'!C9="Aula 2","C112 ","")&amp;IF('C113'!C9="Aula 2","C113 ","")&amp;IF('C121'!C9="Aula 2","C121 ","")&amp;IF('C122'!C9="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D4">
+      <c r="D12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 3","C111 ","")&amp;IF('C112'!C9="Aula 3","C112 ","")&amp;IF('C113'!C9="Aula 3","C113 ","")&amp;IF('C121'!C9="Aula 3","C121 ","")&amp;IF('C122'!C9="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E4">
+      <c r="E12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 4","C111 ","")&amp;IF('C112'!C9="Aula 4","C112 ","")&amp;IF('C113'!C9="Aula 4","C113 ","")&amp;IF('C121'!C9="Aula 4","C121 ","")&amp;IF('C122'!C9="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F4">
+      <c r="F12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 5","C111 ","")&amp;IF('C112'!C9="Aula 5","C112 ","")&amp;IF('C113'!C9="Aula 5","C113 ","")&amp;IF('C121'!C9="Aula 5","C121 ","")&amp;IF('C122'!C9="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="G12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 6","C111 ","")&amp;IF('C112'!C9="Aula 6","C112 ","")&amp;IF('C113'!C9="Aula 6","C113 ","")&amp;IF('C121'!C9="Aula 6","C121 ","")&amp;IF('C122'!C9="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="H12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 7","C111 ","")&amp;IF('C112'!C9="Aula 7","C112 ","")&amp;IF('C113'!C9="Aula 7","C113 ","")&amp;IF('C121'!C9="Aula 7","C121 ","")&amp;IF('C122'!C9="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I4">
+      <c r="I12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 8","C111 ","")&amp;IF('C112'!C9="Aula 8","C112 ","")&amp;IF('C113'!C9="Aula 8","C113 ","")&amp;IF('C121'!C9="Aula 8","C121 ","")&amp;IF('C122'!C9="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J4">
+      <c r="J12" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Aula 9","C111 ","")&amp;IF('C112'!C9="Aula 9","C112 ","")&amp;IF('C113'!C9="Aula 9","C113 ","")&amp;IF('C121'!C9="Aula 9","C121 ","")&amp;IF('C122'!C9="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K4">
+      <c r="K12" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!C9="Lab","C111 ","")&amp;IF('C112'!C9="Lab","C112 ","")&amp;IF('C113'!C9="Lab","C113 ","")&amp;IF('C121'!C9="Lab","C121 ","")&amp;IF('C122'!C9="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 1","C111 ","")&amp;IF('C112'!C11="Aula 1","C112 ","")&amp;IF('C113'!C11="Aula 1","C113 ","")&amp;IF('C121'!C11="Aula 1","C121 ","")&amp;IF('C122'!C11="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C5">
+      <c r="C13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 2","C111 ","")&amp;IF('C112'!C11="Aula 2","C112 ","")&amp;IF('C113'!C11="Aula 2","C113 ","")&amp;IF('C121'!C11="Aula 2","C121 ","")&amp;IF('C122'!C11="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D5">
+      <c r="D13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 3","C111 ","")&amp;IF('C112'!C11="Aula 3","C112 ","")&amp;IF('C113'!C11="Aula 3","C113 ","")&amp;IF('C121'!C11="Aula 3","C121 ","")&amp;IF('C122'!C11="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 4","C111 ","")&amp;IF('C112'!C11="Aula 4","C112 ","")&amp;IF('C113'!C11="Aula 4","C113 ","")&amp;IF('C121'!C11="Aula 4","C121 ","")&amp;IF('C122'!C11="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 5","C111 ","")&amp;IF('C112'!C11="Aula 5","C112 ","")&amp;IF('C113'!C11="Aula 5","C113 ","")&amp;IF('C121'!C11="Aula 5","C121 ","")&amp;IF('C122'!C11="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 6","C111 ","")&amp;IF('C112'!C11="Aula 6","C112 ","")&amp;IF('C113'!C11="Aula 6","C113 ","")&amp;IF('C121'!C11="Aula 6","C121 ","")&amp;IF('C122'!C11="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 7","C111 ","")&amp;IF('C112'!C11="Aula 7","C112 ","")&amp;IF('C113'!C11="Aula 7","C113 ","")&amp;IF('C121'!C11="Aula 7","C121 ","")&amp;IF('C122'!C11="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I5">
+      <c r="I13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 8","C111 ","")&amp;IF('C112'!C11="Aula 8","C112 ","")&amp;IF('C113'!C11="Aula 8","C113 ","")&amp;IF('C121'!C11="Aula 8","C121 ","")&amp;IF('C122'!C11="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J5">
+      <c r="J13" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Aula 9","C111 ","")&amp;IF('C112'!C11="Aula 9","C112 ","")&amp;IF('C113'!C11="Aula 9","C113 ","")&amp;IF('C121'!C11="Aula 9","C121 ","")&amp;IF('C122'!C11="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K5">
+      <c r="K13" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!C11="Lab","C111 ","")&amp;IF('C112'!C11="Lab","C112 ","")&amp;IF('C113'!C11="Lab","C113 ","")&amp;IF('C121'!C11="Lab","C121 ","")&amp;IF('C122'!C11="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 1","C111 ","")&amp;IF('C112'!C13="Aula 1","C112 ","")&amp;IF('C113'!C13="Aula 1","C113 ","")&amp;IF('C121'!C13="Aula 1","C121 ","")&amp;IF('C122'!C13="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 2","C111 ","")&amp;IF('C112'!C13="Aula 2","C112 ","")&amp;IF('C113'!C13="Aula 2","C113 ","")&amp;IF('C121'!C13="Aula 2","C121 ","")&amp;IF('C122'!C13="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 3","C111 ","")&amp;IF('C112'!C13="Aula 3","C112 ","")&amp;IF('C113'!C13="Aula 3","C113 ","")&amp;IF('C121'!C13="Aula 3","C121 ","")&amp;IF('C122'!C13="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 4","C111 ","")&amp;IF('C112'!C13="Aula 4","C112 ","")&amp;IF('C113'!C13="Aula 4","C113 ","")&amp;IF('C121'!C13="Aula 4","C121 ","")&amp;IF('C122'!C13="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 5","C111 ","")&amp;IF('C112'!C13="Aula 5","C112 ","")&amp;IF('C113'!C13="Aula 5","C113 ","")&amp;IF('C121'!C13="Aula 5","C121 ","")&amp;IF('C122'!C13="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 6","C111 ","")&amp;IF('C112'!C13="Aula 6","C112 ","")&amp;IF('C113'!C13="Aula 6","C113 ","")&amp;IF('C121'!C13="Aula 6","C121 ","")&amp;IF('C122'!C13="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 7","C111 ","")&amp;IF('C112'!C13="Aula 7","C112 ","")&amp;IF('C113'!C13="Aula 7","C113 ","")&amp;IF('C121'!C13="Aula 7","C121 ","")&amp;IF('C122'!C13="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I6">
+      <c r="I14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 8","C111 ","")&amp;IF('C112'!C13="Aula 8","C112 ","")&amp;IF('C113'!C13="Aula 8","C113 ","")&amp;IF('C121'!C13="Aula 8","C121 ","")&amp;IF('C122'!C13="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J6">
+      <c r="J14" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Aula 9","C111 ","")&amp;IF('C112'!C13="Aula 9","C112 ","")&amp;IF('C113'!C13="Aula 9","C113 ","")&amp;IF('C121'!C13="Aula 9","C121 ","")&amp;IF('C122'!C13="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K6">
+      <c r="K14" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!C13="Lab","C111 ","")&amp;IF('C112'!C13="Lab","C112 ","")&amp;IF('C113'!C13="Lab","C113 ","")&amp;IF('C121'!C13="Lab","C121 ","")&amp;IF('C122'!C13="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 1","C111 ","")&amp;IF('C112'!C15="Aula 1","C112 ","")&amp;IF('C113'!C15="Aula 1","C113 ","")&amp;IF('C121'!C15="Aula 1","C121 ","")&amp;IF('C122'!C15="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C7">
+      <c r="C15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 2","C111 ","")&amp;IF('C112'!C15="Aula 2","C112 ","")&amp;IF('C113'!C15="Aula 2","C113 ","")&amp;IF('C121'!C15="Aula 2","C121 ","")&amp;IF('C122'!C15="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D7">
+      <c r="D15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 3","C111 ","")&amp;IF('C112'!C15="Aula 3","C112 ","")&amp;IF('C113'!C15="Aula 3","C113 ","")&amp;IF('C121'!C15="Aula 3","C121 ","")&amp;IF('C122'!C15="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E7">
+      <c r="E15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 4","C111 ","")&amp;IF('C112'!C15="Aula 4","C112 ","")&amp;IF('C113'!C15="Aula 4","C113 ","")&amp;IF('C121'!C15="Aula 4","C121 ","")&amp;IF('C122'!C15="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F7">
+      <c r="F15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 5","C111 ","")&amp;IF('C112'!C15="Aula 5","C112 ","")&amp;IF('C113'!C15="Aula 5","C113 ","")&amp;IF('C121'!C15="Aula 5","C121 ","")&amp;IF('C122'!C15="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G7">
+      <c r="G15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 6","C111 ","")&amp;IF('C112'!C15="Aula 6","C112 ","")&amp;IF('C113'!C15="Aula 6","C113 ","")&amp;IF('C121'!C15="Aula 6","C121 ","")&amp;IF('C122'!C15="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="H15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 7","C111 ","")&amp;IF('C112'!C15="Aula 7","C112 ","")&amp;IF('C113'!C15="Aula 7","C113 ","")&amp;IF('C121'!C15="Aula 7","C121 ","")&amp;IF('C122'!C15="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I7">
+      <c r="I15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 8","C111 ","")&amp;IF('C112'!C15="Aula 8","C112 ","")&amp;IF('C113'!C15="Aula 8","C113 ","")&amp;IF('C121'!C15="Aula 8","C121 ","")&amp;IF('C122'!C15="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J7">
+      <c r="J15" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Aula 9","C111 ","")&amp;IF('C112'!C15="Aula 9","C112 ","")&amp;IF('C113'!C15="Aula 9","C113 ","")&amp;IF('C121'!C15="Aula 9","C121 ","")&amp;IF('C122'!C15="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K7">
+      <c r="K15" s="9">
         <f>SUBSTITUTE(TRIM(IF('C111'!C15="Lab","C111 ","")&amp;IF('C112'!C15="Lab","C112 ","")&amp;IF('C113'!C15="Lab","C113 ","")&amp;IF('C121'!C15="Lab","C121 ","")&amp;IF('C122'!C15="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Aula 7</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Aula 9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 1","C111 ","")&amp;IF('C112'!D5="Aula 1","C112 ","")&amp;IF('C113'!D5="Aula 1","C113 ","")&amp;IF('C121'!D5="Aula 1","C121 ","")&amp;IF('C122'!D5="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C10">
+      <c r="C18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 2","C111 ","")&amp;IF('C112'!D5="Aula 2","C112 ","")&amp;IF('C113'!D5="Aula 2","C113 ","")&amp;IF('C121'!D5="Aula 2","C121 ","")&amp;IF('C122'!D5="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D10">
+      <c r="D18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 3","C111 ","")&amp;IF('C112'!D5="Aula 3","C112 ","")&amp;IF('C113'!D5="Aula 3","C113 ","")&amp;IF('C121'!D5="Aula 3","C121 ","")&amp;IF('C122'!D5="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E10">
+      <c r="E18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 4","C111 ","")&amp;IF('C112'!D5="Aula 4","C112 ","")&amp;IF('C113'!D5="Aula 4","C113 ","")&amp;IF('C121'!D5="Aula 4","C121 ","")&amp;IF('C122'!D5="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 5","C111 ","")&amp;IF('C112'!D5="Aula 5","C112 ","")&amp;IF('C113'!D5="Aula 5","C113 ","")&amp;IF('C121'!D5="Aula 5","C121 ","")&amp;IF('C122'!D5="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="G18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 6","C111 ","")&amp;IF('C112'!D5="Aula 6","C112 ","")&amp;IF('C113'!D5="Aula 6","C113 ","")&amp;IF('C121'!D5="Aula 6","C121 ","")&amp;IF('C122'!D5="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H10">
+      <c r="H18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 7","C111 ","")&amp;IF('C112'!D5="Aula 7","C112 ","")&amp;IF('C113'!D5="Aula 7","C113 ","")&amp;IF('C121'!D5="Aula 7","C121 ","")&amp;IF('C122'!D5="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I10">
+      <c r="I18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 8","C111 ","")&amp;IF('C112'!D5="Aula 8","C112 ","")&amp;IF('C113'!D5="Aula 8","C113 ","")&amp;IF('C121'!D5="Aula 8","C121 ","")&amp;IF('C122'!D5="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J10">
+      <c r="J18" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Aula 9","C111 ","")&amp;IF('C112'!D5="Aula 9","C112 ","")&amp;IF('C113'!D5="Aula 9","C113 ","")&amp;IF('C121'!D5="Aula 9","C121 ","")&amp;IF('C122'!D5="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K10">
+      <c r="K18" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!D5="Lab","C111 ","")&amp;IF('C112'!D5="Lab","C112 ","")&amp;IF('C113'!D5="Lab","C113 ","")&amp;IF('C121'!D5="Lab","C121 ","")&amp;IF('C122'!D5="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 1","C111 ","")&amp;IF('C112'!D7="Aula 1","C112 ","")&amp;IF('C113'!D7="Aula 1","C113 ","")&amp;IF('C121'!D7="Aula 1","C121 ","")&amp;IF('C122'!D7="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C11">
+      <c r="C19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 2","C111 ","")&amp;IF('C112'!D7="Aula 2","C112 ","")&amp;IF('C113'!D7="Aula 2","C113 ","")&amp;IF('C121'!D7="Aula 2","C121 ","")&amp;IF('C122'!D7="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D11">
+      <c r="D19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 3","C111 ","")&amp;IF('C112'!D7="Aula 3","C112 ","")&amp;IF('C113'!D7="Aula 3","C113 ","")&amp;IF('C121'!D7="Aula 3","C121 ","")&amp;IF('C122'!D7="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E11">
+      <c r="E19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 4","C111 ","")&amp;IF('C112'!D7="Aula 4","C112 ","")&amp;IF('C113'!D7="Aula 4","C113 ","")&amp;IF('C121'!D7="Aula 4","C121 ","")&amp;IF('C122'!D7="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F11">
+      <c r="F19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 5","C111 ","")&amp;IF('C112'!D7="Aula 5","C112 ","")&amp;IF('C113'!D7="Aula 5","C113 ","")&amp;IF('C121'!D7="Aula 5","C121 ","")&amp;IF('C122'!D7="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G11">
+      <c r="G19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 6","C111 ","")&amp;IF('C112'!D7="Aula 6","C112 ","")&amp;IF('C113'!D7="Aula 6","C113 ","")&amp;IF('C121'!D7="Aula 6","C121 ","")&amp;IF('C122'!D7="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="H19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 7","C111 ","")&amp;IF('C112'!D7="Aula 7","C112 ","")&amp;IF('C113'!D7="Aula 7","C113 ","")&amp;IF('C121'!D7="Aula 7","C121 ","")&amp;IF('C122'!D7="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I11">
+      <c r="I19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 8","C111 ","")&amp;IF('C112'!D7="Aula 8","C112 ","")&amp;IF('C113'!D7="Aula 8","C113 ","")&amp;IF('C121'!D7="Aula 8","C121 ","")&amp;IF('C122'!D7="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J11">
+      <c r="J19" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Aula 9","C111 ","")&amp;IF('C112'!D7="Aula 9","C112 ","")&amp;IF('C113'!D7="Aula 9","C113 ","")&amp;IF('C121'!D7="Aula 9","C121 ","")&amp;IF('C122'!D7="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K11">
+      <c r="K19" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!D7="Lab","C111 ","")&amp;IF('C112'!D7="Lab","C112 ","")&amp;IF('C113'!D7="Lab","C113 ","")&amp;IF('C121'!D7="Lab","C121 ","")&amp;IF('C122'!D7="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 1","C111 ","")&amp;IF('C112'!D9="Aula 1","C112 ","")&amp;IF('C113'!D9="Aula 1","C113 ","")&amp;IF('C121'!D9="Aula 1","C121 ","")&amp;IF('C122'!D9="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C12">
+      <c r="C20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 2","C111 ","")&amp;IF('C112'!D9="Aula 2","C112 ","")&amp;IF('C113'!D9="Aula 2","C113 ","")&amp;IF('C121'!D9="Aula 2","C121 ","")&amp;IF('C122'!D9="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D12">
+      <c r="D20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 3","C111 ","")&amp;IF('C112'!D9="Aula 3","C112 ","")&amp;IF('C113'!D9="Aula 3","C113 ","")&amp;IF('C121'!D9="Aula 3","C121 ","")&amp;IF('C122'!D9="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E12">
+      <c r="E20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 4","C111 ","")&amp;IF('C112'!D9="Aula 4","C112 ","")&amp;IF('C113'!D9="Aula 4","C113 ","")&amp;IF('C121'!D9="Aula 4","C121 ","")&amp;IF('C122'!D9="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 5","C111 ","")&amp;IF('C112'!D9="Aula 5","C112 ","")&amp;IF('C113'!D9="Aula 5","C113 ","")&amp;IF('C121'!D9="Aula 5","C121 ","")&amp;IF('C122'!D9="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G12">
+      <c r="G20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 6","C111 ","")&amp;IF('C112'!D9="Aula 6","C112 ","")&amp;IF('C113'!D9="Aula 6","C113 ","")&amp;IF('C121'!D9="Aula 6","C121 ","")&amp;IF('C122'!D9="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="H20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 7","C111 ","")&amp;IF('C112'!D9="Aula 7","C112 ","")&amp;IF('C113'!D9="Aula 7","C113 ","")&amp;IF('C121'!D9="Aula 7","C121 ","")&amp;IF('C122'!D9="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I12">
+      <c r="I20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 8","C111 ","")&amp;IF('C112'!D9="Aula 8","C112 ","")&amp;IF('C113'!D9="Aula 8","C113 ","")&amp;IF('C121'!D9="Aula 8","C121 ","")&amp;IF('C122'!D9="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J12">
+      <c r="J20" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Aula 9","C111 ","")&amp;IF('C112'!D9="Aula 9","C112 ","")&amp;IF('C113'!D9="Aula 9","C113 ","")&amp;IF('C121'!D9="Aula 9","C121 ","")&amp;IF('C122'!D9="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K12">
+      <c r="K20" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!D9="Lab","C111 ","")&amp;IF('C112'!D9="Lab","C112 ","")&amp;IF('C113'!D9="Lab","C113 ","")&amp;IF('C121'!D9="Lab","C121 ","")&amp;IF('C122'!D9="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 1","C111 ","")&amp;IF('C112'!D11="Aula 1","C112 ","")&amp;IF('C113'!D11="Aula 1","C113 ","")&amp;IF('C121'!D11="Aula 1","C121 ","")&amp;IF('C122'!D11="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C13">
+      <c r="C21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 2","C111 ","")&amp;IF('C112'!D11="Aula 2","C112 ","")&amp;IF('C113'!D11="Aula 2","C113 ","")&amp;IF('C121'!D11="Aula 2","C121 ","")&amp;IF('C122'!D11="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D13">
+      <c r="D21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 3","C111 ","")&amp;IF('C112'!D11="Aula 3","C112 ","")&amp;IF('C113'!D11="Aula 3","C113 ","")&amp;IF('C121'!D11="Aula 3","C121 ","")&amp;IF('C122'!D11="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E13">
+      <c r="E21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 4","C111 ","")&amp;IF('C112'!D11="Aula 4","C112 ","")&amp;IF('C113'!D11="Aula 4","C113 ","")&amp;IF('C121'!D11="Aula 4","C121 ","")&amp;IF('C122'!D11="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="F21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 5","C111 ","")&amp;IF('C112'!D11="Aula 5","C112 ","")&amp;IF('C113'!D11="Aula 5","C113 ","")&amp;IF('C121'!D11="Aula 5","C121 ","")&amp;IF('C122'!D11="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G13">
+      <c r="G21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 6","C111 ","")&amp;IF('C112'!D11="Aula 6","C112 ","")&amp;IF('C113'!D11="Aula 6","C113 ","")&amp;IF('C121'!D11="Aula 6","C121 ","")&amp;IF('C122'!D11="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H13">
+      <c r="H21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 7","C111 ","")&amp;IF('C112'!D11="Aula 7","C112 ","")&amp;IF('C113'!D11="Aula 7","C113 ","")&amp;IF('C121'!D11="Aula 7","C121 ","")&amp;IF('C122'!D11="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I13">
+      <c r="I21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 8","C111 ","")&amp;IF('C112'!D11="Aula 8","C112 ","")&amp;IF('C113'!D11="Aula 8","C113 ","")&amp;IF('C121'!D11="Aula 8","C121 ","")&amp;IF('C122'!D11="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J13">
+      <c r="J21" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Aula 9","C111 ","")&amp;IF('C112'!D11="Aula 9","C112 ","")&amp;IF('C113'!D11="Aula 9","C113 ","")&amp;IF('C121'!D11="Aula 9","C121 ","")&amp;IF('C122'!D11="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K13">
+      <c r="K21" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!D11="Lab","C111 ","")&amp;IF('C112'!D11="Lab","C112 ","")&amp;IF('C113'!D11="Lab","C113 ","")&amp;IF('C121'!D11="Lab","C121 ","")&amp;IF('C122'!D11="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 1","C111 ","")&amp;IF('C112'!D13="Aula 1","C112 ","")&amp;IF('C113'!D13="Aula 1","C113 ","")&amp;IF('C121'!D13="Aula 1","C121 ","")&amp;IF('C122'!D13="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C14">
+      <c r="C22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 2","C111 ","")&amp;IF('C112'!D13="Aula 2","C112 ","")&amp;IF('C113'!D13="Aula 2","C113 ","")&amp;IF('C121'!D13="Aula 2","C121 ","")&amp;IF('C122'!D13="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D14">
+      <c r="D22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 3","C111 ","")&amp;IF('C112'!D13="Aula 3","C112 ","")&amp;IF('C113'!D13="Aula 3","C113 ","")&amp;IF('C121'!D13="Aula 3","C121 ","")&amp;IF('C122'!D13="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E14">
+      <c r="E22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 4","C111 ","")&amp;IF('C112'!D13="Aula 4","C112 ","")&amp;IF('C113'!D13="Aula 4","C113 ","")&amp;IF('C121'!D13="Aula 4","C121 ","")&amp;IF('C122'!D13="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F14">
+      <c r="F22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 5","C111 ","")&amp;IF('C112'!D13="Aula 5","C112 ","")&amp;IF('C113'!D13="Aula 5","C113 ","")&amp;IF('C121'!D13="Aula 5","C121 ","")&amp;IF('C122'!D13="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G14">
+      <c r="G22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 6","C111 ","")&amp;IF('C112'!D13="Aula 6","C112 ","")&amp;IF('C113'!D13="Aula 6","C113 ","")&amp;IF('C121'!D13="Aula 6","C121 ","")&amp;IF('C122'!D13="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H14">
+      <c r="H22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 7","C111 ","")&amp;IF('C112'!D13="Aula 7","C112 ","")&amp;IF('C113'!D13="Aula 7","C113 ","")&amp;IF('C121'!D13="Aula 7","C121 ","")&amp;IF('C122'!D13="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I14">
+      <c r="I22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 8","C111 ","")&amp;IF('C112'!D13="Aula 8","C112 ","")&amp;IF('C113'!D13="Aula 8","C113 ","")&amp;IF('C121'!D13="Aula 8","C121 ","")&amp;IF('C122'!D13="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J14">
+      <c r="J22" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Aula 9","C111 ","")&amp;IF('C112'!D13="Aula 9","C112 ","")&amp;IF('C113'!D13="Aula 9","C113 ","")&amp;IF('C121'!D13="Aula 9","C121 ","")&amp;IF('C122'!D13="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K14">
+      <c r="K22" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!D13="Lab","C111 ","")&amp;IF('C112'!D13="Lab","C112 ","")&amp;IF('C113'!D13="Lab","C113 ","")&amp;IF('C121'!D13="Lab","C121 ","")&amp;IF('C122'!D13="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 1","C111 ","")&amp;IF('C112'!D15="Aula 1","C112 ","")&amp;IF('C113'!D15="Aula 1","C113 ","")&amp;IF('C121'!D15="Aula 1","C121 ","")&amp;IF('C122'!D15="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C15">
+      <c r="C23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 2","C111 ","")&amp;IF('C112'!D15="Aula 2","C112 ","")&amp;IF('C113'!D15="Aula 2","C113 ","")&amp;IF('C121'!D15="Aula 2","C121 ","")&amp;IF('C122'!D15="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D15">
+      <c r="D23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 3","C111 ","")&amp;IF('C112'!D15="Aula 3","C112 ","")&amp;IF('C113'!D15="Aula 3","C113 ","")&amp;IF('C121'!D15="Aula 3","C121 ","")&amp;IF('C122'!D15="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E15">
+      <c r="E23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 4","C111 ","")&amp;IF('C112'!D15="Aula 4","C112 ","")&amp;IF('C113'!D15="Aula 4","C113 ","")&amp;IF('C121'!D15="Aula 4","C121 ","")&amp;IF('C122'!D15="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 5","C111 ","")&amp;IF('C112'!D15="Aula 5","C112 ","")&amp;IF('C113'!D15="Aula 5","C113 ","")&amp;IF('C121'!D15="Aula 5","C121 ","")&amp;IF('C122'!D15="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G15">
+      <c r="G23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 6","C111 ","")&amp;IF('C112'!D15="Aula 6","C112 ","")&amp;IF('C113'!D15="Aula 6","C113 ","")&amp;IF('C121'!D15="Aula 6","C121 ","")&amp;IF('C122'!D15="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H15">
+      <c r="H23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 7","C111 ","")&amp;IF('C112'!D15="Aula 7","C112 ","")&amp;IF('C113'!D15="Aula 7","C113 ","")&amp;IF('C121'!D15="Aula 7","C121 ","")&amp;IF('C122'!D15="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I15">
+      <c r="I23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 8","C111 ","")&amp;IF('C112'!D15="Aula 8","C112 ","")&amp;IF('C113'!D15="Aula 8","C113 ","")&amp;IF('C121'!D15="Aula 8","C121 ","")&amp;IF('C122'!D15="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J15">
+      <c r="J23" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Aula 9","C111 ","")&amp;IF('C112'!D15="Aula 9","C112 ","")&amp;IF('C113'!D15="Aula 9","C113 ","")&amp;IF('C121'!D15="Aula 9","C121 ","")&amp;IF('C122'!D15="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K15">
+      <c r="K23" s="9">
         <f>SUBSTITUTE(TRIM(IF('C111'!D15="Lab","C111 ","")&amp;IF('C112'!D15="Lab","C112 ","")&amp;IF('C113'!D15="Lab","C113 ","")&amp;IF('C121'!D15="Lab","C121 ","")&amp;IF('C122'!D15="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Aula 7</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Aula 9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 1","C111 ","")&amp;IF('C112'!E5="Aula 1","C112 ","")&amp;IF('C113'!E5="Aula 1","C113 ","")&amp;IF('C121'!E5="Aula 1","C121 ","")&amp;IF('C122'!E5="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C18">
+      <c r="C26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 2","C111 ","")&amp;IF('C112'!E5="Aula 2","C112 ","")&amp;IF('C113'!E5="Aula 2","C113 ","")&amp;IF('C121'!E5="Aula 2","C121 ","")&amp;IF('C122'!E5="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D18">
+      <c r="D26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 3","C111 ","")&amp;IF('C112'!E5="Aula 3","C112 ","")&amp;IF('C113'!E5="Aula 3","C113 ","")&amp;IF('C121'!E5="Aula 3","C121 ","")&amp;IF('C122'!E5="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E18">
+      <c r="E26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 4","C111 ","")&amp;IF('C112'!E5="Aula 4","C112 ","")&amp;IF('C113'!E5="Aula 4","C113 ","")&amp;IF('C121'!E5="Aula 4","C121 ","")&amp;IF('C122'!E5="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="F26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 5","C111 ","")&amp;IF('C112'!E5="Aula 5","C112 ","")&amp;IF('C113'!E5="Aula 5","C113 ","")&amp;IF('C121'!E5="Aula 5","C121 ","")&amp;IF('C122'!E5="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G18">
+      <c r="G26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 6","C111 ","")&amp;IF('C112'!E5="Aula 6","C112 ","")&amp;IF('C113'!E5="Aula 6","C113 ","")&amp;IF('C121'!E5="Aula 6","C121 ","")&amp;IF('C122'!E5="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H18">
+      <c r="H26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 7","C111 ","")&amp;IF('C112'!E5="Aula 7","C112 ","")&amp;IF('C113'!E5="Aula 7","C113 ","")&amp;IF('C121'!E5="Aula 7","C121 ","")&amp;IF('C122'!E5="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I18">
+      <c r="I26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 8","C111 ","")&amp;IF('C112'!E5="Aula 8","C112 ","")&amp;IF('C113'!E5="Aula 8","C113 ","")&amp;IF('C121'!E5="Aula 8","C121 ","")&amp;IF('C122'!E5="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J18">
+      <c r="J26" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Aula 9","C111 ","")&amp;IF('C112'!E5="Aula 9","C112 ","")&amp;IF('C113'!E5="Aula 9","C113 ","")&amp;IF('C121'!E5="Aula 9","C121 ","")&amp;IF('C122'!E5="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K18">
+      <c r="K26" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!E5="Lab","C111 ","")&amp;IF('C112'!E5="Lab","C112 ","")&amp;IF('C113'!E5="Lab","C113 ","")&amp;IF('C121'!E5="Lab","C121 ","")&amp;IF('C122'!E5="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 1","C111 ","")&amp;IF('C112'!E7="Aula 1","C112 ","")&amp;IF('C113'!E7="Aula 1","C113 ","")&amp;IF('C121'!E7="Aula 1","C121 ","")&amp;IF('C122'!E7="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C19">
+      <c r="C27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 2","C111 ","")&amp;IF('C112'!E7="Aula 2","C112 ","")&amp;IF('C113'!E7="Aula 2","C113 ","")&amp;IF('C121'!E7="Aula 2","C121 ","")&amp;IF('C122'!E7="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D19">
+      <c r="D27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 3","C111 ","")&amp;IF('C112'!E7="Aula 3","C112 ","")&amp;IF('C113'!E7="Aula 3","C113 ","")&amp;IF('C121'!E7="Aula 3","C121 ","")&amp;IF('C122'!E7="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E19">
+      <c r="E27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 4","C111 ","")&amp;IF('C112'!E7="Aula 4","C112 ","")&amp;IF('C113'!E7="Aula 4","C113 ","")&amp;IF('C121'!E7="Aula 4","C121 ","")&amp;IF('C122'!E7="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="F27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 5","C111 ","")&amp;IF('C112'!E7="Aula 5","C112 ","")&amp;IF('C113'!E7="Aula 5","C113 ","")&amp;IF('C121'!E7="Aula 5","C121 ","")&amp;IF('C122'!E7="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G19">
+      <c r="G27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 6","C111 ","")&amp;IF('C112'!E7="Aula 6","C112 ","")&amp;IF('C113'!E7="Aula 6","C113 ","")&amp;IF('C121'!E7="Aula 6","C121 ","")&amp;IF('C122'!E7="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H19">
+      <c r="H27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 7","C111 ","")&amp;IF('C112'!E7="Aula 7","C112 ","")&amp;IF('C113'!E7="Aula 7","C113 ","")&amp;IF('C121'!E7="Aula 7","C121 ","")&amp;IF('C122'!E7="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I19">
+      <c r="I27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 8","C111 ","")&amp;IF('C112'!E7="Aula 8","C112 ","")&amp;IF('C113'!E7="Aula 8","C113 ","")&amp;IF('C121'!E7="Aula 8","C121 ","")&amp;IF('C122'!E7="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J19">
+      <c r="J27" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Aula 9","C111 ","")&amp;IF('C112'!E7="Aula 9","C112 ","")&amp;IF('C113'!E7="Aula 9","C113 ","")&amp;IF('C121'!E7="Aula 9","C121 ","")&amp;IF('C122'!E7="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K19">
+      <c r="K27" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!E7="Lab","C111 ","")&amp;IF('C112'!E7="Lab","C112 ","")&amp;IF('C113'!E7="Lab","C113 ","")&amp;IF('C121'!E7="Lab","C121 ","")&amp;IF('C122'!E7="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 1","C111 ","")&amp;IF('C112'!E9="Aula 1","C112 ","")&amp;IF('C113'!E9="Aula 1","C113 ","")&amp;IF('C121'!E9="Aula 1","C121 ","")&amp;IF('C122'!E9="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C20">
+      <c r="C28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 2","C111 ","")&amp;IF('C112'!E9="Aula 2","C112 ","")&amp;IF('C113'!E9="Aula 2","C113 ","")&amp;IF('C121'!E9="Aula 2","C121 ","")&amp;IF('C122'!E9="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D20">
+      <c r="D28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 3","C111 ","")&amp;IF('C112'!E9="Aula 3","C112 ","")&amp;IF('C113'!E9="Aula 3","C113 ","")&amp;IF('C121'!E9="Aula 3","C121 ","")&amp;IF('C122'!E9="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E20">
+      <c r="E28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 4","C111 ","")&amp;IF('C112'!E9="Aula 4","C112 ","")&amp;IF('C113'!E9="Aula 4","C113 ","")&amp;IF('C121'!E9="Aula 4","C121 ","")&amp;IF('C122'!E9="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 5","C111 ","")&amp;IF('C112'!E9="Aula 5","C112 ","")&amp;IF('C113'!E9="Aula 5","C113 ","")&amp;IF('C121'!E9="Aula 5","C121 ","")&amp;IF('C122'!E9="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G20">
+      <c r="G28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 6","C111 ","")&amp;IF('C112'!E9="Aula 6","C112 ","")&amp;IF('C113'!E9="Aula 6","C113 ","")&amp;IF('C121'!E9="Aula 6","C121 ","")&amp;IF('C122'!E9="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H20">
+      <c r="H28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 7","C111 ","")&amp;IF('C112'!E9="Aula 7","C112 ","")&amp;IF('C113'!E9="Aula 7","C113 ","")&amp;IF('C121'!E9="Aula 7","C121 ","")&amp;IF('C122'!E9="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I20">
+      <c r="I28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 8","C111 ","")&amp;IF('C112'!E9="Aula 8","C112 ","")&amp;IF('C113'!E9="Aula 8","C113 ","")&amp;IF('C121'!E9="Aula 8","C121 ","")&amp;IF('C122'!E9="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J20">
+      <c r="J28" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Aula 9","C111 ","")&amp;IF('C112'!E9="Aula 9","C112 ","")&amp;IF('C113'!E9="Aula 9","C113 ","")&amp;IF('C121'!E9="Aula 9","C121 ","")&amp;IF('C122'!E9="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K20">
+      <c r="K28" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!E9="Lab","C111 ","")&amp;IF('C112'!E9="Lab","C112 ","")&amp;IF('C113'!E9="Lab","C113 ","")&amp;IF('C121'!E9="Lab","C121 ","")&amp;IF('C122'!E9="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 1","C111 ","")&amp;IF('C112'!E11="Aula 1","C112 ","")&amp;IF('C113'!E11="Aula 1","C113 ","")&amp;IF('C121'!E11="Aula 1","C121 ","")&amp;IF('C122'!E11="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C21">
+      <c r="C29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 2","C111 ","")&amp;IF('C112'!E11="Aula 2","C112 ","")&amp;IF('C113'!E11="Aula 2","C113 ","")&amp;IF('C121'!E11="Aula 2","C121 ","")&amp;IF('C122'!E11="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D21">
+      <c r="D29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 3","C111 ","")&amp;IF('C112'!E11="Aula 3","C112 ","")&amp;IF('C113'!E11="Aula 3","C113 ","")&amp;IF('C121'!E11="Aula 3","C121 ","")&amp;IF('C122'!E11="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E21">
+      <c r="E29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 4","C111 ","")&amp;IF('C112'!E11="Aula 4","C112 ","")&amp;IF('C113'!E11="Aula 4","C113 ","")&amp;IF('C121'!E11="Aula 4","C121 ","")&amp;IF('C122'!E11="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F21">
+      <c r="F29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 5","C111 ","")&amp;IF('C112'!E11="Aula 5","C112 ","")&amp;IF('C113'!E11="Aula 5","C113 ","")&amp;IF('C121'!E11="Aula 5","C121 ","")&amp;IF('C122'!E11="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G21">
+      <c r="G29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 6","C111 ","")&amp;IF('C112'!E11="Aula 6","C112 ","")&amp;IF('C113'!E11="Aula 6","C113 ","")&amp;IF('C121'!E11="Aula 6","C121 ","")&amp;IF('C122'!E11="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H21">
+      <c r="H29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 7","C111 ","")&amp;IF('C112'!E11="Aula 7","C112 ","")&amp;IF('C113'!E11="Aula 7","C113 ","")&amp;IF('C121'!E11="Aula 7","C121 ","")&amp;IF('C122'!E11="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I21">
+      <c r="I29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 8","C111 ","")&amp;IF('C112'!E11="Aula 8","C112 ","")&amp;IF('C113'!E11="Aula 8","C113 ","")&amp;IF('C121'!E11="Aula 8","C121 ","")&amp;IF('C122'!E11="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J21">
+      <c r="J29" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Aula 9","C111 ","")&amp;IF('C112'!E11="Aula 9","C112 ","")&amp;IF('C113'!E11="Aula 9","C113 ","")&amp;IF('C121'!E11="Aula 9","C121 ","")&amp;IF('C122'!E11="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K21">
+      <c r="K29" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!E11="Lab","C111 ","")&amp;IF('C112'!E11="Lab","C112 ","")&amp;IF('C113'!E11="Lab","C113 ","")&amp;IF('C121'!E11="Lab","C121 ","")&amp;IF('C122'!E11="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 1","C111 ","")&amp;IF('C112'!E13="Aula 1","C112 ","")&amp;IF('C113'!E13="Aula 1","C113 ","")&amp;IF('C121'!E13="Aula 1","C121 ","")&amp;IF('C122'!E13="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C22">
+      <c r="C30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 2","C111 ","")&amp;IF('C112'!E13="Aula 2","C112 ","")&amp;IF('C113'!E13="Aula 2","C113 ","")&amp;IF('C121'!E13="Aula 2","C121 ","")&amp;IF('C122'!E13="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D22">
+      <c r="D30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 3","C111 ","")&amp;IF('C112'!E13="Aula 3","C112 ","")&amp;IF('C113'!E13="Aula 3","C113 ","")&amp;IF('C121'!E13="Aula 3","C121 ","")&amp;IF('C122'!E13="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E22">
+      <c r="E30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 4","C111 ","")&amp;IF('C112'!E13="Aula 4","C112 ","")&amp;IF('C113'!E13="Aula 4","C113 ","")&amp;IF('C121'!E13="Aula 4","C121 ","")&amp;IF('C122'!E13="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="F30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 5","C111 ","")&amp;IF('C112'!E13="Aula 5","C112 ","")&amp;IF('C113'!E13="Aula 5","C113 ","")&amp;IF('C121'!E13="Aula 5","C121 ","")&amp;IF('C122'!E13="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G22">
+      <c r="G30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 6","C111 ","")&amp;IF('C112'!E13="Aula 6","C112 ","")&amp;IF('C113'!E13="Aula 6","C113 ","")&amp;IF('C121'!E13="Aula 6","C121 ","")&amp;IF('C122'!E13="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H22">
+      <c r="H30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 7","C111 ","")&amp;IF('C112'!E13="Aula 7","C112 ","")&amp;IF('C113'!E13="Aula 7","C113 ","")&amp;IF('C121'!E13="Aula 7","C121 ","")&amp;IF('C122'!E13="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I22">
+      <c r="I30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 8","C111 ","")&amp;IF('C112'!E13="Aula 8","C112 ","")&amp;IF('C113'!E13="Aula 8","C113 ","")&amp;IF('C121'!E13="Aula 8","C121 ","")&amp;IF('C122'!E13="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J22">
+      <c r="J30" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Aula 9","C111 ","")&amp;IF('C112'!E13="Aula 9","C112 ","")&amp;IF('C113'!E13="Aula 9","C113 ","")&amp;IF('C121'!E13="Aula 9","C121 ","")&amp;IF('C122'!E13="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K22">
+      <c r="K30" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!E13="Lab","C111 ","")&amp;IF('C112'!E13="Lab","C112 ","")&amp;IF('C113'!E13="Lab","C113 ","")&amp;IF('C121'!E13="Lab","C121 ","")&amp;IF('C122'!E13="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 1","C111 ","")&amp;IF('C112'!E15="Aula 1","C112 ","")&amp;IF('C113'!E15="Aula 1","C113 ","")&amp;IF('C121'!E15="Aula 1","C121 ","")&amp;IF('C122'!E15="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C23">
+      <c r="C31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 2","C111 ","")&amp;IF('C112'!E15="Aula 2","C112 ","")&amp;IF('C113'!E15="Aula 2","C113 ","")&amp;IF('C121'!E15="Aula 2","C121 ","")&amp;IF('C122'!E15="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D23">
+      <c r="D31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 3","C111 ","")&amp;IF('C112'!E15="Aula 3","C112 ","")&amp;IF('C113'!E15="Aula 3","C113 ","")&amp;IF('C121'!E15="Aula 3","C121 ","")&amp;IF('C122'!E15="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E23">
+      <c r="E31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 4","C111 ","")&amp;IF('C112'!E15="Aula 4","C112 ","")&amp;IF('C113'!E15="Aula 4","C113 ","")&amp;IF('C121'!E15="Aula 4","C121 ","")&amp;IF('C122'!E15="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F23">
+      <c r="F31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 5","C111 ","")&amp;IF('C112'!E15="Aula 5","C112 ","")&amp;IF('C113'!E15="Aula 5","C113 ","")&amp;IF('C121'!E15="Aula 5","C121 ","")&amp;IF('C122'!E15="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G23">
+      <c r="G31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 6","C111 ","")&amp;IF('C112'!E15="Aula 6","C112 ","")&amp;IF('C113'!E15="Aula 6","C113 ","")&amp;IF('C121'!E15="Aula 6","C121 ","")&amp;IF('C122'!E15="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H23">
+      <c r="H31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 7","C111 ","")&amp;IF('C112'!E15="Aula 7","C112 ","")&amp;IF('C113'!E15="Aula 7","C113 ","")&amp;IF('C121'!E15="Aula 7","C121 ","")&amp;IF('C122'!E15="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I23">
+      <c r="I31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 8","C111 ","")&amp;IF('C112'!E15="Aula 8","C112 ","")&amp;IF('C113'!E15="Aula 8","C113 ","")&amp;IF('C121'!E15="Aula 8","C121 ","")&amp;IF('C122'!E15="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J23">
+      <c r="J31" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Aula 9","C111 ","")&amp;IF('C112'!E15="Aula 9","C112 ","")&amp;IF('C113'!E15="Aula 9","C113 ","")&amp;IF('C121'!E15="Aula 9","C121 ","")&amp;IF('C122'!E15="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K23">
+      <c r="K31" s="9">
         <f>SUBSTITUTE(TRIM(IF('C111'!E15="Lab","C111 ","")&amp;IF('C112'!E15="Lab","C112 ","")&amp;IF('C113'!E15="Lab","C113 ","")&amp;IF('C121'!E15="Lab","C121 ","")&amp;IF('C122'!E15="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Aula 7</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Aula 9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="B34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 1","C111 ","")&amp;IF('C112'!F5="Aula 1","C112 ","")&amp;IF('C113'!F5="Aula 1","C113 ","")&amp;IF('C121'!F5="Aula 1","C121 ","")&amp;IF('C122'!F5="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C26">
+      <c r="C34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 2","C111 ","")&amp;IF('C112'!F5="Aula 2","C112 ","")&amp;IF('C113'!F5="Aula 2","C113 ","")&amp;IF('C121'!F5="Aula 2","C121 ","")&amp;IF('C122'!F5="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D26">
+      <c r="D34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 3","C111 ","")&amp;IF('C112'!F5="Aula 3","C112 ","")&amp;IF('C113'!F5="Aula 3","C113 ","")&amp;IF('C121'!F5="Aula 3","C121 ","")&amp;IF('C122'!F5="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E26">
+      <c r="E34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 4","C111 ","")&amp;IF('C112'!F5="Aula 4","C112 ","")&amp;IF('C113'!F5="Aula 4","C113 ","")&amp;IF('C121'!F5="Aula 4","C121 ","")&amp;IF('C122'!F5="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F26">
+      <c r="F34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 5","C111 ","")&amp;IF('C112'!F5="Aula 5","C112 ","")&amp;IF('C113'!F5="Aula 5","C113 ","")&amp;IF('C121'!F5="Aula 5","C121 ","")&amp;IF('C122'!F5="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 6","C111 ","")&amp;IF('C112'!F5="Aula 6","C112 ","")&amp;IF('C113'!F5="Aula 6","C113 ","")&amp;IF('C121'!F5="Aula 6","C121 ","")&amp;IF('C122'!F5="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H26">
+      <c r="H34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 7","C111 ","")&amp;IF('C112'!F5="Aula 7","C112 ","")&amp;IF('C113'!F5="Aula 7","C113 ","")&amp;IF('C121'!F5="Aula 7","C121 ","")&amp;IF('C122'!F5="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I26">
+      <c r="I34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 8","C111 ","")&amp;IF('C112'!F5="Aula 8","C112 ","")&amp;IF('C113'!F5="Aula 8","C113 ","")&amp;IF('C121'!F5="Aula 8","C121 ","")&amp;IF('C122'!F5="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J26">
+      <c r="J34" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Aula 9","C111 ","")&amp;IF('C112'!F5="Aula 9","C112 ","")&amp;IF('C113'!F5="Aula 9","C113 ","")&amp;IF('C121'!F5="Aula 9","C121 ","")&amp;IF('C122'!F5="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K26">
+      <c r="K34" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!F5="Lab","C111 ","")&amp;IF('C112'!F5="Lab","C112 ","")&amp;IF('C113'!F5="Lab","C113 ","")&amp;IF('C121'!F5="Lab","C121 ","")&amp;IF('C122'!F5="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 1","C111 ","")&amp;IF('C112'!F7="Aula 1","C112 ","")&amp;IF('C113'!F7="Aula 1","C113 ","")&amp;IF('C121'!F7="Aula 1","C121 ","")&amp;IF('C122'!F7="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C27">
+      <c r="C35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 2","C111 ","")&amp;IF('C112'!F7="Aula 2","C112 ","")&amp;IF('C113'!F7="Aula 2","C113 ","")&amp;IF('C121'!F7="Aula 2","C121 ","")&amp;IF('C122'!F7="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D27">
+      <c r="D35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 3","C111 ","")&amp;IF('C112'!F7="Aula 3","C112 ","")&amp;IF('C113'!F7="Aula 3","C113 ","")&amp;IF('C121'!F7="Aula 3","C121 ","")&amp;IF('C122'!F7="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E27">
+      <c r="E35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 4","C111 ","")&amp;IF('C112'!F7="Aula 4","C112 ","")&amp;IF('C113'!F7="Aula 4","C113 ","")&amp;IF('C121'!F7="Aula 4","C121 ","")&amp;IF('C122'!F7="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F27">
+      <c r="F35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 5","C111 ","")&amp;IF('C112'!F7="Aula 5","C112 ","")&amp;IF('C113'!F7="Aula 5","C113 ","")&amp;IF('C121'!F7="Aula 5","C121 ","")&amp;IF('C122'!F7="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 6","C111 ","")&amp;IF('C112'!F7="Aula 6","C112 ","")&amp;IF('C113'!F7="Aula 6","C113 ","")&amp;IF('C121'!F7="Aula 6","C121 ","")&amp;IF('C122'!F7="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H27">
+      <c r="H35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 7","C111 ","")&amp;IF('C112'!F7="Aula 7","C112 ","")&amp;IF('C113'!F7="Aula 7","C113 ","")&amp;IF('C121'!F7="Aula 7","C121 ","")&amp;IF('C122'!F7="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I27">
+      <c r="I35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 8","C111 ","")&amp;IF('C112'!F7="Aula 8","C112 ","")&amp;IF('C113'!F7="Aula 8","C113 ","")&amp;IF('C121'!F7="Aula 8","C121 ","")&amp;IF('C122'!F7="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J27">
+      <c r="J35" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Aula 9","C111 ","")&amp;IF('C112'!F7="Aula 9","C112 ","")&amp;IF('C113'!F7="Aula 9","C113 ","")&amp;IF('C121'!F7="Aula 9","C121 ","")&amp;IF('C122'!F7="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K27">
+      <c r="K35" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!F7="Lab","C111 ","")&amp;IF('C112'!F7="Lab","C112 ","")&amp;IF('C113'!F7="Lab","C113 ","")&amp;IF('C121'!F7="Lab","C121 ","")&amp;IF('C122'!F7="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 1","C111 ","")&amp;IF('C112'!F9="Aula 1","C112 ","")&amp;IF('C113'!F9="Aula 1","C113 ","")&amp;IF('C121'!F9="Aula 1","C121 ","")&amp;IF('C122'!F9="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C28">
+      <c r="C36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 2","C111 ","")&amp;IF('C112'!F9="Aula 2","C112 ","")&amp;IF('C113'!F9="Aula 2","C113 ","")&amp;IF('C121'!F9="Aula 2","C121 ","")&amp;IF('C122'!F9="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D28">
+      <c r="D36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 3","C111 ","")&amp;IF('C112'!F9="Aula 3","C112 ","")&amp;IF('C113'!F9="Aula 3","C113 ","")&amp;IF('C121'!F9="Aula 3","C121 ","")&amp;IF('C122'!F9="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E28">
+      <c r="E36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 4","C111 ","")&amp;IF('C112'!F9="Aula 4","C112 ","")&amp;IF('C113'!F9="Aula 4","C113 ","")&amp;IF('C121'!F9="Aula 4","C121 ","")&amp;IF('C122'!F9="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F28">
+      <c r="F36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 5","C111 ","")&amp;IF('C112'!F9="Aula 5","C112 ","")&amp;IF('C113'!F9="Aula 5","C113 ","")&amp;IF('C121'!F9="Aula 5","C121 ","")&amp;IF('C122'!F9="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 6","C111 ","")&amp;IF('C112'!F9="Aula 6","C112 ","")&amp;IF('C113'!F9="Aula 6","C113 ","")&amp;IF('C121'!F9="Aula 6","C121 ","")&amp;IF('C122'!F9="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H28">
+      <c r="H36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 7","C111 ","")&amp;IF('C112'!F9="Aula 7","C112 ","")&amp;IF('C113'!F9="Aula 7","C113 ","")&amp;IF('C121'!F9="Aula 7","C121 ","")&amp;IF('C122'!F9="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I28">
+      <c r="I36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 8","C111 ","")&amp;IF('C112'!F9="Aula 8","C112 ","")&amp;IF('C113'!F9="Aula 8","C113 ","")&amp;IF('C121'!F9="Aula 8","C121 ","")&amp;IF('C122'!F9="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J28">
+      <c r="J36" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Aula 9","C111 ","")&amp;IF('C112'!F9="Aula 9","C112 ","")&amp;IF('C113'!F9="Aula 9","C113 ","")&amp;IF('C121'!F9="Aula 9","C121 ","")&amp;IF('C122'!F9="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K28">
+      <c r="K36" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!F9="Lab","C111 ","")&amp;IF('C112'!F9="Lab","C112 ","")&amp;IF('C113'!F9="Lab","C113 ","")&amp;IF('C121'!F9="Lab","C121 ","")&amp;IF('C122'!F9="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 1","C111 ","")&amp;IF('C112'!F11="Aula 1","C112 ","")&amp;IF('C113'!F11="Aula 1","C113 ","")&amp;IF('C121'!F11="Aula 1","C121 ","")&amp;IF('C122'!F11="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C29">
+      <c r="C37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 2","C111 ","")&amp;IF('C112'!F11="Aula 2","C112 ","")&amp;IF('C113'!F11="Aula 2","C113 ","")&amp;IF('C121'!F11="Aula 2","C121 ","")&amp;IF('C122'!F11="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D29">
+      <c r="D37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 3","C111 ","")&amp;IF('C112'!F11="Aula 3","C112 ","")&amp;IF('C113'!F11="Aula 3","C113 ","")&amp;IF('C121'!F11="Aula 3","C121 ","")&amp;IF('C122'!F11="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E29">
+      <c r="E37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 4","C111 ","")&amp;IF('C112'!F11="Aula 4","C112 ","")&amp;IF('C113'!F11="Aula 4","C113 ","")&amp;IF('C121'!F11="Aula 4","C121 ","")&amp;IF('C122'!F11="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F29">
+      <c r="F37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 5","C111 ","")&amp;IF('C112'!F11="Aula 5","C112 ","")&amp;IF('C113'!F11="Aula 5","C113 ","")&amp;IF('C121'!F11="Aula 5","C121 ","")&amp;IF('C122'!F11="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G29">
+      <c r="G37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 6","C111 ","")&amp;IF('C112'!F11="Aula 6","C112 ","")&amp;IF('C113'!F11="Aula 6","C113 ","")&amp;IF('C121'!F11="Aula 6","C121 ","")&amp;IF('C122'!F11="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H29">
+      <c r="H37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 7","C111 ","")&amp;IF('C112'!F11="Aula 7","C112 ","")&amp;IF('C113'!F11="Aula 7","C113 ","")&amp;IF('C121'!F11="Aula 7","C121 ","")&amp;IF('C122'!F11="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I29">
+      <c r="I37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 8","C111 ","")&amp;IF('C112'!F11="Aula 8","C112 ","")&amp;IF('C113'!F11="Aula 8","C113 ","")&amp;IF('C121'!F11="Aula 8","C121 ","")&amp;IF('C122'!F11="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J29">
+      <c r="J37" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Aula 9","C111 ","")&amp;IF('C112'!F11="Aula 9","C112 ","")&amp;IF('C113'!F11="Aula 9","C113 ","")&amp;IF('C121'!F11="Aula 9","C121 ","")&amp;IF('C122'!F11="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K29">
+      <c r="K37" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!F11="Lab","C111 ","")&amp;IF('C112'!F11="Lab","C112 ","")&amp;IF('C113'!F11="Lab","C113 ","")&amp;IF('C121'!F11="Lab","C121 ","")&amp;IF('C122'!F11="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 1","C111 ","")&amp;IF('C112'!F13="Aula 1","C112 ","")&amp;IF('C113'!F13="Aula 1","C113 ","")&amp;IF('C121'!F13="Aula 1","C121 ","")&amp;IF('C122'!F13="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C30">
+      <c r="C38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 2","C111 ","")&amp;IF('C112'!F13="Aula 2","C112 ","")&amp;IF('C113'!F13="Aula 2","C113 ","")&amp;IF('C121'!F13="Aula 2","C121 ","")&amp;IF('C122'!F13="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D30">
+      <c r="D38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 3","C111 ","")&amp;IF('C112'!F13="Aula 3","C112 ","")&amp;IF('C113'!F13="Aula 3","C113 ","")&amp;IF('C121'!F13="Aula 3","C121 ","")&amp;IF('C122'!F13="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E30">
+      <c r="E38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 4","C111 ","")&amp;IF('C112'!F13="Aula 4","C112 ","")&amp;IF('C113'!F13="Aula 4","C113 ","")&amp;IF('C121'!F13="Aula 4","C121 ","")&amp;IF('C122'!F13="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F30">
+      <c r="F38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 5","C111 ","")&amp;IF('C112'!F13="Aula 5","C112 ","")&amp;IF('C113'!F13="Aula 5","C113 ","")&amp;IF('C121'!F13="Aula 5","C121 ","")&amp;IF('C122'!F13="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G30">
+      <c r="G38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 6","C111 ","")&amp;IF('C112'!F13="Aula 6","C112 ","")&amp;IF('C113'!F13="Aula 6","C113 ","")&amp;IF('C121'!F13="Aula 6","C121 ","")&amp;IF('C122'!F13="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H30">
+      <c r="H38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 7","C111 ","")&amp;IF('C112'!F13="Aula 7","C112 ","")&amp;IF('C113'!F13="Aula 7","C113 ","")&amp;IF('C121'!F13="Aula 7","C121 ","")&amp;IF('C122'!F13="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I30">
+      <c r="I38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 8","C111 ","")&amp;IF('C112'!F13="Aula 8","C112 ","")&amp;IF('C113'!F13="Aula 8","C113 ","")&amp;IF('C121'!F13="Aula 8","C121 ","")&amp;IF('C122'!F13="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J30">
+      <c r="J38" s="5">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Aula 9","C111 ","")&amp;IF('C112'!F13="Aula 9","C112 ","")&amp;IF('C113'!F13="Aula 9","C113 ","")&amp;IF('C121'!F13="Aula 9","C121 ","")&amp;IF('C122'!F13="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K30">
+      <c r="K38" s="6">
         <f>SUBSTITUTE(TRIM(IF('C111'!F13="Lab","C111 ","")&amp;IF('C112'!F13="Lab","C112 ","")&amp;IF('C113'!F13="Lab","C113 ","")&amp;IF('C121'!F13="Lab","C121 ","")&amp;IF('C122'!F13="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 1","C111 ","")&amp;IF('C112'!F15="Aula 1","C112 ","")&amp;IF('C113'!F15="Aula 1","C113 ","")&amp;IF('C121'!F15="Aula 1","C121 ","")&amp;IF('C122'!F15="Aula 1","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="C31">
+      <c r="C39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 2","C111 ","")&amp;IF('C112'!F15="Aula 2","C112 ","")&amp;IF('C113'!F15="Aula 2","C113 ","")&amp;IF('C121'!F15="Aula 2","C121 ","")&amp;IF('C122'!F15="Aula 2","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="D31">
+      <c r="D39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 3","C111 ","")&amp;IF('C112'!F15="Aula 3","C112 ","")&amp;IF('C113'!F15="Aula 3","C113 ","")&amp;IF('C121'!F15="Aula 3","C121 ","")&amp;IF('C122'!F15="Aula 3","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="E31">
+      <c r="E39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 4","C111 ","")&amp;IF('C112'!F15="Aula 4","C112 ","")&amp;IF('C113'!F15="Aula 4","C113 ","")&amp;IF('C121'!F15="Aula 4","C121 ","")&amp;IF('C122'!F15="Aula 4","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="F31">
+      <c r="F39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 5","C111 ","")&amp;IF('C112'!F15="Aula 5","C112 ","")&amp;IF('C113'!F15="Aula 5","C113 ","")&amp;IF('C121'!F15="Aula 5","C121 ","")&amp;IF('C122'!F15="Aula 5","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 6","C111 ","")&amp;IF('C112'!F15="Aula 6","C112 ","")&amp;IF('C113'!F15="Aula 6","C113 ","")&amp;IF('C121'!F15="Aula 6","C121 ","")&amp;IF('C122'!F15="Aula 6","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="H31">
+      <c r="H39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 7","C111 ","")&amp;IF('C112'!F15="Aula 7","C112 ","")&amp;IF('C113'!F15="Aula 7","C113 ","")&amp;IF('C121'!F15="Aula 7","C121 ","")&amp;IF('C122'!F15="Aula 7","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="I31">
+      <c r="I39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 8","C111 ","")&amp;IF('C112'!F15="Aula 8","C112 ","")&amp;IF('C113'!F15="Aula 8","C113 ","")&amp;IF('C121'!F15="Aula 8","C121 ","")&amp;IF('C122'!F15="Aula 8","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="J31">
+      <c r="J39" s="8">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Aula 9","C111 ","")&amp;IF('C112'!F15="Aula 9","C112 ","")&amp;IF('C113'!F15="Aula 9","C113 ","")&amp;IF('C121'!F15="Aula 9","C121 ","")&amp;IF('C122'!F15="Aula 9","C122 ",""))," ",",")</f>
         <v/>
       </c>
-      <c r="K31">
+      <c r="K39" s="9">
         <f>SUBSTITUTE(TRIM(IF('C111'!F15="Lab","C111 ","")&amp;IF('C112'!F15="Lab","C112 ","")&amp;IF('C113'!F15="Lab","C113 ","")&amp;IF('C121'!F15="Lab","C121 ","")&amp;IF('C122'!F15="Lab","C122 ",""))," ",",")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Aula 1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Aula 2</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Aula 3</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Aula 4</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Aula 5</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Aula 6</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Aula 7</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Aula 8</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Aula 9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Turno 1</t>
-        </is>
-      </c>
-      <c r="B34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 1","C111 ","")&amp;IF('C112'!G5="Aula 1","C112 ","")&amp;IF('C113'!G5="Aula 1","C113 ","")&amp;IF('C121'!G5="Aula 1","C121 ","")&amp;IF('C122'!G5="Aula 1","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 2","C111 ","")&amp;IF('C112'!G5="Aula 2","C112 ","")&amp;IF('C113'!G5="Aula 2","C113 ","")&amp;IF('C121'!G5="Aula 2","C121 ","")&amp;IF('C122'!G5="Aula 2","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 3","C111 ","")&amp;IF('C112'!G5="Aula 3","C112 ","")&amp;IF('C113'!G5="Aula 3","C113 ","")&amp;IF('C121'!G5="Aula 3","C121 ","")&amp;IF('C122'!G5="Aula 3","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 4","C111 ","")&amp;IF('C112'!G5="Aula 4","C112 ","")&amp;IF('C113'!G5="Aula 4","C113 ","")&amp;IF('C121'!G5="Aula 4","C121 ","")&amp;IF('C122'!G5="Aula 4","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 5","C111 ","")&amp;IF('C112'!G5="Aula 5","C112 ","")&amp;IF('C113'!G5="Aula 5","C113 ","")&amp;IF('C121'!G5="Aula 5","C121 ","")&amp;IF('C122'!G5="Aula 5","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 6","C111 ","")&amp;IF('C112'!G5="Aula 6","C112 ","")&amp;IF('C113'!G5="Aula 6","C113 ","")&amp;IF('C121'!G5="Aula 6","C121 ","")&amp;IF('C122'!G5="Aula 6","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 7","C111 ","")&amp;IF('C112'!G5="Aula 7","C112 ","")&amp;IF('C113'!G5="Aula 7","C113 ","")&amp;IF('C121'!G5="Aula 7","C121 ","")&amp;IF('C122'!G5="Aula 7","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 8","C111 ","")&amp;IF('C112'!G5="Aula 8","C112 ","")&amp;IF('C113'!G5="Aula 8","C113 ","")&amp;IF('C121'!G5="Aula 8","C121 ","")&amp;IF('C122'!G5="Aula 8","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Aula 9","C111 ","")&amp;IF('C112'!G5="Aula 9","C112 ","")&amp;IF('C113'!G5="Aula 9","C113 ","")&amp;IF('C121'!G5="Aula 9","C121 ","")&amp;IF('C122'!G5="Aula 9","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K34">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G5="Lab","C111 ","")&amp;IF('C112'!G5="Lab","C112 ","")&amp;IF('C113'!G5="Lab","C113 ","")&amp;IF('C121'!G5="Lab","C121 ","")&amp;IF('C122'!G5="Lab","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Turno 2</t>
-        </is>
-      </c>
-      <c r="B35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 1","C111 ","")&amp;IF('C112'!G7="Aula 1","C112 ","")&amp;IF('C113'!G7="Aula 1","C113 ","")&amp;IF('C121'!G7="Aula 1","C121 ","")&amp;IF('C122'!G7="Aula 1","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 2","C111 ","")&amp;IF('C112'!G7="Aula 2","C112 ","")&amp;IF('C113'!G7="Aula 2","C113 ","")&amp;IF('C121'!G7="Aula 2","C121 ","")&amp;IF('C122'!G7="Aula 2","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 3","C111 ","")&amp;IF('C112'!G7="Aula 3","C112 ","")&amp;IF('C113'!G7="Aula 3","C113 ","")&amp;IF('C121'!G7="Aula 3","C121 ","")&amp;IF('C122'!G7="Aula 3","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 4","C111 ","")&amp;IF('C112'!G7="Aula 4","C112 ","")&amp;IF('C113'!G7="Aula 4","C113 ","")&amp;IF('C121'!G7="Aula 4","C121 ","")&amp;IF('C122'!G7="Aula 4","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 5","C111 ","")&amp;IF('C112'!G7="Aula 5","C112 ","")&amp;IF('C113'!G7="Aula 5","C113 ","")&amp;IF('C121'!G7="Aula 5","C121 ","")&amp;IF('C122'!G7="Aula 5","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 6","C111 ","")&amp;IF('C112'!G7="Aula 6","C112 ","")&amp;IF('C113'!G7="Aula 6","C113 ","")&amp;IF('C121'!G7="Aula 6","C121 ","")&amp;IF('C122'!G7="Aula 6","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 7","C111 ","")&amp;IF('C112'!G7="Aula 7","C112 ","")&amp;IF('C113'!G7="Aula 7","C113 ","")&amp;IF('C121'!G7="Aula 7","C121 ","")&amp;IF('C122'!G7="Aula 7","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 8","C111 ","")&amp;IF('C112'!G7="Aula 8","C112 ","")&amp;IF('C113'!G7="Aula 8","C113 ","")&amp;IF('C121'!G7="Aula 8","C121 ","")&amp;IF('C122'!G7="Aula 8","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Aula 9","C111 ","")&amp;IF('C112'!G7="Aula 9","C112 ","")&amp;IF('C113'!G7="Aula 9","C113 ","")&amp;IF('C121'!G7="Aula 9","C121 ","")&amp;IF('C122'!G7="Aula 9","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K35">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G7="Lab","C111 ","")&amp;IF('C112'!G7="Lab","C112 ","")&amp;IF('C113'!G7="Lab","C113 ","")&amp;IF('C121'!G7="Lab","C121 ","")&amp;IF('C122'!G7="Lab","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Turno 3</t>
-        </is>
-      </c>
-      <c r="B36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 1","C111 ","")&amp;IF('C112'!G9="Aula 1","C112 ","")&amp;IF('C113'!G9="Aula 1","C113 ","")&amp;IF('C121'!G9="Aula 1","C121 ","")&amp;IF('C122'!G9="Aula 1","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 2","C111 ","")&amp;IF('C112'!G9="Aula 2","C112 ","")&amp;IF('C113'!G9="Aula 2","C113 ","")&amp;IF('C121'!G9="Aula 2","C121 ","")&amp;IF('C122'!G9="Aula 2","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 3","C111 ","")&amp;IF('C112'!G9="Aula 3","C112 ","")&amp;IF('C113'!G9="Aula 3","C113 ","")&amp;IF('C121'!G9="Aula 3","C121 ","")&amp;IF('C122'!G9="Aula 3","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 4","C111 ","")&amp;IF('C112'!G9="Aula 4","C112 ","")&amp;IF('C113'!G9="Aula 4","C113 ","")&amp;IF('C121'!G9="Aula 4","C121 ","")&amp;IF('C122'!G9="Aula 4","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 5","C111 ","")&amp;IF('C112'!G9="Aula 5","C112 ","")&amp;IF('C113'!G9="Aula 5","C113 ","")&amp;IF('C121'!G9="Aula 5","C121 ","")&amp;IF('C122'!G9="Aula 5","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 6","C111 ","")&amp;IF('C112'!G9="Aula 6","C112 ","")&amp;IF('C113'!G9="Aula 6","C113 ","")&amp;IF('C121'!G9="Aula 6","C121 ","")&amp;IF('C122'!G9="Aula 6","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 7","C111 ","")&amp;IF('C112'!G9="Aula 7","C112 ","")&amp;IF('C113'!G9="Aula 7","C113 ","")&amp;IF('C121'!G9="Aula 7","C121 ","")&amp;IF('C122'!G9="Aula 7","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 8","C111 ","")&amp;IF('C112'!G9="Aula 8","C112 ","")&amp;IF('C113'!G9="Aula 8","C113 ","")&amp;IF('C121'!G9="Aula 8","C121 ","")&amp;IF('C122'!G9="Aula 8","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Aula 9","C111 ","")&amp;IF('C112'!G9="Aula 9","C112 ","")&amp;IF('C113'!G9="Aula 9","C113 ","")&amp;IF('C121'!G9="Aula 9","C121 ","")&amp;IF('C122'!G9="Aula 9","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G9="Lab","C111 ","")&amp;IF('C112'!G9="Lab","C112 ","")&amp;IF('C113'!G9="Lab","C113 ","")&amp;IF('C121'!G9="Lab","C121 ","")&amp;IF('C122'!G9="Lab","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Turno 4</t>
-        </is>
-      </c>
-      <c r="B37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 1","C111 ","")&amp;IF('C112'!G11="Aula 1","C112 ","")&amp;IF('C113'!G11="Aula 1","C113 ","")&amp;IF('C121'!G11="Aula 1","C121 ","")&amp;IF('C122'!G11="Aula 1","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 2","C111 ","")&amp;IF('C112'!G11="Aula 2","C112 ","")&amp;IF('C113'!G11="Aula 2","C113 ","")&amp;IF('C121'!G11="Aula 2","C121 ","")&amp;IF('C122'!G11="Aula 2","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 3","C111 ","")&amp;IF('C112'!G11="Aula 3","C112 ","")&amp;IF('C113'!G11="Aula 3","C113 ","")&amp;IF('C121'!G11="Aula 3","C121 ","")&amp;IF('C122'!G11="Aula 3","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 4","C111 ","")&amp;IF('C112'!G11="Aula 4","C112 ","")&amp;IF('C113'!G11="Aula 4","C113 ","")&amp;IF('C121'!G11="Aula 4","C121 ","")&amp;IF('C122'!G11="Aula 4","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 5","C111 ","")&amp;IF('C112'!G11="Aula 5","C112 ","")&amp;IF('C113'!G11="Aula 5","C113 ","")&amp;IF('C121'!G11="Aula 5","C121 ","")&amp;IF('C122'!G11="Aula 5","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 6","C111 ","")&amp;IF('C112'!G11="Aula 6","C112 ","")&amp;IF('C113'!G11="Aula 6","C113 ","")&amp;IF('C121'!G11="Aula 6","C121 ","")&amp;IF('C122'!G11="Aula 6","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 7","C111 ","")&amp;IF('C112'!G11="Aula 7","C112 ","")&amp;IF('C113'!G11="Aula 7","C113 ","")&amp;IF('C121'!G11="Aula 7","C121 ","")&amp;IF('C122'!G11="Aula 7","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 8","C111 ","")&amp;IF('C112'!G11="Aula 8","C112 ","")&amp;IF('C113'!G11="Aula 8","C113 ","")&amp;IF('C121'!G11="Aula 8","C121 ","")&amp;IF('C122'!G11="Aula 8","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Aula 9","C111 ","")&amp;IF('C112'!G11="Aula 9","C112 ","")&amp;IF('C113'!G11="Aula 9","C113 ","")&amp;IF('C121'!G11="Aula 9","C121 ","")&amp;IF('C122'!G11="Aula 9","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K37">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G11="Lab","C111 ","")&amp;IF('C112'!G11="Lab","C112 ","")&amp;IF('C113'!G11="Lab","C113 ","")&amp;IF('C121'!G11="Lab","C121 ","")&amp;IF('C122'!G11="Lab","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Turno 5</t>
-        </is>
-      </c>
-      <c r="B38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 1","C111 ","")&amp;IF('C112'!G13="Aula 1","C112 ","")&amp;IF('C113'!G13="Aula 1","C113 ","")&amp;IF('C121'!G13="Aula 1","C121 ","")&amp;IF('C122'!G13="Aula 1","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 2","C111 ","")&amp;IF('C112'!G13="Aula 2","C112 ","")&amp;IF('C113'!G13="Aula 2","C113 ","")&amp;IF('C121'!G13="Aula 2","C121 ","")&amp;IF('C122'!G13="Aula 2","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 3","C111 ","")&amp;IF('C112'!G13="Aula 3","C112 ","")&amp;IF('C113'!G13="Aula 3","C113 ","")&amp;IF('C121'!G13="Aula 3","C121 ","")&amp;IF('C122'!G13="Aula 3","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 4","C111 ","")&amp;IF('C112'!G13="Aula 4","C112 ","")&amp;IF('C113'!G13="Aula 4","C113 ","")&amp;IF('C121'!G13="Aula 4","C121 ","")&amp;IF('C122'!G13="Aula 4","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 5","C111 ","")&amp;IF('C112'!G13="Aula 5","C112 ","")&amp;IF('C113'!G13="Aula 5","C113 ","")&amp;IF('C121'!G13="Aula 5","C121 ","")&amp;IF('C122'!G13="Aula 5","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 6","C111 ","")&amp;IF('C112'!G13="Aula 6","C112 ","")&amp;IF('C113'!G13="Aula 6","C113 ","")&amp;IF('C121'!G13="Aula 6","C121 ","")&amp;IF('C122'!G13="Aula 6","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 7","C111 ","")&amp;IF('C112'!G13="Aula 7","C112 ","")&amp;IF('C113'!G13="Aula 7","C113 ","")&amp;IF('C121'!G13="Aula 7","C121 ","")&amp;IF('C122'!G13="Aula 7","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 8","C111 ","")&amp;IF('C112'!G13="Aula 8","C112 ","")&amp;IF('C113'!G13="Aula 8","C113 ","")&amp;IF('C121'!G13="Aula 8","C121 ","")&amp;IF('C122'!G13="Aula 8","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Aula 9","C111 ","")&amp;IF('C112'!G13="Aula 9","C112 ","")&amp;IF('C113'!G13="Aula 9","C113 ","")&amp;IF('C121'!G13="Aula 9","C121 ","")&amp;IF('C122'!G13="Aula 9","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K38">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G13="Lab","C111 ","")&amp;IF('C112'!G13="Lab","C112 ","")&amp;IF('C113'!G13="Lab","C113 ","")&amp;IF('C121'!G13="Lab","C121 ","")&amp;IF('C122'!G13="Lab","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Turno 6</t>
-        </is>
-      </c>
-      <c r="B39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 1","C111 ","")&amp;IF('C112'!G15="Aula 1","C112 ","")&amp;IF('C113'!G15="Aula 1","C113 ","")&amp;IF('C121'!G15="Aula 1","C121 ","")&amp;IF('C122'!G15="Aula 1","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 2","C111 ","")&amp;IF('C112'!G15="Aula 2","C112 ","")&amp;IF('C113'!G15="Aula 2","C113 ","")&amp;IF('C121'!G15="Aula 2","C121 ","")&amp;IF('C122'!G15="Aula 2","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 3","C111 ","")&amp;IF('C112'!G15="Aula 3","C112 ","")&amp;IF('C113'!G15="Aula 3","C113 ","")&amp;IF('C121'!G15="Aula 3","C121 ","")&amp;IF('C122'!G15="Aula 3","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 4","C111 ","")&amp;IF('C112'!G15="Aula 4","C112 ","")&amp;IF('C113'!G15="Aula 4","C113 ","")&amp;IF('C121'!G15="Aula 4","C121 ","")&amp;IF('C122'!G15="Aula 4","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 5","C111 ","")&amp;IF('C112'!G15="Aula 5","C112 ","")&amp;IF('C113'!G15="Aula 5","C113 ","")&amp;IF('C121'!G15="Aula 5","C121 ","")&amp;IF('C122'!G15="Aula 5","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 6","C111 ","")&amp;IF('C112'!G15="Aula 6","C112 ","")&amp;IF('C113'!G15="Aula 6","C113 ","")&amp;IF('C121'!G15="Aula 6","C121 ","")&amp;IF('C122'!G15="Aula 6","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 7","C111 ","")&amp;IF('C112'!G15="Aula 7","C112 ","")&amp;IF('C113'!G15="Aula 7","C113 ","")&amp;IF('C121'!G15="Aula 7","C121 ","")&amp;IF('C122'!G15="Aula 7","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 8","C111 ","")&amp;IF('C112'!G15="Aula 8","C112 ","")&amp;IF('C113'!G15="Aula 8","C113 ","")&amp;IF('C121'!G15="Aula 8","C121 ","")&amp;IF('C122'!G15="Aula 8","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Aula 9","C111 ","")&amp;IF('C112'!G15="Aula 9","C112 ","")&amp;IF('C113'!G15="Aula 9","C113 ","")&amp;IF('C121'!G15="Aula 9","C121 ","")&amp;IF('C122'!G15="Aula 9","C122 ",""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K39">
-        <f>SUBSTITUTE(TRIM(IF('C111'!G15="Lab","C111 ","")&amp;IF('C112'!G15="Lab","C112 ","")&amp;IF('C113'!G15="Lab","C113 ","")&amp;IF('C121'!G15="Lab","C121 ","")&amp;IF('C122'!G15="Lab","C122 ",""))," ",",")</f>
-        <v/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Leyenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Año C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Conflicto (varios años en la misma aula)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4590,7 +4860,7 @@
         </is>
       </c>
       <c r="C1">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 1")+COUNTIF('C112'!C5,"Aula 1")+COUNTIF('C113'!C5,"Aula 1")+COUNTIF('C121'!C5,"Aula 1")+COUNTIF('C122'!C5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 1")+COUNTIF('C112'!C5,"Aula 1")+COUNTIF('C113'!C5,"Aula 1")+COUNTIF('C121'!C5,"Aula 1")+COUNTIF('C122'!C5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 1")+COUNTIF('C112'!C5,"Aula 1")+COUNTIF('C113'!C5,"Aula 1")+COUNTIF('C121'!C5,"Aula 1")+COUNTIF('C122'!C5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 1")+COUNTIF('C112'!B5,"Aula 1")+COUNTIF('C113'!B5,"Aula 1")+COUNTIF('C121'!B5,"Aula 1")+COUNTIF('C122'!B5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 1")+COUNTIF('C112'!B5,"Aula 1")+COUNTIF('C113'!B5,"Aula 1")+COUNTIF('C121'!B5,"Aula 1")+COUNTIF('C122'!B5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 1")+COUNTIF('C112'!B5,"Aula 1")+COUNTIF('C113'!B5,"Aula 1")+COUNTIF('C121'!B5,"Aula 1")+COUNTIF('C122'!B5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4601,7 +4871,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 2")+COUNTIF('C112'!C5,"Aula 2")+COUNTIF('C113'!C5,"Aula 2")+COUNTIF('C121'!C5,"Aula 2")+COUNTIF('C122'!C5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 2")+COUNTIF('C112'!C5,"Aula 2")+COUNTIF('C113'!C5,"Aula 2")+COUNTIF('C121'!C5,"Aula 2")+COUNTIF('C122'!C5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 2")+COUNTIF('C112'!C5,"Aula 2")+COUNTIF('C113'!C5,"Aula 2")+COUNTIF('C121'!C5,"Aula 2")+COUNTIF('C122'!C5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 2")+COUNTIF('C112'!B5,"Aula 2")+COUNTIF('C113'!B5,"Aula 2")+COUNTIF('C121'!B5,"Aula 2")+COUNTIF('C122'!B5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 2")+COUNTIF('C112'!B5,"Aula 2")+COUNTIF('C113'!B5,"Aula 2")+COUNTIF('C121'!B5,"Aula 2")+COUNTIF('C122'!B5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 2")+COUNTIF('C112'!B5,"Aula 2")+COUNTIF('C113'!B5,"Aula 2")+COUNTIF('C121'!B5,"Aula 2")+COUNTIF('C122'!B5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4612,7 +4882,7 @@
         </is>
       </c>
       <c r="C3">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 3")+COUNTIF('C112'!C5,"Aula 3")+COUNTIF('C113'!C5,"Aula 3")+COUNTIF('C121'!C5,"Aula 3")+COUNTIF('C122'!C5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 3")+COUNTIF('C112'!C5,"Aula 3")+COUNTIF('C113'!C5,"Aula 3")+COUNTIF('C121'!C5,"Aula 3")+COUNTIF('C122'!C5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 3")+COUNTIF('C112'!C5,"Aula 3")+COUNTIF('C113'!C5,"Aula 3")+COUNTIF('C121'!C5,"Aula 3")+COUNTIF('C122'!C5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 3")+COUNTIF('C112'!B5,"Aula 3")+COUNTIF('C113'!B5,"Aula 3")+COUNTIF('C121'!B5,"Aula 3")+COUNTIF('C122'!B5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 3")+COUNTIF('C112'!B5,"Aula 3")+COUNTIF('C113'!B5,"Aula 3")+COUNTIF('C121'!B5,"Aula 3")+COUNTIF('C122'!B5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 3")+COUNTIF('C112'!B5,"Aula 3")+COUNTIF('C113'!B5,"Aula 3")+COUNTIF('C121'!B5,"Aula 3")+COUNTIF('C122'!B5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4623,7 +4893,7 @@
         </is>
       </c>
       <c r="C4">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 4")+COUNTIF('C112'!C5,"Aula 4")+COUNTIF('C113'!C5,"Aula 4")+COUNTIF('C121'!C5,"Aula 4")+COUNTIF('C122'!C5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 4")+COUNTIF('C112'!C5,"Aula 4")+COUNTIF('C113'!C5,"Aula 4")+COUNTIF('C121'!C5,"Aula 4")+COUNTIF('C122'!C5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 4")+COUNTIF('C112'!C5,"Aula 4")+COUNTIF('C113'!C5,"Aula 4")+COUNTIF('C121'!C5,"Aula 4")+COUNTIF('C122'!C5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 4")+COUNTIF('C112'!B5,"Aula 4")+COUNTIF('C113'!B5,"Aula 4")+COUNTIF('C121'!B5,"Aula 4")+COUNTIF('C122'!B5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 4")+COUNTIF('C112'!B5,"Aula 4")+COUNTIF('C113'!B5,"Aula 4")+COUNTIF('C121'!B5,"Aula 4")+COUNTIF('C122'!B5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 4")+COUNTIF('C112'!B5,"Aula 4")+COUNTIF('C113'!B5,"Aula 4")+COUNTIF('C121'!B5,"Aula 4")+COUNTIF('C122'!B5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4634,7 +4904,7 @@
         </is>
       </c>
       <c r="C5">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 5")+COUNTIF('C112'!C5,"Aula 5")+COUNTIF('C113'!C5,"Aula 5")+COUNTIF('C121'!C5,"Aula 5")+COUNTIF('C122'!C5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 5")+COUNTIF('C112'!C5,"Aula 5")+COUNTIF('C113'!C5,"Aula 5")+COUNTIF('C121'!C5,"Aula 5")+COUNTIF('C122'!C5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 5")+COUNTIF('C112'!C5,"Aula 5")+COUNTIF('C113'!C5,"Aula 5")+COUNTIF('C121'!C5,"Aula 5")+COUNTIF('C122'!C5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 5")+COUNTIF('C112'!B5,"Aula 5")+COUNTIF('C113'!B5,"Aula 5")+COUNTIF('C121'!B5,"Aula 5")+COUNTIF('C122'!B5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 5")+COUNTIF('C112'!B5,"Aula 5")+COUNTIF('C113'!B5,"Aula 5")+COUNTIF('C121'!B5,"Aula 5")+COUNTIF('C122'!B5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 5")+COUNTIF('C112'!B5,"Aula 5")+COUNTIF('C113'!B5,"Aula 5")+COUNTIF('C121'!B5,"Aula 5")+COUNTIF('C122'!B5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4645,7 +4915,7 @@
         </is>
       </c>
       <c r="C6">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 6")+COUNTIF('C112'!C5,"Aula 6")+COUNTIF('C113'!C5,"Aula 6")+COUNTIF('C121'!C5,"Aula 6")+COUNTIF('C122'!C5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 6")+COUNTIF('C112'!C5,"Aula 6")+COUNTIF('C113'!C5,"Aula 6")+COUNTIF('C121'!C5,"Aula 6")+COUNTIF('C122'!C5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 6")+COUNTIF('C112'!C5,"Aula 6")+COUNTIF('C113'!C5,"Aula 6")+COUNTIF('C121'!C5,"Aula 6")+COUNTIF('C122'!C5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 6")+COUNTIF('C112'!B5,"Aula 6")+COUNTIF('C113'!B5,"Aula 6")+COUNTIF('C121'!B5,"Aula 6")+COUNTIF('C122'!B5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 6")+COUNTIF('C112'!B5,"Aula 6")+COUNTIF('C113'!B5,"Aula 6")+COUNTIF('C121'!B5,"Aula 6")+COUNTIF('C122'!B5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 6")+COUNTIF('C112'!B5,"Aula 6")+COUNTIF('C113'!B5,"Aula 6")+COUNTIF('C121'!B5,"Aula 6")+COUNTIF('C122'!B5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4656,7 +4926,7 @@
         </is>
       </c>
       <c r="C7">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 7")+COUNTIF('C112'!C5,"Aula 7")+COUNTIF('C113'!C5,"Aula 7")+COUNTIF('C121'!C5,"Aula 7")+COUNTIF('C122'!C5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 7")+COUNTIF('C112'!C5,"Aula 7")+COUNTIF('C113'!C5,"Aula 7")+COUNTIF('C121'!C5,"Aula 7")+COUNTIF('C122'!C5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 7")+COUNTIF('C112'!C5,"Aula 7")+COUNTIF('C113'!C5,"Aula 7")+COUNTIF('C121'!C5,"Aula 7")+COUNTIF('C122'!C5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 7")+COUNTIF('C112'!B5,"Aula 7")+COUNTIF('C113'!B5,"Aula 7")+COUNTIF('C121'!B5,"Aula 7")+COUNTIF('C122'!B5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 7")+COUNTIF('C112'!B5,"Aula 7")+COUNTIF('C113'!B5,"Aula 7")+COUNTIF('C121'!B5,"Aula 7")+COUNTIF('C122'!B5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 7")+COUNTIF('C112'!B5,"Aula 7")+COUNTIF('C113'!B5,"Aula 7")+COUNTIF('C121'!B5,"Aula 7")+COUNTIF('C122'!B5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4667,7 +4937,7 @@
         </is>
       </c>
       <c r="C8">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 8")+COUNTIF('C112'!C5,"Aula 8")+COUNTIF('C113'!C5,"Aula 8")+COUNTIF('C121'!C5,"Aula 8")+COUNTIF('C122'!C5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 8")+COUNTIF('C112'!C5,"Aula 8")+COUNTIF('C113'!C5,"Aula 8")+COUNTIF('C121'!C5,"Aula 8")+COUNTIF('C122'!C5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 8")+COUNTIF('C112'!C5,"Aula 8")+COUNTIF('C113'!C5,"Aula 8")+COUNTIF('C121'!C5,"Aula 8")+COUNTIF('C122'!C5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 8")+COUNTIF('C112'!B5,"Aula 8")+COUNTIF('C113'!B5,"Aula 8")+COUNTIF('C121'!B5,"Aula 8")+COUNTIF('C122'!B5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 8")+COUNTIF('C112'!B5,"Aula 8")+COUNTIF('C113'!B5,"Aula 8")+COUNTIF('C121'!B5,"Aula 8")+COUNTIF('C122'!B5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 8")+COUNTIF('C112'!B5,"Aula 8")+COUNTIF('C113'!B5,"Aula 8")+COUNTIF('C121'!B5,"Aula 8")+COUNTIF('C122'!B5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4678,7 +4948,7 @@
         </is>
       </c>
       <c r="C9">
-        <f>IF((IF((COUNTIF('C111'!C5,"Aula 9")+COUNTIF('C112'!C5,"Aula 9")+COUNTIF('C113'!C5,"Aula 9")+COUNTIF('C121'!C5,"Aula 9")+COUNTIF('C122'!C5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 9")+COUNTIF('C112'!C5,"Aula 9")+COUNTIF('C113'!C5,"Aula 9")+COUNTIF('C121'!C5,"Aula 9")+COUNTIF('C122'!C5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 9")+COUNTIF('C112'!C5,"Aula 9")+COUNTIF('C113'!C5,"Aula 9")+COUNTIF('C121'!C5,"Aula 9")+COUNTIF('C122'!C5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Aula 9")+COUNTIF('C112'!B5,"Aula 9")+COUNTIF('C113'!B5,"Aula 9")+COUNTIF('C121'!B5,"Aula 9")+COUNTIF('C122'!B5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Aula 9")+COUNTIF('C112'!B5,"Aula 9")+COUNTIF('C113'!B5,"Aula 9")+COUNTIF('C121'!B5,"Aula 9")+COUNTIF('C122'!B5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Aula 9")+COUNTIF('C112'!B5,"Aula 9")+COUNTIF('C113'!B5,"Aula 9")+COUNTIF('C121'!B5,"Aula 9")+COUNTIF('C122'!B5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -4689,1747 +4959,1747 @@
         </is>
       </c>
       <c r="C10">
-        <f>IF((IF((COUNTIF('C111'!C5,"Lab")+COUNTIF('C112'!C5,"Lab")+COUNTIF('C113'!C5,"Lab")+COUNTIF('C121'!C5,"Lab")+COUNTIF('C122'!C5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Lab")+COUNTIF('C112'!C5,"Lab")+COUNTIF('C113'!C5,"Lab")+COUNTIF('C121'!C5,"Lab")+COUNTIF('C122'!C5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Lab")+COUNTIF('C112'!C5,"Lab")+COUNTIF('C113'!C5,"Lab")+COUNTIF('C121'!C5,"Lab")+COUNTIF('C122'!C5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B5,"Lab")+COUNTIF('C112'!B5,"Lab")+COUNTIF('C113'!B5,"Lab")+COUNTIF('C121'!B5,"Lab")+COUNTIF('C122'!B5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B5,"Lab")+COUNTIF('C112'!B5,"Lab")+COUNTIF('C113'!B5,"Lab")+COUNTIF('C121'!B5,"Lab")+COUNTIF('C122'!B5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B5,"Lab")+COUNTIF('C112'!B5,"Lab")+COUNTIF('C113'!B5,"Lab")+COUNTIF('C121'!B5,"Lab")+COUNTIF('C122'!B5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="C11">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 1")+COUNTIF('C112'!C7,"Aula 1")+COUNTIF('C113'!C7,"Aula 1")+COUNTIF('C121'!C7,"Aula 1")+COUNTIF('C122'!C7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 1")+COUNTIF('C112'!C7,"Aula 1")+COUNTIF('C113'!C7,"Aula 1")+COUNTIF('C121'!C7,"Aula 1")+COUNTIF('C122'!C7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 1")+COUNTIF('C112'!C7,"Aula 1")+COUNTIF('C113'!C7,"Aula 1")+COUNTIF('C121'!C7,"Aula 1")+COUNTIF('C122'!C7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 1")+COUNTIF('C112'!B7,"Aula 1")+COUNTIF('C113'!B7,"Aula 1")+COUNTIF('C121'!B7,"Aula 1")+COUNTIF('C122'!B7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 1")+COUNTIF('C112'!B7,"Aula 1")+COUNTIF('C113'!B7,"Aula 1")+COUNTIF('C121'!B7,"Aula 1")+COUNTIF('C122'!B7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 1")+COUNTIF('C112'!B7,"Aula 1")+COUNTIF('C113'!B7,"Aula 1")+COUNTIF('C121'!B7,"Aula 1")+COUNTIF('C122'!B7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="C12">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 2")+COUNTIF('C112'!C7,"Aula 2")+COUNTIF('C113'!C7,"Aula 2")+COUNTIF('C121'!C7,"Aula 2")+COUNTIF('C122'!C7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 2")+COUNTIF('C112'!C7,"Aula 2")+COUNTIF('C113'!C7,"Aula 2")+COUNTIF('C121'!C7,"Aula 2")+COUNTIF('C122'!C7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 2")+COUNTIF('C112'!C7,"Aula 2")+COUNTIF('C113'!C7,"Aula 2")+COUNTIF('C121'!C7,"Aula 2")+COUNTIF('C122'!C7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 2")+COUNTIF('C112'!B7,"Aula 2")+COUNTIF('C113'!B7,"Aula 2")+COUNTIF('C121'!B7,"Aula 2")+COUNTIF('C122'!B7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 2")+COUNTIF('C112'!B7,"Aula 2")+COUNTIF('C113'!B7,"Aula 2")+COUNTIF('C121'!B7,"Aula 2")+COUNTIF('C122'!B7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 2")+COUNTIF('C112'!B7,"Aula 2")+COUNTIF('C113'!B7,"Aula 2")+COUNTIF('C121'!B7,"Aula 2")+COUNTIF('C122'!B7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="C13">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 3")+COUNTIF('C112'!C7,"Aula 3")+COUNTIF('C113'!C7,"Aula 3")+COUNTIF('C121'!C7,"Aula 3")+COUNTIF('C122'!C7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 3")+COUNTIF('C112'!C7,"Aula 3")+COUNTIF('C113'!C7,"Aula 3")+COUNTIF('C121'!C7,"Aula 3")+COUNTIF('C122'!C7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 3")+COUNTIF('C112'!C7,"Aula 3")+COUNTIF('C113'!C7,"Aula 3")+COUNTIF('C121'!C7,"Aula 3")+COUNTIF('C122'!C7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 3")+COUNTIF('C112'!B7,"Aula 3")+COUNTIF('C113'!B7,"Aula 3")+COUNTIF('C121'!B7,"Aula 3")+COUNTIF('C122'!B7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 3")+COUNTIF('C112'!B7,"Aula 3")+COUNTIF('C113'!B7,"Aula 3")+COUNTIF('C121'!B7,"Aula 3")+COUNTIF('C122'!B7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 3")+COUNTIF('C112'!B7,"Aula 3")+COUNTIF('C113'!B7,"Aula 3")+COUNTIF('C121'!B7,"Aula 3")+COUNTIF('C122'!B7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="C14">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 4")+COUNTIF('C112'!C7,"Aula 4")+COUNTIF('C113'!C7,"Aula 4")+COUNTIF('C121'!C7,"Aula 4")+COUNTIF('C122'!C7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 4")+COUNTIF('C112'!C7,"Aula 4")+COUNTIF('C113'!C7,"Aula 4")+COUNTIF('C121'!C7,"Aula 4")+COUNTIF('C122'!C7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 4")+COUNTIF('C112'!C7,"Aula 4")+COUNTIF('C113'!C7,"Aula 4")+COUNTIF('C121'!C7,"Aula 4")+COUNTIF('C122'!C7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 4")+COUNTIF('C112'!B7,"Aula 4")+COUNTIF('C113'!B7,"Aula 4")+COUNTIF('C121'!B7,"Aula 4")+COUNTIF('C122'!B7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 4")+COUNTIF('C112'!B7,"Aula 4")+COUNTIF('C113'!B7,"Aula 4")+COUNTIF('C121'!B7,"Aula 4")+COUNTIF('C122'!B7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 4")+COUNTIF('C112'!B7,"Aula 4")+COUNTIF('C113'!B7,"Aula 4")+COUNTIF('C121'!B7,"Aula 4")+COUNTIF('C122'!B7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="C15">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 5")+COUNTIF('C112'!C7,"Aula 5")+COUNTIF('C113'!C7,"Aula 5")+COUNTIF('C121'!C7,"Aula 5")+COUNTIF('C122'!C7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 5")+COUNTIF('C112'!C7,"Aula 5")+COUNTIF('C113'!C7,"Aula 5")+COUNTIF('C121'!C7,"Aula 5")+COUNTIF('C122'!C7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 5")+COUNTIF('C112'!C7,"Aula 5")+COUNTIF('C113'!C7,"Aula 5")+COUNTIF('C121'!C7,"Aula 5")+COUNTIF('C122'!C7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 5")+COUNTIF('C112'!B7,"Aula 5")+COUNTIF('C113'!B7,"Aula 5")+COUNTIF('C121'!B7,"Aula 5")+COUNTIF('C122'!B7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 5")+COUNTIF('C112'!B7,"Aula 5")+COUNTIF('C113'!B7,"Aula 5")+COUNTIF('C121'!B7,"Aula 5")+COUNTIF('C122'!B7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 5")+COUNTIF('C112'!B7,"Aula 5")+COUNTIF('C113'!B7,"Aula 5")+COUNTIF('C121'!B7,"Aula 5")+COUNTIF('C122'!B7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="C16">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 6")+COUNTIF('C112'!C7,"Aula 6")+COUNTIF('C113'!C7,"Aula 6")+COUNTIF('C121'!C7,"Aula 6")+COUNTIF('C122'!C7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 6")+COUNTIF('C112'!C7,"Aula 6")+COUNTIF('C113'!C7,"Aula 6")+COUNTIF('C121'!C7,"Aula 6")+COUNTIF('C122'!C7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 6")+COUNTIF('C112'!C7,"Aula 6")+COUNTIF('C113'!C7,"Aula 6")+COUNTIF('C121'!C7,"Aula 6")+COUNTIF('C122'!C7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 6")+COUNTIF('C112'!B7,"Aula 6")+COUNTIF('C113'!B7,"Aula 6")+COUNTIF('C121'!B7,"Aula 6")+COUNTIF('C122'!B7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 6")+COUNTIF('C112'!B7,"Aula 6")+COUNTIF('C113'!B7,"Aula 6")+COUNTIF('C121'!B7,"Aula 6")+COUNTIF('C122'!B7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 6")+COUNTIF('C112'!B7,"Aula 6")+COUNTIF('C113'!B7,"Aula 6")+COUNTIF('C121'!B7,"Aula 6")+COUNTIF('C122'!B7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="C17">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 7")+COUNTIF('C112'!C7,"Aula 7")+COUNTIF('C113'!C7,"Aula 7")+COUNTIF('C121'!C7,"Aula 7")+COUNTIF('C122'!C7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 7")+COUNTIF('C112'!C7,"Aula 7")+COUNTIF('C113'!C7,"Aula 7")+COUNTIF('C121'!C7,"Aula 7")+COUNTIF('C122'!C7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 7")+COUNTIF('C112'!C7,"Aula 7")+COUNTIF('C113'!C7,"Aula 7")+COUNTIF('C121'!C7,"Aula 7")+COUNTIF('C122'!C7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 7")+COUNTIF('C112'!B7,"Aula 7")+COUNTIF('C113'!B7,"Aula 7")+COUNTIF('C121'!B7,"Aula 7")+COUNTIF('C122'!B7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 7")+COUNTIF('C112'!B7,"Aula 7")+COUNTIF('C113'!B7,"Aula 7")+COUNTIF('C121'!B7,"Aula 7")+COUNTIF('C122'!B7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 7")+COUNTIF('C112'!B7,"Aula 7")+COUNTIF('C113'!B7,"Aula 7")+COUNTIF('C121'!B7,"Aula 7")+COUNTIF('C122'!B7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="C18">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 8")+COUNTIF('C112'!C7,"Aula 8")+COUNTIF('C113'!C7,"Aula 8")+COUNTIF('C121'!C7,"Aula 8")+COUNTIF('C122'!C7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 8")+COUNTIF('C112'!C7,"Aula 8")+COUNTIF('C113'!C7,"Aula 8")+COUNTIF('C121'!C7,"Aula 8")+COUNTIF('C122'!C7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 8")+COUNTIF('C112'!C7,"Aula 8")+COUNTIF('C113'!C7,"Aula 8")+COUNTIF('C121'!C7,"Aula 8")+COUNTIF('C122'!C7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 8")+COUNTIF('C112'!B7,"Aula 8")+COUNTIF('C113'!B7,"Aula 8")+COUNTIF('C121'!B7,"Aula 8")+COUNTIF('C122'!B7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 8")+COUNTIF('C112'!B7,"Aula 8")+COUNTIF('C113'!B7,"Aula 8")+COUNTIF('C121'!B7,"Aula 8")+COUNTIF('C122'!B7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 8")+COUNTIF('C112'!B7,"Aula 8")+COUNTIF('C113'!B7,"Aula 8")+COUNTIF('C121'!B7,"Aula 8")+COUNTIF('C122'!B7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="C19">
-        <f>IF((IF((COUNTIF('C111'!C7,"Aula 9")+COUNTIF('C112'!C7,"Aula 9")+COUNTIF('C113'!C7,"Aula 9")+COUNTIF('C121'!C7,"Aula 9")+COUNTIF('C122'!C7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 9")+COUNTIF('C112'!C7,"Aula 9")+COUNTIF('C113'!C7,"Aula 9")+COUNTIF('C121'!C7,"Aula 9")+COUNTIF('C122'!C7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 9")+COUNTIF('C112'!C7,"Aula 9")+COUNTIF('C113'!C7,"Aula 9")+COUNTIF('C121'!C7,"Aula 9")+COUNTIF('C122'!C7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Aula 9")+COUNTIF('C112'!B7,"Aula 9")+COUNTIF('C113'!B7,"Aula 9")+COUNTIF('C121'!B7,"Aula 9")+COUNTIF('C122'!B7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Aula 9")+COUNTIF('C112'!B7,"Aula 9")+COUNTIF('C113'!B7,"Aula 9")+COUNTIF('C121'!B7,"Aula 9")+COUNTIF('C122'!B7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Aula 9")+COUNTIF('C112'!B7,"Aula 9")+COUNTIF('C113'!B7,"Aula 9")+COUNTIF('C121'!B7,"Aula 9")+COUNTIF('C122'!B7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="C20">
-        <f>IF((IF((COUNTIF('C111'!C7,"Lab")+COUNTIF('C112'!C7,"Lab")+COUNTIF('C113'!C7,"Lab")+COUNTIF('C121'!C7,"Lab")+COUNTIF('C122'!C7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Lab")+COUNTIF('C112'!C7,"Lab")+COUNTIF('C113'!C7,"Lab")+COUNTIF('C121'!C7,"Lab")+COUNTIF('C122'!C7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Lab")+COUNTIF('C112'!C7,"Lab")+COUNTIF('C113'!C7,"Lab")+COUNTIF('C121'!C7,"Lab")+COUNTIF('C122'!C7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B7,"Lab")+COUNTIF('C112'!B7,"Lab")+COUNTIF('C113'!B7,"Lab")+COUNTIF('C121'!B7,"Lab")+COUNTIF('C122'!B7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B7,"Lab")+COUNTIF('C112'!B7,"Lab")+COUNTIF('C113'!B7,"Lab")+COUNTIF('C121'!B7,"Lab")+COUNTIF('C122'!B7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B7,"Lab")+COUNTIF('C112'!B7,"Lab")+COUNTIF('C113'!B7,"Lab")+COUNTIF('C121'!B7,"Lab")+COUNTIF('C122'!B7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="C21">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 1")+COUNTIF('C112'!C9,"Aula 1")+COUNTIF('C113'!C9,"Aula 1")+COUNTIF('C121'!C9,"Aula 1")+COUNTIF('C122'!C9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 1")+COUNTIF('C112'!C9,"Aula 1")+COUNTIF('C113'!C9,"Aula 1")+COUNTIF('C121'!C9,"Aula 1")+COUNTIF('C122'!C9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 1")+COUNTIF('C112'!C9,"Aula 1")+COUNTIF('C113'!C9,"Aula 1")+COUNTIF('C121'!C9,"Aula 1")+COUNTIF('C122'!C9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 1")+COUNTIF('C112'!B9,"Aula 1")+COUNTIF('C113'!B9,"Aula 1")+COUNTIF('C121'!B9,"Aula 1")+COUNTIF('C122'!B9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 1")+COUNTIF('C112'!B9,"Aula 1")+COUNTIF('C113'!B9,"Aula 1")+COUNTIF('C121'!B9,"Aula 1")+COUNTIF('C122'!B9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 1")+COUNTIF('C112'!B9,"Aula 1")+COUNTIF('C113'!B9,"Aula 1")+COUNTIF('C121'!B9,"Aula 1")+COUNTIF('C122'!B9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="C22">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 2")+COUNTIF('C112'!C9,"Aula 2")+COUNTIF('C113'!C9,"Aula 2")+COUNTIF('C121'!C9,"Aula 2")+COUNTIF('C122'!C9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 2")+COUNTIF('C112'!C9,"Aula 2")+COUNTIF('C113'!C9,"Aula 2")+COUNTIF('C121'!C9,"Aula 2")+COUNTIF('C122'!C9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 2")+COUNTIF('C112'!C9,"Aula 2")+COUNTIF('C113'!C9,"Aula 2")+COUNTIF('C121'!C9,"Aula 2")+COUNTIF('C122'!C9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 2")+COUNTIF('C112'!B9,"Aula 2")+COUNTIF('C113'!B9,"Aula 2")+COUNTIF('C121'!B9,"Aula 2")+COUNTIF('C122'!B9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 2")+COUNTIF('C112'!B9,"Aula 2")+COUNTIF('C113'!B9,"Aula 2")+COUNTIF('C121'!B9,"Aula 2")+COUNTIF('C122'!B9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 2")+COUNTIF('C112'!B9,"Aula 2")+COUNTIF('C113'!B9,"Aula 2")+COUNTIF('C121'!B9,"Aula 2")+COUNTIF('C122'!B9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="C23">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 3")+COUNTIF('C112'!C9,"Aula 3")+COUNTIF('C113'!C9,"Aula 3")+COUNTIF('C121'!C9,"Aula 3")+COUNTIF('C122'!C9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 3")+COUNTIF('C112'!C9,"Aula 3")+COUNTIF('C113'!C9,"Aula 3")+COUNTIF('C121'!C9,"Aula 3")+COUNTIF('C122'!C9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 3")+COUNTIF('C112'!C9,"Aula 3")+COUNTIF('C113'!C9,"Aula 3")+COUNTIF('C121'!C9,"Aula 3")+COUNTIF('C122'!C9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 3")+COUNTIF('C112'!B9,"Aula 3")+COUNTIF('C113'!B9,"Aula 3")+COUNTIF('C121'!B9,"Aula 3")+COUNTIF('C122'!B9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 3")+COUNTIF('C112'!B9,"Aula 3")+COUNTIF('C113'!B9,"Aula 3")+COUNTIF('C121'!B9,"Aula 3")+COUNTIF('C122'!B9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 3")+COUNTIF('C112'!B9,"Aula 3")+COUNTIF('C113'!B9,"Aula 3")+COUNTIF('C121'!B9,"Aula 3")+COUNTIF('C122'!B9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="C24">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 4")+COUNTIF('C112'!C9,"Aula 4")+COUNTIF('C113'!C9,"Aula 4")+COUNTIF('C121'!C9,"Aula 4")+COUNTIF('C122'!C9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 4")+COUNTIF('C112'!C9,"Aula 4")+COUNTIF('C113'!C9,"Aula 4")+COUNTIF('C121'!C9,"Aula 4")+COUNTIF('C122'!C9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 4")+COUNTIF('C112'!C9,"Aula 4")+COUNTIF('C113'!C9,"Aula 4")+COUNTIF('C121'!C9,"Aula 4")+COUNTIF('C122'!C9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 4")+COUNTIF('C112'!B9,"Aula 4")+COUNTIF('C113'!B9,"Aula 4")+COUNTIF('C121'!B9,"Aula 4")+COUNTIF('C122'!B9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 4")+COUNTIF('C112'!B9,"Aula 4")+COUNTIF('C113'!B9,"Aula 4")+COUNTIF('C121'!B9,"Aula 4")+COUNTIF('C122'!B9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 4")+COUNTIF('C112'!B9,"Aula 4")+COUNTIF('C113'!B9,"Aula 4")+COUNTIF('C121'!B9,"Aula 4")+COUNTIF('C122'!B9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="C25">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 5")+COUNTIF('C112'!C9,"Aula 5")+COUNTIF('C113'!C9,"Aula 5")+COUNTIF('C121'!C9,"Aula 5")+COUNTIF('C122'!C9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 5")+COUNTIF('C112'!C9,"Aula 5")+COUNTIF('C113'!C9,"Aula 5")+COUNTIF('C121'!C9,"Aula 5")+COUNTIF('C122'!C9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 5")+COUNTIF('C112'!C9,"Aula 5")+COUNTIF('C113'!C9,"Aula 5")+COUNTIF('C121'!C9,"Aula 5")+COUNTIF('C122'!C9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 5")+COUNTIF('C112'!B9,"Aula 5")+COUNTIF('C113'!B9,"Aula 5")+COUNTIF('C121'!B9,"Aula 5")+COUNTIF('C122'!B9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 5")+COUNTIF('C112'!B9,"Aula 5")+COUNTIF('C113'!B9,"Aula 5")+COUNTIF('C121'!B9,"Aula 5")+COUNTIF('C122'!B9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 5")+COUNTIF('C112'!B9,"Aula 5")+COUNTIF('C113'!B9,"Aula 5")+COUNTIF('C121'!B9,"Aula 5")+COUNTIF('C122'!B9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="C26">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 6")+COUNTIF('C112'!C9,"Aula 6")+COUNTIF('C113'!C9,"Aula 6")+COUNTIF('C121'!C9,"Aula 6")+COUNTIF('C122'!C9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 6")+COUNTIF('C112'!C9,"Aula 6")+COUNTIF('C113'!C9,"Aula 6")+COUNTIF('C121'!C9,"Aula 6")+COUNTIF('C122'!C9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 6")+COUNTIF('C112'!C9,"Aula 6")+COUNTIF('C113'!C9,"Aula 6")+COUNTIF('C121'!C9,"Aula 6")+COUNTIF('C122'!C9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 6")+COUNTIF('C112'!B9,"Aula 6")+COUNTIF('C113'!B9,"Aula 6")+COUNTIF('C121'!B9,"Aula 6")+COUNTIF('C122'!B9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 6")+COUNTIF('C112'!B9,"Aula 6")+COUNTIF('C113'!B9,"Aula 6")+COUNTIF('C121'!B9,"Aula 6")+COUNTIF('C122'!B9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 6")+COUNTIF('C112'!B9,"Aula 6")+COUNTIF('C113'!B9,"Aula 6")+COUNTIF('C121'!B9,"Aula 6")+COUNTIF('C122'!B9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="C27">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 7")+COUNTIF('C112'!C9,"Aula 7")+COUNTIF('C113'!C9,"Aula 7")+COUNTIF('C121'!C9,"Aula 7")+COUNTIF('C122'!C9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 7")+COUNTIF('C112'!C9,"Aula 7")+COUNTIF('C113'!C9,"Aula 7")+COUNTIF('C121'!C9,"Aula 7")+COUNTIF('C122'!C9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 7")+COUNTIF('C112'!C9,"Aula 7")+COUNTIF('C113'!C9,"Aula 7")+COUNTIF('C121'!C9,"Aula 7")+COUNTIF('C122'!C9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 7")+COUNTIF('C112'!B9,"Aula 7")+COUNTIF('C113'!B9,"Aula 7")+COUNTIF('C121'!B9,"Aula 7")+COUNTIF('C122'!B9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 7")+COUNTIF('C112'!B9,"Aula 7")+COUNTIF('C113'!B9,"Aula 7")+COUNTIF('C121'!B9,"Aula 7")+COUNTIF('C122'!B9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 7")+COUNTIF('C112'!B9,"Aula 7")+COUNTIF('C113'!B9,"Aula 7")+COUNTIF('C121'!B9,"Aula 7")+COUNTIF('C122'!B9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="C28">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 8")+COUNTIF('C112'!C9,"Aula 8")+COUNTIF('C113'!C9,"Aula 8")+COUNTIF('C121'!C9,"Aula 8")+COUNTIF('C122'!C9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 8")+COUNTIF('C112'!C9,"Aula 8")+COUNTIF('C113'!C9,"Aula 8")+COUNTIF('C121'!C9,"Aula 8")+COUNTIF('C122'!C9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 8")+COUNTIF('C112'!C9,"Aula 8")+COUNTIF('C113'!C9,"Aula 8")+COUNTIF('C121'!C9,"Aula 8")+COUNTIF('C122'!C9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 8")+COUNTIF('C112'!B9,"Aula 8")+COUNTIF('C113'!B9,"Aula 8")+COUNTIF('C121'!B9,"Aula 8")+COUNTIF('C122'!B9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 8")+COUNTIF('C112'!B9,"Aula 8")+COUNTIF('C113'!B9,"Aula 8")+COUNTIF('C121'!B9,"Aula 8")+COUNTIF('C122'!B9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 8")+COUNTIF('C112'!B9,"Aula 8")+COUNTIF('C113'!B9,"Aula 8")+COUNTIF('C121'!B9,"Aula 8")+COUNTIF('C122'!B9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="C29">
-        <f>IF((IF((COUNTIF('C111'!C9,"Aula 9")+COUNTIF('C112'!C9,"Aula 9")+COUNTIF('C113'!C9,"Aula 9")+COUNTIF('C121'!C9,"Aula 9")+COUNTIF('C122'!C9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 9")+COUNTIF('C112'!C9,"Aula 9")+COUNTIF('C113'!C9,"Aula 9")+COUNTIF('C121'!C9,"Aula 9")+COUNTIF('C122'!C9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 9")+COUNTIF('C112'!C9,"Aula 9")+COUNTIF('C113'!C9,"Aula 9")+COUNTIF('C121'!C9,"Aula 9")+COUNTIF('C122'!C9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Aula 9")+COUNTIF('C112'!B9,"Aula 9")+COUNTIF('C113'!B9,"Aula 9")+COUNTIF('C121'!B9,"Aula 9")+COUNTIF('C122'!B9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Aula 9")+COUNTIF('C112'!B9,"Aula 9")+COUNTIF('C113'!B9,"Aula 9")+COUNTIF('C121'!B9,"Aula 9")+COUNTIF('C122'!B9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Aula 9")+COUNTIF('C112'!B9,"Aula 9")+COUNTIF('C113'!B9,"Aula 9")+COUNTIF('C121'!B9,"Aula 9")+COUNTIF('C122'!B9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="C30">
-        <f>IF((IF((COUNTIF('C111'!C9,"Lab")+COUNTIF('C112'!C9,"Lab")+COUNTIF('C113'!C9,"Lab")+COUNTIF('C121'!C9,"Lab")+COUNTIF('C122'!C9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Lab")+COUNTIF('C112'!C9,"Lab")+COUNTIF('C113'!C9,"Lab")+COUNTIF('C121'!C9,"Lab")+COUNTIF('C122'!C9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Lab")+COUNTIF('C112'!C9,"Lab")+COUNTIF('C113'!C9,"Lab")+COUNTIF('C121'!C9,"Lab")+COUNTIF('C122'!C9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B9,"Lab")+COUNTIF('C112'!B9,"Lab")+COUNTIF('C113'!B9,"Lab")+COUNTIF('C121'!B9,"Lab")+COUNTIF('C122'!B9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B9,"Lab")+COUNTIF('C112'!B9,"Lab")+COUNTIF('C113'!B9,"Lab")+COUNTIF('C121'!B9,"Lab")+COUNTIF('C122'!B9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B9,"Lab")+COUNTIF('C112'!B9,"Lab")+COUNTIF('C113'!B9,"Lab")+COUNTIF('C121'!B9,"Lab")+COUNTIF('C122'!B9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="C31">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 1")+COUNTIF('C112'!C11,"Aula 1")+COUNTIF('C113'!C11,"Aula 1")+COUNTIF('C121'!C11,"Aula 1")+COUNTIF('C122'!C11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 1")+COUNTIF('C112'!C11,"Aula 1")+COUNTIF('C113'!C11,"Aula 1")+COUNTIF('C121'!C11,"Aula 1")+COUNTIF('C122'!C11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 1")+COUNTIF('C112'!C11,"Aula 1")+COUNTIF('C113'!C11,"Aula 1")+COUNTIF('C121'!C11,"Aula 1")+COUNTIF('C122'!C11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 1")+COUNTIF('C112'!B11,"Aula 1")+COUNTIF('C113'!B11,"Aula 1")+COUNTIF('C121'!B11,"Aula 1")+COUNTIF('C122'!B11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 1")+COUNTIF('C112'!B11,"Aula 1")+COUNTIF('C113'!B11,"Aula 1")+COUNTIF('C121'!B11,"Aula 1")+COUNTIF('C122'!B11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 1")+COUNTIF('C112'!B11,"Aula 1")+COUNTIF('C113'!B11,"Aula 1")+COUNTIF('C121'!B11,"Aula 1")+COUNTIF('C122'!B11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="C32">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 2")+COUNTIF('C112'!C11,"Aula 2")+COUNTIF('C113'!C11,"Aula 2")+COUNTIF('C121'!C11,"Aula 2")+COUNTIF('C122'!C11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 2")+COUNTIF('C112'!C11,"Aula 2")+COUNTIF('C113'!C11,"Aula 2")+COUNTIF('C121'!C11,"Aula 2")+COUNTIF('C122'!C11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 2")+COUNTIF('C112'!C11,"Aula 2")+COUNTIF('C113'!C11,"Aula 2")+COUNTIF('C121'!C11,"Aula 2")+COUNTIF('C122'!C11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 2")+COUNTIF('C112'!B11,"Aula 2")+COUNTIF('C113'!B11,"Aula 2")+COUNTIF('C121'!B11,"Aula 2")+COUNTIF('C122'!B11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 2")+COUNTIF('C112'!B11,"Aula 2")+COUNTIF('C113'!B11,"Aula 2")+COUNTIF('C121'!B11,"Aula 2")+COUNTIF('C122'!B11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 2")+COUNTIF('C112'!B11,"Aula 2")+COUNTIF('C113'!B11,"Aula 2")+COUNTIF('C121'!B11,"Aula 2")+COUNTIF('C122'!B11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="C33">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 3")+COUNTIF('C112'!C11,"Aula 3")+COUNTIF('C113'!C11,"Aula 3")+COUNTIF('C121'!C11,"Aula 3")+COUNTIF('C122'!C11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 3")+COUNTIF('C112'!C11,"Aula 3")+COUNTIF('C113'!C11,"Aula 3")+COUNTIF('C121'!C11,"Aula 3")+COUNTIF('C122'!C11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 3")+COUNTIF('C112'!C11,"Aula 3")+COUNTIF('C113'!C11,"Aula 3")+COUNTIF('C121'!C11,"Aula 3")+COUNTIF('C122'!C11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 3")+COUNTIF('C112'!B11,"Aula 3")+COUNTIF('C113'!B11,"Aula 3")+COUNTIF('C121'!B11,"Aula 3")+COUNTIF('C122'!B11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 3")+COUNTIF('C112'!B11,"Aula 3")+COUNTIF('C113'!B11,"Aula 3")+COUNTIF('C121'!B11,"Aula 3")+COUNTIF('C122'!B11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 3")+COUNTIF('C112'!B11,"Aula 3")+COUNTIF('C113'!B11,"Aula 3")+COUNTIF('C121'!B11,"Aula 3")+COUNTIF('C122'!B11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="C34">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 4")+COUNTIF('C112'!C11,"Aula 4")+COUNTIF('C113'!C11,"Aula 4")+COUNTIF('C121'!C11,"Aula 4")+COUNTIF('C122'!C11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 4")+COUNTIF('C112'!C11,"Aula 4")+COUNTIF('C113'!C11,"Aula 4")+COUNTIF('C121'!C11,"Aula 4")+COUNTIF('C122'!C11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 4")+COUNTIF('C112'!C11,"Aula 4")+COUNTIF('C113'!C11,"Aula 4")+COUNTIF('C121'!C11,"Aula 4")+COUNTIF('C122'!C11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 4")+COUNTIF('C112'!B11,"Aula 4")+COUNTIF('C113'!B11,"Aula 4")+COUNTIF('C121'!B11,"Aula 4")+COUNTIF('C122'!B11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 4")+COUNTIF('C112'!B11,"Aula 4")+COUNTIF('C113'!B11,"Aula 4")+COUNTIF('C121'!B11,"Aula 4")+COUNTIF('C122'!B11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 4")+COUNTIF('C112'!B11,"Aula 4")+COUNTIF('C113'!B11,"Aula 4")+COUNTIF('C121'!B11,"Aula 4")+COUNTIF('C122'!B11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="C35">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 5")+COUNTIF('C112'!C11,"Aula 5")+COUNTIF('C113'!C11,"Aula 5")+COUNTIF('C121'!C11,"Aula 5")+COUNTIF('C122'!C11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 5")+COUNTIF('C112'!C11,"Aula 5")+COUNTIF('C113'!C11,"Aula 5")+COUNTIF('C121'!C11,"Aula 5")+COUNTIF('C122'!C11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 5")+COUNTIF('C112'!C11,"Aula 5")+COUNTIF('C113'!C11,"Aula 5")+COUNTIF('C121'!C11,"Aula 5")+COUNTIF('C122'!C11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 5")+COUNTIF('C112'!B11,"Aula 5")+COUNTIF('C113'!B11,"Aula 5")+COUNTIF('C121'!B11,"Aula 5")+COUNTIF('C122'!B11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 5")+COUNTIF('C112'!B11,"Aula 5")+COUNTIF('C113'!B11,"Aula 5")+COUNTIF('C121'!B11,"Aula 5")+COUNTIF('C122'!B11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 5")+COUNTIF('C112'!B11,"Aula 5")+COUNTIF('C113'!B11,"Aula 5")+COUNTIF('C121'!B11,"Aula 5")+COUNTIF('C122'!B11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="C36">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 6")+COUNTIF('C112'!C11,"Aula 6")+COUNTIF('C113'!C11,"Aula 6")+COUNTIF('C121'!C11,"Aula 6")+COUNTIF('C122'!C11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 6")+COUNTIF('C112'!C11,"Aula 6")+COUNTIF('C113'!C11,"Aula 6")+COUNTIF('C121'!C11,"Aula 6")+COUNTIF('C122'!C11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 6")+COUNTIF('C112'!C11,"Aula 6")+COUNTIF('C113'!C11,"Aula 6")+COUNTIF('C121'!C11,"Aula 6")+COUNTIF('C122'!C11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 6")+COUNTIF('C112'!B11,"Aula 6")+COUNTIF('C113'!B11,"Aula 6")+COUNTIF('C121'!B11,"Aula 6")+COUNTIF('C122'!B11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 6")+COUNTIF('C112'!B11,"Aula 6")+COUNTIF('C113'!B11,"Aula 6")+COUNTIF('C121'!B11,"Aula 6")+COUNTIF('C122'!B11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 6")+COUNTIF('C112'!B11,"Aula 6")+COUNTIF('C113'!B11,"Aula 6")+COUNTIF('C121'!B11,"Aula 6")+COUNTIF('C122'!B11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="C37">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 7")+COUNTIF('C112'!C11,"Aula 7")+COUNTIF('C113'!C11,"Aula 7")+COUNTIF('C121'!C11,"Aula 7")+COUNTIF('C122'!C11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 7")+COUNTIF('C112'!C11,"Aula 7")+COUNTIF('C113'!C11,"Aula 7")+COUNTIF('C121'!C11,"Aula 7")+COUNTIF('C122'!C11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 7")+COUNTIF('C112'!C11,"Aula 7")+COUNTIF('C113'!C11,"Aula 7")+COUNTIF('C121'!C11,"Aula 7")+COUNTIF('C122'!C11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 7")+COUNTIF('C112'!B11,"Aula 7")+COUNTIF('C113'!B11,"Aula 7")+COUNTIF('C121'!B11,"Aula 7")+COUNTIF('C122'!B11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 7")+COUNTIF('C112'!B11,"Aula 7")+COUNTIF('C113'!B11,"Aula 7")+COUNTIF('C121'!B11,"Aula 7")+COUNTIF('C122'!B11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 7")+COUNTIF('C112'!B11,"Aula 7")+COUNTIF('C113'!B11,"Aula 7")+COUNTIF('C121'!B11,"Aula 7")+COUNTIF('C122'!B11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="C38">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 8")+COUNTIF('C112'!C11,"Aula 8")+COUNTIF('C113'!C11,"Aula 8")+COUNTIF('C121'!C11,"Aula 8")+COUNTIF('C122'!C11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 8")+COUNTIF('C112'!C11,"Aula 8")+COUNTIF('C113'!C11,"Aula 8")+COUNTIF('C121'!C11,"Aula 8")+COUNTIF('C122'!C11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 8")+COUNTIF('C112'!C11,"Aula 8")+COUNTIF('C113'!C11,"Aula 8")+COUNTIF('C121'!C11,"Aula 8")+COUNTIF('C122'!C11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 8")+COUNTIF('C112'!B11,"Aula 8")+COUNTIF('C113'!B11,"Aula 8")+COUNTIF('C121'!B11,"Aula 8")+COUNTIF('C122'!B11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 8")+COUNTIF('C112'!B11,"Aula 8")+COUNTIF('C113'!B11,"Aula 8")+COUNTIF('C121'!B11,"Aula 8")+COUNTIF('C122'!B11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 8")+COUNTIF('C112'!B11,"Aula 8")+COUNTIF('C113'!B11,"Aula 8")+COUNTIF('C121'!B11,"Aula 8")+COUNTIF('C122'!B11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="C39">
-        <f>IF((IF((COUNTIF('C111'!C11,"Aula 9")+COUNTIF('C112'!C11,"Aula 9")+COUNTIF('C113'!C11,"Aula 9")+COUNTIF('C121'!C11,"Aula 9")+COUNTIF('C122'!C11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 9")+COUNTIF('C112'!C11,"Aula 9")+COUNTIF('C113'!C11,"Aula 9")+COUNTIF('C121'!C11,"Aula 9")+COUNTIF('C122'!C11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 9")+COUNTIF('C112'!C11,"Aula 9")+COUNTIF('C113'!C11,"Aula 9")+COUNTIF('C121'!C11,"Aula 9")+COUNTIF('C122'!C11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Aula 9")+COUNTIF('C112'!B11,"Aula 9")+COUNTIF('C113'!B11,"Aula 9")+COUNTIF('C121'!B11,"Aula 9")+COUNTIF('C122'!B11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Aula 9")+COUNTIF('C112'!B11,"Aula 9")+COUNTIF('C113'!B11,"Aula 9")+COUNTIF('C121'!B11,"Aula 9")+COUNTIF('C122'!B11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Aula 9")+COUNTIF('C112'!B11,"Aula 9")+COUNTIF('C113'!B11,"Aula 9")+COUNTIF('C121'!B11,"Aula 9")+COUNTIF('C122'!B11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="C40">
-        <f>IF((IF((COUNTIF('C111'!C11,"Lab")+COUNTIF('C112'!C11,"Lab")+COUNTIF('C113'!C11,"Lab")+COUNTIF('C121'!C11,"Lab")+COUNTIF('C122'!C11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Lab")+COUNTIF('C112'!C11,"Lab")+COUNTIF('C113'!C11,"Lab")+COUNTIF('C121'!C11,"Lab")+COUNTIF('C122'!C11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Lab")+COUNTIF('C112'!C11,"Lab")+COUNTIF('C113'!C11,"Lab")+COUNTIF('C121'!C11,"Lab")+COUNTIF('C122'!C11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B11,"Lab")+COUNTIF('C112'!B11,"Lab")+COUNTIF('C113'!B11,"Lab")+COUNTIF('C121'!B11,"Lab")+COUNTIF('C122'!B11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B11,"Lab")+COUNTIF('C112'!B11,"Lab")+COUNTIF('C113'!B11,"Lab")+COUNTIF('C121'!B11,"Lab")+COUNTIF('C122'!B11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B11,"Lab")+COUNTIF('C112'!B11,"Lab")+COUNTIF('C113'!B11,"Lab")+COUNTIF('C121'!B11,"Lab")+COUNTIF('C122'!B11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="C41">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 1")+COUNTIF('C112'!C13,"Aula 1")+COUNTIF('C113'!C13,"Aula 1")+COUNTIF('C121'!C13,"Aula 1")+COUNTIF('C122'!C13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 1")+COUNTIF('C112'!C13,"Aula 1")+COUNTIF('C113'!C13,"Aula 1")+COUNTIF('C121'!C13,"Aula 1")+COUNTIF('C122'!C13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 1")+COUNTIF('C112'!C13,"Aula 1")+COUNTIF('C113'!C13,"Aula 1")+COUNTIF('C121'!C13,"Aula 1")+COUNTIF('C122'!C13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 1")+COUNTIF('C112'!B13,"Aula 1")+COUNTIF('C113'!B13,"Aula 1")+COUNTIF('C121'!B13,"Aula 1")+COUNTIF('C122'!B13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 1")+COUNTIF('C112'!B13,"Aula 1")+COUNTIF('C113'!B13,"Aula 1")+COUNTIF('C121'!B13,"Aula 1")+COUNTIF('C122'!B13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 1")+COUNTIF('C112'!B13,"Aula 1")+COUNTIF('C113'!B13,"Aula 1")+COUNTIF('C121'!B13,"Aula 1")+COUNTIF('C122'!B13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="C42">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 2")+COUNTIF('C112'!C13,"Aula 2")+COUNTIF('C113'!C13,"Aula 2")+COUNTIF('C121'!C13,"Aula 2")+COUNTIF('C122'!C13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 2")+COUNTIF('C112'!C13,"Aula 2")+COUNTIF('C113'!C13,"Aula 2")+COUNTIF('C121'!C13,"Aula 2")+COUNTIF('C122'!C13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 2")+COUNTIF('C112'!C13,"Aula 2")+COUNTIF('C113'!C13,"Aula 2")+COUNTIF('C121'!C13,"Aula 2")+COUNTIF('C122'!C13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 2")+COUNTIF('C112'!B13,"Aula 2")+COUNTIF('C113'!B13,"Aula 2")+COUNTIF('C121'!B13,"Aula 2")+COUNTIF('C122'!B13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 2")+COUNTIF('C112'!B13,"Aula 2")+COUNTIF('C113'!B13,"Aula 2")+COUNTIF('C121'!B13,"Aula 2")+COUNTIF('C122'!B13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 2")+COUNTIF('C112'!B13,"Aula 2")+COUNTIF('C113'!B13,"Aula 2")+COUNTIF('C121'!B13,"Aula 2")+COUNTIF('C122'!B13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="C43">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 3")+COUNTIF('C112'!C13,"Aula 3")+COUNTIF('C113'!C13,"Aula 3")+COUNTIF('C121'!C13,"Aula 3")+COUNTIF('C122'!C13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 3")+COUNTIF('C112'!C13,"Aula 3")+COUNTIF('C113'!C13,"Aula 3")+COUNTIF('C121'!C13,"Aula 3")+COUNTIF('C122'!C13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 3")+COUNTIF('C112'!C13,"Aula 3")+COUNTIF('C113'!C13,"Aula 3")+COUNTIF('C121'!C13,"Aula 3")+COUNTIF('C122'!C13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 3")+COUNTIF('C112'!B13,"Aula 3")+COUNTIF('C113'!B13,"Aula 3")+COUNTIF('C121'!B13,"Aula 3")+COUNTIF('C122'!B13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 3")+COUNTIF('C112'!B13,"Aula 3")+COUNTIF('C113'!B13,"Aula 3")+COUNTIF('C121'!B13,"Aula 3")+COUNTIF('C122'!B13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 3")+COUNTIF('C112'!B13,"Aula 3")+COUNTIF('C113'!B13,"Aula 3")+COUNTIF('C121'!B13,"Aula 3")+COUNTIF('C122'!B13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="C44">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 4")+COUNTIF('C112'!C13,"Aula 4")+COUNTIF('C113'!C13,"Aula 4")+COUNTIF('C121'!C13,"Aula 4")+COUNTIF('C122'!C13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 4")+COUNTIF('C112'!C13,"Aula 4")+COUNTIF('C113'!C13,"Aula 4")+COUNTIF('C121'!C13,"Aula 4")+COUNTIF('C122'!C13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 4")+COUNTIF('C112'!C13,"Aula 4")+COUNTIF('C113'!C13,"Aula 4")+COUNTIF('C121'!C13,"Aula 4")+COUNTIF('C122'!C13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 4")+COUNTIF('C112'!B13,"Aula 4")+COUNTIF('C113'!B13,"Aula 4")+COUNTIF('C121'!B13,"Aula 4")+COUNTIF('C122'!B13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 4")+COUNTIF('C112'!B13,"Aula 4")+COUNTIF('C113'!B13,"Aula 4")+COUNTIF('C121'!B13,"Aula 4")+COUNTIF('C122'!B13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 4")+COUNTIF('C112'!B13,"Aula 4")+COUNTIF('C113'!B13,"Aula 4")+COUNTIF('C121'!B13,"Aula 4")+COUNTIF('C122'!B13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="C45">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 5")+COUNTIF('C112'!C13,"Aula 5")+COUNTIF('C113'!C13,"Aula 5")+COUNTIF('C121'!C13,"Aula 5")+COUNTIF('C122'!C13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 5")+COUNTIF('C112'!C13,"Aula 5")+COUNTIF('C113'!C13,"Aula 5")+COUNTIF('C121'!C13,"Aula 5")+COUNTIF('C122'!C13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 5")+COUNTIF('C112'!C13,"Aula 5")+COUNTIF('C113'!C13,"Aula 5")+COUNTIF('C121'!C13,"Aula 5")+COUNTIF('C122'!C13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 5")+COUNTIF('C112'!B13,"Aula 5")+COUNTIF('C113'!B13,"Aula 5")+COUNTIF('C121'!B13,"Aula 5")+COUNTIF('C122'!B13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 5")+COUNTIF('C112'!B13,"Aula 5")+COUNTIF('C113'!B13,"Aula 5")+COUNTIF('C121'!B13,"Aula 5")+COUNTIF('C122'!B13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 5")+COUNTIF('C112'!B13,"Aula 5")+COUNTIF('C113'!B13,"Aula 5")+COUNTIF('C121'!B13,"Aula 5")+COUNTIF('C122'!B13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="C46">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 6")+COUNTIF('C112'!C13,"Aula 6")+COUNTIF('C113'!C13,"Aula 6")+COUNTIF('C121'!C13,"Aula 6")+COUNTIF('C122'!C13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 6")+COUNTIF('C112'!C13,"Aula 6")+COUNTIF('C113'!C13,"Aula 6")+COUNTIF('C121'!C13,"Aula 6")+COUNTIF('C122'!C13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 6")+COUNTIF('C112'!C13,"Aula 6")+COUNTIF('C113'!C13,"Aula 6")+COUNTIF('C121'!C13,"Aula 6")+COUNTIF('C122'!C13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 6")+COUNTIF('C112'!B13,"Aula 6")+COUNTIF('C113'!B13,"Aula 6")+COUNTIF('C121'!B13,"Aula 6")+COUNTIF('C122'!B13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 6")+COUNTIF('C112'!B13,"Aula 6")+COUNTIF('C113'!B13,"Aula 6")+COUNTIF('C121'!B13,"Aula 6")+COUNTIF('C122'!B13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 6")+COUNTIF('C112'!B13,"Aula 6")+COUNTIF('C113'!B13,"Aula 6")+COUNTIF('C121'!B13,"Aula 6")+COUNTIF('C122'!B13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="C47">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 7")+COUNTIF('C112'!C13,"Aula 7")+COUNTIF('C113'!C13,"Aula 7")+COUNTIF('C121'!C13,"Aula 7")+COUNTIF('C122'!C13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 7")+COUNTIF('C112'!C13,"Aula 7")+COUNTIF('C113'!C13,"Aula 7")+COUNTIF('C121'!C13,"Aula 7")+COUNTIF('C122'!C13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 7")+COUNTIF('C112'!C13,"Aula 7")+COUNTIF('C113'!C13,"Aula 7")+COUNTIF('C121'!C13,"Aula 7")+COUNTIF('C122'!C13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 7")+COUNTIF('C112'!B13,"Aula 7")+COUNTIF('C113'!B13,"Aula 7")+COUNTIF('C121'!B13,"Aula 7")+COUNTIF('C122'!B13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 7")+COUNTIF('C112'!B13,"Aula 7")+COUNTIF('C113'!B13,"Aula 7")+COUNTIF('C121'!B13,"Aula 7")+COUNTIF('C122'!B13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 7")+COUNTIF('C112'!B13,"Aula 7")+COUNTIF('C113'!B13,"Aula 7")+COUNTIF('C121'!B13,"Aula 7")+COUNTIF('C122'!B13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="C48">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 8")+COUNTIF('C112'!C13,"Aula 8")+COUNTIF('C113'!C13,"Aula 8")+COUNTIF('C121'!C13,"Aula 8")+COUNTIF('C122'!C13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 8")+COUNTIF('C112'!C13,"Aula 8")+COUNTIF('C113'!C13,"Aula 8")+COUNTIF('C121'!C13,"Aula 8")+COUNTIF('C122'!C13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 8")+COUNTIF('C112'!C13,"Aula 8")+COUNTIF('C113'!C13,"Aula 8")+COUNTIF('C121'!C13,"Aula 8")+COUNTIF('C122'!C13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 8")+COUNTIF('C112'!B13,"Aula 8")+COUNTIF('C113'!B13,"Aula 8")+COUNTIF('C121'!B13,"Aula 8")+COUNTIF('C122'!B13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 8")+COUNTIF('C112'!B13,"Aula 8")+COUNTIF('C113'!B13,"Aula 8")+COUNTIF('C121'!B13,"Aula 8")+COUNTIF('C122'!B13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 8")+COUNTIF('C112'!B13,"Aula 8")+COUNTIF('C113'!B13,"Aula 8")+COUNTIF('C121'!B13,"Aula 8")+COUNTIF('C122'!B13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="C49">
-        <f>IF((IF((COUNTIF('C111'!C13,"Aula 9")+COUNTIF('C112'!C13,"Aula 9")+COUNTIF('C113'!C13,"Aula 9")+COUNTIF('C121'!C13,"Aula 9")+COUNTIF('C122'!C13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 9")+COUNTIF('C112'!C13,"Aula 9")+COUNTIF('C113'!C13,"Aula 9")+COUNTIF('C121'!C13,"Aula 9")+COUNTIF('C122'!C13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 9")+COUNTIF('C112'!C13,"Aula 9")+COUNTIF('C113'!C13,"Aula 9")+COUNTIF('C121'!C13,"Aula 9")+COUNTIF('C122'!C13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Aula 9")+COUNTIF('C112'!B13,"Aula 9")+COUNTIF('C113'!B13,"Aula 9")+COUNTIF('C121'!B13,"Aula 9")+COUNTIF('C122'!B13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Aula 9")+COUNTIF('C112'!B13,"Aula 9")+COUNTIF('C113'!B13,"Aula 9")+COUNTIF('C121'!B13,"Aula 9")+COUNTIF('C122'!B13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Aula 9")+COUNTIF('C112'!B13,"Aula 9")+COUNTIF('C113'!B13,"Aula 9")+COUNTIF('C121'!B13,"Aula 9")+COUNTIF('C122'!B13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="C50">
-        <f>IF((IF((COUNTIF('C111'!C13,"Lab")+COUNTIF('C112'!C13,"Lab")+COUNTIF('C113'!C13,"Lab")+COUNTIF('C121'!C13,"Lab")+COUNTIF('C122'!C13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Lab")+COUNTIF('C112'!C13,"Lab")+COUNTIF('C113'!C13,"Lab")+COUNTIF('C121'!C13,"Lab")+COUNTIF('C122'!C13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Lab")+COUNTIF('C112'!C13,"Lab")+COUNTIF('C113'!C13,"Lab")+COUNTIF('C121'!C13,"Lab")+COUNTIF('C122'!C13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B13,"Lab")+COUNTIF('C112'!B13,"Lab")+COUNTIF('C113'!B13,"Lab")+COUNTIF('C121'!B13,"Lab")+COUNTIF('C122'!B13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B13,"Lab")+COUNTIF('C112'!B13,"Lab")+COUNTIF('C113'!B13,"Lab")+COUNTIF('C121'!B13,"Lab")+COUNTIF('C122'!B13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B13,"Lab")+COUNTIF('C112'!B13,"Lab")+COUNTIF('C113'!B13,"Lab")+COUNTIF('C121'!B13,"Lab")+COUNTIF('C122'!B13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="C51">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 1")+COUNTIF('C112'!C15,"Aula 1")+COUNTIF('C113'!C15,"Aula 1")+COUNTIF('C121'!C15,"Aula 1")+COUNTIF('C122'!C15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 1")+COUNTIF('C112'!C15,"Aula 1")+COUNTIF('C113'!C15,"Aula 1")+COUNTIF('C121'!C15,"Aula 1")+COUNTIF('C122'!C15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 1")+COUNTIF('C112'!C15,"Aula 1")+COUNTIF('C113'!C15,"Aula 1")+COUNTIF('C121'!C15,"Aula 1")+COUNTIF('C122'!C15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 1")+COUNTIF('C112'!B15,"Aula 1")+COUNTIF('C113'!B15,"Aula 1")+COUNTIF('C121'!B15,"Aula 1")+COUNTIF('C122'!B15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 1")+COUNTIF('C112'!B15,"Aula 1")+COUNTIF('C113'!B15,"Aula 1")+COUNTIF('C121'!B15,"Aula 1")+COUNTIF('C122'!B15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 1")+COUNTIF('C112'!B15,"Aula 1")+COUNTIF('C113'!B15,"Aula 1")+COUNTIF('C121'!B15,"Aula 1")+COUNTIF('C122'!B15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="C52">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 2")+COUNTIF('C112'!C15,"Aula 2")+COUNTIF('C113'!C15,"Aula 2")+COUNTIF('C121'!C15,"Aula 2")+COUNTIF('C122'!C15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 2")+COUNTIF('C112'!C15,"Aula 2")+COUNTIF('C113'!C15,"Aula 2")+COUNTIF('C121'!C15,"Aula 2")+COUNTIF('C122'!C15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 2")+COUNTIF('C112'!C15,"Aula 2")+COUNTIF('C113'!C15,"Aula 2")+COUNTIF('C121'!C15,"Aula 2")+COUNTIF('C122'!C15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 2")+COUNTIF('C112'!B15,"Aula 2")+COUNTIF('C113'!B15,"Aula 2")+COUNTIF('C121'!B15,"Aula 2")+COUNTIF('C122'!B15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 2")+COUNTIF('C112'!B15,"Aula 2")+COUNTIF('C113'!B15,"Aula 2")+COUNTIF('C121'!B15,"Aula 2")+COUNTIF('C122'!B15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 2")+COUNTIF('C112'!B15,"Aula 2")+COUNTIF('C113'!B15,"Aula 2")+COUNTIF('C121'!B15,"Aula 2")+COUNTIF('C122'!B15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="C53">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 3")+COUNTIF('C112'!C15,"Aula 3")+COUNTIF('C113'!C15,"Aula 3")+COUNTIF('C121'!C15,"Aula 3")+COUNTIF('C122'!C15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 3")+COUNTIF('C112'!C15,"Aula 3")+COUNTIF('C113'!C15,"Aula 3")+COUNTIF('C121'!C15,"Aula 3")+COUNTIF('C122'!C15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 3")+COUNTIF('C112'!C15,"Aula 3")+COUNTIF('C113'!C15,"Aula 3")+COUNTIF('C121'!C15,"Aula 3")+COUNTIF('C122'!C15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 3")+COUNTIF('C112'!B15,"Aula 3")+COUNTIF('C113'!B15,"Aula 3")+COUNTIF('C121'!B15,"Aula 3")+COUNTIF('C122'!B15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 3")+COUNTIF('C112'!B15,"Aula 3")+COUNTIF('C113'!B15,"Aula 3")+COUNTIF('C121'!B15,"Aula 3")+COUNTIF('C122'!B15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 3")+COUNTIF('C112'!B15,"Aula 3")+COUNTIF('C113'!B15,"Aula 3")+COUNTIF('C121'!B15,"Aula 3")+COUNTIF('C122'!B15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="C54">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 4")+COUNTIF('C112'!C15,"Aula 4")+COUNTIF('C113'!C15,"Aula 4")+COUNTIF('C121'!C15,"Aula 4")+COUNTIF('C122'!C15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 4")+COUNTIF('C112'!C15,"Aula 4")+COUNTIF('C113'!C15,"Aula 4")+COUNTIF('C121'!C15,"Aula 4")+COUNTIF('C122'!C15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 4")+COUNTIF('C112'!C15,"Aula 4")+COUNTIF('C113'!C15,"Aula 4")+COUNTIF('C121'!C15,"Aula 4")+COUNTIF('C122'!C15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 4")+COUNTIF('C112'!B15,"Aula 4")+COUNTIF('C113'!B15,"Aula 4")+COUNTIF('C121'!B15,"Aula 4")+COUNTIF('C122'!B15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 4")+COUNTIF('C112'!B15,"Aula 4")+COUNTIF('C113'!B15,"Aula 4")+COUNTIF('C121'!B15,"Aula 4")+COUNTIF('C122'!B15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 4")+COUNTIF('C112'!B15,"Aula 4")+COUNTIF('C113'!B15,"Aula 4")+COUNTIF('C121'!B15,"Aula 4")+COUNTIF('C122'!B15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="C55">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 5")+COUNTIF('C112'!C15,"Aula 5")+COUNTIF('C113'!C15,"Aula 5")+COUNTIF('C121'!C15,"Aula 5")+COUNTIF('C122'!C15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 5")+COUNTIF('C112'!C15,"Aula 5")+COUNTIF('C113'!C15,"Aula 5")+COUNTIF('C121'!C15,"Aula 5")+COUNTIF('C122'!C15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 5")+COUNTIF('C112'!C15,"Aula 5")+COUNTIF('C113'!C15,"Aula 5")+COUNTIF('C121'!C15,"Aula 5")+COUNTIF('C122'!C15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 5")+COUNTIF('C112'!B15,"Aula 5")+COUNTIF('C113'!B15,"Aula 5")+COUNTIF('C121'!B15,"Aula 5")+COUNTIF('C122'!B15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 5")+COUNTIF('C112'!B15,"Aula 5")+COUNTIF('C113'!B15,"Aula 5")+COUNTIF('C121'!B15,"Aula 5")+COUNTIF('C122'!B15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 5")+COUNTIF('C112'!B15,"Aula 5")+COUNTIF('C113'!B15,"Aula 5")+COUNTIF('C121'!B15,"Aula 5")+COUNTIF('C122'!B15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="C56">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 6")+COUNTIF('C112'!C15,"Aula 6")+COUNTIF('C113'!C15,"Aula 6")+COUNTIF('C121'!C15,"Aula 6")+COUNTIF('C122'!C15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 6")+COUNTIF('C112'!C15,"Aula 6")+COUNTIF('C113'!C15,"Aula 6")+COUNTIF('C121'!C15,"Aula 6")+COUNTIF('C122'!C15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 6")+COUNTIF('C112'!C15,"Aula 6")+COUNTIF('C113'!C15,"Aula 6")+COUNTIF('C121'!C15,"Aula 6")+COUNTIF('C122'!C15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 6")+COUNTIF('C112'!B15,"Aula 6")+COUNTIF('C113'!B15,"Aula 6")+COUNTIF('C121'!B15,"Aula 6")+COUNTIF('C122'!B15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 6")+COUNTIF('C112'!B15,"Aula 6")+COUNTIF('C113'!B15,"Aula 6")+COUNTIF('C121'!B15,"Aula 6")+COUNTIF('C122'!B15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 6")+COUNTIF('C112'!B15,"Aula 6")+COUNTIF('C113'!B15,"Aula 6")+COUNTIF('C121'!B15,"Aula 6")+COUNTIF('C122'!B15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="C57">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 7")+COUNTIF('C112'!C15,"Aula 7")+COUNTIF('C113'!C15,"Aula 7")+COUNTIF('C121'!C15,"Aula 7")+COUNTIF('C122'!C15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 7")+COUNTIF('C112'!C15,"Aula 7")+COUNTIF('C113'!C15,"Aula 7")+COUNTIF('C121'!C15,"Aula 7")+COUNTIF('C122'!C15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 7")+COUNTIF('C112'!C15,"Aula 7")+COUNTIF('C113'!C15,"Aula 7")+COUNTIF('C121'!C15,"Aula 7")+COUNTIF('C122'!C15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 7")+COUNTIF('C112'!B15,"Aula 7")+COUNTIF('C113'!B15,"Aula 7")+COUNTIF('C121'!B15,"Aula 7")+COUNTIF('C122'!B15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 7")+COUNTIF('C112'!B15,"Aula 7")+COUNTIF('C113'!B15,"Aula 7")+COUNTIF('C121'!B15,"Aula 7")+COUNTIF('C122'!B15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 7")+COUNTIF('C112'!B15,"Aula 7")+COUNTIF('C113'!B15,"Aula 7")+COUNTIF('C121'!B15,"Aula 7")+COUNTIF('C122'!B15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="C58">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 8")+COUNTIF('C112'!C15,"Aula 8")+COUNTIF('C113'!C15,"Aula 8")+COUNTIF('C121'!C15,"Aula 8")+COUNTIF('C122'!C15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 8")+COUNTIF('C112'!C15,"Aula 8")+COUNTIF('C113'!C15,"Aula 8")+COUNTIF('C121'!C15,"Aula 8")+COUNTIF('C122'!C15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 8")+COUNTIF('C112'!C15,"Aula 8")+COUNTIF('C113'!C15,"Aula 8")+COUNTIF('C121'!C15,"Aula 8")+COUNTIF('C122'!C15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 8")+COUNTIF('C112'!B15,"Aula 8")+COUNTIF('C113'!B15,"Aula 8")+COUNTIF('C121'!B15,"Aula 8")+COUNTIF('C122'!B15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 8")+COUNTIF('C112'!B15,"Aula 8")+COUNTIF('C113'!B15,"Aula 8")+COUNTIF('C121'!B15,"Aula 8")+COUNTIF('C122'!B15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 8")+COUNTIF('C112'!B15,"Aula 8")+COUNTIF('C113'!B15,"Aula 8")+COUNTIF('C121'!B15,"Aula 8")+COUNTIF('C122'!B15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="C59">
-        <f>IF((IF((COUNTIF('C111'!C15,"Aula 9")+COUNTIF('C112'!C15,"Aula 9")+COUNTIF('C113'!C15,"Aula 9")+COUNTIF('C121'!C15,"Aula 9")+COUNTIF('C122'!C15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 9")+COUNTIF('C112'!C15,"Aula 9")+COUNTIF('C113'!C15,"Aula 9")+COUNTIF('C121'!C15,"Aula 9")+COUNTIF('C122'!C15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 9")+COUNTIF('C112'!C15,"Aula 9")+COUNTIF('C113'!C15,"Aula 9")+COUNTIF('C121'!C15,"Aula 9")+COUNTIF('C122'!C15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Aula 9")+COUNTIF('C112'!B15,"Aula 9")+COUNTIF('C113'!B15,"Aula 9")+COUNTIF('C121'!B15,"Aula 9")+COUNTIF('C122'!B15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Aula 9")+COUNTIF('C112'!B15,"Aula 9")+COUNTIF('C113'!B15,"Aula 9")+COUNTIF('C121'!B15,"Aula 9")+COUNTIF('C122'!B15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Aula 9")+COUNTIF('C112'!B15,"Aula 9")+COUNTIF('C113'!B15,"Aula 9")+COUNTIF('C121'!B15,"Aula 9")+COUNTIF('C122'!B15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="C60">
-        <f>IF((IF((COUNTIF('C111'!C15,"Lab")+COUNTIF('C112'!C15,"Lab")+COUNTIF('C113'!C15,"Lab")+COUNTIF('C121'!C15,"Lab")+COUNTIF('C122'!C15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Lab")+COUNTIF('C112'!C15,"Lab")+COUNTIF('C113'!C15,"Lab")+COUNTIF('C121'!C15,"Lab")+COUNTIF('C122'!C15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Lab")+COUNTIF('C112'!C15,"Lab")+COUNTIF('C113'!C15,"Lab")+COUNTIF('C121'!C15,"Lab")+COUNTIF('C122'!C15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!B15,"Lab")+COUNTIF('C112'!B15,"Lab")+COUNTIF('C113'!B15,"Lab")+COUNTIF('C121'!B15,"Lab")+COUNTIF('C122'!B15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!B15,"Lab")+COUNTIF('C112'!B15,"Lab")+COUNTIF('C113'!B15,"Lab")+COUNTIF('C121'!B15,"Lab")+COUNTIF('C122'!B15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!B15,"Lab")+COUNTIF('C112'!B15,"Lab")+COUNTIF('C113'!B15,"Lab")+COUNTIF('C121'!B15,"Lab")+COUNTIF('C122'!B15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="C61">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 1")+COUNTIF('C112'!D5,"Aula 1")+COUNTIF('C113'!D5,"Aula 1")+COUNTIF('C121'!D5,"Aula 1")+COUNTIF('C122'!D5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 1")+COUNTIF('C112'!D5,"Aula 1")+COUNTIF('C113'!D5,"Aula 1")+COUNTIF('C121'!D5,"Aula 1")+COUNTIF('C122'!D5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 1")+COUNTIF('C112'!D5,"Aula 1")+COUNTIF('C113'!D5,"Aula 1")+COUNTIF('C121'!D5,"Aula 1")+COUNTIF('C122'!D5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 1")+COUNTIF('C112'!C5,"Aula 1")+COUNTIF('C113'!C5,"Aula 1")+COUNTIF('C121'!C5,"Aula 1")+COUNTIF('C122'!C5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 1")+COUNTIF('C112'!C5,"Aula 1")+COUNTIF('C113'!C5,"Aula 1")+COUNTIF('C121'!C5,"Aula 1")+COUNTIF('C122'!C5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 1")+COUNTIF('C112'!C5,"Aula 1")+COUNTIF('C113'!C5,"Aula 1")+COUNTIF('C121'!C5,"Aula 1")+COUNTIF('C122'!C5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="C62">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 2")+COUNTIF('C112'!D5,"Aula 2")+COUNTIF('C113'!D5,"Aula 2")+COUNTIF('C121'!D5,"Aula 2")+COUNTIF('C122'!D5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 2")+COUNTIF('C112'!D5,"Aula 2")+COUNTIF('C113'!D5,"Aula 2")+COUNTIF('C121'!D5,"Aula 2")+COUNTIF('C122'!D5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 2")+COUNTIF('C112'!D5,"Aula 2")+COUNTIF('C113'!D5,"Aula 2")+COUNTIF('C121'!D5,"Aula 2")+COUNTIF('C122'!D5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 2")+COUNTIF('C112'!C5,"Aula 2")+COUNTIF('C113'!C5,"Aula 2")+COUNTIF('C121'!C5,"Aula 2")+COUNTIF('C122'!C5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 2")+COUNTIF('C112'!C5,"Aula 2")+COUNTIF('C113'!C5,"Aula 2")+COUNTIF('C121'!C5,"Aula 2")+COUNTIF('C122'!C5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 2")+COUNTIF('C112'!C5,"Aula 2")+COUNTIF('C113'!C5,"Aula 2")+COUNTIF('C121'!C5,"Aula 2")+COUNTIF('C122'!C5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="C63">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 3")+COUNTIF('C112'!D5,"Aula 3")+COUNTIF('C113'!D5,"Aula 3")+COUNTIF('C121'!D5,"Aula 3")+COUNTIF('C122'!D5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 3")+COUNTIF('C112'!D5,"Aula 3")+COUNTIF('C113'!D5,"Aula 3")+COUNTIF('C121'!D5,"Aula 3")+COUNTIF('C122'!D5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 3")+COUNTIF('C112'!D5,"Aula 3")+COUNTIF('C113'!D5,"Aula 3")+COUNTIF('C121'!D5,"Aula 3")+COUNTIF('C122'!D5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 3")+COUNTIF('C112'!C5,"Aula 3")+COUNTIF('C113'!C5,"Aula 3")+COUNTIF('C121'!C5,"Aula 3")+COUNTIF('C122'!C5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 3")+COUNTIF('C112'!C5,"Aula 3")+COUNTIF('C113'!C5,"Aula 3")+COUNTIF('C121'!C5,"Aula 3")+COUNTIF('C122'!C5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 3")+COUNTIF('C112'!C5,"Aula 3")+COUNTIF('C113'!C5,"Aula 3")+COUNTIF('C121'!C5,"Aula 3")+COUNTIF('C122'!C5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="C64">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 4")+COUNTIF('C112'!D5,"Aula 4")+COUNTIF('C113'!D5,"Aula 4")+COUNTIF('C121'!D5,"Aula 4")+COUNTIF('C122'!D5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 4")+COUNTIF('C112'!D5,"Aula 4")+COUNTIF('C113'!D5,"Aula 4")+COUNTIF('C121'!D5,"Aula 4")+COUNTIF('C122'!D5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 4")+COUNTIF('C112'!D5,"Aula 4")+COUNTIF('C113'!D5,"Aula 4")+COUNTIF('C121'!D5,"Aula 4")+COUNTIF('C122'!D5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 4")+COUNTIF('C112'!C5,"Aula 4")+COUNTIF('C113'!C5,"Aula 4")+COUNTIF('C121'!C5,"Aula 4")+COUNTIF('C122'!C5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 4")+COUNTIF('C112'!C5,"Aula 4")+COUNTIF('C113'!C5,"Aula 4")+COUNTIF('C121'!C5,"Aula 4")+COUNTIF('C122'!C5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 4")+COUNTIF('C112'!C5,"Aula 4")+COUNTIF('C113'!C5,"Aula 4")+COUNTIF('C121'!C5,"Aula 4")+COUNTIF('C122'!C5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="C65">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 5")+COUNTIF('C112'!D5,"Aula 5")+COUNTIF('C113'!D5,"Aula 5")+COUNTIF('C121'!D5,"Aula 5")+COUNTIF('C122'!D5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 5")+COUNTIF('C112'!D5,"Aula 5")+COUNTIF('C113'!D5,"Aula 5")+COUNTIF('C121'!D5,"Aula 5")+COUNTIF('C122'!D5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 5")+COUNTIF('C112'!D5,"Aula 5")+COUNTIF('C113'!D5,"Aula 5")+COUNTIF('C121'!D5,"Aula 5")+COUNTIF('C122'!D5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 5")+COUNTIF('C112'!C5,"Aula 5")+COUNTIF('C113'!C5,"Aula 5")+COUNTIF('C121'!C5,"Aula 5")+COUNTIF('C122'!C5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 5")+COUNTIF('C112'!C5,"Aula 5")+COUNTIF('C113'!C5,"Aula 5")+COUNTIF('C121'!C5,"Aula 5")+COUNTIF('C122'!C5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 5")+COUNTIF('C112'!C5,"Aula 5")+COUNTIF('C113'!C5,"Aula 5")+COUNTIF('C121'!C5,"Aula 5")+COUNTIF('C122'!C5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="C66">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 6")+COUNTIF('C112'!D5,"Aula 6")+COUNTIF('C113'!D5,"Aula 6")+COUNTIF('C121'!D5,"Aula 6")+COUNTIF('C122'!D5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 6")+COUNTIF('C112'!D5,"Aula 6")+COUNTIF('C113'!D5,"Aula 6")+COUNTIF('C121'!D5,"Aula 6")+COUNTIF('C122'!D5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 6")+COUNTIF('C112'!D5,"Aula 6")+COUNTIF('C113'!D5,"Aula 6")+COUNTIF('C121'!D5,"Aula 6")+COUNTIF('C122'!D5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 6")+COUNTIF('C112'!C5,"Aula 6")+COUNTIF('C113'!C5,"Aula 6")+COUNTIF('C121'!C5,"Aula 6")+COUNTIF('C122'!C5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 6")+COUNTIF('C112'!C5,"Aula 6")+COUNTIF('C113'!C5,"Aula 6")+COUNTIF('C121'!C5,"Aula 6")+COUNTIF('C122'!C5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 6")+COUNTIF('C112'!C5,"Aula 6")+COUNTIF('C113'!C5,"Aula 6")+COUNTIF('C121'!C5,"Aula 6")+COUNTIF('C122'!C5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="C67">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 7")+COUNTIF('C112'!D5,"Aula 7")+COUNTIF('C113'!D5,"Aula 7")+COUNTIF('C121'!D5,"Aula 7")+COUNTIF('C122'!D5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 7")+COUNTIF('C112'!D5,"Aula 7")+COUNTIF('C113'!D5,"Aula 7")+COUNTIF('C121'!D5,"Aula 7")+COUNTIF('C122'!D5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 7")+COUNTIF('C112'!D5,"Aula 7")+COUNTIF('C113'!D5,"Aula 7")+COUNTIF('C121'!D5,"Aula 7")+COUNTIF('C122'!D5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 7")+COUNTIF('C112'!C5,"Aula 7")+COUNTIF('C113'!C5,"Aula 7")+COUNTIF('C121'!C5,"Aula 7")+COUNTIF('C122'!C5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 7")+COUNTIF('C112'!C5,"Aula 7")+COUNTIF('C113'!C5,"Aula 7")+COUNTIF('C121'!C5,"Aula 7")+COUNTIF('C122'!C5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 7")+COUNTIF('C112'!C5,"Aula 7")+COUNTIF('C113'!C5,"Aula 7")+COUNTIF('C121'!C5,"Aula 7")+COUNTIF('C122'!C5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="C68">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 8")+COUNTIF('C112'!D5,"Aula 8")+COUNTIF('C113'!D5,"Aula 8")+COUNTIF('C121'!D5,"Aula 8")+COUNTIF('C122'!D5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 8")+COUNTIF('C112'!D5,"Aula 8")+COUNTIF('C113'!D5,"Aula 8")+COUNTIF('C121'!D5,"Aula 8")+COUNTIF('C122'!D5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 8")+COUNTIF('C112'!D5,"Aula 8")+COUNTIF('C113'!D5,"Aula 8")+COUNTIF('C121'!D5,"Aula 8")+COUNTIF('C122'!D5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 8")+COUNTIF('C112'!C5,"Aula 8")+COUNTIF('C113'!C5,"Aula 8")+COUNTIF('C121'!C5,"Aula 8")+COUNTIF('C122'!C5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 8")+COUNTIF('C112'!C5,"Aula 8")+COUNTIF('C113'!C5,"Aula 8")+COUNTIF('C121'!C5,"Aula 8")+COUNTIF('C122'!C5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 8")+COUNTIF('C112'!C5,"Aula 8")+COUNTIF('C113'!C5,"Aula 8")+COUNTIF('C121'!C5,"Aula 8")+COUNTIF('C122'!C5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="C69">
-        <f>IF((IF((COUNTIF('C111'!D5,"Aula 9")+COUNTIF('C112'!D5,"Aula 9")+COUNTIF('C113'!D5,"Aula 9")+COUNTIF('C121'!D5,"Aula 9")+COUNTIF('C122'!D5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 9")+COUNTIF('C112'!D5,"Aula 9")+COUNTIF('C113'!D5,"Aula 9")+COUNTIF('C121'!D5,"Aula 9")+COUNTIF('C122'!D5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 9")+COUNTIF('C112'!D5,"Aula 9")+COUNTIF('C113'!D5,"Aula 9")+COUNTIF('C121'!D5,"Aula 9")+COUNTIF('C122'!D5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Aula 9")+COUNTIF('C112'!C5,"Aula 9")+COUNTIF('C113'!C5,"Aula 9")+COUNTIF('C121'!C5,"Aula 9")+COUNTIF('C122'!C5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Aula 9")+COUNTIF('C112'!C5,"Aula 9")+COUNTIF('C113'!C5,"Aula 9")+COUNTIF('C121'!C5,"Aula 9")+COUNTIF('C122'!C5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Aula 9")+COUNTIF('C112'!C5,"Aula 9")+COUNTIF('C113'!C5,"Aula 9")+COUNTIF('C121'!C5,"Aula 9")+COUNTIF('C122'!C5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="C70">
-        <f>IF((IF((COUNTIF('C111'!D5,"Lab")+COUNTIF('C112'!D5,"Lab")+COUNTIF('C113'!D5,"Lab")+COUNTIF('C121'!D5,"Lab")+COUNTIF('C122'!D5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Lab")+COUNTIF('C112'!D5,"Lab")+COUNTIF('C113'!D5,"Lab")+COUNTIF('C121'!D5,"Lab")+COUNTIF('C122'!D5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Lab")+COUNTIF('C112'!D5,"Lab")+COUNTIF('C113'!D5,"Lab")+COUNTIF('C121'!D5,"Lab")+COUNTIF('C122'!D5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C5,"Lab")+COUNTIF('C112'!C5,"Lab")+COUNTIF('C113'!C5,"Lab")+COUNTIF('C121'!C5,"Lab")+COUNTIF('C122'!C5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C5,"Lab")+COUNTIF('C112'!C5,"Lab")+COUNTIF('C113'!C5,"Lab")+COUNTIF('C121'!C5,"Lab")+COUNTIF('C122'!C5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C5,"Lab")+COUNTIF('C112'!C5,"Lab")+COUNTIF('C113'!C5,"Lab")+COUNTIF('C121'!C5,"Lab")+COUNTIF('C122'!C5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="C71">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 1")+COUNTIF('C112'!D7,"Aula 1")+COUNTIF('C113'!D7,"Aula 1")+COUNTIF('C121'!D7,"Aula 1")+COUNTIF('C122'!D7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 1")+COUNTIF('C112'!D7,"Aula 1")+COUNTIF('C113'!D7,"Aula 1")+COUNTIF('C121'!D7,"Aula 1")+COUNTIF('C122'!D7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 1")+COUNTIF('C112'!D7,"Aula 1")+COUNTIF('C113'!D7,"Aula 1")+COUNTIF('C121'!D7,"Aula 1")+COUNTIF('C122'!D7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 1")+COUNTIF('C112'!C7,"Aula 1")+COUNTIF('C113'!C7,"Aula 1")+COUNTIF('C121'!C7,"Aula 1")+COUNTIF('C122'!C7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 1")+COUNTIF('C112'!C7,"Aula 1")+COUNTIF('C113'!C7,"Aula 1")+COUNTIF('C121'!C7,"Aula 1")+COUNTIF('C122'!C7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 1")+COUNTIF('C112'!C7,"Aula 1")+COUNTIF('C113'!C7,"Aula 1")+COUNTIF('C121'!C7,"Aula 1")+COUNTIF('C122'!C7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="C72">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 2")+COUNTIF('C112'!D7,"Aula 2")+COUNTIF('C113'!D7,"Aula 2")+COUNTIF('C121'!D7,"Aula 2")+COUNTIF('C122'!D7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 2")+COUNTIF('C112'!D7,"Aula 2")+COUNTIF('C113'!D7,"Aula 2")+COUNTIF('C121'!D7,"Aula 2")+COUNTIF('C122'!D7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 2")+COUNTIF('C112'!D7,"Aula 2")+COUNTIF('C113'!D7,"Aula 2")+COUNTIF('C121'!D7,"Aula 2")+COUNTIF('C122'!D7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 2")+COUNTIF('C112'!C7,"Aula 2")+COUNTIF('C113'!C7,"Aula 2")+COUNTIF('C121'!C7,"Aula 2")+COUNTIF('C122'!C7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 2")+COUNTIF('C112'!C7,"Aula 2")+COUNTIF('C113'!C7,"Aula 2")+COUNTIF('C121'!C7,"Aula 2")+COUNTIF('C122'!C7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 2")+COUNTIF('C112'!C7,"Aula 2")+COUNTIF('C113'!C7,"Aula 2")+COUNTIF('C121'!C7,"Aula 2")+COUNTIF('C122'!C7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="C73">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 3")+COUNTIF('C112'!D7,"Aula 3")+COUNTIF('C113'!D7,"Aula 3")+COUNTIF('C121'!D7,"Aula 3")+COUNTIF('C122'!D7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 3")+COUNTIF('C112'!D7,"Aula 3")+COUNTIF('C113'!D7,"Aula 3")+COUNTIF('C121'!D7,"Aula 3")+COUNTIF('C122'!D7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 3")+COUNTIF('C112'!D7,"Aula 3")+COUNTIF('C113'!D7,"Aula 3")+COUNTIF('C121'!D7,"Aula 3")+COUNTIF('C122'!D7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 3")+COUNTIF('C112'!C7,"Aula 3")+COUNTIF('C113'!C7,"Aula 3")+COUNTIF('C121'!C7,"Aula 3")+COUNTIF('C122'!C7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 3")+COUNTIF('C112'!C7,"Aula 3")+COUNTIF('C113'!C7,"Aula 3")+COUNTIF('C121'!C7,"Aula 3")+COUNTIF('C122'!C7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 3")+COUNTIF('C112'!C7,"Aula 3")+COUNTIF('C113'!C7,"Aula 3")+COUNTIF('C121'!C7,"Aula 3")+COUNTIF('C122'!C7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="C74">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 4")+COUNTIF('C112'!D7,"Aula 4")+COUNTIF('C113'!D7,"Aula 4")+COUNTIF('C121'!D7,"Aula 4")+COUNTIF('C122'!D7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 4")+COUNTIF('C112'!D7,"Aula 4")+COUNTIF('C113'!D7,"Aula 4")+COUNTIF('C121'!D7,"Aula 4")+COUNTIF('C122'!D7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 4")+COUNTIF('C112'!D7,"Aula 4")+COUNTIF('C113'!D7,"Aula 4")+COUNTIF('C121'!D7,"Aula 4")+COUNTIF('C122'!D7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 4")+COUNTIF('C112'!C7,"Aula 4")+COUNTIF('C113'!C7,"Aula 4")+COUNTIF('C121'!C7,"Aula 4")+COUNTIF('C122'!C7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 4")+COUNTIF('C112'!C7,"Aula 4")+COUNTIF('C113'!C7,"Aula 4")+COUNTIF('C121'!C7,"Aula 4")+COUNTIF('C122'!C7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 4")+COUNTIF('C112'!C7,"Aula 4")+COUNTIF('C113'!C7,"Aula 4")+COUNTIF('C121'!C7,"Aula 4")+COUNTIF('C122'!C7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="C75">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 5")+COUNTIF('C112'!D7,"Aula 5")+COUNTIF('C113'!D7,"Aula 5")+COUNTIF('C121'!D7,"Aula 5")+COUNTIF('C122'!D7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 5")+COUNTIF('C112'!D7,"Aula 5")+COUNTIF('C113'!D7,"Aula 5")+COUNTIF('C121'!D7,"Aula 5")+COUNTIF('C122'!D7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 5")+COUNTIF('C112'!D7,"Aula 5")+COUNTIF('C113'!D7,"Aula 5")+COUNTIF('C121'!D7,"Aula 5")+COUNTIF('C122'!D7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 5")+COUNTIF('C112'!C7,"Aula 5")+COUNTIF('C113'!C7,"Aula 5")+COUNTIF('C121'!C7,"Aula 5")+COUNTIF('C122'!C7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 5")+COUNTIF('C112'!C7,"Aula 5")+COUNTIF('C113'!C7,"Aula 5")+COUNTIF('C121'!C7,"Aula 5")+COUNTIF('C122'!C7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 5")+COUNTIF('C112'!C7,"Aula 5")+COUNTIF('C113'!C7,"Aula 5")+COUNTIF('C121'!C7,"Aula 5")+COUNTIF('C122'!C7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="C76">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 6")+COUNTIF('C112'!D7,"Aula 6")+COUNTIF('C113'!D7,"Aula 6")+COUNTIF('C121'!D7,"Aula 6")+COUNTIF('C122'!D7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 6")+COUNTIF('C112'!D7,"Aula 6")+COUNTIF('C113'!D7,"Aula 6")+COUNTIF('C121'!D7,"Aula 6")+COUNTIF('C122'!D7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 6")+COUNTIF('C112'!D7,"Aula 6")+COUNTIF('C113'!D7,"Aula 6")+COUNTIF('C121'!D7,"Aula 6")+COUNTIF('C122'!D7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 6")+COUNTIF('C112'!C7,"Aula 6")+COUNTIF('C113'!C7,"Aula 6")+COUNTIF('C121'!C7,"Aula 6")+COUNTIF('C122'!C7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 6")+COUNTIF('C112'!C7,"Aula 6")+COUNTIF('C113'!C7,"Aula 6")+COUNTIF('C121'!C7,"Aula 6")+COUNTIF('C122'!C7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 6")+COUNTIF('C112'!C7,"Aula 6")+COUNTIF('C113'!C7,"Aula 6")+COUNTIF('C121'!C7,"Aula 6")+COUNTIF('C122'!C7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="C77">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 7")+COUNTIF('C112'!D7,"Aula 7")+COUNTIF('C113'!D7,"Aula 7")+COUNTIF('C121'!D7,"Aula 7")+COUNTIF('C122'!D7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 7")+COUNTIF('C112'!D7,"Aula 7")+COUNTIF('C113'!D7,"Aula 7")+COUNTIF('C121'!D7,"Aula 7")+COUNTIF('C122'!D7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 7")+COUNTIF('C112'!D7,"Aula 7")+COUNTIF('C113'!D7,"Aula 7")+COUNTIF('C121'!D7,"Aula 7")+COUNTIF('C122'!D7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 7")+COUNTIF('C112'!C7,"Aula 7")+COUNTIF('C113'!C7,"Aula 7")+COUNTIF('C121'!C7,"Aula 7")+COUNTIF('C122'!C7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 7")+COUNTIF('C112'!C7,"Aula 7")+COUNTIF('C113'!C7,"Aula 7")+COUNTIF('C121'!C7,"Aula 7")+COUNTIF('C122'!C7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 7")+COUNTIF('C112'!C7,"Aula 7")+COUNTIF('C113'!C7,"Aula 7")+COUNTIF('C121'!C7,"Aula 7")+COUNTIF('C122'!C7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="C78">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 8")+COUNTIF('C112'!D7,"Aula 8")+COUNTIF('C113'!D7,"Aula 8")+COUNTIF('C121'!D7,"Aula 8")+COUNTIF('C122'!D7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 8")+COUNTIF('C112'!D7,"Aula 8")+COUNTIF('C113'!D7,"Aula 8")+COUNTIF('C121'!D7,"Aula 8")+COUNTIF('C122'!D7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 8")+COUNTIF('C112'!D7,"Aula 8")+COUNTIF('C113'!D7,"Aula 8")+COUNTIF('C121'!D7,"Aula 8")+COUNTIF('C122'!D7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 8")+COUNTIF('C112'!C7,"Aula 8")+COUNTIF('C113'!C7,"Aula 8")+COUNTIF('C121'!C7,"Aula 8")+COUNTIF('C122'!C7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 8")+COUNTIF('C112'!C7,"Aula 8")+COUNTIF('C113'!C7,"Aula 8")+COUNTIF('C121'!C7,"Aula 8")+COUNTIF('C122'!C7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 8")+COUNTIF('C112'!C7,"Aula 8")+COUNTIF('C113'!C7,"Aula 8")+COUNTIF('C121'!C7,"Aula 8")+COUNTIF('C122'!C7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="C79">
-        <f>IF((IF((COUNTIF('C111'!D7,"Aula 9")+COUNTIF('C112'!D7,"Aula 9")+COUNTIF('C113'!D7,"Aula 9")+COUNTIF('C121'!D7,"Aula 9")+COUNTIF('C122'!D7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 9")+COUNTIF('C112'!D7,"Aula 9")+COUNTIF('C113'!D7,"Aula 9")+COUNTIF('C121'!D7,"Aula 9")+COUNTIF('C122'!D7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 9")+COUNTIF('C112'!D7,"Aula 9")+COUNTIF('C113'!D7,"Aula 9")+COUNTIF('C121'!D7,"Aula 9")+COUNTIF('C122'!D7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Aula 9")+COUNTIF('C112'!C7,"Aula 9")+COUNTIF('C113'!C7,"Aula 9")+COUNTIF('C121'!C7,"Aula 9")+COUNTIF('C122'!C7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Aula 9")+COUNTIF('C112'!C7,"Aula 9")+COUNTIF('C113'!C7,"Aula 9")+COUNTIF('C121'!C7,"Aula 9")+COUNTIF('C122'!C7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Aula 9")+COUNTIF('C112'!C7,"Aula 9")+COUNTIF('C113'!C7,"Aula 9")+COUNTIF('C121'!C7,"Aula 9")+COUNTIF('C122'!C7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="C80">
-        <f>IF((IF((COUNTIF('C111'!D7,"Lab")+COUNTIF('C112'!D7,"Lab")+COUNTIF('C113'!D7,"Lab")+COUNTIF('C121'!D7,"Lab")+COUNTIF('C122'!D7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Lab")+COUNTIF('C112'!D7,"Lab")+COUNTIF('C113'!D7,"Lab")+COUNTIF('C121'!D7,"Lab")+COUNTIF('C122'!D7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Lab")+COUNTIF('C112'!D7,"Lab")+COUNTIF('C113'!D7,"Lab")+COUNTIF('C121'!D7,"Lab")+COUNTIF('C122'!D7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C7,"Lab")+COUNTIF('C112'!C7,"Lab")+COUNTIF('C113'!C7,"Lab")+COUNTIF('C121'!C7,"Lab")+COUNTIF('C122'!C7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C7,"Lab")+COUNTIF('C112'!C7,"Lab")+COUNTIF('C113'!C7,"Lab")+COUNTIF('C121'!C7,"Lab")+COUNTIF('C122'!C7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C7,"Lab")+COUNTIF('C112'!C7,"Lab")+COUNTIF('C113'!C7,"Lab")+COUNTIF('C121'!C7,"Lab")+COUNTIF('C122'!C7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="C81">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 1")+COUNTIF('C112'!D9,"Aula 1")+COUNTIF('C113'!D9,"Aula 1")+COUNTIF('C121'!D9,"Aula 1")+COUNTIF('C122'!D9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 1")+COUNTIF('C112'!D9,"Aula 1")+COUNTIF('C113'!D9,"Aula 1")+COUNTIF('C121'!D9,"Aula 1")+COUNTIF('C122'!D9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 1")+COUNTIF('C112'!D9,"Aula 1")+COUNTIF('C113'!D9,"Aula 1")+COUNTIF('C121'!D9,"Aula 1")+COUNTIF('C122'!D9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 1")+COUNTIF('C112'!C9,"Aula 1")+COUNTIF('C113'!C9,"Aula 1")+COUNTIF('C121'!C9,"Aula 1")+COUNTIF('C122'!C9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 1")+COUNTIF('C112'!C9,"Aula 1")+COUNTIF('C113'!C9,"Aula 1")+COUNTIF('C121'!C9,"Aula 1")+COUNTIF('C122'!C9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 1")+COUNTIF('C112'!C9,"Aula 1")+COUNTIF('C113'!C9,"Aula 1")+COUNTIF('C121'!C9,"Aula 1")+COUNTIF('C122'!C9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="C82">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 2")+COUNTIF('C112'!D9,"Aula 2")+COUNTIF('C113'!D9,"Aula 2")+COUNTIF('C121'!D9,"Aula 2")+COUNTIF('C122'!D9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 2")+COUNTIF('C112'!D9,"Aula 2")+COUNTIF('C113'!D9,"Aula 2")+COUNTIF('C121'!D9,"Aula 2")+COUNTIF('C122'!D9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 2")+COUNTIF('C112'!D9,"Aula 2")+COUNTIF('C113'!D9,"Aula 2")+COUNTIF('C121'!D9,"Aula 2")+COUNTIF('C122'!D9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 2")+COUNTIF('C112'!C9,"Aula 2")+COUNTIF('C113'!C9,"Aula 2")+COUNTIF('C121'!C9,"Aula 2")+COUNTIF('C122'!C9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 2")+COUNTIF('C112'!C9,"Aula 2")+COUNTIF('C113'!C9,"Aula 2")+COUNTIF('C121'!C9,"Aula 2")+COUNTIF('C122'!C9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 2")+COUNTIF('C112'!C9,"Aula 2")+COUNTIF('C113'!C9,"Aula 2")+COUNTIF('C121'!C9,"Aula 2")+COUNTIF('C122'!C9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="C83">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 3")+COUNTIF('C112'!D9,"Aula 3")+COUNTIF('C113'!D9,"Aula 3")+COUNTIF('C121'!D9,"Aula 3")+COUNTIF('C122'!D9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 3")+COUNTIF('C112'!D9,"Aula 3")+COUNTIF('C113'!D9,"Aula 3")+COUNTIF('C121'!D9,"Aula 3")+COUNTIF('C122'!D9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 3")+COUNTIF('C112'!D9,"Aula 3")+COUNTIF('C113'!D9,"Aula 3")+COUNTIF('C121'!D9,"Aula 3")+COUNTIF('C122'!D9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 3")+COUNTIF('C112'!C9,"Aula 3")+COUNTIF('C113'!C9,"Aula 3")+COUNTIF('C121'!C9,"Aula 3")+COUNTIF('C122'!C9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 3")+COUNTIF('C112'!C9,"Aula 3")+COUNTIF('C113'!C9,"Aula 3")+COUNTIF('C121'!C9,"Aula 3")+COUNTIF('C122'!C9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 3")+COUNTIF('C112'!C9,"Aula 3")+COUNTIF('C113'!C9,"Aula 3")+COUNTIF('C121'!C9,"Aula 3")+COUNTIF('C122'!C9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="C84">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 4")+COUNTIF('C112'!D9,"Aula 4")+COUNTIF('C113'!D9,"Aula 4")+COUNTIF('C121'!D9,"Aula 4")+COUNTIF('C122'!D9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 4")+COUNTIF('C112'!D9,"Aula 4")+COUNTIF('C113'!D9,"Aula 4")+COUNTIF('C121'!D9,"Aula 4")+COUNTIF('C122'!D9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 4")+COUNTIF('C112'!D9,"Aula 4")+COUNTIF('C113'!D9,"Aula 4")+COUNTIF('C121'!D9,"Aula 4")+COUNTIF('C122'!D9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 4")+COUNTIF('C112'!C9,"Aula 4")+COUNTIF('C113'!C9,"Aula 4")+COUNTIF('C121'!C9,"Aula 4")+COUNTIF('C122'!C9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 4")+COUNTIF('C112'!C9,"Aula 4")+COUNTIF('C113'!C9,"Aula 4")+COUNTIF('C121'!C9,"Aula 4")+COUNTIF('C122'!C9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 4")+COUNTIF('C112'!C9,"Aula 4")+COUNTIF('C113'!C9,"Aula 4")+COUNTIF('C121'!C9,"Aula 4")+COUNTIF('C122'!C9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="C85">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 5")+COUNTIF('C112'!D9,"Aula 5")+COUNTIF('C113'!D9,"Aula 5")+COUNTIF('C121'!D9,"Aula 5")+COUNTIF('C122'!D9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 5")+COUNTIF('C112'!D9,"Aula 5")+COUNTIF('C113'!D9,"Aula 5")+COUNTIF('C121'!D9,"Aula 5")+COUNTIF('C122'!D9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 5")+COUNTIF('C112'!D9,"Aula 5")+COUNTIF('C113'!D9,"Aula 5")+COUNTIF('C121'!D9,"Aula 5")+COUNTIF('C122'!D9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 5")+COUNTIF('C112'!C9,"Aula 5")+COUNTIF('C113'!C9,"Aula 5")+COUNTIF('C121'!C9,"Aula 5")+COUNTIF('C122'!C9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 5")+COUNTIF('C112'!C9,"Aula 5")+COUNTIF('C113'!C9,"Aula 5")+COUNTIF('C121'!C9,"Aula 5")+COUNTIF('C122'!C9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 5")+COUNTIF('C112'!C9,"Aula 5")+COUNTIF('C113'!C9,"Aula 5")+COUNTIF('C121'!C9,"Aula 5")+COUNTIF('C122'!C9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="C86">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 6")+COUNTIF('C112'!D9,"Aula 6")+COUNTIF('C113'!D9,"Aula 6")+COUNTIF('C121'!D9,"Aula 6")+COUNTIF('C122'!D9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 6")+COUNTIF('C112'!D9,"Aula 6")+COUNTIF('C113'!D9,"Aula 6")+COUNTIF('C121'!D9,"Aula 6")+COUNTIF('C122'!D9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 6")+COUNTIF('C112'!D9,"Aula 6")+COUNTIF('C113'!D9,"Aula 6")+COUNTIF('C121'!D9,"Aula 6")+COUNTIF('C122'!D9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 6")+COUNTIF('C112'!C9,"Aula 6")+COUNTIF('C113'!C9,"Aula 6")+COUNTIF('C121'!C9,"Aula 6")+COUNTIF('C122'!C9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 6")+COUNTIF('C112'!C9,"Aula 6")+COUNTIF('C113'!C9,"Aula 6")+COUNTIF('C121'!C9,"Aula 6")+COUNTIF('C122'!C9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 6")+COUNTIF('C112'!C9,"Aula 6")+COUNTIF('C113'!C9,"Aula 6")+COUNTIF('C121'!C9,"Aula 6")+COUNTIF('C122'!C9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="C87">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 7")+COUNTIF('C112'!D9,"Aula 7")+COUNTIF('C113'!D9,"Aula 7")+COUNTIF('C121'!D9,"Aula 7")+COUNTIF('C122'!D9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 7")+COUNTIF('C112'!D9,"Aula 7")+COUNTIF('C113'!D9,"Aula 7")+COUNTIF('C121'!D9,"Aula 7")+COUNTIF('C122'!D9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 7")+COUNTIF('C112'!D9,"Aula 7")+COUNTIF('C113'!D9,"Aula 7")+COUNTIF('C121'!D9,"Aula 7")+COUNTIF('C122'!D9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 7")+COUNTIF('C112'!C9,"Aula 7")+COUNTIF('C113'!C9,"Aula 7")+COUNTIF('C121'!C9,"Aula 7")+COUNTIF('C122'!C9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 7")+COUNTIF('C112'!C9,"Aula 7")+COUNTIF('C113'!C9,"Aula 7")+COUNTIF('C121'!C9,"Aula 7")+COUNTIF('C122'!C9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 7")+COUNTIF('C112'!C9,"Aula 7")+COUNTIF('C113'!C9,"Aula 7")+COUNTIF('C121'!C9,"Aula 7")+COUNTIF('C122'!C9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="C88">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 8")+COUNTIF('C112'!D9,"Aula 8")+COUNTIF('C113'!D9,"Aula 8")+COUNTIF('C121'!D9,"Aula 8")+COUNTIF('C122'!D9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 8")+COUNTIF('C112'!D9,"Aula 8")+COUNTIF('C113'!D9,"Aula 8")+COUNTIF('C121'!D9,"Aula 8")+COUNTIF('C122'!D9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 8")+COUNTIF('C112'!D9,"Aula 8")+COUNTIF('C113'!D9,"Aula 8")+COUNTIF('C121'!D9,"Aula 8")+COUNTIF('C122'!D9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 8")+COUNTIF('C112'!C9,"Aula 8")+COUNTIF('C113'!C9,"Aula 8")+COUNTIF('C121'!C9,"Aula 8")+COUNTIF('C122'!C9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 8")+COUNTIF('C112'!C9,"Aula 8")+COUNTIF('C113'!C9,"Aula 8")+COUNTIF('C121'!C9,"Aula 8")+COUNTIF('C122'!C9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 8")+COUNTIF('C112'!C9,"Aula 8")+COUNTIF('C113'!C9,"Aula 8")+COUNTIF('C121'!C9,"Aula 8")+COUNTIF('C122'!C9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="C89">
-        <f>IF((IF((COUNTIF('C111'!D9,"Aula 9")+COUNTIF('C112'!D9,"Aula 9")+COUNTIF('C113'!D9,"Aula 9")+COUNTIF('C121'!D9,"Aula 9")+COUNTIF('C122'!D9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 9")+COUNTIF('C112'!D9,"Aula 9")+COUNTIF('C113'!D9,"Aula 9")+COUNTIF('C121'!D9,"Aula 9")+COUNTIF('C122'!D9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 9")+COUNTIF('C112'!D9,"Aula 9")+COUNTIF('C113'!D9,"Aula 9")+COUNTIF('C121'!D9,"Aula 9")+COUNTIF('C122'!D9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Aula 9")+COUNTIF('C112'!C9,"Aula 9")+COUNTIF('C113'!C9,"Aula 9")+COUNTIF('C121'!C9,"Aula 9")+COUNTIF('C122'!C9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Aula 9")+COUNTIF('C112'!C9,"Aula 9")+COUNTIF('C113'!C9,"Aula 9")+COUNTIF('C121'!C9,"Aula 9")+COUNTIF('C122'!C9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Aula 9")+COUNTIF('C112'!C9,"Aula 9")+COUNTIF('C113'!C9,"Aula 9")+COUNTIF('C121'!C9,"Aula 9")+COUNTIF('C122'!C9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="C90">
-        <f>IF((IF((COUNTIF('C111'!D9,"Lab")+COUNTIF('C112'!D9,"Lab")+COUNTIF('C113'!D9,"Lab")+COUNTIF('C121'!D9,"Lab")+COUNTIF('C122'!D9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Lab")+COUNTIF('C112'!D9,"Lab")+COUNTIF('C113'!D9,"Lab")+COUNTIF('C121'!D9,"Lab")+COUNTIF('C122'!D9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Lab")+COUNTIF('C112'!D9,"Lab")+COUNTIF('C113'!D9,"Lab")+COUNTIF('C121'!D9,"Lab")+COUNTIF('C122'!D9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C9,"Lab")+COUNTIF('C112'!C9,"Lab")+COUNTIF('C113'!C9,"Lab")+COUNTIF('C121'!C9,"Lab")+COUNTIF('C122'!C9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C9,"Lab")+COUNTIF('C112'!C9,"Lab")+COUNTIF('C113'!C9,"Lab")+COUNTIF('C121'!C9,"Lab")+COUNTIF('C122'!C9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C9,"Lab")+COUNTIF('C112'!C9,"Lab")+COUNTIF('C113'!C9,"Lab")+COUNTIF('C121'!C9,"Lab")+COUNTIF('C122'!C9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="C91">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 1")+COUNTIF('C112'!D11,"Aula 1")+COUNTIF('C113'!D11,"Aula 1")+COUNTIF('C121'!D11,"Aula 1")+COUNTIF('C122'!D11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 1")+COUNTIF('C112'!D11,"Aula 1")+COUNTIF('C113'!D11,"Aula 1")+COUNTIF('C121'!D11,"Aula 1")+COUNTIF('C122'!D11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 1")+COUNTIF('C112'!D11,"Aula 1")+COUNTIF('C113'!D11,"Aula 1")+COUNTIF('C121'!D11,"Aula 1")+COUNTIF('C122'!D11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 1")+COUNTIF('C112'!C11,"Aula 1")+COUNTIF('C113'!C11,"Aula 1")+COUNTIF('C121'!C11,"Aula 1")+COUNTIF('C122'!C11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 1")+COUNTIF('C112'!C11,"Aula 1")+COUNTIF('C113'!C11,"Aula 1")+COUNTIF('C121'!C11,"Aula 1")+COUNTIF('C122'!C11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 1")+COUNTIF('C112'!C11,"Aula 1")+COUNTIF('C113'!C11,"Aula 1")+COUNTIF('C121'!C11,"Aula 1")+COUNTIF('C122'!C11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="C92">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 2")+COUNTIF('C112'!D11,"Aula 2")+COUNTIF('C113'!D11,"Aula 2")+COUNTIF('C121'!D11,"Aula 2")+COUNTIF('C122'!D11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 2")+COUNTIF('C112'!D11,"Aula 2")+COUNTIF('C113'!D11,"Aula 2")+COUNTIF('C121'!D11,"Aula 2")+COUNTIF('C122'!D11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 2")+COUNTIF('C112'!D11,"Aula 2")+COUNTIF('C113'!D11,"Aula 2")+COUNTIF('C121'!D11,"Aula 2")+COUNTIF('C122'!D11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 2")+COUNTIF('C112'!C11,"Aula 2")+COUNTIF('C113'!C11,"Aula 2")+COUNTIF('C121'!C11,"Aula 2")+COUNTIF('C122'!C11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 2")+COUNTIF('C112'!C11,"Aula 2")+COUNTIF('C113'!C11,"Aula 2")+COUNTIF('C121'!C11,"Aula 2")+COUNTIF('C122'!C11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 2")+COUNTIF('C112'!C11,"Aula 2")+COUNTIF('C113'!C11,"Aula 2")+COUNTIF('C121'!C11,"Aula 2")+COUNTIF('C122'!C11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="C93">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 3")+COUNTIF('C112'!D11,"Aula 3")+COUNTIF('C113'!D11,"Aula 3")+COUNTIF('C121'!D11,"Aula 3")+COUNTIF('C122'!D11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 3")+COUNTIF('C112'!D11,"Aula 3")+COUNTIF('C113'!D11,"Aula 3")+COUNTIF('C121'!D11,"Aula 3")+COUNTIF('C122'!D11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 3")+COUNTIF('C112'!D11,"Aula 3")+COUNTIF('C113'!D11,"Aula 3")+COUNTIF('C121'!D11,"Aula 3")+COUNTIF('C122'!D11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 3")+COUNTIF('C112'!C11,"Aula 3")+COUNTIF('C113'!C11,"Aula 3")+COUNTIF('C121'!C11,"Aula 3")+COUNTIF('C122'!C11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 3")+COUNTIF('C112'!C11,"Aula 3")+COUNTIF('C113'!C11,"Aula 3")+COUNTIF('C121'!C11,"Aula 3")+COUNTIF('C122'!C11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 3")+COUNTIF('C112'!C11,"Aula 3")+COUNTIF('C113'!C11,"Aula 3")+COUNTIF('C121'!C11,"Aula 3")+COUNTIF('C122'!C11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="C94">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 4")+COUNTIF('C112'!D11,"Aula 4")+COUNTIF('C113'!D11,"Aula 4")+COUNTIF('C121'!D11,"Aula 4")+COUNTIF('C122'!D11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 4")+COUNTIF('C112'!D11,"Aula 4")+COUNTIF('C113'!D11,"Aula 4")+COUNTIF('C121'!D11,"Aula 4")+COUNTIF('C122'!D11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 4")+COUNTIF('C112'!D11,"Aula 4")+COUNTIF('C113'!D11,"Aula 4")+COUNTIF('C121'!D11,"Aula 4")+COUNTIF('C122'!D11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 4")+COUNTIF('C112'!C11,"Aula 4")+COUNTIF('C113'!C11,"Aula 4")+COUNTIF('C121'!C11,"Aula 4")+COUNTIF('C122'!C11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 4")+COUNTIF('C112'!C11,"Aula 4")+COUNTIF('C113'!C11,"Aula 4")+COUNTIF('C121'!C11,"Aula 4")+COUNTIF('C122'!C11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 4")+COUNTIF('C112'!C11,"Aula 4")+COUNTIF('C113'!C11,"Aula 4")+COUNTIF('C121'!C11,"Aula 4")+COUNTIF('C122'!C11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="C95">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 5")+COUNTIF('C112'!D11,"Aula 5")+COUNTIF('C113'!D11,"Aula 5")+COUNTIF('C121'!D11,"Aula 5")+COUNTIF('C122'!D11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 5")+COUNTIF('C112'!D11,"Aula 5")+COUNTIF('C113'!D11,"Aula 5")+COUNTIF('C121'!D11,"Aula 5")+COUNTIF('C122'!D11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 5")+COUNTIF('C112'!D11,"Aula 5")+COUNTIF('C113'!D11,"Aula 5")+COUNTIF('C121'!D11,"Aula 5")+COUNTIF('C122'!D11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 5")+COUNTIF('C112'!C11,"Aula 5")+COUNTIF('C113'!C11,"Aula 5")+COUNTIF('C121'!C11,"Aula 5")+COUNTIF('C122'!C11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 5")+COUNTIF('C112'!C11,"Aula 5")+COUNTIF('C113'!C11,"Aula 5")+COUNTIF('C121'!C11,"Aula 5")+COUNTIF('C122'!C11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 5")+COUNTIF('C112'!C11,"Aula 5")+COUNTIF('C113'!C11,"Aula 5")+COUNTIF('C121'!C11,"Aula 5")+COUNTIF('C122'!C11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="C96">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 6")+COUNTIF('C112'!D11,"Aula 6")+COUNTIF('C113'!D11,"Aula 6")+COUNTIF('C121'!D11,"Aula 6")+COUNTIF('C122'!D11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 6")+COUNTIF('C112'!D11,"Aula 6")+COUNTIF('C113'!D11,"Aula 6")+COUNTIF('C121'!D11,"Aula 6")+COUNTIF('C122'!D11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 6")+COUNTIF('C112'!D11,"Aula 6")+COUNTIF('C113'!D11,"Aula 6")+COUNTIF('C121'!D11,"Aula 6")+COUNTIF('C122'!D11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 6")+COUNTIF('C112'!C11,"Aula 6")+COUNTIF('C113'!C11,"Aula 6")+COUNTIF('C121'!C11,"Aula 6")+COUNTIF('C122'!C11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 6")+COUNTIF('C112'!C11,"Aula 6")+COUNTIF('C113'!C11,"Aula 6")+COUNTIF('C121'!C11,"Aula 6")+COUNTIF('C122'!C11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 6")+COUNTIF('C112'!C11,"Aula 6")+COUNTIF('C113'!C11,"Aula 6")+COUNTIF('C121'!C11,"Aula 6")+COUNTIF('C122'!C11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="C97">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 7")+COUNTIF('C112'!D11,"Aula 7")+COUNTIF('C113'!D11,"Aula 7")+COUNTIF('C121'!D11,"Aula 7")+COUNTIF('C122'!D11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 7")+COUNTIF('C112'!D11,"Aula 7")+COUNTIF('C113'!D11,"Aula 7")+COUNTIF('C121'!D11,"Aula 7")+COUNTIF('C122'!D11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 7")+COUNTIF('C112'!D11,"Aula 7")+COUNTIF('C113'!D11,"Aula 7")+COUNTIF('C121'!D11,"Aula 7")+COUNTIF('C122'!D11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 7")+COUNTIF('C112'!C11,"Aula 7")+COUNTIF('C113'!C11,"Aula 7")+COUNTIF('C121'!C11,"Aula 7")+COUNTIF('C122'!C11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 7")+COUNTIF('C112'!C11,"Aula 7")+COUNTIF('C113'!C11,"Aula 7")+COUNTIF('C121'!C11,"Aula 7")+COUNTIF('C122'!C11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 7")+COUNTIF('C112'!C11,"Aula 7")+COUNTIF('C113'!C11,"Aula 7")+COUNTIF('C121'!C11,"Aula 7")+COUNTIF('C122'!C11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="C98">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 8")+COUNTIF('C112'!D11,"Aula 8")+COUNTIF('C113'!D11,"Aula 8")+COUNTIF('C121'!D11,"Aula 8")+COUNTIF('C122'!D11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 8")+COUNTIF('C112'!D11,"Aula 8")+COUNTIF('C113'!D11,"Aula 8")+COUNTIF('C121'!D11,"Aula 8")+COUNTIF('C122'!D11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 8")+COUNTIF('C112'!D11,"Aula 8")+COUNTIF('C113'!D11,"Aula 8")+COUNTIF('C121'!D11,"Aula 8")+COUNTIF('C122'!D11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 8")+COUNTIF('C112'!C11,"Aula 8")+COUNTIF('C113'!C11,"Aula 8")+COUNTIF('C121'!C11,"Aula 8")+COUNTIF('C122'!C11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 8")+COUNTIF('C112'!C11,"Aula 8")+COUNTIF('C113'!C11,"Aula 8")+COUNTIF('C121'!C11,"Aula 8")+COUNTIF('C122'!C11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 8")+COUNTIF('C112'!C11,"Aula 8")+COUNTIF('C113'!C11,"Aula 8")+COUNTIF('C121'!C11,"Aula 8")+COUNTIF('C122'!C11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="C99">
-        <f>IF((IF((COUNTIF('C111'!D11,"Aula 9")+COUNTIF('C112'!D11,"Aula 9")+COUNTIF('C113'!D11,"Aula 9")+COUNTIF('C121'!D11,"Aula 9")+COUNTIF('C122'!D11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 9")+COUNTIF('C112'!D11,"Aula 9")+COUNTIF('C113'!D11,"Aula 9")+COUNTIF('C121'!D11,"Aula 9")+COUNTIF('C122'!D11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 9")+COUNTIF('C112'!D11,"Aula 9")+COUNTIF('C113'!D11,"Aula 9")+COUNTIF('C121'!D11,"Aula 9")+COUNTIF('C122'!D11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Aula 9")+COUNTIF('C112'!C11,"Aula 9")+COUNTIF('C113'!C11,"Aula 9")+COUNTIF('C121'!C11,"Aula 9")+COUNTIF('C122'!C11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Aula 9")+COUNTIF('C112'!C11,"Aula 9")+COUNTIF('C113'!C11,"Aula 9")+COUNTIF('C121'!C11,"Aula 9")+COUNTIF('C122'!C11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Aula 9")+COUNTIF('C112'!C11,"Aula 9")+COUNTIF('C113'!C11,"Aula 9")+COUNTIF('C121'!C11,"Aula 9")+COUNTIF('C122'!C11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="C100">
-        <f>IF((IF((COUNTIF('C111'!D11,"Lab")+COUNTIF('C112'!D11,"Lab")+COUNTIF('C113'!D11,"Lab")+COUNTIF('C121'!D11,"Lab")+COUNTIF('C122'!D11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Lab")+COUNTIF('C112'!D11,"Lab")+COUNTIF('C113'!D11,"Lab")+COUNTIF('C121'!D11,"Lab")+COUNTIF('C122'!D11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Lab")+COUNTIF('C112'!D11,"Lab")+COUNTIF('C113'!D11,"Lab")+COUNTIF('C121'!D11,"Lab")+COUNTIF('C122'!D11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C11,"Lab")+COUNTIF('C112'!C11,"Lab")+COUNTIF('C113'!C11,"Lab")+COUNTIF('C121'!C11,"Lab")+COUNTIF('C122'!C11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C11,"Lab")+COUNTIF('C112'!C11,"Lab")+COUNTIF('C113'!C11,"Lab")+COUNTIF('C121'!C11,"Lab")+COUNTIF('C122'!C11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C11,"Lab")+COUNTIF('C112'!C11,"Lab")+COUNTIF('C113'!C11,"Lab")+COUNTIF('C121'!C11,"Lab")+COUNTIF('C122'!C11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="C101">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 1")+COUNTIF('C112'!D13,"Aula 1")+COUNTIF('C113'!D13,"Aula 1")+COUNTIF('C121'!D13,"Aula 1")+COUNTIF('C122'!D13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 1")+COUNTIF('C112'!D13,"Aula 1")+COUNTIF('C113'!D13,"Aula 1")+COUNTIF('C121'!D13,"Aula 1")+COUNTIF('C122'!D13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 1")+COUNTIF('C112'!D13,"Aula 1")+COUNTIF('C113'!D13,"Aula 1")+COUNTIF('C121'!D13,"Aula 1")+COUNTIF('C122'!D13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 1")+COUNTIF('C112'!C13,"Aula 1")+COUNTIF('C113'!C13,"Aula 1")+COUNTIF('C121'!C13,"Aula 1")+COUNTIF('C122'!C13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 1")+COUNTIF('C112'!C13,"Aula 1")+COUNTIF('C113'!C13,"Aula 1")+COUNTIF('C121'!C13,"Aula 1")+COUNTIF('C122'!C13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 1")+COUNTIF('C112'!C13,"Aula 1")+COUNTIF('C113'!C13,"Aula 1")+COUNTIF('C121'!C13,"Aula 1")+COUNTIF('C122'!C13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="C102">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 2")+COUNTIF('C112'!D13,"Aula 2")+COUNTIF('C113'!D13,"Aula 2")+COUNTIF('C121'!D13,"Aula 2")+COUNTIF('C122'!D13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 2")+COUNTIF('C112'!D13,"Aula 2")+COUNTIF('C113'!D13,"Aula 2")+COUNTIF('C121'!D13,"Aula 2")+COUNTIF('C122'!D13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 2")+COUNTIF('C112'!D13,"Aula 2")+COUNTIF('C113'!D13,"Aula 2")+COUNTIF('C121'!D13,"Aula 2")+COUNTIF('C122'!D13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 2")+COUNTIF('C112'!C13,"Aula 2")+COUNTIF('C113'!C13,"Aula 2")+COUNTIF('C121'!C13,"Aula 2")+COUNTIF('C122'!C13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 2")+COUNTIF('C112'!C13,"Aula 2")+COUNTIF('C113'!C13,"Aula 2")+COUNTIF('C121'!C13,"Aula 2")+COUNTIF('C122'!C13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 2")+COUNTIF('C112'!C13,"Aula 2")+COUNTIF('C113'!C13,"Aula 2")+COUNTIF('C121'!C13,"Aula 2")+COUNTIF('C122'!C13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="C103">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 3")+COUNTIF('C112'!D13,"Aula 3")+COUNTIF('C113'!D13,"Aula 3")+COUNTIF('C121'!D13,"Aula 3")+COUNTIF('C122'!D13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 3")+COUNTIF('C112'!D13,"Aula 3")+COUNTIF('C113'!D13,"Aula 3")+COUNTIF('C121'!D13,"Aula 3")+COUNTIF('C122'!D13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 3")+COUNTIF('C112'!D13,"Aula 3")+COUNTIF('C113'!D13,"Aula 3")+COUNTIF('C121'!D13,"Aula 3")+COUNTIF('C122'!D13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 3")+COUNTIF('C112'!C13,"Aula 3")+COUNTIF('C113'!C13,"Aula 3")+COUNTIF('C121'!C13,"Aula 3")+COUNTIF('C122'!C13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 3")+COUNTIF('C112'!C13,"Aula 3")+COUNTIF('C113'!C13,"Aula 3")+COUNTIF('C121'!C13,"Aula 3")+COUNTIF('C122'!C13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 3")+COUNTIF('C112'!C13,"Aula 3")+COUNTIF('C113'!C13,"Aula 3")+COUNTIF('C121'!C13,"Aula 3")+COUNTIF('C122'!C13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="C104">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 4")+COUNTIF('C112'!D13,"Aula 4")+COUNTIF('C113'!D13,"Aula 4")+COUNTIF('C121'!D13,"Aula 4")+COUNTIF('C122'!D13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 4")+COUNTIF('C112'!D13,"Aula 4")+COUNTIF('C113'!D13,"Aula 4")+COUNTIF('C121'!D13,"Aula 4")+COUNTIF('C122'!D13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 4")+COUNTIF('C112'!D13,"Aula 4")+COUNTIF('C113'!D13,"Aula 4")+COUNTIF('C121'!D13,"Aula 4")+COUNTIF('C122'!D13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 4")+COUNTIF('C112'!C13,"Aula 4")+COUNTIF('C113'!C13,"Aula 4")+COUNTIF('C121'!C13,"Aula 4")+COUNTIF('C122'!C13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 4")+COUNTIF('C112'!C13,"Aula 4")+COUNTIF('C113'!C13,"Aula 4")+COUNTIF('C121'!C13,"Aula 4")+COUNTIF('C122'!C13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 4")+COUNTIF('C112'!C13,"Aula 4")+COUNTIF('C113'!C13,"Aula 4")+COUNTIF('C121'!C13,"Aula 4")+COUNTIF('C122'!C13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="C105">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 5")+COUNTIF('C112'!D13,"Aula 5")+COUNTIF('C113'!D13,"Aula 5")+COUNTIF('C121'!D13,"Aula 5")+COUNTIF('C122'!D13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 5")+COUNTIF('C112'!D13,"Aula 5")+COUNTIF('C113'!D13,"Aula 5")+COUNTIF('C121'!D13,"Aula 5")+COUNTIF('C122'!D13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 5")+COUNTIF('C112'!D13,"Aula 5")+COUNTIF('C113'!D13,"Aula 5")+COUNTIF('C121'!D13,"Aula 5")+COUNTIF('C122'!D13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 5")+COUNTIF('C112'!C13,"Aula 5")+COUNTIF('C113'!C13,"Aula 5")+COUNTIF('C121'!C13,"Aula 5")+COUNTIF('C122'!C13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 5")+COUNTIF('C112'!C13,"Aula 5")+COUNTIF('C113'!C13,"Aula 5")+COUNTIF('C121'!C13,"Aula 5")+COUNTIF('C122'!C13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 5")+COUNTIF('C112'!C13,"Aula 5")+COUNTIF('C113'!C13,"Aula 5")+COUNTIF('C121'!C13,"Aula 5")+COUNTIF('C122'!C13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="C106">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 6")+COUNTIF('C112'!D13,"Aula 6")+COUNTIF('C113'!D13,"Aula 6")+COUNTIF('C121'!D13,"Aula 6")+COUNTIF('C122'!D13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 6")+COUNTIF('C112'!D13,"Aula 6")+COUNTIF('C113'!D13,"Aula 6")+COUNTIF('C121'!D13,"Aula 6")+COUNTIF('C122'!D13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 6")+COUNTIF('C112'!D13,"Aula 6")+COUNTIF('C113'!D13,"Aula 6")+COUNTIF('C121'!D13,"Aula 6")+COUNTIF('C122'!D13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 6")+COUNTIF('C112'!C13,"Aula 6")+COUNTIF('C113'!C13,"Aula 6")+COUNTIF('C121'!C13,"Aula 6")+COUNTIF('C122'!C13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 6")+COUNTIF('C112'!C13,"Aula 6")+COUNTIF('C113'!C13,"Aula 6")+COUNTIF('C121'!C13,"Aula 6")+COUNTIF('C122'!C13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 6")+COUNTIF('C112'!C13,"Aula 6")+COUNTIF('C113'!C13,"Aula 6")+COUNTIF('C121'!C13,"Aula 6")+COUNTIF('C122'!C13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="C107">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 7")+COUNTIF('C112'!D13,"Aula 7")+COUNTIF('C113'!D13,"Aula 7")+COUNTIF('C121'!D13,"Aula 7")+COUNTIF('C122'!D13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 7")+COUNTIF('C112'!D13,"Aula 7")+COUNTIF('C113'!D13,"Aula 7")+COUNTIF('C121'!D13,"Aula 7")+COUNTIF('C122'!D13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 7")+COUNTIF('C112'!D13,"Aula 7")+COUNTIF('C113'!D13,"Aula 7")+COUNTIF('C121'!D13,"Aula 7")+COUNTIF('C122'!D13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 7")+COUNTIF('C112'!C13,"Aula 7")+COUNTIF('C113'!C13,"Aula 7")+COUNTIF('C121'!C13,"Aula 7")+COUNTIF('C122'!C13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 7")+COUNTIF('C112'!C13,"Aula 7")+COUNTIF('C113'!C13,"Aula 7")+COUNTIF('C121'!C13,"Aula 7")+COUNTIF('C122'!C13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 7")+COUNTIF('C112'!C13,"Aula 7")+COUNTIF('C113'!C13,"Aula 7")+COUNTIF('C121'!C13,"Aula 7")+COUNTIF('C122'!C13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="C108">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 8")+COUNTIF('C112'!D13,"Aula 8")+COUNTIF('C113'!D13,"Aula 8")+COUNTIF('C121'!D13,"Aula 8")+COUNTIF('C122'!D13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 8")+COUNTIF('C112'!D13,"Aula 8")+COUNTIF('C113'!D13,"Aula 8")+COUNTIF('C121'!D13,"Aula 8")+COUNTIF('C122'!D13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 8")+COUNTIF('C112'!D13,"Aula 8")+COUNTIF('C113'!D13,"Aula 8")+COUNTIF('C121'!D13,"Aula 8")+COUNTIF('C122'!D13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 8")+COUNTIF('C112'!C13,"Aula 8")+COUNTIF('C113'!C13,"Aula 8")+COUNTIF('C121'!C13,"Aula 8")+COUNTIF('C122'!C13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 8")+COUNTIF('C112'!C13,"Aula 8")+COUNTIF('C113'!C13,"Aula 8")+COUNTIF('C121'!C13,"Aula 8")+COUNTIF('C122'!C13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 8")+COUNTIF('C112'!C13,"Aula 8")+COUNTIF('C113'!C13,"Aula 8")+COUNTIF('C121'!C13,"Aula 8")+COUNTIF('C122'!C13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="C109">
-        <f>IF((IF((COUNTIF('C111'!D13,"Aula 9")+COUNTIF('C112'!D13,"Aula 9")+COUNTIF('C113'!D13,"Aula 9")+COUNTIF('C121'!D13,"Aula 9")+COUNTIF('C122'!D13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 9")+COUNTIF('C112'!D13,"Aula 9")+COUNTIF('C113'!D13,"Aula 9")+COUNTIF('C121'!D13,"Aula 9")+COUNTIF('C122'!D13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 9")+COUNTIF('C112'!D13,"Aula 9")+COUNTIF('C113'!D13,"Aula 9")+COUNTIF('C121'!D13,"Aula 9")+COUNTIF('C122'!D13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Aula 9")+COUNTIF('C112'!C13,"Aula 9")+COUNTIF('C113'!C13,"Aula 9")+COUNTIF('C121'!C13,"Aula 9")+COUNTIF('C122'!C13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Aula 9")+COUNTIF('C112'!C13,"Aula 9")+COUNTIF('C113'!C13,"Aula 9")+COUNTIF('C121'!C13,"Aula 9")+COUNTIF('C122'!C13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Aula 9")+COUNTIF('C112'!C13,"Aula 9")+COUNTIF('C113'!C13,"Aula 9")+COUNTIF('C121'!C13,"Aula 9")+COUNTIF('C122'!C13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="C110">
-        <f>IF((IF((COUNTIF('C111'!D13,"Lab")+COUNTIF('C112'!D13,"Lab")+COUNTIF('C113'!D13,"Lab")+COUNTIF('C121'!D13,"Lab")+COUNTIF('C122'!D13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Lab")+COUNTIF('C112'!D13,"Lab")+COUNTIF('C113'!D13,"Lab")+COUNTIF('C121'!D13,"Lab")+COUNTIF('C122'!D13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Lab")+COUNTIF('C112'!D13,"Lab")+COUNTIF('C113'!D13,"Lab")+COUNTIF('C121'!D13,"Lab")+COUNTIF('C122'!D13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C13,"Lab")+COUNTIF('C112'!C13,"Lab")+COUNTIF('C113'!C13,"Lab")+COUNTIF('C121'!C13,"Lab")+COUNTIF('C122'!C13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C13,"Lab")+COUNTIF('C112'!C13,"Lab")+COUNTIF('C113'!C13,"Lab")+COUNTIF('C121'!C13,"Lab")+COUNTIF('C122'!C13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C13,"Lab")+COUNTIF('C112'!C13,"Lab")+COUNTIF('C113'!C13,"Lab")+COUNTIF('C121'!C13,"Lab")+COUNTIF('C122'!C13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="C111">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 1")+COUNTIF('C112'!D15,"Aula 1")+COUNTIF('C113'!D15,"Aula 1")+COUNTIF('C121'!D15,"Aula 1")+COUNTIF('C122'!D15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 1")+COUNTIF('C112'!D15,"Aula 1")+COUNTIF('C113'!D15,"Aula 1")+COUNTIF('C121'!D15,"Aula 1")+COUNTIF('C122'!D15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 1")+COUNTIF('C112'!D15,"Aula 1")+COUNTIF('C113'!D15,"Aula 1")+COUNTIF('C121'!D15,"Aula 1")+COUNTIF('C122'!D15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 1")+COUNTIF('C112'!C15,"Aula 1")+COUNTIF('C113'!C15,"Aula 1")+COUNTIF('C121'!C15,"Aula 1")+COUNTIF('C122'!C15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 1")+COUNTIF('C112'!C15,"Aula 1")+COUNTIF('C113'!C15,"Aula 1")+COUNTIF('C121'!C15,"Aula 1")+COUNTIF('C122'!C15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 1")+COUNTIF('C112'!C15,"Aula 1")+COUNTIF('C113'!C15,"Aula 1")+COUNTIF('C121'!C15,"Aula 1")+COUNTIF('C122'!C15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="C112">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 2")+COUNTIF('C112'!D15,"Aula 2")+COUNTIF('C113'!D15,"Aula 2")+COUNTIF('C121'!D15,"Aula 2")+COUNTIF('C122'!D15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 2")+COUNTIF('C112'!D15,"Aula 2")+COUNTIF('C113'!D15,"Aula 2")+COUNTIF('C121'!D15,"Aula 2")+COUNTIF('C122'!D15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 2")+COUNTIF('C112'!D15,"Aula 2")+COUNTIF('C113'!D15,"Aula 2")+COUNTIF('C121'!D15,"Aula 2")+COUNTIF('C122'!D15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 2")+COUNTIF('C112'!C15,"Aula 2")+COUNTIF('C113'!C15,"Aula 2")+COUNTIF('C121'!C15,"Aula 2")+COUNTIF('C122'!C15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 2")+COUNTIF('C112'!C15,"Aula 2")+COUNTIF('C113'!C15,"Aula 2")+COUNTIF('C121'!C15,"Aula 2")+COUNTIF('C122'!C15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 2")+COUNTIF('C112'!C15,"Aula 2")+COUNTIF('C113'!C15,"Aula 2")+COUNTIF('C121'!C15,"Aula 2")+COUNTIF('C122'!C15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="C113">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 3")+COUNTIF('C112'!D15,"Aula 3")+COUNTIF('C113'!D15,"Aula 3")+COUNTIF('C121'!D15,"Aula 3")+COUNTIF('C122'!D15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 3")+COUNTIF('C112'!D15,"Aula 3")+COUNTIF('C113'!D15,"Aula 3")+COUNTIF('C121'!D15,"Aula 3")+COUNTIF('C122'!D15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 3")+COUNTIF('C112'!D15,"Aula 3")+COUNTIF('C113'!D15,"Aula 3")+COUNTIF('C121'!D15,"Aula 3")+COUNTIF('C122'!D15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 3")+COUNTIF('C112'!C15,"Aula 3")+COUNTIF('C113'!C15,"Aula 3")+COUNTIF('C121'!C15,"Aula 3")+COUNTIF('C122'!C15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 3")+COUNTIF('C112'!C15,"Aula 3")+COUNTIF('C113'!C15,"Aula 3")+COUNTIF('C121'!C15,"Aula 3")+COUNTIF('C122'!C15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 3")+COUNTIF('C112'!C15,"Aula 3")+COUNTIF('C113'!C15,"Aula 3")+COUNTIF('C121'!C15,"Aula 3")+COUNTIF('C122'!C15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="C114">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 4")+COUNTIF('C112'!D15,"Aula 4")+COUNTIF('C113'!D15,"Aula 4")+COUNTIF('C121'!D15,"Aula 4")+COUNTIF('C122'!D15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 4")+COUNTIF('C112'!D15,"Aula 4")+COUNTIF('C113'!D15,"Aula 4")+COUNTIF('C121'!D15,"Aula 4")+COUNTIF('C122'!D15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 4")+COUNTIF('C112'!D15,"Aula 4")+COUNTIF('C113'!D15,"Aula 4")+COUNTIF('C121'!D15,"Aula 4")+COUNTIF('C122'!D15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 4")+COUNTIF('C112'!C15,"Aula 4")+COUNTIF('C113'!C15,"Aula 4")+COUNTIF('C121'!C15,"Aula 4")+COUNTIF('C122'!C15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 4")+COUNTIF('C112'!C15,"Aula 4")+COUNTIF('C113'!C15,"Aula 4")+COUNTIF('C121'!C15,"Aula 4")+COUNTIF('C122'!C15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 4")+COUNTIF('C112'!C15,"Aula 4")+COUNTIF('C113'!C15,"Aula 4")+COUNTIF('C121'!C15,"Aula 4")+COUNTIF('C122'!C15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="C115">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 5")+COUNTIF('C112'!D15,"Aula 5")+COUNTIF('C113'!D15,"Aula 5")+COUNTIF('C121'!D15,"Aula 5")+COUNTIF('C122'!D15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 5")+COUNTIF('C112'!D15,"Aula 5")+COUNTIF('C113'!D15,"Aula 5")+COUNTIF('C121'!D15,"Aula 5")+COUNTIF('C122'!D15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 5")+COUNTIF('C112'!D15,"Aula 5")+COUNTIF('C113'!D15,"Aula 5")+COUNTIF('C121'!D15,"Aula 5")+COUNTIF('C122'!D15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 5")+COUNTIF('C112'!C15,"Aula 5")+COUNTIF('C113'!C15,"Aula 5")+COUNTIF('C121'!C15,"Aula 5")+COUNTIF('C122'!C15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 5")+COUNTIF('C112'!C15,"Aula 5")+COUNTIF('C113'!C15,"Aula 5")+COUNTIF('C121'!C15,"Aula 5")+COUNTIF('C122'!C15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 5")+COUNTIF('C112'!C15,"Aula 5")+COUNTIF('C113'!C15,"Aula 5")+COUNTIF('C121'!C15,"Aula 5")+COUNTIF('C122'!C15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="C116">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 6")+COUNTIF('C112'!D15,"Aula 6")+COUNTIF('C113'!D15,"Aula 6")+COUNTIF('C121'!D15,"Aula 6")+COUNTIF('C122'!D15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 6")+COUNTIF('C112'!D15,"Aula 6")+COUNTIF('C113'!D15,"Aula 6")+COUNTIF('C121'!D15,"Aula 6")+COUNTIF('C122'!D15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 6")+COUNTIF('C112'!D15,"Aula 6")+COUNTIF('C113'!D15,"Aula 6")+COUNTIF('C121'!D15,"Aula 6")+COUNTIF('C122'!D15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 6")+COUNTIF('C112'!C15,"Aula 6")+COUNTIF('C113'!C15,"Aula 6")+COUNTIF('C121'!C15,"Aula 6")+COUNTIF('C122'!C15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 6")+COUNTIF('C112'!C15,"Aula 6")+COUNTIF('C113'!C15,"Aula 6")+COUNTIF('C121'!C15,"Aula 6")+COUNTIF('C122'!C15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 6")+COUNTIF('C112'!C15,"Aula 6")+COUNTIF('C113'!C15,"Aula 6")+COUNTIF('C121'!C15,"Aula 6")+COUNTIF('C122'!C15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="C117">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 7")+COUNTIF('C112'!D15,"Aula 7")+COUNTIF('C113'!D15,"Aula 7")+COUNTIF('C121'!D15,"Aula 7")+COUNTIF('C122'!D15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 7")+COUNTIF('C112'!D15,"Aula 7")+COUNTIF('C113'!D15,"Aula 7")+COUNTIF('C121'!D15,"Aula 7")+COUNTIF('C122'!D15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 7")+COUNTIF('C112'!D15,"Aula 7")+COUNTIF('C113'!D15,"Aula 7")+COUNTIF('C121'!D15,"Aula 7")+COUNTIF('C122'!D15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 7")+COUNTIF('C112'!C15,"Aula 7")+COUNTIF('C113'!C15,"Aula 7")+COUNTIF('C121'!C15,"Aula 7")+COUNTIF('C122'!C15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 7")+COUNTIF('C112'!C15,"Aula 7")+COUNTIF('C113'!C15,"Aula 7")+COUNTIF('C121'!C15,"Aula 7")+COUNTIF('C122'!C15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 7")+COUNTIF('C112'!C15,"Aula 7")+COUNTIF('C113'!C15,"Aula 7")+COUNTIF('C121'!C15,"Aula 7")+COUNTIF('C122'!C15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="C118">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 8")+COUNTIF('C112'!D15,"Aula 8")+COUNTIF('C113'!D15,"Aula 8")+COUNTIF('C121'!D15,"Aula 8")+COUNTIF('C122'!D15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 8")+COUNTIF('C112'!D15,"Aula 8")+COUNTIF('C113'!D15,"Aula 8")+COUNTIF('C121'!D15,"Aula 8")+COUNTIF('C122'!D15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 8")+COUNTIF('C112'!D15,"Aula 8")+COUNTIF('C113'!D15,"Aula 8")+COUNTIF('C121'!D15,"Aula 8")+COUNTIF('C122'!D15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 8")+COUNTIF('C112'!C15,"Aula 8")+COUNTIF('C113'!C15,"Aula 8")+COUNTIF('C121'!C15,"Aula 8")+COUNTIF('C122'!C15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 8")+COUNTIF('C112'!C15,"Aula 8")+COUNTIF('C113'!C15,"Aula 8")+COUNTIF('C121'!C15,"Aula 8")+COUNTIF('C122'!C15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 8")+COUNTIF('C112'!C15,"Aula 8")+COUNTIF('C113'!C15,"Aula 8")+COUNTIF('C121'!C15,"Aula 8")+COUNTIF('C122'!C15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="C119">
-        <f>IF((IF((COUNTIF('C111'!D15,"Aula 9")+COUNTIF('C112'!D15,"Aula 9")+COUNTIF('C113'!D15,"Aula 9")+COUNTIF('C121'!D15,"Aula 9")+COUNTIF('C122'!D15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 9")+COUNTIF('C112'!D15,"Aula 9")+COUNTIF('C113'!D15,"Aula 9")+COUNTIF('C121'!D15,"Aula 9")+COUNTIF('C122'!D15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 9")+COUNTIF('C112'!D15,"Aula 9")+COUNTIF('C113'!D15,"Aula 9")+COUNTIF('C121'!D15,"Aula 9")+COUNTIF('C122'!D15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Aula 9")+COUNTIF('C112'!C15,"Aula 9")+COUNTIF('C113'!C15,"Aula 9")+COUNTIF('C121'!C15,"Aula 9")+COUNTIF('C122'!C15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Aula 9")+COUNTIF('C112'!C15,"Aula 9")+COUNTIF('C113'!C15,"Aula 9")+COUNTIF('C121'!C15,"Aula 9")+COUNTIF('C122'!C15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Aula 9")+COUNTIF('C112'!C15,"Aula 9")+COUNTIF('C113'!C15,"Aula 9")+COUNTIF('C121'!C15,"Aula 9")+COUNTIF('C122'!C15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="C120">
-        <f>IF((IF((COUNTIF('C111'!D15,"Lab")+COUNTIF('C112'!D15,"Lab")+COUNTIF('C113'!D15,"Lab")+COUNTIF('C121'!D15,"Lab")+COUNTIF('C122'!D15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Lab")+COUNTIF('C112'!D15,"Lab")+COUNTIF('C113'!D15,"Lab")+COUNTIF('C121'!D15,"Lab")+COUNTIF('C122'!D15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Lab")+COUNTIF('C112'!D15,"Lab")+COUNTIF('C113'!D15,"Lab")+COUNTIF('C121'!D15,"Lab")+COUNTIF('C122'!D15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!C15,"Lab")+COUNTIF('C112'!C15,"Lab")+COUNTIF('C113'!C15,"Lab")+COUNTIF('C121'!C15,"Lab")+COUNTIF('C122'!C15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!C15,"Lab")+COUNTIF('C112'!C15,"Lab")+COUNTIF('C113'!C15,"Lab")+COUNTIF('C121'!C15,"Lab")+COUNTIF('C122'!C15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!C15,"Lab")+COUNTIF('C112'!C15,"Lab")+COUNTIF('C113'!C15,"Lab")+COUNTIF('C121'!C15,"Lab")+COUNTIF('C122'!C15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="C121">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 1")+COUNTIF('C112'!E5,"Aula 1")+COUNTIF('C113'!E5,"Aula 1")+COUNTIF('C121'!E5,"Aula 1")+COUNTIF('C122'!E5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 1")+COUNTIF('C112'!E5,"Aula 1")+COUNTIF('C113'!E5,"Aula 1")+COUNTIF('C121'!E5,"Aula 1")+COUNTIF('C122'!E5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 1")+COUNTIF('C112'!E5,"Aula 1")+COUNTIF('C113'!E5,"Aula 1")+COUNTIF('C121'!E5,"Aula 1")+COUNTIF('C122'!E5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 1")+COUNTIF('C112'!D5,"Aula 1")+COUNTIF('C113'!D5,"Aula 1")+COUNTIF('C121'!D5,"Aula 1")+COUNTIF('C122'!D5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 1")+COUNTIF('C112'!D5,"Aula 1")+COUNTIF('C113'!D5,"Aula 1")+COUNTIF('C121'!D5,"Aula 1")+COUNTIF('C122'!D5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 1")+COUNTIF('C112'!D5,"Aula 1")+COUNTIF('C113'!D5,"Aula 1")+COUNTIF('C121'!D5,"Aula 1")+COUNTIF('C122'!D5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="C122">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 2")+COUNTIF('C112'!E5,"Aula 2")+COUNTIF('C113'!E5,"Aula 2")+COUNTIF('C121'!E5,"Aula 2")+COUNTIF('C122'!E5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 2")+COUNTIF('C112'!E5,"Aula 2")+COUNTIF('C113'!E5,"Aula 2")+COUNTIF('C121'!E5,"Aula 2")+COUNTIF('C122'!E5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 2")+COUNTIF('C112'!E5,"Aula 2")+COUNTIF('C113'!E5,"Aula 2")+COUNTIF('C121'!E5,"Aula 2")+COUNTIF('C122'!E5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 2")+COUNTIF('C112'!D5,"Aula 2")+COUNTIF('C113'!D5,"Aula 2")+COUNTIF('C121'!D5,"Aula 2")+COUNTIF('C122'!D5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 2")+COUNTIF('C112'!D5,"Aula 2")+COUNTIF('C113'!D5,"Aula 2")+COUNTIF('C121'!D5,"Aula 2")+COUNTIF('C122'!D5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 2")+COUNTIF('C112'!D5,"Aula 2")+COUNTIF('C113'!D5,"Aula 2")+COUNTIF('C121'!D5,"Aula 2")+COUNTIF('C122'!D5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="C123">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 3")+COUNTIF('C112'!E5,"Aula 3")+COUNTIF('C113'!E5,"Aula 3")+COUNTIF('C121'!E5,"Aula 3")+COUNTIF('C122'!E5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 3")+COUNTIF('C112'!E5,"Aula 3")+COUNTIF('C113'!E5,"Aula 3")+COUNTIF('C121'!E5,"Aula 3")+COUNTIF('C122'!E5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 3")+COUNTIF('C112'!E5,"Aula 3")+COUNTIF('C113'!E5,"Aula 3")+COUNTIF('C121'!E5,"Aula 3")+COUNTIF('C122'!E5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 3")+COUNTIF('C112'!D5,"Aula 3")+COUNTIF('C113'!D5,"Aula 3")+COUNTIF('C121'!D5,"Aula 3")+COUNTIF('C122'!D5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 3")+COUNTIF('C112'!D5,"Aula 3")+COUNTIF('C113'!D5,"Aula 3")+COUNTIF('C121'!D5,"Aula 3")+COUNTIF('C122'!D5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 3")+COUNTIF('C112'!D5,"Aula 3")+COUNTIF('C113'!D5,"Aula 3")+COUNTIF('C121'!D5,"Aula 3")+COUNTIF('C122'!D5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="C124">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 4")+COUNTIF('C112'!E5,"Aula 4")+COUNTIF('C113'!E5,"Aula 4")+COUNTIF('C121'!E5,"Aula 4")+COUNTIF('C122'!E5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 4")+COUNTIF('C112'!E5,"Aula 4")+COUNTIF('C113'!E5,"Aula 4")+COUNTIF('C121'!E5,"Aula 4")+COUNTIF('C122'!E5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 4")+COUNTIF('C112'!E5,"Aula 4")+COUNTIF('C113'!E5,"Aula 4")+COUNTIF('C121'!E5,"Aula 4")+COUNTIF('C122'!E5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 4")+COUNTIF('C112'!D5,"Aula 4")+COUNTIF('C113'!D5,"Aula 4")+COUNTIF('C121'!D5,"Aula 4")+COUNTIF('C122'!D5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 4")+COUNTIF('C112'!D5,"Aula 4")+COUNTIF('C113'!D5,"Aula 4")+COUNTIF('C121'!D5,"Aula 4")+COUNTIF('C122'!D5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 4")+COUNTIF('C112'!D5,"Aula 4")+COUNTIF('C113'!D5,"Aula 4")+COUNTIF('C121'!D5,"Aula 4")+COUNTIF('C122'!D5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="C125">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 5")+COUNTIF('C112'!E5,"Aula 5")+COUNTIF('C113'!E5,"Aula 5")+COUNTIF('C121'!E5,"Aula 5")+COUNTIF('C122'!E5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 5")+COUNTIF('C112'!E5,"Aula 5")+COUNTIF('C113'!E5,"Aula 5")+COUNTIF('C121'!E5,"Aula 5")+COUNTIF('C122'!E5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 5")+COUNTIF('C112'!E5,"Aula 5")+COUNTIF('C113'!E5,"Aula 5")+COUNTIF('C121'!E5,"Aula 5")+COUNTIF('C122'!E5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 5")+COUNTIF('C112'!D5,"Aula 5")+COUNTIF('C113'!D5,"Aula 5")+COUNTIF('C121'!D5,"Aula 5")+COUNTIF('C122'!D5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 5")+COUNTIF('C112'!D5,"Aula 5")+COUNTIF('C113'!D5,"Aula 5")+COUNTIF('C121'!D5,"Aula 5")+COUNTIF('C122'!D5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 5")+COUNTIF('C112'!D5,"Aula 5")+COUNTIF('C113'!D5,"Aula 5")+COUNTIF('C121'!D5,"Aula 5")+COUNTIF('C122'!D5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="C126">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 6")+COUNTIF('C112'!E5,"Aula 6")+COUNTIF('C113'!E5,"Aula 6")+COUNTIF('C121'!E5,"Aula 6")+COUNTIF('C122'!E5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 6")+COUNTIF('C112'!E5,"Aula 6")+COUNTIF('C113'!E5,"Aula 6")+COUNTIF('C121'!E5,"Aula 6")+COUNTIF('C122'!E5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 6")+COUNTIF('C112'!E5,"Aula 6")+COUNTIF('C113'!E5,"Aula 6")+COUNTIF('C121'!E5,"Aula 6")+COUNTIF('C122'!E5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 6")+COUNTIF('C112'!D5,"Aula 6")+COUNTIF('C113'!D5,"Aula 6")+COUNTIF('C121'!D5,"Aula 6")+COUNTIF('C122'!D5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 6")+COUNTIF('C112'!D5,"Aula 6")+COUNTIF('C113'!D5,"Aula 6")+COUNTIF('C121'!D5,"Aula 6")+COUNTIF('C122'!D5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 6")+COUNTIF('C112'!D5,"Aula 6")+COUNTIF('C113'!D5,"Aula 6")+COUNTIF('C121'!D5,"Aula 6")+COUNTIF('C122'!D5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="C127">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 7")+COUNTIF('C112'!E5,"Aula 7")+COUNTIF('C113'!E5,"Aula 7")+COUNTIF('C121'!E5,"Aula 7")+COUNTIF('C122'!E5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 7")+COUNTIF('C112'!E5,"Aula 7")+COUNTIF('C113'!E5,"Aula 7")+COUNTIF('C121'!E5,"Aula 7")+COUNTIF('C122'!E5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 7")+COUNTIF('C112'!E5,"Aula 7")+COUNTIF('C113'!E5,"Aula 7")+COUNTIF('C121'!E5,"Aula 7")+COUNTIF('C122'!E5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 7")+COUNTIF('C112'!D5,"Aula 7")+COUNTIF('C113'!D5,"Aula 7")+COUNTIF('C121'!D5,"Aula 7")+COUNTIF('C122'!D5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 7")+COUNTIF('C112'!D5,"Aula 7")+COUNTIF('C113'!D5,"Aula 7")+COUNTIF('C121'!D5,"Aula 7")+COUNTIF('C122'!D5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 7")+COUNTIF('C112'!D5,"Aula 7")+COUNTIF('C113'!D5,"Aula 7")+COUNTIF('C121'!D5,"Aula 7")+COUNTIF('C122'!D5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="C128">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 8")+COUNTIF('C112'!E5,"Aula 8")+COUNTIF('C113'!E5,"Aula 8")+COUNTIF('C121'!E5,"Aula 8")+COUNTIF('C122'!E5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 8")+COUNTIF('C112'!E5,"Aula 8")+COUNTIF('C113'!E5,"Aula 8")+COUNTIF('C121'!E5,"Aula 8")+COUNTIF('C122'!E5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 8")+COUNTIF('C112'!E5,"Aula 8")+COUNTIF('C113'!E5,"Aula 8")+COUNTIF('C121'!E5,"Aula 8")+COUNTIF('C122'!E5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 8")+COUNTIF('C112'!D5,"Aula 8")+COUNTIF('C113'!D5,"Aula 8")+COUNTIF('C121'!D5,"Aula 8")+COUNTIF('C122'!D5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 8")+COUNTIF('C112'!D5,"Aula 8")+COUNTIF('C113'!D5,"Aula 8")+COUNTIF('C121'!D5,"Aula 8")+COUNTIF('C122'!D5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 8")+COUNTIF('C112'!D5,"Aula 8")+COUNTIF('C113'!D5,"Aula 8")+COUNTIF('C121'!D5,"Aula 8")+COUNTIF('C122'!D5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="C129">
-        <f>IF((IF((COUNTIF('C111'!E5,"Aula 9")+COUNTIF('C112'!E5,"Aula 9")+COUNTIF('C113'!E5,"Aula 9")+COUNTIF('C121'!E5,"Aula 9")+COUNTIF('C122'!E5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 9")+COUNTIF('C112'!E5,"Aula 9")+COUNTIF('C113'!E5,"Aula 9")+COUNTIF('C121'!E5,"Aula 9")+COUNTIF('C122'!E5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 9")+COUNTIF('C112'!E5,"Aula 9")+COUNTIF('C113'!E5,"Aula 9")+COUNTIF('C121'!E5,"Aula 9")+COUNTIF('C122'!E5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Aula 9")+COUNTIF('C112'!D5,"Aula 9")+COUNTIF('C113'!D5,"Aula 9")+COUNTIF('C121'!D5,"Aula 9")+COUNTIF('C122'!D5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Aula 9")+COUNTIF('C112'!D5,"Aula 9")+COUNTIF('C113'!D5,"Aula 9")+COUNTIF('C121'!D5,"Aula 9")+COUNTIF('C122'!D5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Aula 9")+COUNTIF('C112'!D5,"Aula 9")+COUNTIF('C113'!D5,"Aula 9")+COUNTIF('C121'!D5,"Aula 9")+COUNTIF('C122'!D5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="C130">
-        <f>IF((IF((COUNTIF('C111'!E5,"Lab")+COUNTIF('C112'!E5,"Lab")+COUNTIF('C113'!E5,"Lab")+COUNTIF('C121'!E5,"Lab")+COUNTIF('C122'!E5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Lab")+COUNTIF('C112'!E5,"Lab")+COUNTIF('C113'!E5,"Lab")+COUNTIF('C121'!E5,"Lab")+COUNTIF('C122'!E5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Lab")+COUNTIF('C112'!E5,"Lab")+COUNTIF('C113'!E5,"Lab")+COUNTIF('C121'!E5,"Lab")+COUNTIF('C122'!E5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D5,"Lab")+COUNTIF('C112'!D5,"Lab")+COUNTIF('C113'!D5,"Lab")+COUNTIF('C121'!D5,"Lab")+COUNTIF('C122'!D5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D5,"Lab")+COUNTIF('C112'!D5,"Lab")+COUNTIF('C113'!D5,"Lab")+COUNTIF('C121'!D5,"Lab")+COUNTIF('C122'!D5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D5,"Lab")+COUNTIF('C112'!D5,"Lab")+COUNTIF('C113'!D5,"Lab")+COUNTIF('C121'!D5,"Lab")+COUNTIF('C122'!D5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="C131">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 1")+COUNTIF('C112'!E7,"Aula 1")+COUNTIF('C113'!E7,"Aula 1")+COUNTIF('C121'!E7,"Aula 1")+COUNTIF('C122'!E7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 1")+COUNTIF('C112'!E7,"Aula 1")+COUNTIF('C113'!E7,"Aula 1")+COUNTIF('C121'!E7,"Aula 1")+COUNTIF('C122'!E7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 1")+COUNTIF('C112'!E7,"Aula 1")+COUNTIF('C113'!E7,"Aula 1")+COUNTIF('C121'!E7,"Aula 1")+COUNTIF('C122'!E7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 1")+COUNTIF('C112'!D7,"Aula 1")+COUNTIF('C113'!D7,"Aula 1")+COUNTIF('C121'!D7,"Aula 1")+COUNTIF('C122'!D7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 1")+COUNTIF('C112'!D7,"Aula 1")+COUNTIF('C113'!D7,"Aula 1")+COUNTIF('C121'!D7,"Aula 1")+COUNTIF('C122'!D7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 1")+COUNTIF('C112'!D7,"Aula 1")+COUNTIF('C113'!D7,"Aula 1")+COUNTIF('C121'!D7,"Aula 1")+COUNTIF('C122'!D7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="C132">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 2")+COUNTIF('C112'!E7,"Aula 2")+COUNTIF('C113'!E7,"Aula 2")+COUNTIF('C121'!E7,"Aula 2")+COUNTIF('C122'!E7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 2")+COUNTIF('C112'!E7,"Aula 2")+COUNTIF('C113'!E7,"Aula 2")+COUNTIF('C121'!E7,"Aula 2")+COUNTIF('C122'!E7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 2")+COUNTIF('C112'!E7,"Aula 2")+COUNTIF('C113'!E7,"Aula 2")+COUNTIF('C121'!E7,"Aula 2")+COUNTIF('C122'!E7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 2")+COUNTIF('C112'!D7,"Aula 2")+COUNTIF('C113'!D7,"Aula 2")+COUNTIF('C121'!D7,"Aula 2")+COUNTIF('C122'!D7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 2")+COUNTIF('C112'!D7,"Aula 2")+COUNTIF('C113'!D7,"Aula 2")+COUNTIF('C121'!D7,"Aula 2")+COUNTIF('C122'!D7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 2")+COUNTIF('C112'!D7,"Aula 2")+COUNTIF('C113'!D7,"Aula 2")+COUNTIF('C121'!D7,"Aula 2")+COUNTIF('C122'!D7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="C133">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 3")+COUNTIF('C112'!E7,"Aula 3")+COUNTIF('C113'!E7,"Aula 3")+COUNTIF('C121'!E7,"Aula 3")+COUNTIF('C122'!E7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 3")+COUNTIF('C112'!E7,"Aula 3")+COUNTIF('C113'!E7,"Aula 3")+COUNTIF('C121'!E7,"Aula 3")+COUNTIF('C122'!E7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 3")+COUNTIF('C112'!E7,"Aula 3")+COUNTIF('C113'!E7,"Aula 3")+COUNTIF('C121'!E7,"Aula 3")+COUNTIF('C122'!E7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 3")+COUNTIF('C112'!D7,"Aula 3")+COUNTIF('C113'!D7,"Aula 3")+COUNTIF('C121'!D7,"Aula 3")+COUNTIF('C122'!D7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 3")+COUNTIF('C112'!D7,"Aula 3")+COUNTIF('C113'!D7,"Aula 3")+COUNTIF('C121'!D7,"Aula 3")+COUNTIF('C122'!D7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 3")+COUNTIF('C112'!D7,"Aula 3")+COUNTIF('C113'!D7,"Aula 3")+COUNTIF('C121'!D7,"Aula 3")+COUNTIF('C122'!D7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="C134">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 4")+COUNTIF('C112'!E7,"Aula 4")+COUNTIF('C113'!E7,"Aula 4")+COUNTIF('C121'!E7,"Aula 4")+COUNTIF('C122'!E7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 4")+COUNTIF('C112'!E7,"Aula 4")+COUNTIF('C113'!E7,"Aula 4")+COUNTIF('C121'!E7,"Aula 4")+COUNTIF('C122'!E7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 4")+COUNTIF('C112'!E7,"Aula 4")+COUNTIF('C113'!E7,"Aula 4")+COUNTIF('C121'!E7,"Aula 4")+COUNTIF('C122'!E7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 4")+COUNTIF('C112'!D7,"Aula 4")+COUNTIF('C113'!D7,"Aula 4")+COUNTIF('C121'!D7,"Aula 4")+COUNTIF('C122'!D7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 4")+COUNTIF('C112'!D7,"Aula 4")+COUNTIF('C113'!D7,"Aula 4")+COUNTIF('C121'!D7,"Aula 4")+COUNTIF('C122'!D7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 4")+COUNTIF('C112'!D7,"Aula 4")+COUNTIF('C113'!D7,"Aula 4")+COUNTIF('C121'!D7,"Aula 4")+COUNTIF('C122'!D7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="C135">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 5")+COUNTIF('C112'!E7,"Aula 5")+COUNTIF('C113'!E7,"Aula 5")+COUNTIF('C121'!E7,"Aula 5")+COUNTIF('C122'!E7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 5")+COUNTIF('C112'!E7,"Aula 5")+COUNTIF('C113'!E7,"Aula 5")+COUNTIF('C121'!E7,"Aula 5")+COUNTIF('C122'!E7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 5")+COUNTIF('C112'!E7,"Aula 5")+COUNTIF('C113'!E7,"Aula 5")+COUNTIF('C121'!E7,"Aula 5")+COUNTIF('C122'!E7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 5")+COUNTIF('C112'!D7,"Aula 5")+COUNTIF('C113'!D7,"Aula 5")+COUNTIF('C121'!D7,"Aula 5")+COUNTIF('C122'!D7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 5")+COUNTIF('C112'!D7,"Aula 5")+COUNTIF('C113'!D7,"Aula 5")+COUNTIF('C121'!D7,"Aula 5")+COUNTIF('C122'!D7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 5")+COUNTIF('C112'!D7,"Aula 5")+COUNTIF('C113'!D7,"Aula 5")+COUNTIF('C121'!D7,"Aula 5")+COUNTIF('C122'!D7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="C136">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 6")+COUNTIF('C112'!E7,"Aula 6")+COUNTIF('C113'!E7,"Aula 6")+COUNTIF('C121'!E7,"Aula 6")+COUNTIF('C122'!E7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 6")+COUNTIF('C112'!E7,"Aula 6")+COUNTIF('C113'!E7,"Aula 6")+COUNTIF('C121'!E7,"Aula 6")+COUNTIF('C122'!E7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 6")+COUNTIF('C112'!E7,"Aula 6")+COUNTIF('C113'!E7,"Aula 6")+COUNTIF('C121'!E7,"Aula 6")+COUNTIF('C122'!E7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 6")+COUNTIF('C112'!D7,"Aula 6")+COUNTIF('C113'!D7,"Aula 6")+COUNTIF('C121'!D7,"Aula 6")+COUNTIF('C122'!D7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 6")+COUNTIF('C112'!D7,"Aula 6")+COUNTIF('C113'!D7,"Aula 6")+COUNTIF('C121'!D7,"Aula 6")+COUNTIF('C122'!D7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 6")+COUNTIF('C112'!D7,"Aula 6")+COUNTIF('C113'!D7,"Aula 6")+COUNTIF('C121'!D7,"Aula 6")+COUNTIF('C122'!D7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="C137">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 7")+COUNTIF('C112'!E7,"Aula 7")+COUNTIF('C113'!E7,"Aula 7")+COUNTIF('C121'!E7,"Aula 7")+COUNTIF('C122'!E7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 7")+COUNTIF('C112'!E7,"Aula 7")+COUNTIF('C113'!E7,"Aula 7")+COUNTIF('C121'!E7,"Aula 7")+COUNTIF('C122'!E7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 7")+COUNTIF('C112'!E7,"Aula 7")+COUNTIF('C113'!E7,"Aula 7")+COUNTIF('C121'!E7,"Aula 7")+COUNTIF('C122'!E7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 7")+COUNTIF('C112'!D7,"Aula 7")+COUNTIF('C113'!D7,"Aula 7")+COUNTIF('C121'!D7,"Aula 7")+COUNTIF('C122'!D7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 7")+COUNTIF('C112'!D7,"Aula 7")+COUNTIF('C113'!D7,"Aula 7")+COUNTIF('C121'!D7,"Aula 7")+COUNTIF('C122'!D7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 7")+COUNTIF('C112'!D7,"Aula 7")+COUNTIF('C113'!D7,"Aula 7")+COUNTIF('C121'!D7,"Aula 7")+COUNTIF('C122'!D7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="C138">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 8")+COUNTIF('C112'!E7,"Aula 8")+COUNTIF('C113'!E7,"Aula 8")+COUNTIF('C121'!E7,"Aula 8")+COUNTIF('C122'!E7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 8")+COUNTIF('C112'!E7,"Aula 8")+COUNTIF('C113'!E7,"Aula 8")+COUNTIF('C121'!E7,"Aula 8")+COUNTIF('C122'!E7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 8")+COUNTIF('C112'!E7,"Aula 8")+COUNTIF('C113'!E7,"Aula 8")+COUNTIF('C121'!E7,"Aula 8")+COUNTIF('C122'!E7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 8")+COUNTIF('C112'!D7,"Aula 8")+COUNTIF('C113'!D7,"Aula 8")+COUNTIF('C121'!D7,"Aula 8")+COUNTIF('C122'!D7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 8")+COUNTIF('C112'!D7,"Aula 8")+COUNTIF('C113'!D7,"Aula 8")+COUNTIF('C121'!D7,"Aula 8")+COUNTIF('C122'!D7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 8")+COUNTIF('C112'!D7,"Aula 8")+COUNTIF('C113'!D7,"Aula 8")+COUNTIF('C121'!D7,"Aula 8")+COUNTIF('C122'!D7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="C139">
-        <f>IF((IF((COUNTIF('C111'!E7,"Aula 9")+COUNTIF('C112'!E7,"Aula 9")+COUNTIF('C113'!E7,"Aula 9")+COUNTIF('C121'!E7,"Aula 9")+COUNTIF('C122'!E7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 9")+COUNTIF('C112'!E7,"Aula 9")+COUNTIF('C113'!E7,"Aula 9")+COUNTIF('C121'!E7,"Aula 9")+COUNTIF('C122'!E7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 9")+COUNTIF('C112'!E7,"Aula 9")+COUNTIF('C113'!E7,"Aula 9")+COUNTIF('C121'!E7,"Aula 9")+COUNTIF('C122'!E7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Aula 9")+COUNTIF('C112'!D7,"Aula 9")+COUNTIF('C113'!D7,"Aula 9")+COUNTIF('C121'!D7,"Aula 9")+COUNTIF('C122'!D7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Aula 9")+COUNTIF('C112'!D7,"Aula 9")+COUNTIF('C113'!D7,"Aula 9")+COUNTIF('C121'!D7,"Aula 9")+COUNTIF('C122'!D7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Aula 9")+COUNTIF('C112'!D7,"Aula 9")+COUNTIF('C113'!D7,"Aula 9")+COUNTIF('C121'!D7,"Aula 9")+COUNTIF('C122'!D7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="C140">
-        <f>IF((IF((COUNTIF('C111'!E7,"Lab")+COUNTIF('C112'!E7,"Lab")+COUNTIF('C113'!E7,"Lab")+COUNTIF('C121'!E7,"Lab")+COUNTIF('C122'!E7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Lab")+COUNTIF('C112'!E7,"Lab")+COUNTIF('C113'!E7,"Lab")+COUNTIF('C121'!E7,"Lab")+COUNTIF('C122'!E7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Lab")+COUNTIF('C112'!E7,"Lab")+COUNTIF('C113'!E7,"Lab")+COUNTIF('C121'!E7,"Lab")+COUNTIF('C122'!E7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D7,"Lab")+COUNTIF('C112'!D7,"Lab")+COUNTIF('C113'!D7,"Lab")+COUNTIF('C121'!D7,"Lab")+COUNTIF('C122'!D7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D7,"Lab")+COUNTIF('C112'!D7,"Lab")+COUNTIF('C113'!D7,"Lab")+COUNTIF('C121'!D7,"Lab")+COUNTIF('C122'!D7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D7,"Lab")+COUNTIF('C112'!D7,"Lab")+COUNTIF('C113'!D7,"Lab")+COUNTIF('C121'!D7,"Lab")+COUNTIF('C122'!D7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="C141">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 1")+COUNTIF('C112'!E9,"Aula 1")+COUNTIF('C113'!E9,"Aula 1")+COUNTIF('C121'!E9,"Aula 1")+COUNTIF('C122'!E9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 1")+COUNTIF('C112'!E9,"Aula 1")+COUNTIF('C113'!E9,"Aula 1")+COUNTIF('C121'!E9,"Aula 1")+COUNTIF('C122'!E9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 1")+COUNTIF('C112'!E9,"Aula 1")+COUNTIF('C113'!E9,"Aula 1")+COUNTIF('C121'!E9,"Aula 1")+COUNTIF('C122'!E9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 1")+COUNTIF('C112'!D9,"Aula 1")+COUNTIF('C113'!D9,"Aula 1")+COUNTIF('C121'!D9,"Aula 1")+COUNTIF('C122'!D9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 1")+COUNTIF('C112'!D9,"Aula 1")+COUNTIF('C113'!D9,"Aula 1")+COUNTIF('C121'!D9,"Aula 1")+COUNTIF('C122'!D9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 1")+COUNTIF('C112'!D9,"Aula 1")+COUNTIF('C113'!D9,"Aula 1")+COUNTIF('C121'!D9,"Aula 1")+COUNTIF('C122'!D9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="C142">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 2")+COUNTIF('C112'!E9,"Aula 2")+COUNTIF('C113'!E9,"Aula 2")+COUNTIF('C121'!E9,"Aula 2")+COUNTIF('C122'!E9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 2")+COUNTIF('C112'!E9,"Aula 2")+COUNTIF('C113'!E9,"Aula 2")+COUNTIF('C121'!E9,"Aula 2")+COUNTIF('C122'!E9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 2")+COUNTIF('C112'!E9,"Aula 2")+COUNTIF('C113'!E9,"Aula 2")+COUNTIF('C121'!E9,"Aula 2")+COUNTIF('C122'!E9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 2")+COUNTIF('C112'!D9,"Aula 2")+COUNTIF('C113'!D9,"Aula 2")+COUNTIF('C121'!D9,"Aula 2")+COUNTIF('C122'!D9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 2")+COUNTIF('C112'!D9,"Aula 2")+COUNTIF('C113'!D9,"Aula 2")+COUNTIF('C121'!D9,"Aula 2")+COUNTIF('C122'!D9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 2")+COUNTIF('C112'!D9,"Aula 2")+COUNTIF('C113'!D9,"Aula 2")+COUNTIF('C121'!D9,"Aula 2")+COUNTIF('C122'!D9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="C143">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 3")+COUNTIF('C112'!E9,"Aula 3")+COUNTIF('C113'!E9,"Aula 3")+COUNTIF('C121'!E9,"Aula 3")+COUNTIF('C122'!E9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 3")+COUNTIF('C112'!E9,"Aula 3")+COUNTIF('C113'!E9,"Aula 3")+COUNTIF('C121'!E9,"Aula 3")+COUNTIF('C122'!E9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 3")+COUNTIF('C112'!E9,"Aula 3")+COUNTIF('C113'!E9,"Aula 3")+COUNTIF('C121'!E9,"Aula 3")+COUNTIF('C122'!E9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 3")+COUNTIF('C112'!D9,"Aula 3")+COUNTIF('C113'!D9,"Aula 3")+COUNTIF('C121'!D9,"Aula 3")+COUNTIF('C122'!D9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 3")+COUNTIF('C112'!D9,"Aula 3")+COUNTIF('C113'!D9,"Aula 3")+COUNTIF('C121'!D9,"Aula 3")+COUNTIF('C122'!D9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 3")+COUNTIF('C112'!D9,"Aula 3")+COUNTIF('C113'!D9,"Aula 3")+COUNTIF('C121'!D9,"Aula 3")+COUNTIF('C122'!D9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="C144">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 4")+COUNTIF('C112'!E9,"Aula 4")+COUNTIF('C113'!E9,"Aula 4")+COUNTIF('C121'!E9,"Aula 4")+COUNTIF('C122'!E9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 4")+COUNTIF('C112'!E9,"Aula 4")+COUNTIF('C113'!E9,"Aula 4")+COUNTIF('C121'!E9,"Aula 4")+COUNTIF('C122'!E9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 4")+COUNTIF('C112'!E9,"Aula 4")+COUNTIF('C113'!E9,"Aula 4")+COUNTIF('C121'!E9,"Aula 4")+COUNTIF('C122'!E9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 4")+COUNTIF('C112'!D9,"Aula 4")+COUNTIF('C113'!D9,"Aula 4")+COUNTIF('C121'!D9,"Aula 4")+COUNTIF('C122'!D9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 4")+COUNTIF('C112'!D9,"Aula 4")+COUNTIF('C113'!D9,"Aula 4")+COUNTIF('C121'!D9,"Aula 4")+COUNTIF('C122'!D9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 4")+COUNTIF('C112'!D9,"Aula 4")+COUNTIF('C113'!D9,"Aula 4")+COUNTIF('C121'!D9,"Aula 4")+COUNTIF('C122'!D9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="C145">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 5")+COUNTIF('C112'!E9,"Aula 5")+COUNTIF('C113'!E9,"Aula 5")+COUNTIF('C121'!E9,"Aula 5")+COUNTIF('C122'!E9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 5")+COUNTIF('C112'!E9,"Aula 5")+COUNTIF('C113'!E9,"Aula 5")+COUNTIF('C121'!E9,"Aula 5")+COUNTIF('C122'!E9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 5")+COUNTIF('C112'!E9,"Aula 5")+COUNTIF('C113'!E9,"Aula 5")+COUNTIF('C121'!E9,"Aula 5")+COUNTIF('C122'!E9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 5")+COUNTIF('C112'!D9,"Aula 5")+COUNTIF('C113'!D9,"Aula 5")+COUNTIF('C121'!D9,"Aula 5")+COUNTIF('C122'!D9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 5")+COUNTIF('C112'!D9,"Aula 5")+COUNTIF('C113'!D9,"Aula 5")+COUNTIF('C121'!D9,"Aula 5")+COUNTIF('C122'!D9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 5")+COUNTIF('C112'!D9,"Aula 5")+COUNTIF('C113'!D9,"Aula 5")+COUNTIF('C121'!D9,"Aula 5")+COUNTIF('C122'!D9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="C146">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 6")+COUNTIF('C112'!E9,"Aula 6")+COUNTIF('C113'!E9,"Aula 6")+COUNTIF('C121'!E9,"Aula 6")+COUNTIF('C122'!E9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 6")+COUNTIF('C112'!E9,"Aula 6")+COUNTIF('C113'!E9,"Aula 6")+COUNTIF('C121'!E9,"Aula 6")+COUNTIF('C122'!E9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 6")+COUNTIF('C112'!E9,"Aula 6")+COUNTIF('C113'!E9,"Aula 6")+COUNTIF('C121'!E9,"Aula 6")+COUNTIF('C122'!E9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 6")+COUNTIF('C112'!D9,"Aula 6")+COUNTIF('C113'!D9,"Aula 6")+COUNTIF('C121'!D9,"Aula 6")+COUNTIF('C122'!D9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 6")+COUNTIF('C112'!D9,"Aula 6")+COUNTIF('C113'!D9,"Aula 6")+COUNTIF('C121'!D9,"Aula 6")+COUNTIF('C122'!D9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 6")+COUNTIF('C112'!D9,"Aula 6")+COUNTIF('C113'!D9,"Aula 6")+COUNTIF('C121'!D9,"Aula 6")+COUNTIF('C122'!D9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="C147">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 7")+COUNTIF('C112'!E9,"Aula 7")+COUNTIF('C113'!E9,"Aula 7")+COUNTIF('C121'!E9,"Aula 7")+COUNTIF('C122'!E9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 7")+COUNTIF('C112'!E9,"Aula 7")+COUNTIF('C113'!E9,"Aula 7")+COUNTIF('C121'!E9,"Aula 7")+COUNTIF('C122'!E9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 7")+COUNTIF('C112'!E9,"Aula 7")+COUNTIF('C113'!E9,"Aula 7")+COUNTIF('C121'!E9,"Aula 7")+COUNTIF('C122'!E9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 7")+COUNTIF('C112'!D9,"Aula 7")+COUNTIF('C113'!D9,"Aula 7")+COUNTIF('C121'!D9,"Aula 7")+COUNTIF('C122'!D9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 7")+COUNTIF('C112'!D9,"Aula 7")+COUNTIF('C113'!D9,"Aula 7")+COUNTIF('C121'!D9,"Aula 7")+COUNTIF('C122'!D9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 7")+COUNTIF('C112'!D9,"Aula 7")+COUNTIF('C113'!D9,"Aula 7")+COUNTIF('C121'!D9,"Aula 7")+COUNTIF('C122'!D9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="C148">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 8")+COUNTIF('C112'!E9,"Aula 8")+COUNTIF('C113'!E9,"Aula 8")+COUNTIF('C121'!E9,"Aula 8")+COUNTIF('C122'!E9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 8")+COUNTIF('C112'!E9,"Aula 8")+COUNTIF('C113'!E9,"Aula 8")+COUNTIF('C121'!E9,"Aula 8")+COUNTIF('C122'!E9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 8")+COUNTIF('C112'!E9,"Aula 8")+COUNTIF('C113'!E9,"Aula 8")+COUNTIF('C121'!E9,"Aula 8")+COUNTIF('C122'!E9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 8")+COUNTIF('C112'!D9,"Aula 8")+COUNTIF('C113'!D9,"Aula 8")+COUNTIF('C121'!D9,"Aula 8")+COUNTIF('C122'!D9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 8")+COUNTIF('C112'!D9,"Aula 8")+COUNTIF('C113'!D9,"Aula 8")+COUNTIF('C121'!D9,"Aula 8")+COUNTIF('C122'!D9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 8")+COUNTIF('C112'!D9,"Aula 8")+COUNTIF('C113'!D9,"Aula 8")+COUNTIF('C121'!D9,"Aula 8")+COUNTIF('C122'!D9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="C149">
-        <f>IF((IF((COUNTIF('C111'!E9,"Aula 9")+COUNTIF('C112'!E9,"Aula 9")+COUNTIF('C113'!E9,"Aula 9")+COUNTIF('C121'!E9,"Aula 9")+COUNTIF('C122'!E9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 9")+COUNTIF('C112'!E9,"Aula 9")+COUNTIF('C113'!E9,"Aula 9")+COUNTIF('C121'!E9,"Aula 9")+COUNTIF('C122'!E9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 9")+COUNTIF('C112'!E9,"Aula 9")+COUNTIF('C113'!E9,"Aula 9")+COUNTIF('C121'!E9,"Aula 9")+COUNTIF('C122'!E9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Aula 9")+COUNTIF('C112'!D9,"Aula 9")+COUNTIF('C113'!D9,"Aula 9")+COUNTIF('C121'!D9,"Aula 9")+COUNTIF('C122'!D9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Aula 9")+COUNTIF('C112'!D9,"Aula 9")+COUNTIF('C113'!D9,"Aula 9")+COUNTIF('C121'!D9,"Aula 9")+COUNTIF('C122'!D9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Aula 9")+COUNTIF('C112'!D9,"Aula 9")+COUNTIF('C113'!D9,"Aula 9")+COUNTIF('C121'!D9,"Aula 9")+COUNTIF('C122'!D9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="C150">
-        <f>IF((IF((COUNTIF('C111'!E9,"Lab")+COUNTIF('C112'!E9,"Lab")+COUNTIF('C113'!E9,"Lab")+COUNTIF('C121'!E9,"Lab")+COUNTIF('C122'!E9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Lab")+COUNTIF('C112'!E9,"Lab")+COUNTIF('C113'!E9,"Lab")+COUNTIF('C121'!E9,"Lab")+COUNTIF('C122'!E9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Lab")+COUNTIF('C112'!E9,"Lab")+COUNTIF('C113'!E9,"Lab")+COUNTIF('C121'!E9,"Lab")+COUNTIF('C122'!E9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D9,"Lab")+COUNTIF('C112'!D9,"Lab")+COUNTIF('C113'!D9,"Lab")+COUNTIF('C121'!D9,"Lab")+COUNTIF('C122'!D9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D9,"Lab")+COUNTIF('C112'!D9,"Lab")+COUNTIF('C113'!D9,"Lab")+COUNTIF('C121'!D9,"Lab")+COUNTIF('C122'!D9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D9,"Lab")+COUNTIF('C112'!D9,"Lab")+COUNTIF('C113'!D9,"Lab")+COUNTIF('C121'!D9,"Lab")+COUNTIF('C122'!D9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="C151">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 1")+COUNTIF('C112'!E11,"Aula 1")+COUNTIF('C113'!E11,"Aula 1")+COUNTIF('C121'!E11,"Aula 1")+COUNTIF('C122'!E11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 1")+COUNTIF('C112'!E11,"Aula 1")+COUNTIF('C113'!E11,"Aula 1")+COUNTIF('C121'!E11,"Aula 1")+COUNTIF('C122'!E11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 1")+COUNTIF('C112'!E11,"Aula 1")+COUNTIF('C113'!E11,"Aula 1")+COUNTIF('C121'!E11,"Aula 1")+COUNTIF('C122'!E11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 1")+COUNTIF('C112'!D11,"Aula 1")+COUNTIF('C113'!D11,"Aula 1")+COUNTIF('C121'!D11,"Aula 1")+COUNTIF('C122'!D11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 1")+COUNTIF('C112'!D11,"Aula 1")+COUNTIF('C113'!D11,"Aula 1")+COUNTIF('C121'!D11,"Aula 1")+COUNTIF('C122'!D11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 1")+COUNTIF('C112'!D11,"Aula 1")+COUNTIF('C113'!D11,"Aula 1")+COUNTIF('C121'!D11,"Aula 1")+COUNTIF('C122'!D11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="C152">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 2")+COUNTIF('C112'!E11,"Aula 2")+COUNTIF('C113'!E11,"Aula 2")+COUNTIF('C121'!E11,"Aula 2")+COUNTIF('C122'!E11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 2")+COUNTIF('C112'!E11,"Aula 2")+COUNTIF('C113'!E11,"Aula 2")+COUNTIF('C121'!E11,"Aula 2")+COUNTIF('C122'!E11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 2")+COUNTIF('C112'!E11,"Aula 2")+COUNTIF('C113'!E11,"Aula 2")+COUNTIF('C121'!E11,"Aula 2")+COUNTIF('C122'!E11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 2")+COUNTIF('C112'!D11,"Aula 2")+COUNTIF('C113'!D11,"Aula 2")+COUNTIF('C121'!D11,"Aula 2")+COUNTIF('C122'!D11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 2")+COUNTIF('C112'!D11,"Aula 2")+COUNTIF('C113'!D11,"Aula 2")+COUNTIF('C121'!D11,"Aula 2")+COUNTIF('C122'!D11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 2")+COUNTIF('C112'!D11,"Aula 2")+COUNTIF('C113'!D11,"Aula 2")+COUNTIF('C121'!D11,"Aula 2")+COUNTIF('C122'!D11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="C153">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 3")+COUNTIF('C112'!E11,"Aula 3")+COUNTIF('C113'!E11,"Aula 3")+COUNTIF('C121'!E11,"Aula 3")+COUNTIF('C122'!E11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 3")+COUNTIF('C112'!E11,"Aula 3")+COUNTIF('C113'!E11,"Aula 3")+COUNTIF('C121'!E11,"Aula 3")+COUNTIF('C122'!E11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 3")+COUNTIF('C112'!E11,"Aula 3")+COUNTIF('C113'!E11,"Aula 3")+COUNTIF('C121'!E11,"Aula 3")+COUNTIF('C122'!E11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 3")+COUNTIF('C112'!D11,"Aula 3")+COUNTIF('C113'!D11,"Aula 3")+COUNTIF('C121'!D11,"Aula 3")+COUNTIF('C122'!D11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 3")+COUNTIF('C112'!D11,"Aula 3")+COUNTIF('C113'!D11,"Aula 3")+COUNTIF('C121'!D11,"Aula 3")+COUNTIF('C122'!D11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 3")+COUNTIF('C112'!D11,"Aula 3")+COUNTIF('C113'!D11,"Aula 3")+COUNTIF('C121'!D11,"Aula 3")+COUNTIF('C122'!D11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="C154">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 4")+COUNTIF('C112'!E11,"Aula 4")+COUNTIF('C113'!E11,"Aula 4")+COUNTIF('C121'!E11,"Aula 4")+COUNTIF('C122'!E11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 4")+COUNTIF('C112'!E11,"Aula 4")+COUNTIF('C113'!E11,"Aula 4")+COUNTIF('C121'!E11,"Aula 4")+COUNTIF('C122'!E11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 4")+COUNTIF('C112'!E11,"Aula 4")+COUNTIF('C113'!E11,"Aula 4")+COUNTIF('C121'!E11,"Aula 4")+COUNTIF('C122'!E11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 4")+COUNTIF('C112'!D11,"Aula 4")+COUNTIF('C113'!D11,"Aula 4")+COUNTIF('C121'!D11,"Aula 4")+COUNTIF('C122'!D11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 4")+COUNTIF('C112'!D11,"Aula 4")+COUNTIF('C113'!D11,"Aula 4")+COUNTIF('C121'!D11,"Aula 4")+COUNTIF('C122'!D11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 4")+COUNTIF('C112'!D11,"Aula 4")+COUNTIF('C113'!D11,"Aula 4")+COUNTIF('C121'!D11,"Aula 4")+COUNTIF('C122'!D11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="C155">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 5")+COUNTIF('C112'!E11,"Aula 5")+COUNTIF('C113'!E11,"Aula 5")+COUNTIF('C121'!E11,"Aula 5")+COUNTIF('C122'!E11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 5")+COUNTIF('C112'!E11,"Aula 5")+COUNTIF('C113'!E11,"Aula 5")+COUNTIF('C121'!E11,"Aula 5")+COUNTIF('C122'!E11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 5")+COUNTIF('C112'!E11,"Aula 5")+COUNTIF('C113'!E11,"Aula 5")+COUNTIF('C121'!E11,"Aula 5")+COUNTIF('C122'!E11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 5")+COUNTIF('C112'!D11,"Aula 5")+COUNTIF('C113'!D11,"Aula 5")+COUNTIF('C121'!D11,"Aula 5")+COUNTIF('C122'!D11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 5")+COUNTIF('C112'!D11,"Aula 5")+COUNTIF('C113'!D11,"Aula 5")+COUNTIF('C121'!D11,"Aula 5")+COUNTIF('C122'!D11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 5")+COUNTIF('C112'!D11,"Aula 5")+COUNTIF('C113'!D11,"Aula 5")+COUNTIF('C121'!D11,"Aula 5")+COUNTIF('C122'!D11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="C156">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 6")+COUNTIF('C112'!E11,"Aula 6")+COUNTIF('C113'!E11,"Aula 6")+COUNTIF('C121'!E11,"Aula 6")+COUNTIF('C122'!E11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 6")+COUNTIF('C112'!E11,"Aula 6")+COUNTIF('C113'!E11,"Aula 6")+COUNTIF('C121'!E11,"Aula 6")+COUNTIF('C122'!E11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 6")+COUNTIF('C112'!E11,"Aula 6")+COUNTIF('C113'!E11,"Aula 6")+COUNTIF('C121'!E11,"Aula 6")+COUNTIF('C122'!E11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 6")+COUNTIF('C112'!D11,"Aula 6")+COUNTIF('C113'!D11,"Aula 6")+COUNTIF('C121'!D11,"Aula 6")+COUNTIF('C122'!D11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 6")+COUNTIF('C112'!D11,"Aula 6")+COUNTIF('C113'!D11,"Aula 6")+COUNTIF('C121'!D11,"Aula 6")+COUNTIF('C122'!D11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 6")+COUNTIF('C112'!D11,"Aula 6")+COUNTIF('C113'!D11,"Aula 6")+COUNTIF('C121'!D11,"Aula 6")+COUNTIF('C122'!D11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="C157">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 7")+COUNTIF('C112'!E11,"Aula 7")+COUNTIF('C113'!E11,"Aula 7")+COUNTIF('C121'!E11,"Aula 7")+COUNTIF('C122'!E11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 7")+COUNTIF('C112'!E11,"Aula 7")+COUNTIF('C113'!E11,"Aula 7")+COUNTIF('C121'!E11,"Aula 7")+COUNTIF('C122'!E11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 7")+COUNTIF('C112'!E11,"Aula 7")+COUNTIF('C113'!E11,"Aula 7")+COUNTIF('C121'!E11,"Aula 7")+COUNTIF('C122'!E11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 7")+COUNTIF('C112'!D11,"Aula 7")+COUNTIF('C113'!D11,"Aula 7")+COUNTIF('C121'!D11,"Aula 7")+COUNTIF('C122'!D11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 7")+COUNTIF('C112'!D11,"Aula 7")+COUNTIF('C113'!D11,"Aula 7")+COUNTIF('C121'!D11,"Aula 7")+COUNTIF('C122'!D11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 7")+COUNTIF('C112'!D11,"Aula 7")+COUNTIF('C113'!D11,"Aula 7")+COUNTIF('C121'!D11,"Aula 7")+COUNTIF('C122'!D11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="C158">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 8")+COUNTIF('C112'!E11,"Aula 8")+COUNTIF('C113'!E11,"Aula 8")+COUNTIF('C121'!E11,"Aula 8")+COUNTIF('C122'!E11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 8")+COUNTIF('C112'!E11,"Aula 8")+COUNTIF('C113'!E11,"Aula 8")+COUNTIF('C121'!E11,"Aula 8")+COUNTIF('C122'!E11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 8")+COUNTIF('C112'!E11,"Aula 8")+COUNTIF('C113'!E11,"Aula 8")+COUNTIF('C121'!E11,"Aula 8")+COUNTIF('C122'!E11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 8")+COUNTIF('C112'!D11,"Aula 8")+COUNTIF('C113'!D11,"Aula 8")+COUNTIF('C121'!D11,"Aula 8")+COUNTIF('C122'!D11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 8")+COUNTIF('C112'!D11,"Aula 8")+COUNTIF('C113'!D11,"Aula 8")+COUNTIF('C121'!D11,"Aula 8")+COUNTIF('C122'!D11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 8")+COUNTIF('C112'!D11,"Aula 8")+COUNTIF('C113'!D11,"Aula 8")+COUNTIF('C121'!D11,"Aula 8")+COUNTIF('C122'!D11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="C159">
-        <f>IF((IF((COUNTIF('C111'!E11,"Aula 9")+COUNTIF('C112'!E11,"Aula 9")+COUNTIF('C113'!E11,"Aula 9")+COUNTIF('C121'!E11,"Aula 9")+COUNTIF('C122'!E11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 9")+COUNTIF('C112'!E11,"Aula 9")+COUNTIF('C113'!E11,"Aula 9")+COUNTIF('C121'!E11,"Aula 9")+COUNTIF('C122'!E11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 9")+COUNTIF('C112'!E11,"Aula 9")+COUNTIF('C113'!E11,"Aula 9")+COUNTIF('C121'!E11,"Aula 9")+COUNTIF('C122'!E11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Aula 9")+COUNTIF('C112'!D11,"Aula 9")+COUNTIF('C113'!D11,"Aula 9")+COUNTIF('C121'!D11,"Aula 9")+COUNTIF('C122'!D11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Aula 9")+COUNTIF('C112'!D11,"Aula 9")+COUNTIF('C113'!D11,"Aula 9")+COUNTIF('C121'!D11,"Aula 9")+COUNTIF('C122'!D11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Aula 9")+COUNTIF('C112'!D11,"Aula 9")+COUNTIF('C113'!D11,"Aula 9")+COUNTIF('C121'!D11,"Aula 9")+COUNTIF('C122'!D11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="C160">
-        <f>IF((IF((COUNTIF('C111'!E11,"Lab")+COUNTIF('C112'!E11,"Lab")+COUNTIF('C113'!E11,"Lab")+COUNTIF('C121'!E11,"Lab")+COUNTIF('C122'!E11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Lab")+COUNTIF('C112'!E11,"Lab")+COUNTIF('C113'!E11,"Lab")+COUNTIF('C121'!E11,"Lab")+COUNTIF('C122'!E11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Lab")+COUNTIF('C112'!E11,"Lab")+COUNTIF('C113'!E11,"Lab")+COUNTIF('C121'!E11,"Lab")+COUNTIF('C122'!E11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D11,"Lab")+COUNTIF('C112'!D11,"Lab")+COUNTIF('C113'!D11,"Lab")+COUNTIF('C121'!D11,"Lab")+COUNTIF('C122'!D11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D11,"Lab")+COUNTIF('C112'!D11,"Lab")+COUNTIF('C113'!D11,"Lab")+COUNTIF('C121'!D11,"Lab")+COUNTIF('C122'!D11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D11,"Lab")+COUNTIF('C112'!D11,"Lab")+COUNTIF('C113'!D11,"Lab")+COUNTIF('C121'!D11,"Lab")+COUNTIF('C122'!D11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="C161">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 1")+COUNTIF('C112'!E13,"Aula 1")+COUNTIF('C113'!E13,"Aula 1")+COUNTIF('C121'!E13,"Aula 1")+COUNTIF('C122'!E13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 1")+COUNTIF('C112'!E13,"Aula 1")+COUNTIF('C113'!E13,"Aula 1")+COUNTIF('C121'!E13,"Aula 1")+COUNTIF('C122'!E13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 1")+COUNTIF('C112'!E13,"Aula 1")+COUNTIF('C113'!E13,"Aula 1")+COUNTIF('C121'!E13,"Aula 1")+COUNTIF('C122'!E13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 1")+COUNTIF('C112'!D13,"Aula 1")+COUNTIF('C113'!D13,"Aula 1")+COUNTIF('C121'!D13,"Aula 1")+COUNTIF('C122'!D13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 1")+COUNTIF('C112'!D13,"Aula 1")+COUNTIF('C113'!D13,"Aula 1")+COUNTIF('C121'!D13,"Aula 1")+COUNTIF('C122'!D13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 1")+COUNTIF('C112'!D13,"Aula 1")+COUNTIF('C113'!D13,"Aula 1")+COUNTIF('C121'!D13,"Aula 1")+COUNTIF('C122'!D13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="C162">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 2")+COUNTIF('C112'!E13,"Aula 2")+COUNTIF('C113'!E13,"Aula 2")+COUNTIF('C121'!E13,"Aula 2")+COUNTIF('C122'!E13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 2")+COUNTIF('C112'!E13,"Aula 2")+COUNTIF('C113'!E13,"Aula 2")+COUNTIF('C121'!E13,"Aula 2")+COUNTIF('C122'!E13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 2")+COUNTIF('C112'!E13,"Aula 2")+COUNTIF('C113'!E13,"Aula 2")+COUNTIF('C121'!E13,"Aula 2")+COUNTIF('C122'!E13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 2")+COUNTIF('C112'!D13,"Aula 2")+COUNTIF('C113'!D13,"Aula 2")+COUNTIF('C121'!D13,"Aula 2")+COUNTIF('C122'!D13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 2")+COUNTIF('C112'!D13,"Aula 2")+COUNTIF('C113'!D13,"Aula 2")+COUNTIF('C121'!D13,"Aula 2")+COUNTIF('C122'!D13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 2")+COUNTIF('C112'!D13,"Aula 2")+COUNTIF('C113'!D13,"Aula 2")+COUNTIF('C121'!D13,"Aula 2")+COUNTIF('C122'!D13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="C163">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 3")+COUNTIF('C112'!E13,"Aula 3")+COUNTIF('C113'!E13,"Aula 3")+COUNTIF('C121'!E13,"Aula 3")+COUNTIF('C122'!E13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 3")+COUNTIF('C112'!E13,"Aula 3")+COUNTIF('C113'!E13,"Aula 3")+COUNTIF('C121'!E13,"Aula 3")+COUNTIF('C122'!E13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 3")+COUNTIF('C112'!E13,"Aula 3")+COUNTIF('C113'!E13,"Aula 3")+COUNTIF('C121'!E13,"Aula 3")+COUNTIF('C122'!E13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 3")+COUNTIF('C112'!D13,"Aula 3")+COUNTIF('C113'!D13,"Aula 3")+COUNTIF('C121'!D13,"Aula 3")+COUNTIF('C122'!D13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 3")+COUNTIF('C112'!D13,"Aula 3")+COUNTIF('C113'!D13,"Aula 3")+COUNTIF('C121'!D13,"Aula 3")+COUNTIF('C122'!D13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 3")+COUNTIF('C112'!D13,"Aula 3")+COUNTIF('C113'!D13,"Aula 3")+COUNTIF('C121'!D13,"Aula 3")+COUNTIF('C122'!D13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="C164">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 4")+COUNTIF('C112'!E13,"Aula 4")+COUNTIF('C113'!E13,"Aula 4")+COUNTIF('C121'!E13,"Aula 4")+COUNTIF('C122'!E13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 4")+COUNTIF('C112'!E13,"Aula 4")+COUNTIF('C113'!E13,"Aula 4")+COUNTIF('C121'!E13,"Aula 4")+COUNTIF('C122'!E13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 4")+COUNTIF('C112'!E13,"Aula 4")+COUNTIF('C113'!E13,"Aula 4")+COUNTIF('C121'!E13,"Aula 4")+COUNTIF('C122'!E13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 4")+COUNTIF('C112'!D13,"Aula 4")+COUNTIF('C113'!D13,"Aula 4")+COUNTIF('C121'!D13,"Aula 4")+COUNTIF('C122'!D13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 4")+COUNTIF('C112'!D13,"Aula 4")+COUNTIF('C113'!D13,"Aula 4")+COUNTIF('C121'!D13,"Aula 4")+COUNTIF('C122'!D13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 4")+COUNTIF('C112'!D13,"Aula 4")+COUNTIF('C113'!D13,"Aula 4")+COUNTIF('C121'!D13,"Aula 4")+COUNTIF('C122'!D13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="C165">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 5")+COUNTIF('C112'!E13,"Aula 5")+COUNTIF('C113'!E13,"Aula 5")+COUNTIF('C121'!E13,"Aula 5")+COUNTIF('C122'!E13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 5")+COUNTIF('C112'!E13,"Aula 5")+COUNTIF('C113'!E13,"Aula 5")+COUNTIF('C121'!E13,"Aula 5")+COUNTIF('C122'!E13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 5")+COUNTIF('C112'!E13,"Aula 5")+COUNTIF('C113'!E13,"Aula 5")+COUNTIF('C121'!E13,"Aula 5")+COUNTIF('C122'!E13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 5")+COUNTIF('C112'!D13,"Aula 5")+COUNTIF('C113'!D13,"Aula 5")+COUNTIF('C121'!D13,"Aula 5")+COUNTIF('C122'!D13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 5")+COUNTIF('C112'!D13,"Aula 5")+COUNTIF('C113'!D13,"Aula 5")+COUNTIF('C121'!D13,"Aula 5")+COUNTIF('C122'!D13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 5")+COUNTIF('C112'!D13,"Aula 5")+COUNTIF('C113'!D13,"Aula 5")+COUNTIF('C121'!D13,"Aula 5")+COUNTIF('C122'!D13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="C166">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 6")+COUNTIF('C112'!E13,"Aula 6")+COUNTIF('C113'!E13,"Aula 6")+COUNTIF('C121'!E13,"Aula 6")+COUNTIF('C122'!E13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 6")+COUNTIF('C112'!E13,"Aula 6")+COUNTIF('C113'!E13,"Aula 6")+COUNTIF('C121'!E13,"Aula 6")+COUNTIF('C122'!E13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 6")+COUNTIF('C112'!E13,"Aula 6")+COUNTIF('C113'!E13,"Aula 6")+COUNTIF('C121'!E13,"Aula 6")+COUNTIF('C122'!E13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 6")+COUNTIF('C112'!D13,"Aula 6")+COUNTIF('C113'!D13,"Aula 6")+COUNTIF('C121'!D13,"Aula 6")+COUNTIF('C122'!D13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 6")+COUNTIF('C112'!D13,"Aula 6")+COUNTIF('C113'!D13,"Aula 6")+COUNTIF('C121'!D13,"Aula 6")+COUNTIF('C122'!D13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 6")+COUNTIF('C112'!D13,"Aula 6")+COUNTIF('C113'!D13,"Aula 6")+COUNTIF('C121'!D13,"Aula 6")+COUNTIF('C122'!D13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="C167">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 7")+COUNTIF('C112'!E13,"Aula 7")+COUNTIF('C113'!E13,"Aula 7")+COUNTIF('C121'!E13,"Aula 7")+COUNTIF('C122'!E13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 7")+COUNTIF('C112'!E13,"Aula 7")+COUNTIF('C113'!E13,"Aula 7")+COUNTIF('C121'!E13,"Aula 7")+COUNTIF('C122'!E13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 7")+COUNTIF('C112'!E13,"Aula 7")+COUNTIF('C113'!E13,"Aula 7")+COUNTIF('C121'!E13,"Aula 7")+COUNTIF('C122'!E13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 7")+COUNTIF('C112'!D13,"Aula 7")+COUNTIF('C113'!D13,"Aula 7")+COUNTIF('C121'!D13,"Aula 7")+COUNTIF('C122'!D13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 7")+COUNTIF('C112'!D13,"Aula 7")+COUNTIF('C113'!D13,"Aula 7")+COUNTIF('C121'!D13,"Aula 7")+COUNTIF('C122'!D13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 7")+COUNTIF('C112'!D13,"Aula 7")+COUNTIF('C113'!D13,"Aula 7")+COUNTIF('C121'!D13,"Aula 7")+COUNTIF('C122'!D13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="C168">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 8")+COUNTIF('C112'!E13,"Aula 8")+COUNTIF('C113'!E13,"Aula 8")+COUNTIF('C121'!E13,"Aula 8")+COUNTIF('C122'!E13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 8")+COUNTIF('C112'!E13,"Aula 8")+COUNTIF('C113'!E13,"Aula 8")+COUNTIF('C121'!E13,"Aula 8")+COUNTIF('C122'!E13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 8")+COUNTIF('C112'!E13,"Aula 8")+COUNTIF('C113'!E13,"Aula 8")+COUNTIF('C121'!E13,"Aula 8")+COUNTIF('C122'!E13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 8")+COUNTIF('C112'!D13,"Aula 8")+COUNTIF('C113'!D13,"Aula 8")+COUNTIF('C121'!D13,"Aula 8")+COUNTIF('C122'!D13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 8")+COUNTIF('C112'!D13,"Aula 8")+COUNTIF('C113'!D13,"Aula 8")+COUNTIF('C121'!D13,"Aula 8")+COUNTIF('C122'!D13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 8")+COUNTIF('C112'!D13,"Aula 8")+COUNTIF('C113'!D13,"Aula 8")+COUNTIF('C121'!D13,"Aula 8")+COUNTIF('C122'!D13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="C169">
-        <f>IF((IF((COUNTIF('C111'!E13,"Aula 9")+COUNTIF('C112'!E13,"Aula 9")+COUNTIF('C113'!E13,"Aula 9")+COUNTIF('C121'!E13,"Aula 9")+COUNTIF('C122'!E13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 9")+COUNTIF('C112'!E13,"Aula 9")+COUNTIF('C113'!E13,"Aula 9")+COUNTIF('C121'!E13,"Aula 9")+COUNTIF('C122'!E13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 9")+COUNTIF('C112'!E13,"Aula 9")+COUNTIF('C113'!E13,"Aula 9")+COUNTIF('C121'!E13,"Aula 9")+COUNTIF('C122'!E13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Aula 9")+COUNTIF('C112'!D13,"Aula 9")+COUNTIF('C113'!D13,"Aula 9")+COUNTIF('C121'!D13,"Aula 9")+COUNTIF('C122'!D13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Aula 9")+COUNTIF('C112'!D13,"Aula 9")+COUNTIF('C113'!D13,"Aula 9")+COUNTIF('C121'!D13,"Aula 9")+COUNTIF('C122'!D13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Aula 9")+COUNTIF('C112'!D13,"Aula 9")+COUNTIF('C113'!D13,"Aula 9")+COUNTIF('C121'!D13,"Aula 9")+COUNTIF('C122'!D13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="C170">
-        <f>IF((IF((COUNTIF('C111'!E13,"Lab")+COUNTIF('C112'!E13,"Lab")+COUNTIF('C113'!E13,"Lab")+COUNTIF('C121'!E13,"Lab")+COUNTIF('C122'!E13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Lab")+COUNTIF('C112'!E13,"Lab")+COUNTIF('C113'!E13,"Lab")+COUNTIF('C121'!E13,"Lab")+COUNTIF('C122'!E13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Lab")+COUNTIF('C112'!E13,"Lab")+COUNTIF('C113'!E13,"Lab")+COUNTIF('C121'!E13,"Lab")+COUNTIF('C122'!E13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D13,"Lab")+COUNTIF('C112'!D13,"Lab")+COUNTIF('C113'!D13,"Lab")+COUNTIF('C121'!D13,"Lab")+COUNTIF('C122'!D13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D13,"Lab")+COUNTIF('C112'!D13,"Lab")+COUNTIF('C113'!D13,"Lab")+COUNTIF('C121'!D13,"Lab")+COUNTIF('C122'!D13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D13,"Lab")+COUNTIF('C112'!D13,"Lab")+COUNTIF('C113'!D13,"Lab")+COUNTIF('C121'!D13,"Lab")+COUNTIF('C122'!D13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="C171">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 1")+COUNTIF('C112'!E15,"Aula 1")+COUNTIF('C113'!E15,"Aula 1")+COUNTIF('C121'!E15,"Aula 1")+COUNTIF('C122'!E15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 1")+COUNTIF('C112'!E15,"Aula 1")+COUNTIF('C113'!E15,"Aula 1")+COUNTIF('C121'!E15,"Aula 1")+COUNTIF('C122'!E15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 1")+COUNTIF('C112'!E15,"Aula 1")+COUNTIF('C113'!E15,"Aula 1")+COUNTIF('C121'!E15,"Aula 1")+COUNTIF('C122'!E15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 1")+COUNTIF('C112'!D15,"Aula 1")+COUNTIF('C113'!D15,"Aula 1")+COUNTIF('C121'!D15,"Aula 1")+COUNTIF('C122'!D15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 1")+COUNTIF('C112'!D15,"Aula 1")+COUNTIF('C113'!D15,"Aula 1")+COUNTIF('C121'!D15,"Aula 1")+COUNTIF('C122'!D15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 1")+COUNTIF('C112'!D15,"Aula 1")+COUNTIF('C113'!D15,"Aula 1")+COUNTIF('C121'!D15,"Aula 1")+COUNTIF('C122'!D15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="C172">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 2")+COUNTIF('C112'!E15,"Aula 2")+COUNTIF('C113'!E15,"Aula 2")+COUNTIF('C121'!E15,"Aula 2")+COUNTIF('C122'!E15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 2")+COUNTIF('C112'!E15,"Aula 2")+COUNTIF('C113'!E15,"Aula 2")+COUNTIF('C121'!E15,"Aula 2")+COUNTIF('C122'!E15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 2")+COUNTIF('C112'!E15,"Aula 2")+COUNTIF('C113'!E15,"Aula 2")+COUNTIF('C121'!E15,"Aula 2")+COUNTIF('C122'!E15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 2")+COUNTIF('C112'!D15,"Aula 2")+COUNTIF('C113'!D15,"Aula 2")+COUNTIF('C121'!D15,"Aula 2")+COUNTIF('C122'!D15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 2")+COUNTIF('C112'!D15,"Aula 2")+COUNTIF('C113'!D15,"Aula 2")+COUNTIF('C121'!D15,"Aula 2")+COUNTIF('C122'!D15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 2")+COUNTIF('C112'!D15,"Aula 2")+COUNTIF('C113'!D15,"Aula 2")+COUNTIF('C121'!D15,"Aula 2")+COUNTIF('C122'!D15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="C173">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 3")+COUNTIF('C112'!E15,"Aula 3")+COUNTIF('C113'!E15,"Aula 3")+COUNTIF('C121'!E15,"Aula 3")+COUNTIF('C122'!E15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 3")+COUNTIF('C112'!E15,"Aula 3")+COUNTIF('C113'!E15,"Aula 3")+COUNTIF('C121'!E15,"Aula 3")+COUNTIF('C122'!E15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 3")+COUNTIF('C112'!E15,"Aula 3")+COUNTIF('C113'!E15,"Aula 3")+COUNTIF('C121'!E15,"Aula 3")+COUNTIF('C122'!E15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 3")+COUNTIF('C112'!D15,"Aula 3")+COUNTIF('C113'!D15,"Aula 3")+COUNTIF('C121'!D15,"Aula 3")+COUNTIF('C122'!D15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 3")+COUNTIF('C112'!D15,"Aula 3")+COUNTIF('C113'!D15,"Aula 3")+COUNTIF('C121'!D15,"Aula 3")+COUNTIF('C122'!D15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 3")+COUNTIF('C112'!D15,"Aula 3")+COUNTIF('C113'!D15,"Aula 3")+COUNTIF('C121'!D15,"Aula 3")+COUNTIF('C122'!D15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="C174">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 4")+COUNTIF('C112'!E15,"Aula 4")+COUNTIF('C113'!E15,"Aula 4")+COUNTIF('C121'!E15,"Aula 4")+COUNTIF('C122'!E15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 4")+COUNTIF('C112'!E15,"Aula 4")+COUNTIF('C113'!E15,"Aula 4")+COUNTIF('C121'!E15,"Aula 4")+COUNTIF('C122'!E15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 4")+COUNTIF('C112'!E15,"Aula 4")+COUNTIF('C113'!E15,"Aula 4")+COUNTIF('C121'!E15,"Aula 4")+COUNTIF('C122'!E15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 4")+COUNTIF('C112'!D15,"Aula 4")+COUNTIF('C113'!D15,"Aula 4")+COUNTIF('C121'!D15,"Aula 4")+COUNTIF('C122'!D15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 4")+COUNTIF('C112'!D15,"Aula 4")+COUNTIF('C113'!D15,"Aula 4")+COUNTIF('C121'!D15,"Aula 4")+COUNTIF('C122'!D15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 4")+COUNTIF('C112'!D15,"Aula 4")+COUNTIF('C113'!D15,"Aula 4")+COUNTIF('C121'!D15,"Aula 4")+COUNTIF('C122'!D15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="C175">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 5")+COUNTIF('C112'!E15,"Aula 5")+COUNTIF('C113'!E15,"Aula 5")+COUNTIF('C121'!E15,"Aula 5")+COUNTIF('C122'!E15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 5")+COUNTIF('C112'!E15,"Aula 5")+COUNTIF('C113'!E15,"Aula 5")+COUNTIF('C121'!E15,"Aula 5")+COUNTIF('C122'!E15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 5")+COUNTIF('C112'!E15,"Aula 5")+COUNTIF('C113'!E15,"Aula 5")+COUNTIF('C121'!E15,"Aula 5")+COUNTIF('C122'!E15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 5")+COUNTIF('C112'!D15,"Aula 5")+COUNTIF('C113'!D15,"Aula 5")+COUNTIF('C121'!D15,"Aula 5")+COUNTIF('C122'!D15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 5")+COUNTIF('C112'!D15,"Aula 5")+COUNTIF('C113'!D15,"Aula 5")+COUNTIF('C121'!D15,"Aula 5")+COUNTIF('C122'!D15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 5")+COUNTIF('C112'!D15,"Aula 5")+COUNTIF('C113'!D15,"Aula 5")+COUNTIF('C121'!D15,"Aula 5")+COUNTIF('C122'!D15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="C176">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 6")+COUNTIF('C112'!E15,"Aula 6")+COUNTIF('C113'!E15,"Aula 6")+COUNTIF('C121'!E15,"Aula 6")+COUNTIF('C122'!E15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 6")+COUNTIF('C112'!E15,"Aula 6")+COUNTIF('C113'!E15,"Aula 6")+COUNTIF('C121'!E15,"Aula 6")+COUNTIF('C122'!E15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 6")+COUNTIF('C112'!E15,"Aula 6")+COUNTIF('C113'!E15,"Aula 6")+COUNTIF('C121'!E15,"Aula 6")+COUNTIF('C122'!E15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 6")+COUNTIF('C112'!D15,"Aula 6")+COUNTIF('C113'!D15,"Aula 6")+COUNTIF('C121'!D15,"Aula 6")+COUNTIF('C122'!D15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 6")+COUNTIF('C112'!D15,"Aula 6")+COUNTIF('C113'!D15,"Aula 6")+COUNTIF('C121'!D15,"Aula 6")+COUNTIF('C122'!D15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 6")+COUNTIF('C112'!D15,"Aula 6")+COUNTIF('C113'!D15,"Aula 6")+COUNTIF('C121'!D15,"Aula 6")+COUNTIF('C122'!D15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="C177">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 7")+COUNTIF('C112'!E15,"Aula 7")+COUNTIF('C113'!E15,"Aula 7")+COUNTIF('C121'!E15,"Aula 7")+COUNTIF('C122'!E15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 7")+COUNTIF('C112'!E15,"Aula 7")+COUNTIF('C113'!E15,"Aula 7")+COUNTIF('C121'!E15,"Aula 7")+COUNTIF('C122'!E15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 7")+COUNTIF('C112'!E15,"Aula 7")+COUNTIF('C113'!E15,"Aula 7")+COUNTIF('C121'!E15,"Aula 7")+COUNTIF('C122'!E15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 7")+COUNTIF('C112'!D15,"Aula 7")+COUNTIF('C113'!D15,"Aula 7")+COUNTIF('C121'!D15,"Aula 7")+COUNTIF('C122'!D15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 7")+COUNTIF('C112'!D15,"Aula 7")+COUNTIF('C113'!D15,"Aula 7")+COUNTIF('C121'!D15,"Aula 7")+COUNTIF('C122'!D15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 7")+COUNTIF('C112'!D15,"Aula 7")+COUNTIF('C113'!D15,"Aula 7")+COUNTIF('C121'!D15,"Aula 7")+COUNTIF('C122'!D15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="C178">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 8")+COUNTIF('C112'!E15,"Aula 8")+COUNTIF('C113'!E15,"Aula 8")+COUNTIF('C121'!E15,"Aula 8")+COUNTIF('C122'!E15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 8")+COUNTIF('C112'!E15,"Aula 8")+COUNTIF('C113'!E15,"Aula 8")+COUNTIF('C121'!E15,"Aula 8")+COUNTIF('C122'!E15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 8")+COUNTIF('C112'!E15,"Aula 8")+COUNTIF('C113'!E15,"Aula 8")+COUNTIF('C121'!E15,"Aula 8")+COUNTIF('C122'!E15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 8")+COUNTIF('C112'!D15,"Aula 8")+COUNTIF('C113'!D15,"Aula 8")+COUNTIF('C121'!D15,"Aula 8")+COUNTIF('C122'!D15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 8")+COUNTIF('C112'!D15,"Aula 8")+COUNTIF('C113'!D15,"Aula 8")+COUNTIF('C121'!D15,"Aula 8")+COUNTIF('C122'!D15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 8")+COUNTIF('C112'!D15,"Aula 8")+COUNTIF('C113'!D15,"Aula 8")+COUNTIF('C121'!D15,"Aula 8")+COUNTIF('C122'!D15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="C179">
-        <f>IF((IF((COUNTIF('C111'!E15,"Aula 9")+COUNTIF('C112'!E15,"Aula 9")+COUNTIF('C113'!E15,"Aula 9")+COUNTIF('C121'!E15,"Aula 9")+COUNTIF('C122'!E15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 9")+COUNTIF('C112'!E15,"Aula 9")+COUNTIF('C113'!E15,"Aula 9")+COUNTIF('C121'!E15,"Aula 9")+COUNTIF('C122'!E15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 9")+COUNTIF('C112'!E15,"Aula 9")+COUNTIF('C113'!E15,"Aula 9")+COUNTIF('C121'!E15,"Aula 9")+COUNTIF('C122'!E15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Aula 9")+COUNTIF('C112'!D15,"Aula 9")+COUNTIF('C113'!D15,"Aula 9")+COUNTIF('C121'!D15,"Aula 9")+COUNTIF('C122'!D15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Aula 9")+COUNTIF('C112'!D15,"Aula 9")+COUNTIF('C113'!D15,"Aula 9")+COUNTIF('C121'!D15,"Aula 9")+COUNTIF('C122'!D15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Aula 9")+COUNTIF('C112'!D15,"Aula 9")+COUNTIF('C113'!D15,"Aula 9")+COUNTIF('C121'!D15,"Aula 9")+COUNTIF('C122'!D15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="C180">
-        <f>IF((IF((COUNTIF('C111'!E15,"Lab")+COUNTIF('C112'!E15,"Lab")+COUNTIF('C113'!E15,"Lab")+COUNTIF('C121'!E15,"Lab")+COUNTIF('C122'!E15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Lab")+COUNTIF('C112'!E15,"Lab")+COUNTIF('C113'!E15,"Lab")+COUNTIF('C121'!E15,"Lab")+COUNTIF('C122'!E15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Lab")+COUNTIF('C112'!E15,"Lab")+COUNTIF('C113'!E15,"Lab")+COUNTIF('C121'!E15,"Lab")+COUNTIF('C122'!E15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!D15,"Lab")+COUNTIF('C112'!D15,"Lab")+COUNTIF('C113'!D15,"Lab")+COUNTIF('C121'!D15,"Lab")+COUNTIF('C122'!D15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!D15,"Lab")+COUNTIF('C112'!D15,"Lab")+COUNTIF('C113'!D15,"Lab")+COUNTIF('C121'!D15,"Lab")+COUNTIF('C122'!D15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!D15,"Lab")+COUNTIF('C112'!D15,"Lab")+COUNTIF('C113'!D15,"Lab")+COUNTIF('C121'!D15,"Lab")+COUNTIF('C122'!D15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="C181">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 1")+COUNTIF('C112'!F5,"Aula 1")+COUNTIF('C113'!F5,"Aula 1")+COUNTIF('C121'!F5,"Aula 1")+COUNTIF('C122'!F5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 1")+COUNTIF('C112'!F5,"Aula 1")+COUNTIF('C113'!F5,"Aula 1")+COUNTIF('C121'!F5,"Aula 1")+COUNTIF('C122'!F5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 1")+COUNTIF('C112'!F5,"Aula 1")+COUNTIF('C113'!F5,"Aula 1")+COUNTIF('C121'!F5,"Aula 1")+COUNTIF('C122'!F5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 1")+COUNTIF('C112'!E5,"Aula 1")+COUNTIF('C113'!E5,"Aula 1")+COUNTIF('C121'!E5,"Aula 1")+COUNTIF('C122'!E5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 1")+COUNTIF('C112'!E5,"Aula 1")+COUNTIF('C113'!E5,"Aula 1")+COUNTIF('C121'!E5,"Aula 1")+COUNTIF('C122'!E5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 1")+COUNTIF('C112'!E5,"Aula 1")+COUNTIF('C113'!E5,"Aula 1")+COUNTIF('C121'!E5,"Aula 1")+COUNTIF('C122'!E5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="C182">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 2")+COUNTIF('C112'!F5,"Aula 2")+COUNTIF('C113'!F5,"Aula 2")+COUNTIF('C121'!F5,"Aula 2")+COUNTIF('C122'!F5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 2")+COUNTIF('C112'!F5,"Aula 2")+COUNTIF('C113'!F5,"Aula 2")+COUNTIF('C121'!F5,"Aula 2")+COUNTIF('C122'!F5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 2")+COUNTIF('C112'!F5,"Aula 2")+COUNTIF('C113'!F5,"Aula 2")+COUNTIF('C121'!F5,"Aula 2")+COUNTIF('C122'!F5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 2")+COUNTIF('C112'!E5,"Aula 2")+COUNTIF('C113'!E5,"Aula 2")+COUNTIF('C121'!E5,"Aula 2")+COUNTIF('C122'!E5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 2")+COUNTIF('C112'!E5,"Aula 2")+COUNTIF('C113'!E5,"Aula 2")+COUNTIF('C121'!E5,"Aula 2")+COUNTIF('C122'!E5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 2")+COUNTIF('C112'!E5,"Aula 2")+COUNTIF('C113'!E5,"Aula 2")+COUNTIF('C121'!E5,"Aula 2")+COUNTIF('C122'!E5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="C183">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 3")+COUNTIF('C112'!F5,"Aula 3")+COUNTIF('C113'!F5,"Aula 3")+COUNTIF('C121'!F5,"Aula 3")+COUNTIF('C122'!F5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 3")+COUNTIF('C112'!F5,"Aula 3")+COUNTIF('C113'!F5,"Aula 3")+COUNTIF('C121'!F5,"Aula 3")+COUNTIF('C122'!F5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 3")+COUNTIF('C112'!F5,"Aula 3")+COUNTIF('C113'!F5,"Aula 3")+COUNTIF('C121'!F5,"Aula 3")+COUNTIF('C122'!F5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 3")+COUNTIF('C112'!E5,"Aula 3")+COUNTIF('C113'!E5,"Aula 3")+COUNTIF('C121'!E5,"Aula 3")+COUNTIF('C122'!E5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 3")+COUNTIF('C112'!E5,"Aula 3")+COUNTIF('C113'!E5,"Aula 3")+COUNTIF('C121'!E5,"Aula 3")+COUNTIF('C122'!E5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 3")+COUNTIF('C112'!E5,"Aula 3")+COUNTIF('C113'!E5,"Aula 3")+COUNTIF('C121'!E5,"Aula 3")+COUNTIF('C122'!E5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="C184">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 4")+COUNTIF('C112'!F5,"Aula 4")+COUNTIF('C113'!F5,"Aula 4")+COUNTIF('C121'!F5,"Aula 4")+COUNTIF('C122'!F5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 4")+COUNTIF('C112'!F5,"Aula 4")+COUNTIF('C113'!F5,"Aula 4")+COUNTIF('C121'!F5,"Aula 4")+COUNTIF('C122'!F5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 4")+COUNTIF('C112'!F5,"Aula 4")+COUNTIF('C113'!F5,"Aula 4")+COUNTIF('C121'!F5,"Aula 4")+COUNTIF('C122'!F5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 4")+COUNTIF('C112'!E5,"Aula 4")+COUNTIF('C113'!E5,"Aula 4")+COUNTIF('C121'!E5,"Aula 4")+COUNTIF('C122'!E5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 4")+COUNTIF('C112'!E5,"Aula 4")+COUNTIF('C113'!E5,"Aula 4")+COUNTIF('C121'!E5,"Aula 4")+COUNTIF('C122'!E5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 4")+COUNTIF('C112'!E5,"Aula 4")+COUNTIF('C113'!E5,"Aula 4")+COUNTIF('C121'!E5,"Aula 4")+COUNTIF('C122'!E5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="C185">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 5")+COUNTIF('C112'!F5,"Aula 5")+COUNTIF('C113'!F5,"Aula 5")+COUNTIF('C121'!F5,"Aula 5")+COUNTIF('C122'!F5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 5")+COUNTIF('C112'!F5,"Aula 5")+COUNTIF('C113'!F5,"Aula 5")+COUNTIF('C121'!F5,"Aula 5")+COUNTIF('C122'!F5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 5")+COUNTIF('C112'!F5,"Aula 5")+COUNTIF('C113'!F5,"Aula 5")+COUNTIF('C121'!F5,"Aula 5")+COUNTIF('C122'!F5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 5")+COUNTIF('C112'!E5,"Aula 5")+COUNTIF('C113'!E5,"Aula 5")+COUNTIF('C121'!E5,"Aula 5")+COUNTIF('C122'!E5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 5")+COUNTIF('C112'!E5,"Aula 5")+COUNTIF('C113'!E5,"Aula 5")+COUNTIF('C121'!E5,"Aula 5")+COUNTIF('C122'!E5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 5")+COUNTIF('C112'!E5,"Aula 5")+COUNTIF('C113'!E5,"Aula 5")+COUNTIF('C121'!E5,"Aula 5")+COUNTIF('C122'!E5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="C186">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 6")+COUNTIF('C112'!F5,"Aula 6")+COUNTIF('C113'!F5,"Aula 6")+COUNTIF('C121'!F5,"Aula 6")+COUNTIF('C122'!F5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 6")+COUNTIF('C112'!F5,"Aula 6")+COUNTIF('C113'!F5,"Aula 6")+COUNTIF('C121'!F5,"Aula 6")+COUNTIF('C122'!F5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 6")+COUNTIF('C112'!F5,"Aula 6")+COUNTIF('C113'!F5,"Aula 6")+COUNTIF('C121'!F5,"Aula 6")+COUNTIF('C122'!F5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 6")+COUNTIF('C112'!E5,"Aula 6")+COUNTIF('C113'!E5,"Aula 6")+COUNTIF('C121'!E5,"Aula 6")+COUNTIF('C122'!E5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 6")+COUNTIF('C112'!E5,"Aula 6")+COUNTIF('C113'!E5,"Aula 6")+COUNTIF('C121'!E5,"Aula 6")+COUNTIF('C122'!E5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 6")+COUNTIF('C112'!E5,"Aula 6")+COUNTIF('C113'!E5,"Aula 6")+COUNTIF('C121'!E5,"Aula 6")+COUNTIF('C122'!E5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="C187">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 7")+COUNTIF('C112'!F5,"Aula 7")+COUNTIF('C113'!F5,"Aula 7")+COUNTIF('C121'!F5,"Aula 7")+COUNTIF('C122'!F5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 7")+COUNTIF('C112'!F5,"Aula 7")+COUNTIF('C113'!F5,"Aula 7")+COUNTIF('C121'!F5,"Aula 7")+COUNTIF('C122'!F5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 7")+COUNTIF('C112'!F5,"Aula 7")+COUNTIF('C113'!F5,"Aula 7")+COUNTIF('C121'!F5,"Aula 7")+COUNTIF('C122'!F5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 7")+COUNTIF('C112'!E5,"Aula 7")+COUNTIF('C113'!E5,"Aula 7")+COUNTIF('C121'!E5,"Aula 7")+COUNTIF('C122'!E5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 7")+COUNTIF('C112'!E5,"Aula 7")+COUNTIF('C113'!E5,"Aula 7")+COUNTIF('C121'!E5,"Aula 7")+COUNTIF('C122'!E5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 7")+COUNTIF('C112'!E5,"Aula 7")+COUNTIF('C113'!E5,"Aula 7")+COUNTIF('C121'!E5,"Aula 7")+COUNTIF('C122'!E5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="C188">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 8")+COUNTIF('C112'!F5,"Aula 8")+COUNTIF('C113'!F5,"Aula 8")+COUNTIF('C121'!F5,"Aula 8")+COUNTIF('C122'!F5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 8")+COUNTIF('C112'!F5,"Aula 8")+COUNTIF('C113'!F5,"Aula 8")+COUNTIF('C121'!F5,"Aula 8")+COUNTIF('C122'!F5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 8")+COUNTIF('C112'!F5,"Aula 8")+COUNTIF('C113'!F5,"Aula 8")+COUNTIF('C121'!F5,"Aula 8")+COUNTIF('C122'!F5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 8")+COUNTIF('C112'!E5,"Aula 8")+COUNTIF('C113'!E5,"Aula 8")+COUNTIF('C121'!E5,"Aula 8")+COUNTIF('C122'!E5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 8")+COUNTIF('C112'!E5,"Aula 8")+COUNTIF('C113'!E5,"Aula 8")+COUNTIF('C121'!E5,"Aula 8")+COUNTIF('C122'!E5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 8")+COUNTIF('C112'!E5,"Aula 8")+COUNTIF('C113'!E5,"Aula 8")+COUNTIF('C121'!E5,"Aula 8")+COUNTIF('C122'!E5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="C189">
-        <f>IF((IF((COUNTIF('C111'!F5,"Aula 9")+COUNTIF('C112'!F5,"Aula 9")+COUNTIF('C113'!F5,"Aula 9")+COUNTIF('C121'!F5,"Aula 9")+COUNTIF('C122'!F5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 9")+COUNTIF('C112'!F5,"Aula 9")+COUNTIF('C113'!F5,"Aula 9")+COUNTIF('C121'!F5,"Aula 9")+COUNTIF('C122'!F5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 9")+COUNTIF('C112'!F5,"Aula 9")+COUNTIF('C113'!F5,"Aula 9")+COUNTIF('C121'!F5,"Aula 9")+COUNTIF('C122'!F5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Aula 9")+COUNTIF('C112'!E5,"Aula 9")+COUNTIF('C113'!E5,"Aula 9")+COUNTIF('C121'!E5,"Aula 9")+COUNTIF('C122'!E5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Aula 9")+COUNTIF('C112'!E5,"Aula 9")+COUNTIF('C113'!E5,"Aula 9")+COUNTIF('C121'!E5,"Aula 9")+COUNTIF('C122'!E5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Aula 9")+COUNTIF('C112'!E5,"Aula 9")+COUNTIF('C113'!E5,"Aula 9")+COUNTIF('C121'!E5,"Aula 9")+COUNTIF('C122'!E5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="C190">
-        <f>IF((IF((COUNTIF('C111'!F5,"Lab")+COUNTIF('C112'!F5,"Lab")+COUNTIF('C113'!F5,"Lab")+COUNTIF('C121'!F5,"Lab")+COUNTIF('C122'!F5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Lab")+COUNTIF('C112'!F5,"Lab")+COUNTIF('C113'!F5,"Lab")+COUNTIF('C121'!F5,"Lab")+COUNTIF('C122'!F5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Lab")+COUNTIF('C112'!F5,"Lab")+COUNTIF('C113'!F5,"Lab")+COUNTIF('C121'!F5,"Lab")+COUNTIF('C122'!F5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E5,"Lab")+COUNTIF('C112'!E5,"Lab")+COUNTIF('C113'!E5,"Lab")+COUNTIF('C121'!E5,"Lab")+COUNTIF('C122'!E5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E5,"Lab")+COUNTIF('C112'!E5,"Lab")+COUNTIF('C113'!E5,"Lab")+COUNTIF('C121'!E5,"Lab")+COUNTIF('C122'!E5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E5,"Lab")+COUNTIF('C112'!E5,"Lab")+COUNTIF('C113'!E5,"Lab")+COUNTIF('C121'!E5,"Lab")+COUNTIF('C122'!E5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="C191">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 1")+COUNTIF('C112'!F7,"Aula 1")+COUNTIF('C113'!F7,"Aula 1")+COUNTIF('C121'!F7,"Aula 1")+COUNTIF('C122'!F7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 1")+COUNTIF('C112'!F7,"Aula 1")+COUNTIF('C113'!F7,"Aula 1")+COUNTIF('C121'!F7,"Aula 1")+COUNTIF('C122'!F7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 1")+COUNTIF('C112'!F7,"Aula 1")+COUNTIF('C113'!F7,"Aula 1")+COUNTIF('C121'!F7,"Aula 1")+COUNTIF('C122'!F7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 1")+COUNTIF('C112'!E7,"Aula 1")+COUNTIF('C113'!E7,"Aula 1")+COUNTIF('C121'!E7,"Aula 1")+COUNTIF('C122'!E7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 1")+COUNTIF('C112'!E7,"Aula 1")+COUNTIF('C113'!E7,"Aula 1")+COUNTIF('C121'!E7,"Aula 1")+COUNTIF('C122'!E7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 1")+COUNTIF('C112'!E7,"Aula 1")+COUNTIF('C113'!E7,"Aula 1")+COUNTIF('C121'!E7,"Aula 1")+COUNTIF('C122'!E7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="C192">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 2")+COUNTIF('C112'!F7,"Aula 2")+COUNTIF('C113'!F7,"Aula 2")+COUNTIF('C121'!F7,"Aula 2")+COUNTIF('C122'!F7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 2")+COUNTIF('C112'!F7,"Aula 2")+COUNTIF('C113'!F7,"Aula 2")+COUNTIF('C121'!F7,"Aula 2")+COUNTIF('C122'!F7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 2")+COUNTIF('C112'!F7,"Aula 2")+COUNTIF('C113'!F7,"Aula 2")+COUNTIF('C121'!F7,"Aula 2")+COUNTIF('C122'!F7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 2")+COUNTIF('C112'!E7,"Aula 2")+COUNTIF('C113'!E7,"Aula 2")+COUNTIF('C121'!E7,"Aula 2")+COUNTIF('C122'!E7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 2")+COUNTIF('C112'!E7,"Aula 2")+COUNTIF('C113'!E7,"Aula 2")+COUNTIF('C121'!E7,"Aula 2")+COUNTIF('C122'!E7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 2")+COUNTIF('C112'!E7,"Aula 2")+COUNTIF('C113'!E7,"Aula 2")+COUNTIF('C121'!E7,"Aula 2")+COUNTIF('C122'!E7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="C193">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 3")+COUNTIF('C112'!F7,"Aula 3")+COUNTIF('C113'!F7,"Aula 3")+COUNTIF('C121'!F7,"Aula 3")+COUNTIF('C122'!F7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 3")+COUNTIF('C112'!F7,"Aula 3")+COUNTIF('C113'!F7,"Aula 3")+COUNTIF('C121'!F7,"Aula 3")+COUNTIF('C122'!F7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 3")+COUNTIF('C112'!F7,"Aula 3")+COUNTIF('C113'!F7,"Aula 3")+COUNTIF('C121'!F7,"Aula 3")+COUNTIF('C122'!F7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 3")+COUNTIF('C112'!E7,"Aula 3")+COUNTIF('C113'!E7,"Aula 3")+COUNTIF('C121'!E7,"Aula 3")+COUNTIF('C122'!E7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 3")+COUNTIF('C112'!E7,"Aula 3")+COUNTIF('C113'!E7,"Aula 3")+COUNTIF('C121'!E7,"Aula 3")+COUNTIF('C122'!E7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 3")+COUNTIF('C112'!E7,"Aula 3")+COUNTIF('C113'!E7,"Aula 3")+COUNTIF('C121'!E7,"Aula 3")+COUNTIF('C122'!E7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="C194">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 4")+COUNTIF('C112'!F7,"Aula 4")+COUNTIF('C113'!F7,"Aula 4")+COUNTIF('C121'!F7,"Aula 4")+COUNTIF('C122'!F7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 4")+COUNTIF('C112'!F7,"Aula 4")+COUNTIF('C113'!F7,"Aula 4")+COUNTIF('C121'!F7,"Aula 4")+COUNTIF('C122'!F7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 4")+COUNTIF('C112'!F7,"Aula 4")+COUNTIF('C113'!F7,"Aula 4")+COUNTIF('C121'!F7,"Aula 4")+COUNTIF('C122'!F7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 4")+COUNTIF('C112'!E7,"Aula 4")+COUNTIF('C113'!E7,"Aula 4")+COUNTIF('C121'!E7,"Aula 4")+COUNTIF('C122'!E7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 4")+COUNTIF('C112'!E7,"Aula 4")+COUNTIF('C113'!E7,"Aula 4")+COUNTIF('C121'!E7,"Aula 4")+COUNTIF('C122'!E7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 4")+COUNTIF('C112'!E7,"Aula 4")+COUNTIF('C113'!E7,"Aula 4")+COUNTIF('C121'!E7,"Aula 4")+COUNTIF('C122'!E7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="C195">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 5")+COUNTIF('C112'!F7,"Aula 5")+COUNTIF('C113'!F7,"Aula 5")+COUNTIF('C121'!F7,"Aula 5")+COUNTIF('C122'!F7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 5")+COUNTIF('C112'!F7,"Aula 5")+COUNTIF('C113'!F7,"Aula 5")+COUNTIF('C121'!F7,"Aula 5")+COUNTIF('C122'!F7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 5")+COUNTIF('C112'!F7,"Aula 5")+COUNTIF('C113'!F7,"Aula 5")+COUNTIF('C121'!F7,"Aula 5")+COUNTIF('C122'!F7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 5")+COUNTIF('C112'!E7,"Aula 5")+COUNTIF('C113'!E7,"Aula 5")+COUNTIF('C121'!E7,"Aula 5")+COUNTIF('C122'!E7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 5")+COUNTIF('C112'!E7,"Aula 5")+COUNTIF('C113'!E7,"Aula 5")+COUNTIF('C121'!E7,"Aula 5")+COUNTIF('C122'!E7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 5")+COUNTIF('C112'!E7,"Aula 5")+COUNTIF('C113'!E7,"Aula 5")+COUNTIF('C121'!E7,"Aula 5")+COUNTIF('C122'!E7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="C196">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 6")+COUNTIF('C112'!F7,"Aula 6")+COUNTIF('C113'!F7,"Aula 6")+COUNTIF('C121'!F7,"Aula 6")+COUNTIF('C122'!F7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 6")+COUNTIF('C112'!F7,"Aula 6")+COUNTIF('C113'!F7,"Aula 6")+COUNTIF('C121'!F7,"Aula 6")+COUNTIF('C122'!F7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 6")+COUNTIF('C112'!F7,"Aula 6")+COUNTIF('C113'!F7,"Aula 6")+COUNTIF('C121'!F7,"Aula 6")+COUNTIF('C122'!F7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 6")+COUNTIF('C112'!E7,"Aula 6")+COUNTIF('C113'!E7,"Aula 6")+COUNTIF('C121'!E7,"Aula 6")+COUNTIF('C122'!E7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 6")+COUNTIF('C112'!E7,"Aula 6")+COUNTIF('C113'!E7,"Aula 6")+COUNTIF('C121'!E7,"Aula 6")+COUNTIF('C122'!E7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 6")+COUNTIF('C112'!E7,"Aula 6")+COUNTIF('C113'!E7,"Aula 6")+COUNTIF('C121'!E7,"Aula 6")+COUNTIF('C122'!E7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="C197">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 7")+COUNTIF('C112'!F7,"Aula 7")+COUNTIF('C113'!F7,"Aula 7")+COUNTIF('C121'!F7,"Aula 7")+COUNTIF('C122'!F7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 7")+COUNTIF('C112'!F7,"Aula 7")+COUNTIF('C113'!F7,"Aula 7")+COUNTIF('C121'!F7,"Aula 7")+COUNTIF('C122'!F7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 7")+COUNTIF('C112'!F7,"Aula 7")+COUNTIF('C113'!F7,"Aula 7")+COUNTIF('C121'!F7,"Aula 7")+COUNTIF('C122'!F7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 7")+COUNTIF('C112'!E7,"Aula 7")+COUNTIF('C113'!E7,"Aula 7")+COUNTIF('C121'!E7,"Aula 7")+COUNTIF('C122'!E7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 7")+COUNTIF('C112'!E7,"Aula 7")+COUNTIF('C113'!E7,"Aula 7")+COUNTIF('C121'!E7,"Aula 7")+COUNTIF('C122'!E7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 7")+COUNTIF('C112'!E7,"Aula 7")+COUNTIF('C113'!E7,"Aula 7")+COUNTIF('C121'!E7,"Aula 7")+COUNTIF('C122'!E7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="C198">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 8")+COUNTIF('C112'!F7,"Aula 8")+COUNTIF('C113'!F7,"Aula 8")+COUNTIF('C121'!F7,"Aula 8")+COUNTIF('C122'!F7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 8")+COUNTIF('C112'!F7,"Aula 8")+COUNTIF('C113'!F7,"Aula 8")+COUNTIF('C121'!F7,"Aula 8")+COUNTIF('C122'!F7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 8")+COUNTIF('C112'!F7,"Aula 8")+COUNTIF('C113'!F7,"Aula 8")+COUNTIF('C121'!F7,"Aula 8")+COUNTIF('C122'!F7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 8")+COUNTIF('C112'!E7,"Aula 8")+COUNTIF('C113'!E7,"Aula 8")+COUNTIF('C121'!E7,"Aula 8")+COUNTIF('C122'!E7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 8")+COUNTIF('C112'!E7,"Aula 8")+COUNTIF('C113'!E7,"Aula 8")+COUNTIF('C121'!E7,"Aula 8")+COUNTIF('C122'!E7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 8")+COUNTIF('C112'!E7,"Aula 8")+COUNTIF('C113'!E7,"Aula 8")+COUNTIF('C121'!E7,"Aula 8")+COUNTIF('C122'!E7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="C199">
-        <f>IF((IF((COUNTIF('C111'!F7,"Aula 9")+COUNTIF('C112'!F7,"Aula 9")+COUNTIF('C113'!F7,"Aula 9")+COUNTIF('C121'!F7,"Aula 9")+COUNTIF('C122'!F7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 9")+COUNTIF('C112'!F7,"Aula 9")+COUNTIF('C113'!F7,"Aula 9")+COUNTIF('C121'!F7,"Aula 9")+COUNTIF('C122'!F7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 9")+COUNTIF('C112'!F7,"Aula 9")+COUNTIF('C113'!F7,"Aula 9")+COUNTIF('C121'!F7,"Aula 9")+COUNTIF('C122'!F7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Aula 9")+COUNTIF('C112'!E7,"Aula 9")+COUNTIF('C113'!E7,"Aula 9")+COUNTIF('C121'!E7,"Aula 9")+COUNTIF('C122'!E7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Aula 9")+COUNTIF('C112'!E7,"Aula 9")+COUNTIF('C113'!E7,"Aula 9")+COUNTIF('C121'!E7,"Aula 9")+COUNTIF('C122'!E7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Aula 9")+COUNTIF('C112'!E7,"Aula 9")+COUNTIF('C113'!E7,"Aula 9")+COUNTIF('C121'!E7,"Aula 9")+COUNTIF('C122'!E7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="C200">
-        <f>IF((IF((COUNTIF('C111'!F7,"Lab")+COUNTIF('C112'!F7,"Lab")+COUNTIF('C113'!F7,"Lab")+COUNTIF('C121'!F7,"Lab")+COUNTIF('C122'!F7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Lab")+COUNTIF('C112'!F7,"Lab")+COUNTIF('C113'!F7,"Lab")+COUNTIF('C121'!F7,"Lab")+COUNTIF('C122'!F7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Lab")+COUNTIF('C112'!F7,"Lab")+COUNTIF('C113'!F7,"Lab")+COUNTIF('C121'!F7,"Lab")+COUNTIF('C122'!F7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E7,"Lab")+COUNTIF('C112'!E7,"Lab")+COUNTIF('C113'!E7,"Lab")+COUNTIF('C121'!E7,"Lab")+COUNTIF('C122'!E7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E7,"Lab")+COUNTIF('C112'!E7,"Lab")+COUNTIF('C113'!E7,"Lab")+COUNTIF('C121'!E7,"Lab")+COUNTIF('C122'!E7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E7,"Lab")+COUNTIF('C112'!E7,"Lab")+COUNTIF('C113'!E7,"Lab")+COUNTIF('C121'!E7,"Lab")+COUNTIF('C122'!E7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="C201">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 1")+COUNTIF('C112'!F9,"Aula 1")+COUNTIF('C113'!F9,"Aula 1")+COUNTIF('C121'!F9,"Aula 1")+COUNTIF('C122'!F9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 1")+COUNTIF('C112'!F9,"Aula 1")+COUNTIF('C113'!F9,"Aula 1")+COUNTIF('C121'!F9,"Aula 1")+COUNTIF('C122'!F9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 1")+COUNTIF('C112'!F9,"Aula 1")+COUNTIF('C113'!F9,"Aula 1")+COUNTIF('C121'!F9,"Aula 1")+COUNTIF('C122'!F9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 1")+COUNTIF('C112'!E9,"Aula 1")+COUNTIF('C113'!E9,"Aula 1")+COUNTIF('C121'!E9,"Aula 1")+COUNTIF('C122'!E9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 1")+COUNTIF('C112'!E9,"Aula 1")+COUNTIF('C113'!E9,"Aula 1")+COUNTIF('C121'!E9,"Aula 1")+COUNTIF('C122'!E9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 1")+COUNTIF('C112'!E9,"Aula 1")+COUNTIF('C113'!E9,"Aula 1")+COUNTIF('C121'!E9,"Aula 1")+COUNTIF('C122'!E9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="C202">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 2")+COUNTIF('C112'!F9,"Aula 2")+COUNTIF('C113'!F9,"Aula 2")+COUNTIF('C121'!F9,"Aula 2")+COUNTIF('C122'!F9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 2")+COUNTIF('C112'!F9,"Aula 2")+COUNTIF('C113'!F9,"Aula 2")+COUNTIF('C121'!F9,"Aula 2")+COUNTIF('C122'!F9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 2")+COUNTIF('C112'!F9,"Aula 2")+COUNTIF('C113'!F9,"Aula 2")+COUNTIF('C121'!F9,"Aula 2")+COUNTIF('C122'!F9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 2")+COUNTIF('C112'!E9,"Aula 2")+COUNTIF('C113'!E9,"Aula 2")+COUNTIF('C121'!E9,"Aula 2")+COUNTIF('C122'!E9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 2")+COUNTIF('C112'!E9,"Aula 2")+COUNTIF('C113'!E9,"Aula 2")+COUNTIF('C121'!E9,"Aula 2")+COUNTIF('C122'!E9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 2")+COUNTIF('C112'!E9,"Aula 2")+COUNTIF('C113'!E9,"Aula 2")+COUNTIF('C121'!E9,"Aula 2")+COUNTIF('C122'!E9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="C203">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 3")+COUNTIF('C112'!F9,"Aula 3")+COUNTIF('C113'!F9,"Aula 3")+COUNTIF('C121'!F9,"Aula 3")+COUNTIF('C122'!F9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 3")+COUNTIF('C112'!F9,"Aula 3")+COUNTIF('C113'!F9,"Aula 3")+COUNTIF('C121'!F9,"Aula 3")+COUNTIF('C122'!F9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 3")+COUNTIF('C112'!F9,"Aula 3")+COUNTIF('C113'!F9,"Aula 3")+COUNTIF('C121'!F9,"Aula 3")+COUNTIF('C122'!F9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 3")+COUNTIF('C112'!E9,"Aula 3")+COUNTIF('C113'!E9,"Aula 3")+COUNTIF('C121'!E9,"Aula 3")+COUNTIF('C122'!E9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 3")+COUNTIF('C112'!E9,"Aula 3")+COUNTIF('C113'!E9,"Aula 3")+COUNTIF('C121'!E9,"Aula 3")+COUNTIF('C122'!E9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 3")+COUNTIF('C112'!E9,"Aula 3")+COUNTIF('C113'!E9,"Aula 3")+COUNTIF('C121'!E9,"Aula 3")+COUNTIF('C122'!E9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="C204">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 4")+COUNTIF('C112'!F9,"Aula 4")+COUNTIF('C113'!F9,"Aula 4")+COUNTIF('C121'!F9,"Aula 4")+COUNTIF('C122'!F9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 4")+COUNTIF('C112'!F9,"Aula 4")+COUNTIF('C113'!F9,"Aula 4")+COUNTIF('C121'!F9,"Aula 4")+COUNTIF('C122'!F9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 4")+COUNTIF('C112'!F9,"Aula 4")+COUNTIF('C113'!F9,"Aula 4")+COUNTIF('C121'!F9,"Aula 4")+COUNTIF('C122'!F9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 4")+COUNTIF('C112'!E9,"Aula 4")+COUNTIF('C113'!E9,"Aula 4")+COUNTIF('C121'!E9,"Aula 4")+COUNTIF('C122'!E9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 4")+COUNTIF('C112'!E9,"Aula 4")+COUNTIF('C113'!E9,"Aula 4")+COUNTIF('C121'!E9,"Aula 4")+COUNTIF('C122'!E9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 4")+COUNTIF('C112'!E9,"Aula 4")+COUNTIF('C113'!E9,"Aula 4")+COUNTIF('C121'!E9,"Aula 4")+COUNTIF('C122'!E9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="C205">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 5")+COUNTIF('C112'!F9,"Aula 5")+COUNTIF('C113'!F9,"Aula 5")+COUNTIF('C121'!F9,"Aula 5")+COUNTIF('C122'!F9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 5")+COUNTIF('C112'!F9,"Aula 5")+COUNTIF('C113'!F9,"Aula 5")+COUNTIF('C121'!F9,"Aula 5")+COUNTIF('C122'!F9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 5")+COUNTIF('C112'!F9,"Aula 5")+COUNTIF('C113'!F9,"Aula 5")+COUNTIF('C121'!F9,"Aula 5")+COUNTIF('C122'!F9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 5")+COUNTIF('C112'!E9,"Aula 5")+COUNTIF('C113'!E9,"Aula 5")+COUNTIF('C121'!E9,"Aula 5")+COUNTIF('C122'!E9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 5")+COUNTIF('C112'!E9,"Aula 5")+COUNTIF('C113'!E9,"Aula 5")+COUNTIF('C121'!E9,"Aula 5")+COUNTIF('C122'!E9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 5")+COUNTIF('C112'!E9,"Aula 5")+COUNTIF('C113'!E9,"Aula 5")+COUNTIF('C121'!E9,"Aula 5")+COUNTIF('C122'!E9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="C206">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 6")+COUNTIF('C112'!F9,"Aula 6")+COUNTIF('C113'!F9,"Aula 6")+COUNTIF('C121'!F9,"Aula 6")+COUNTIF('C122'!F9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 6")+COUNTIF('C112'!F9,"Aula 6")+COUNTIF('C113'!F9,"Aula 6")+COUNTIF('C121'!F9,"Aula 6")+COUNTIF('C122'!F9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 6")+COUNTIF('C112'!F9,"Aula 6")+COUNTIF('C113'!F9,"Aula 6")+COUNTIF('C121'!F9,"Aula 6")+COUNTIF('C122'!F9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 6")+COUNTIF('C112'!E9,"Aula 6")+COUNTIF('C113'!E9,"Aula 6")+COUNTIF('C121'!E9,"Aula 6")+COUNTIF('C122'!E9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 6")+COUNTIF('C112'!E9,"Aula 6")+COUNTIF('C113'!E9,"Aula 6")+COUNTIF('C121'!E9,"Aula 6")+COUNTIF('C122'!E9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 6")+COUNTIF('C112'!E9,"Aula 6")+COUNTIF('C113'!E9,"Aula 6")+COUNTIF('C121'!E9,"Aula 6")+COUNTIF('C122'!E9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="C207">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 7")+COUNTIF('C112'!F9,"Aula 7")+COUNTIF('C113'!F9,"Aula 7")+COUNTIF('C121'!F9,"Aula 7")+COUNTIF('C122'!F9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 7")+COUNTIF('C112'!F9,"Aula 7")+COUNTIF('C113'!F9,"Aula 7")+COUNTIF('C121'!F9,"Aula 7")+COUNTIF('C122'!F9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 7")+COUNTIF('C112'!F9,"Aula 7")+COUNTIF('C113'!F9,"Aula 7")+COUNTIF('C121'!F9,"Aula 7")+COUNTIF('C122'!F9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 7")+COUNTIF('C112'!E9,"Aula 7")+COUNTIF('C113'!E9,"Aula 7")+COUNTIF('C121'!E9,"Aula 7")+COUNTIF('C122'!E9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 7")+COUNTIF('C112'!E9,"Aula 7")+COUNTIF('C113'!E9,"Aula 7")+COUNTIF('C121'!E9,"Aula 7")+COUNTIF('C122'!E9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 7")+COUNTIF('C112'!E9,"Aula 7")+COUNTIF('C113'!E9,"Aula 7")+COUNTIF('C121'!E9,"Aula 7")+COUNTIF('C122'!E9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="C208">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 8")+COUNTIF('C112'!F9,"Aula 8")+COUNTIF('C113'!F9,"Aula 8")+COUNTIF('C121'!F9,"Aula 8")+COUNTIF('C122'!F9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 8")+COUNTIF('C112'!F9,"Aula 8")+COUNTIF('C113'!F9,"Aula 8")+COUNTIF('C121'!F9,"Aula 8")+COUNTIF('C122'!F9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 8")+COUNTIF('C112'!F9,"Aula 8")+COUNTIF('C113'!F9,"Aula 8")+COUNTIF('C121'!F9,"Aula 8")+COUNTIF('C122'!F9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 8")+COUNTIF('C112'!E9,"Aula 8")+COUNTIF('C113'!E9,"Aula 8")+COUNTIF('C121'!E9,"Aula 8")+COUNTIF('C122'!E9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 8")+COUNTIF('C112'!E9,"Aula 8")+COUNTIF('C113'!E9,"Aula 8")+COUNTIF('C121'!E9,"Aula 8")+COUNTIF('C122'!E9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 8")+COUNTIF('C112'!E9,"Aula 8")+COUNTIF('C113'!E9,"Aula 8")+COUNTIF('C121'!E9,"Aula 8")+COUNTIF('C122'!E9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="C209">
-        <f>IF((IF((COUNTIF('C111'!F9,"Aula 9")+COUNTIF('C112'!F9,"Aula 9")+COUNTIF('C113'!F9,"Aula 9")+COUNTIF('C121'!F9,"Aula 9")+COUNTIF('C122'!F9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 9")+COUNTIF('C112'!F9,"Aula 9")+COUNTIF('C113'!F9,"Aula 9")+COUNTIF('C121'!F9,"Aula 9")+COUNTIF('C122'!F9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 9")+COUNTIF('C112'!F9,"Aula 9")+COUNTIF('C113'!F9,"Aula 9")+COUNTIF('C121'!F9,"Aula 9")+COUNTIF('C122'!F9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Aula 9")+COUNTIF('C112'!E9,"Aula 9")+COUNTIF('C113'!E9,"Aula 9")+COUNTIF('C121'!E9,"Aula 9")+COUNTIF('C122'!E9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Aula 9")+COUNTIF('C112'!E9,"Aula 9")+COUNTIF('C113'!E9,"Aula 9")+COUNTIF('C121'!E9,"Aula 9")+COUNTIF('C122'!E9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Aula 9")+COUNTIF('C112'!E9,"Aula 9")+COUNTIF('C113'!E9,"Aula 9")+COUNTIF('C121'!E9,"Aula 9")+COUNTIF('C122'!E9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="210">
       <c r="C210">
-        <f>IF((IF((COUNTIF('C111'!F9,"Lab")+COUNTIF('C112'!F9,"Lab")+COUNTIF('C113'!F9,"Lab")+COUNTIF('C121'!F9,"Lab")+COUNTIF('C122'!F9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Lab")+COUNTIF('C112'!F9,"Lab")+COUNTIF('C113'!F9,"Lab")+COUNTIF('C121'!F9,"Lab")+COUNTIF('C122'!F9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Lab")+COUNTIF('C112'!F9,"Lab")+COUNTIF('C113'!F9,"Lab")+COUNTIF('C121'!F9,"Lab")+COUNTIF('C122'!F9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E9,"Lab")+COUNTIF('C112'!E9,"Lab")+COUNTIF('C113'!E9,"Lab")+COUNTIF('C121'!E9,"Lab")+COUNTIF('C122'!E9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E9,"Lab")+COUNTIF('C112'!E9,"Lab")+COUNTIF('C113'!E9,"Lab")+COUNTIF('C121'!E9,"Lab")+COUNTIF('C122'!E9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E9,"Lab")+COUNTIF('C112'!E9,"Lab")+COUNTIF('C113'!E9,"Lab")+COUNTIF('C121'!E9,"Lab")+COUNTIF('C122'!E9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="211">
       <c r="C211">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 1")+COUNTIF('C112'!F11,"Aula 1")+COUNTIF('C113'!F11,"Aula 1")+COUNTIF('C121'!F11,"Aula 1")+COUNTIF('C122'!F11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 1")+COUNTIF('C112'!F11,"Aula 1")+COUNTIF('C113'!F11,"Aula 1")+COUNTIF('C121'!F11,"Aula 1")+COUNTIF('C122'!F11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 1")+COUNTIF('C112'!F11,"Aula 1")+COUNTIF('C113'!F11,"Aula 1")+COUNTIF('C121'!F11,"Aula 1")+COUNTIF('C122'!F11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 1")+COUNTIF('C112'!E11,"Aula 1")+COUNTIF('C113'!E11,"Aula 1")+COUNTIF('C121'!E11,"Aula 1")+COUNTIF('C122'!E11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 1")+COUNTIF('C112'!E11,"Aula 1")+COUNTIF('C113'!E11,"Aula 1")+COUNTIF('C121'!E11,"Aula 1")+COUNTIF('C122'!E11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 1")+COUNTIF('C112'!E11,"Aula 1")+COUNTIF('C113'!E11,"Aula 1")+COUNTIF('C121'!E11,"Aula 1")+COUNTIF('C122'!E11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="212">
       <c r="C212">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 2")+COUNTIF('C112'!F11,"Aula 2")+COUNTIF('C113'!F11,"Aula 2")+COUNTIF('C121'!F11,"Aula 2")+COUNTIF('C122'!F11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 2")+COUNTIF('C112'!F11,"Aula 2")+COUNTIF('C113'!F11,"Aula 2")+COUNTIF('C121'!F11,"Aula 2")+COUNTIF('C122'!F11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 2")+COUNTIF('C112'!F11,"Aula 2")+COUNTIF('C113'!F11,"Aula 2")+COUNTIF('C121'!F11,"Aula 2")+COUNTIF('C122'!F11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 2")+COUNTIF('C112'!E11,"Aula 2")+COUNTIF('C113'!E11,"Aula 2")+COUNTIF('C121'!E11,"Aula 2")+COUNTIF('C122'!E11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 2")+COUNTIF('C112'!E11,"Aula 2")+COUNTIF('C113'!E11,"Aula 2")+COUNTIF('C121'!E11,"Aula 2")+COUNTIF('C122'!E11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 2")+COUNTIF('C112'!E11,"Aula 2")+COUNTIF('C113'!E11,"Aula 2")+COUNTIF('C121'!E11,"Aula 2")+COUNTIF('C122'!E11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="213">
       <c r="C213">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 3")+COUNTIF('C112'!F11,"Aula 3")+COUNTIF('C113'!F11,"Aula 3")+COUNTIF('C121'!F11,"Aula 3")+COUNTIF('C122'!F11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 3")+COUNTIF('C112'!F11,"Aula 3")+COUNTIF('C113'!F11,"Aula 3")+COUNTIF('C121'!F11,"Aula 3")+COUNTIF('C122'!F11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 3")+COUNTIF('C112'!F11,"Aula 3")+COUNTIF('C113'!F11,"Aula 3")+COUNTIF('C121'!F11,"Aula 3")+COUNTIF('C122'!F11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 3")+COUNTIF('C112'!E11,"Aula 3")+COUNTIF('C113'!E11,"Aula 3")+COUNTIF('C121'!E11,"Aula 3")+COUNTIF('C122'!E11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 3")+COUNTIF('C112'!E11,"Aula 3")+COUNTIF('C113'!E11,"Aula 3")+COUNTIF('C121'!E11,"Aula 3")+COUNTIF('C122'!E11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 3")+COUNTIF('C112'!E11,"Aula 3")+COUNTIF('C113'!E11,"Aula 3")+COUNTIF('C121'!E11,"Aula 3")+COUNTIF('C122'!E11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="C214">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 4")+COUNTIF('C112'!F11,"Aula 4")+COUNTIF('C113'!F11,"Aula 4")+COUNTIF('C121'!F11,"Aula 4")+COUNTIF('C122'!F11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 4")+COUNTIF('C112'!F11,"Aula 4")+COUNTIF('C113'!F11,"Aula 4")+COUNTIF('C121'!F11,"Aula 4")+COUNTIF('C122'!F11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 4")+COUNTIF('C112'!F11,"Aula 4")+COUNTIF('C113'!F11,"Aula 4")+COUNTIF('C121'!F11,"Aula 4")+COUNTIF('C122'!F11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 4")+COUNTIF('C112'!E11,"Aula 4")+COUNTIF('C113'!E11,"Aula 4")+COUNTIF('C121'!E11,"Aula 4")+COUNTIF('C122'!E11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 4")+COUNTIF('C112'!E11,"Aula 4")+COUNTIF('C113'!E11,"Aula 4")+COUNTIF('C121'!E11,"Aula 4")+COUNTIF('C122'!E11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 4")+COUNTIF('C112'!E11,"Aula 4")+COUNTIF('C113'!E11,"Aula 4")+COUNTIF('C121'!E11,"Aula 4")+COUNTIF('C122'!E11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="215">
       <c r="C215">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 5")+COUNTIF('C112'!F11,"Aula 5")+COUNTIF('C113'!F11,"Aula 5")+COUNTIF('C121'!F11,"Aula 5")+COUNTIF('C122'!F11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 5")+COUNTIF('C112'!F11,"Aula 5")+COUNTIF('C113'!F11,"Aula 5")+COUNTIF('C121'!F11,"Aula 5")+COUNTIF('C122'!F11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 5")+COUNTIF('C112'!F11,"Aula 5")+COUNTIF('C113'!F11,"Aula 5")+COUNTIF('C121'!F11,"Aula 5")+COUNTIF('C122'!F11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 5")+COUNTIF('C112'!E11,"Aula 5")+COUNTIF('C113'!E11,"Aula 5")+COUNTIF('C121'!E11,"Aula 5")+COUNTIF('C122'!E11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 5")+COUNTIF('C112'!E11,"Aula 5")+COUNTIF('C113'!E11,"Aula 5")+COUNTIF('C121'!E11,"Aula 5")+COUNTIF('C122'!E11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 5")+COUNTIF('C112'!E11,"Aula 5")+COUNTIF('C113'!E11,"Aula 5")+COUNTIF('C121'!E11,"Aula 5")+COUNTIF('C122'!E11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="216">
       <c r="C216">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 6")+COUNTIF('C112'!F11,"Aula 6")+COUNTIF('C113'!F11,"Aula 6")+COUNTIF('C121'!F11,"Aula 6")+COUNTIF('C122'!F11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 6")+COUNTIF('C112'!F11,"Aula 6")+COUNTIF('C113'!F11,"Aula 6")+COUNTIF('C121'!F11,"Aula 6")+COUNTIF('C122'!F11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 6")+COUNTIF('C112'!F11,"Aula 6")+COUNTIF('C113'!F11,"Aula 6")+COUNTIF('C121'!F11,"Aula 6")+COUNTIF('C122'!F11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 6")+COUNTIF('C112'!E11,"Aula 6")+COUNTIF('C113'!E11,"Aula 6")+COUNTIF('C121'!E11,"Aula 6")+COUNTIF('C122'!E11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 6")+COUNTIF('C112'!E11,"Aula 6")+COUNTIF('C113'!E11,"Aula 6")+COUNTIF('C121'!E11,"Aula 6")+COUNTIF('C122'!E11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 6")+COUNTIF('C112'!E11,"Aula 6")+COUNTIF('C113'!E11,"Aula 6")+COUNTIF('C121'!E11,"Aula 6")+COUNTIF('C122'!E11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="217">
       <c r="C217">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 7")+COUNTIF('C112'!F11,"Aula 7")+COUNTIF('C113'!F11,"Aula 7")+COUNTIF('C121'!F11,"Aula 7")+COUNTIF('C122'!F11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 7")+COUNTIF('C112'!F11,"Aula 7")+COUNTIF('C113'!F11,"Aula 7")+COUNTIF('C121'!F11,"Aula 7")+COUNTIF('C122'!F11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 7")+COUNTIF('C112'!F11,"Aula 7")+COUNTIF('C113'!F11,"Aula 7")+COUNTIF('C121'!F11,"Aula 7")+COUNTIF('C122'!F11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 7")+COUNTIF('C112'!E11,"Aula 7")+COUNTIF('C113'!E11,"Aula 7")+COUNTIF('C121'!E11,"Aula 7")+COUNTIF('C122'!E11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 7")+COUNTIF('C112'!E11,"Aula 7")+COUNTIF('C113'!E11,"Aula 7")+COUNTIF('C121'!E11,"Aula 7")+COUNTIF('C122'!E11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 7")+COUNTIF('C112'!E11,"Aula 7")+COUNTIF('C113'!E11,"Aula 7")+COUNTIF('C121'!E11,"Aula 7")+COUNTIF('C122'!E11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="218">
       <c r="C218">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 8")+COUNTIF('C112'!F11,"Aula 8")+COUNTIF('C113'!F11,"Aula 8")+COUNTIF('C121'!F11,"Aula 8")+COUNTIF('C122'!F11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 8")+COUNTIF('C112'!F11,"Aula 8")+COUNTIF('C113'!F11,"Aula 8")+COUNTIF('C121'!F11,"Aula 8")+COUNTIF('C122'!F11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 8")+COUNTIF('C112'!F11,"Aula 8")+COUNTIF('C113'!F11,"Aula 8")+COUNTIF('C121'!F11,"Aula 8")+COUNTIF('C122'!F11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 8")+COUNTIF('C112'!E11,"Aula 8")+COUNTIF('C113'!E11,"Aula 8")+COUNTIF('C121'!E11,"Aula 8")+COUNTIF('C122'!E11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 8")+COUNTIF('C112'!E11,"Aula 8")+COUNTIF('C113'!E11,"Aula 8")+COUNTIF('C121'!E11,"Aula 8")+COUNTIF('C122'!E11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 8")+COUNTIF('C112'!E11,"Aula 8")+COUNTIF('C113'!E11,"Aula 8")+COUNTIF('C121'!E11,"Aula 8")+COUNTIF('C122'!E11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="219">
       <c r="C219">
-        <f>IF((IF((COUNTIF('C111'!F11,"Aula 9")+COUNTIF('C112'!F11,"Aula 9")+COUNTIF('C113'!F11,"Aula 9")+COUNTIF('C121'!F11,"Aula 9")+COUNTIF('C122'!F11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 9")+COUNTIF('C112'!F11,"Aula 9")+COUNTIF('C113'!F11,"Aula 9")+COUNTIF('C121'!F11,"Aula 9")+COUNTIF('C122'!F11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 9")+COUNTIF('C112'!F11,"Aula 9")+COUNTIF('C113'!F11,"Aula 9")+COUNTIF('C121'!F11,"Aula 9")+COUNTIF('C122'!F11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Aula 9")+COUNTIF('C112'!E11,"Aula 9")+COUNTIF('C113'!E11,"Aula 9")+COUNTIF('C121'!E11,"Aula 9")+COUNTIF('C122'!E11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Aula 9")+COUNTIF('C112'!E11,"Aula 9")+COUNTIF('C113'!E11,"Aula 9")+COUNTIF('C121'!E11,"Aula 9")+COUNTIF('C122'!E11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Aula 9")+COUNTIF('C112'!E11,"Aula 9")+COUNTIF('C113'!E11,"Aula 9")+COUNTIF('C121'!E11,"Aula 9")+COUNTIF('C122'!E11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="220">
       <c r="C220">
-        <f>IF((IF((COUNTIF('C111'!F11,"Lab")+COUNTIF('C112'!F11,"Lab")+COUNTIF('C113'!F11,"Lab")+COUNTIF('C121'!F11,"Lab")+COUNTIF('C122'!F11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Lab")+COUNTIF('C112'!F11,"Lab")+COUNTIF('C113'!F11,"Lab")+COUNTIF('C121'!F11,"Lab")+COUNTIF('C122'!F11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Lab")+COUNTIF('C112'!F11,"Lab")+COUNTIF('C113'!F11,"Lab")+COUNTIF('C121'!F11,"Lab")+COUNTIF('C122'!F11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E11,"Lab")+COUNTIF('C112'!E11,"Lab")+COUNTIF('C113'!E11,"Lab")+COUNTIF('C121'!E11,"Lab")+COUNTIF('C122'!E11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E11,"Lab")+COUNTIF('C112'!E11,"Lab")+COUNTIF('C113'!E11,"Lab")+COUNTIF('C121'!E11,"Lab")+COUNTIF('C122'!E11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E11,"Lab")+COUNTIF('C112'!E11,"Lab")+COUNTIF('C113'!E11,"Lab")+COUNTIF('C121'!E11,"Lab")+COUNTIF('C122'!E11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="221">
       <c r="C221">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 1")+COUNTIF('C112'!F13,"Aula 1")+COUNTIF('C113'!F13,"Aula 1")+COUNTIF('C121'!F13,"Aula 1")+COUNTIF('C122'!F13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 1")+COUNTIF('C112'!F13,"Aula 1")+COUNTIF('C113'!F13,"Aula 1")+COUNTIF('C121'!F13,"Aula 1")+COUNTIF('C122'!F13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 1")+COUNTIF('C112'!F13,"Aula 1")+COUNTIF('C113'!F13,"Aula 1")+COUNTIF('C121'!F13,"Aula 1")+COUNTIF('C122'!F13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 1")+COUNTIF('C112'!E13,"Aula 1")+COUNTIF('C113'!E13,"Aula 1")+COUNTIF('C121'!E13,"Aula 1")+COUNTIF('C122'!E13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 1")+COUNTIF('C112'!E13,"Aula 1")+COUNTIF('C113'!E13,"Aula 1")+COUNTIF('C121'!E13,"Aula 1")+COUNTIF('C122'!E13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 1")+COUNTIF('C112'!E13,"Aula 1")+COUNTIF('C113'!E13,"Aula 1")+COUNTIF('C121'!E13,"Aula 1")+COUNTIF('C122'!E13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="222">
       <c r="C222">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 2")+COUNTIF('C112'!F13,"Aula 2")+COUNTIF('C113'!F13,"Aula 2")+COUNTIF('C121'!F13,"Aula 2")+COUNTIF('C122'!F13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 2")+COUNTIF('C112'!F13,"Aula 2")+COUNTIF('C113'!F13,"Aula 2")+COUNTIF('C121'!F13,"Aula 2")+COUNTIF('C122'!F13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 2")+COUNTIF('C112'!F13,"Aula 2")+COUNTIF('C113'!F13,"Aula 2")+COUNTIF('C121'!F13,"Aula 2")+COUNTIF('C122'!F13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 2")+COUNTIF('C112'!E13,"Aula 2")+COUNTIF('C113'!E13,"Aula 2")+COUNTIF('C121'!E13,"Aula 2")+COUNTIF('C122'!E13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 2")+COUNTIF('C112'!E13,"Aula 2")+COUNTIF('C113'!E13,"Aula 2")+COUNTIF('C121'!E13,"Aula 2")+COUNTIF('C122'!E13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 2")+COUNTIF('C112'!E13,"Aula 2")+COUNTIF('C113'!E13,"Aula 2")+COUNTIF('C121'!E13,"Aula 2")+COUNTIF('C122'!E13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="223">
       <c r="C223">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 3")+COUNTIF('C112'!F13,"Aula 3")+COUNTIF('C113'!F13,"Aula 3")+COUNTIF('C121'!F13,"Aula 3")+COUNTIF('C122'!F13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 3")+COUNTIF('C112'!F13,"Aula 3")+COUNTIF('C113'!F13,"Aula 3")+COUNTIF('C121'!F13,"Aula 3")+COUNTIF('C122'!F13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 3")+COUNTIF('C112'!F13,"Aula 3")+COUNTIF('C113'!F13,"Aula 3")+COUNTIF('C121'!F13,"Aula 3")+COUNTIF('C122'!F13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 3")+COUNTIF('C112'!E13,"Aula 3")+COUNTIF('C113'!E13,"Aula 3")+COUNTIF('C121'!E13,"Aula 3")+COUNTIF('C122'!E13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 3")+COUNTIF('C112'!E13,"Aula 3")+COUNTIF('C113'!E13,"Aula 3")+COUNTIF('C121'!E13,"Aula 3")+COUNTIF('C122'!E13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 3")+COUNTIF('C112'!E13,"Aula 3")+COUNTIF('C113'!E13,"Aula 3")+COUNTIF('C121'!E13,"Aula 3")+COUNTIF('C122'!E13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="224">
       <c r="C224">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 4")+COUNTIF('C112'!F13,"Aula 4")+COUNTIF('C113'!F13,"Aula 4")+COUNTIF('C121'!F13,"Aula 4")+COUNTIF('C122'!F13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 4")+COUNTIF('C112'!F13,"Aula 4")+COUNTIF('C113'!F13,"Aula 4")+COUNTIF('C121'!F13,"Aula 4")+COUNTIF('C122'!F13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 4")+COUNTIF('C112'!F13,"Aula 4")+COUNTIF('C113'!F13,"Aula 4")+COUNTIF('C121'!F13,"Aula 4")+COUNTIF('C122'!F13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 4")+COUNTIF('C112'!E13,"Aula 4")+COUNTIF('C113'!E13,"Aula 4")+COUNTIF('C121'!E13,"Aula 4")+COUNTIF('C122'!E13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 4")+COUNTIF('C112'!E13,"Aula 4")+COUNTIF('C113'!E13,"Aula 4")+COUNTIF('C121'!E13,"Aula 4")+COUNTIF('C122'!E13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 4")+COUNTIF('C112'!E13,"Aula 4")+COUNTIF('C113'!E13,"Aula 4")+COUNTIF('C121'!E13,"Aula 4")+COUNTIF('C122'!E13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="225">
       <c r="C225">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 5")+COUNTIF('C112'!F13,"Aula 5")+COUNTIF('C113'!F13,"Aula 5")+COUNTIF('C121'!F13,"Aula 5")+COUNTIF('C122'!F13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 5")+COUNTIF('C112'!F13,"Aula 5")+COUNTIF('C113'!F13,"Aula 5")+COUNTIF('C121'!F13,"Aula 5")+COUNTIF('C122'!F13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 5")+COUNTIF('C112'!F13,"Aula 5")+COUNTIF('C113'!F13,"Aula 5")+COUNTIF('C121'!F13,"Aula 5")+COUNTIF('C122'!F13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 5")+COUNTIF('C112'!E13,"Aula 5")+COUNTIF('C113'!E13,"Aula 5")+COUNTIF('C121'!E13,"Aula 5")+COUNTIF('C122'!E13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 5")+COUNTIF('C112'!E13,"Aula 5")+COUNTIF('C113'!E13,"Aula 5")+COUNTIF('C121'!E13,"Aula 5")+COUNTIF('C122'!E13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 5")+COUNTIF('C112'!E13,"Aula 5")+COUNTIF('C113'!E13,"Aula 5")+COUNTIF('C121'!E13,"Aula 5")+COUNTIF('C122'!E13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="226">
       <c r="C226">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 6")+COUNTIF('C112'!F13,"Aula 6")+COUNTIF('C113'!F13,"Aula 6")+COUNTIF('C121'!F13,"Aula 6")+COUNTIF('C122'!F13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 6")+COUNTIF('C112'!F13,"Aula 6")+COUNTIF('C113'!F13,"Aula 6")+COUNTIF('C121'!F13,"Aula 6")+COUNTIF('C122'!F13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 6")+COUNTIF('C112'!F13,"Aula 6")+COUNTIF('C113'!F13,"Aula 6")+COUNTIF('C121'!F13,"Aula 6")+COUNTIF('C122'!F13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 6")+COUNTIF('C112'!E13,"Aula 6")+COUNTIF('C113'!E13,"Aula 6")+COUNTIF('C121'!E13,"Aula 6")+COUNTIF('C122'!E13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 6")+COUNTIF('C112'!E13,"Aula 6")+COUNTIF('C113'!E13,"Aula 6")+COUNTIF('C121'!E13,"Aula 6")+COUNTIF('C122'!E13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 6")+COUNTIF('C112'!E13,"Aula 6")+COUNTIF('C113'!E13,"Aula 6")+COUNTIF('C121'!E13,"Aula 6")+COUNTIF('C122'!E13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="227">
       <c r="C227">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 7")+COUNTIF('C112'!F13,"Aula 7")+COUNTIF('C113'!F13,"Aula 7")+COUNTIF('C121'!F13,"Aula 7")+COUNTIF('C122'!F13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 7")+COUNTIF('C112'!F13,"Aula 7")+COUNTIF('C113'!F13,"Aula 7")+COUNTIF('C121'!F13,"Aula 7")+COUNTIF('C122'!F13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 7")+COUNTIF('C112'!F13,"Aula 7")+COUNTIF('C113'!F13,"Aula 7")+COUNTIF('C121'!F13,"Aula 7")+COUNTIF('C122'!F13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 7")+COUNTIF('C112'!E13,"Aula 7")+COUNTIF('C113'!E13,"Aula 7")+COUNTIF('C121'!E13,"Aula 7")+COUNTIF('C122'!E13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 7")+COUNTIF('C112'!E13,"Aula 7")+COUNTIF('C113'!E13,"Aula 7")+COUNTIF('C121'!E13,"Aula 7")+COUNTIF('C122'!E13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 7")+COUNTIF('C112'!E13,"Aula 7")+COUNTIF('C113'!E13,"Aula 7")+COUNTIF('C121'!E13,"Aula 7")+COUNTIF('C122'!E13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="C228">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 8")+COUNTIF('C112'!F13,"Aula 8")+COUNTIF('C113'!F13,"Aula 8")+COUNTIF('C121'!F13,"Aula 8")+COUNTIF('C122'!F13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 8")+COUNTIF('C112'!F13,"Aula 8")+COUNTIF('C113'!F13,"Aula 8")+COUNTIF('C121'!F13,"Aula 8")+COUNTIF('C122'!F13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 8")+COUNTIF('C112'!F13,"Aula 8")+COUNTIF('C113'!F13,"Aula 8")+COUNTIF('C121'!F13,"Aula 8")+COUNTIF('C122'!F13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 8")+COUNTIF('C112'!E13,"Aula 8")+COUNTIF('C113'!E13,"Aula 8")+COUNTIF('C121'!E13,"Aula 8")+COUNTIF('C122'!E13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 8")+COUNTIF('C112'!E13,"Aula 8")+COUNTIF('C113'!E13,"Aula 8")+COUNTIF('C121'!E13,"Aula 8")+COUNTIF('C122'!E13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 8")+COUNTIF('C112'!E13,"Aula 8")+COUNTIF('C113'!E13,"Aula 8")+COUNTIF('C121'!E13,"Aula 8")+COUNTIF('C122'!E13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="C229">
-        <f>IF((IF((COUNTIF('C111'!F13,"Aula 9")+COUNTIF('C112'!F13,"Aula 9")+COUNTIF('C113'!F13,"Aula 9")+COUNTIF('C121'!F13,"Aula 9")+COUNTIF('C122'!F13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 9")+COUNTIF('C112'!F13,"Aula 9")+COUNTIF('C113'!F13,"Aula 9")+COUNTIF('C121'!F13,"Aula 9")+COUNTIF('C122'!F13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 9")+COUNTIF('C112'!F13,"Aula 9")+COUNTIF('C113'!F13,"Aula 9")+COUNTIF('C121'!F13,"Aula 9")+COUNTIF('C122'!F13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Aula 9")+COUNTIF('C112'!E13,"Aula 9")+COUNTIF('C113'!E13,"Aula 9")+COUNTIF('C121'!E13,"Aula 9")+COUNTIF('C122'!E13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Aula 9")+COUNTIF('C112'!E13,"Aula 9")+COUNTIF('C113'!E13,"Aula 9")+COUNTIF('C121'!E13,"Aula 9")+COUNTIF('C122'!E13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Aula 9")+COUNTIF('C112'!E13,"Aula 9")+COUNTIF('C113'!E13,"Aula 9")+COUNTIF('C121'!E13,"Aula 9")+COUNTIF('C122'!E13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="C230">
-        <f>IF((IF((COUNTIF('C111'!F13,"Lab")+COUNTIF('C112'!F13,"Lab")+COUNTIF('C113'!F13,"Lab")+COUNTIF('C121'!F13,"Lab")+COUNTIF('C122'!F13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Lab")+COUNTIF('C112'!F13,"Lab")+COUNTIF('C113'!F13,"Lab")+COUNTIF('C121'!F13,"Lab")+COUNTIF('C122'!F13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Lab")+COUNTIF('C112'!F13,"Lab")+COUNTIF('C113'!F13,"Lab")+COUNTIF('C121'!F13,"Lab")+COUNTIF('C122'!F13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E13,"Lab")+COUNTIF('C112'!E13,"Lab")+COUNTIF('C113'!E13,"Lab")+COUNTIF('C121'!E13,"Lab")+COUNTIF('C122'!E13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E13,"Lab")+COUNTIF('C112'!E13,"Lab")+COUNTIF('C113'!E13,"Lab")+COUNTIF('C121'!E13,"Lab")+COUNTIF('C122'!E13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E13,"Lab")+COUNTIF('C112'!E13,"Lab")+COUNTIF('C113'!E13,"Lab")+COUNTIF('C121'!E13,"Lab")+COUNTIF('C122'!E13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="C231">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 1")+COUNTIF('C112'!F15,"Aula 1")+COUNTIF('C113'!F15,"Aula 1")+COUNTIF('C121'!F15,"Aula 1")+COUNTIF('C122'!F15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 1")+COUNTIF('C112'!F15,"Aula 1")+COUNTIF('C113'!F15,"Aula 1")+COUNTIF('C121'!F15,"Aula 1")+COUNTIF('C122'!F15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 1")+COUNTIF('C112'!F15,"Aula 1")+COUNTIF('C113'!F15,"Aula 1")+COUNTIF('C121'!F15,"Aula 1")+COUNTIF('C122'!F15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 1")+COUNTIF('C112'!E15,"Aula 1")+COUNTIF('C113'!E15,"Aula 1")+COUNTIF('C121'!E15,"Aula 1")+COUNTIF('C122'!E15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 1")+COUNTIF('C112'!E15,"Aula 1")+COUNTIF('C113'!E15,"Aula 1")+COUNTIF('C121'!E15,"Aula 1")+COUNTIF('C122'!E15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 1")+COUNTIF('C112'!E15,"Aula 1")+COUNTIF('C113'!E15,"Aula 1")+COUNTIF('C121'!E15,"Aula 1")+COUNTIF('C122'!E15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="232">
       <c r="C232">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 2")+COUNTIF('C112'!F15,"Aula 2")+COUNTIF('C113'!F15,"Aula 2")+COUNTIF('C121'!F15,"Aula 2")+COUNTIF('C122'!F15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 2")+COUNTIF('C112'!F15,"Aula 2")+COUNTIF('C113'!F15,"Aula 2")+COUNTIF('C121'!F15,"Aula 2")+COUNTIF('C122'!F15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 2")+COUNTIF('C112'!F15,"Aula 2")+COUNTIF('C113'!F15,"Aula 2")+COUNTIF('C121'!F15,"Aula 2")+COUNTIF('C122'!F15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 2")+COUNTIF('C112'!E15,"Aula 2")+COUNTIF('C113'!E15,"Aula 2")+COUNTIF('C121'!E15,"Aula 2")+COUNTIF('C122'!E15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 2")+COUNTIF('C112'!E15,"Aula 2")+COUNTIF('C113'!E15,"Aula 2")+COUNTIF('C121'!E15,"Aula 2")+COUNTIF('C122'!E15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 2")+COUNTIF('C112'!E15,"Aula 2")+COUNTIF('C113'!E15,"Aula 2")+COUNTIF('C121'!E15,"Aula 2")+COUNTIF('C122'!E15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="233">
       <c r="C233">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 3")+COUNTIF('C112'!F15,"Aula 3")+COUNTIF('C113'!F15,"Aula 3")+COUNTIF('C121'!F15,"Aula 3")+COUNTIF('C122'!F15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 3")+COUNTIF('C112'!F15,"Aula 3")+COUNTIF('C113'!F15,"Aula 3")+COUNTIF('C121'!F15,"Aula 3")+COUNTIF('C122'!F15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 3")+COUNTIF('C112'!F15,"Aula 3")+COUNTIF('C113'!F15,"Aula 3")+COUNTIF('C121'!F15,"Aula 3")+COUNTIF('C122'!F15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 3")+COUNTIF('C112'!E15,"Aula 3")+COUNTIF('C113'!E15,"Aula 3")+COUNTIF('C121'!E15,"Aula 3")+COUNTIF('C122'!E15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 3")+COUNTIF('C112'!E15,"Aula 3")+COUNTIF('C113'!E15,"Aula 3")+COUNTIF('C121'!E15,"Aula 3")+COUNTIF('C122'!E15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 3")+COUNTIF('C112'!E15,"Aula 3")+COUNTIF('C113'!E15,"Aula 3")+COUNTIF('C121'!E15,"Aula 3")+COUNTIF('C122'!E15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="C234">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 4")+COUNTIF('C112'!F15,"Aula 4")+COUNTIF('C113'!F15,"Aula 4")+COUNTIF('C121'!F15,"Aula 4")+COUNTIF('C122'!F15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 4")+COUNTIF('C112'!F15,"Aula 4")+COUNTIF('C113'!F15,"Aula 4")+COUNTIF('C121'!F15,"Aula 4")+COUNTIF('C122'!F15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 4")+COUNTIF('C112'!F15,"Aula 4")+COUNTIF('C113'!F15,"Aula 4")+COUNTIF('C121'!F15,"Aula 4")+COUNTIF('C122'!F15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 4")+COUNTIF('C112'!E15,"Aula 4")+COUNTIF('C113'!E15,"Aula 4")+COUNTIF('C121'!E15,"Aula 4")+COUNTIF('C122'!E15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 4")+COUNTIF('C112'!E15,"Aula 4")+COUNTIF('C113'!E15,"Aula 4")+COUNTIF('C121'!E15,"Aula 4")+COUNTIF('C122'!E15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 4")+COUNTIF('C112'!E15,"Aula 4")+COUNTIF('C113'!E15,"Aula 4")+COUNTIF('C121'!E15,"Aula 4")+COUNTIF('C122'!E15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="C235">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 5")+COUNTIF('C112'!F15,"Aula 5")+COUNTIF('C113'!F15,"Aula 5")+COUNTIF('C121'!F15,"Aula 5")+COUNTIF('C122'!F15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 5")+COUNTIF('C112'!F15,"Aula 5")+COUNTIF('C113'!F15,"Aula 5")+COUNTIF('C121'!F15,"Aula 5")+COUNTIF('C122'!F15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 5")+COUNTIF('C112'!F15,"Aula 5")+COUNTIF('C113'!F15,"Aula 5")+COUNTIF('C121'!F15,"Aula 5")+COUNTIF('C122'!F15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 5")+COUNTIF('C112'!E15,"Aula 5")+COUNTIF('C113'!E15,"Aula 5")+COUNTIF('C121'!E15,"Aula 5")+COUNTIF('C122'!E15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 5")+COUNTIF('C112'!E15,"Aula 5")+COUNTIF('C113'!E15,"Aula 5")+COUNTIF('C121'!E15,"Aula 5")+COUNTIF('C122'!E15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 5")+COUNTIF('C112'!E15,"Aula 5")+COUNTIF('C113'!E15,"Aula 5")+COUNTIF('C121'!E15,"Aula 5")+COUNTIF('C122'!E15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="C236">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 6")+COUNTIF('C112'!F15,"Aula 6")+COUNTIF('C113'!F15,"Aula 6")+COUNTIF('C121'!F15,"Aula 6")+COUNTIF('C122'!F15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 6")+COUNTIF('C112'!F15,"Aula 6")+COUNTIF('C113'!F15,"Aula 6")+COUNTIF('C121'!F15,"Aula 6")+COUNTIF('C122'!F15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 6")+COUNTIF('C112'!F15,"Aula 6")+COUNTIF('C113'!F15,"Aula 6")+COUNTIF('C121'!F15,"Aula 6")+COUNTIF('C122'!F15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 6")+COUNTIF('C112'!E15,"Aula 6")+COUNTIF('C113'!E15,"Aula 6")+COUNTIF('C121'!E15,"Aula 6")+COUNTIF('C122'!E15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 6")+COUNTIF('C112'!E15,"Aula 6")+COUNTIF('C113'!E15,"Aula 6")+COUNTIF('C121'!E15,"Aula 6")+COUNTIF('C122'!E15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 6")+COUNTIF('C112'!E15,"Aula 6")+COUNTIF('C113'!E15,"Aula 6")+COUNTIF('C121'!E15,"Aula 6")+COUNTIF('C122'!E15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="C237">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 7")+COUNTIF('C112'!F15,"Aula 7")+COUNTIF('C113'!F15,"Aula 7")+COUNTIF('C121'!F15,"Aula 7")+COUNTIF('C122'!F15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 7")+COUNTIF('C112'!F15,"Aula 7")+COUNTIF('C113'!F15,"Aula 7")+COUNTIF('C121'!F15,"Aula 7")+COUNTIF('C122'!F15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 7")+COUNTIF('C112'!F15,"Aula 7")+COUNTIF('C113'!F15,"Aula 7")+COUNTIF('C121'!F15,"Aula 7")+COUNTIF('C122'!F15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 7")+COUNTIF('C112'!E15,"Aula 7")+COUNTIF('C113'!E15,"Aula 7")+COUNTIF('C121'!E15,"Aula 7")+COUNTIF('C122'!E15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 7")+COUNTIF('C112'!E15,"Aula 7")+COUNTIF('C113'!E15,"Aula 7")+COUNTIF('C121'!E15,"Aula 7")+COUNTIF('C122'!E15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 7")+COUNTIF('C112'!E15,"Aula 7")+COUNTIF('C113'!E15,"Aula 7")+COUNTIF('C121'!E15,"Aula 7")+COUNTIF('C122'!E15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="238">
       <c r="C238">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 8")+COUNTIF('C112'!F15,"Aula 8")+COUNTIF('C113'!F15,"Aula 8")+COUNTIF('C121'!F15,"Aula 8")+COUNTIF('C122'!F15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 8")+COUNTIF('C112'!F15,"Aula 8")+COUNTIF('C113'!F15,"Aula 8")+COUNTIF('C121'!F15,"Aula 8")+COUNTIF('C122'!F15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 8")+COUNTIF('C112'!F15,"Aula 8")+COUNTIF('C113'!F15,"Aula 8")+COUNTIF('C121'!F15,"Aula 8")+COUNTIF('C122'!F15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 8")+COUNTIF('C112'!E15,"Aula 8")+COUNTIF('C113'!E15,"Aula 8")+COUNTIF('C121'!E15,"Aula 8")+COUNTIF('C122'!E15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 8")+COUNTIF('C112'!E15,"Aula 8")+COUNTIF('C113'!E15,"Aula 8")+COUNTIF('C121'!E15,"Aula 8")+COUNTIF('C122'!E15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 8")+COUNTIF('C112'!E15,"Aula 8")+COUNTIF('C113'!E15,"Aula 8")+COUNTIF('C121'!E15,"Aula 8")+COUNTIF('C122'!E15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="239">
       <c r="C239">
-        <f>IF((IF((COUNTIF('C111'!F15,"Aula 9")+COUNTIF('C112'!F15,"Aula 9")+COUNTIF('C113'!F15,"Aula 9")+COUNTIF('C121'!F15,"Aula 9")+COUNTIF('C122'!F15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 9")+COUNTIF('C112'!F15,"Aula 9")+COUNTIF('C113'!F15,"Aula 9")+COUNTIF('C121'!F15,"Aula 9")+COUNTIF('C122'!F15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 9")+COUNTIF('C112'!F15,"Aula 9")+COUNTIF('C113'!F15,"Aula 9")+COUNTIF('C121'!F15,"Aula 9")+COUNTIF('C122'!F15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Aula 9")+COUNTIF('C112'!E15,"Aula 9")+COUNTIF('C113'!E15,"Aula 9")+COUNTIF('C121'!E15,"Aula 9")+COUNTIF('C122'!E15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Aula 9")+COUNTIF('C112'!E15,"Aula 9")+COUNTIF('C113'!E15,"Aula 9")+COUNTIF('C121'!E15,"Aula 9")+COUNTIF('C122'!E15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Aula 9")+COUNTIF('C112'!E15,"Aula 9")+COUNTIF('C113'!E15,"Aula 9")+COUNTIF('C121'!E15,"Aula 9")+COUNTIF('C122'!E15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="240">
       <c r="C240">
-        <f>IF((IF((COUNTIF('C111'!F15,"Lab")+COUNTIF('C112'!F15,"Lab")+COUNTIF('C113'!F15,"Lab")+COUNTIF('C121'!F15,"Lab")+COUNTIF('C122'!F15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Lab")+COUNTIF('C112'!F15,"Lab")+COUNTIF('C113'!F15,"Lab")+COUNTIF('C121'!F15,"Lab")+COUNTIF('C122'!F15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Lab")+COUNTIF('C112'!F15,"Lab")+COUNTIF('C113'!F15,"Lab")+COUNTIF('C121'!F15,"Lab")+COUNTIF('C122'!F15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!E15,"Lab")+COUNTIF('C112'!E15,"Lab")+COUNTIF('C113'!E15,"Lab")+COUNTIF('C121'!E15,"Lab")+COUNTIF('C122'!E15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!E15,"Lab")+COUNTIF('C112'!E15,"Lab")+COUNTIF('C113'!E15,"Lab")+COUNTIF('C121'!E15,"Lab")+COUNTIF('C122'!E15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!E15,"Lab")+COUNTIF('C112'!E15,"Lab")+COUNTIF('C113'!E15,"Lab")+COUNTIF('C121'!E15,"Lab")+COUNTIF('C122'!E15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="241">
       <c r="C241">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 1")+COUNTIF('C112'!G5,"Aula 1")+COUNTIF('C113'!G5,"Aula 1")+COUNTIF('C121'!G5,"Aula 1")+COUNTIF('C122'!G5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 1")+COUNTIF('C112'!G5,"Aula 1")+COUNTIF('C113'!G5,"Aula 1")+COUNTIF('C121'!G5,"Aula 1")+COUNTIF('C122'!G5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 1")+COUNTIF('C112'!G5,"Aula 1")+COUNTIF('C113'!G5,"Aula 1")+COUNTIF('C121'!G5,"Aula 1")+COUNTIF('C122'!G5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 1")+COUNTIF('C112'!F5,"Aula 1")+COUNTIF('C113'!F5,"Aula 1")+COUNTIF('C121'!F5,"Aula 1")+COUNTIF('C122'!F5,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 1")+COUNTIF('C112'!F5,"Aula 1")+COUNTIF('C113'!F5,"Aula 1")+COUNTIF('C121'!F5,"Aula 1")+COUNTIF('C122'!F5,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 1")+COUNTIF('C112'!F5,"Aula 1")+COUNTIF('C113'!F5,"Aula 1")+COUNTIF('C121'!F5,"Aula 1")+COUNTIF('C122'!F5,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="242">
       <c r="C242">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 2")+COUNTIF('C112'!G5,"Aula 2")+COUNTIF('C113'!G5,"Aula 2")+COUNTIF('C121'!G5,"Aula 2")+COUNTIF('C122'!G5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 2")+COUNTIF('C112'!G5,"Aula 2")+COUNTIF('C113'!G5,"Aula 2")+COUNTIF('C121'!G5,"Aula 2")+COUNTIF('C122'!G5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 2")+COUNTIF('C112'!G5,"Aula 2")+COUNTIF('C113'!G5,"Aula 2")+COUNTIF('C121'!G5,"Aula 2")+COUNTIF('C122'!G5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 2")+COUNTIF('C112'!F5,"Aula 2")+COUNTIF('C113'!F5,"Aula 2")+COUNTIF('C121'!F5,"Aula 2")+COUNTIF('C122'!F5,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 2")+COUNTIF('C112'!F5,"Aula 2")+COUNTIF('C113'!F5,"Aula 2")+COUNTIF('C121'!F5,"Aula 2")+COUNTIF('C122'!F5,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 2")+COUNTIF('C112'!F5,"Aula 2")+COUNTIF('C113'!F5,"Aula 2")+COUNTIF('C121'!F5,"Aula 2")+COUNTIF('C122'!F5,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="243">
       <c r="C243">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 3")+COUNTIF('C112'!G5,"Aula 3")+COUNTIF('C113'!G5,"Aula 3")+COUNTIF('C121'!G5,"Aula 3")+COUNTIF('C122'!G5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 3")+COUNTIF('C112'!G5,"Aula 3")+COUNTIF('C113'!G5,"Aula 3")+COUNTIF('C121'!G5,"Aula 3")+COUNTIF('C122'!G5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 3")+COUNTIF('C112'!G5,"Aula 3")+COUNTIF('C113'!G5,"Aula 3")+COUNTIF('C121'!G5,"Aula 3")+COUNTIF('C122'!G5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 3")+COUNTIF('C112'!F5,"Aula 3")+COUNTIF('C113'!F5,"Aula 3")+COUNTIF('C121'!F5,"Aula 3")+COUNTIF('C122'!F5,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 3")+COUNTIF('C112'!F5,"Aula 3")+COUNTIF('C113'!F5,"Aula 3")+COUNTIF('C121'!F5,"Aula 3")+COUNTIF('C122'!F5,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 3")+COUNTIF('C112'!F5,"Aula 3")+COUNTIF('C113'!F5,"Aula 3")+COUNTIF('C121'!F5,"Aula 3")+COUNTIF('C122'!F5,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="244">
       <c r="C244">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 4")+COUNTIF('C112'!G5,"Aula 4")+COUNTIF('C113'!G5,"Aula 4")+COUNTIF('C121'!G5,"Aula 4")+COUNTIF('C122'!G5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 4")+COUNTIF('C112'!G5,"Aula 4")+COUNTIF('C113'!G5,"Aula 4")+COUNTIF('C121'!G5,"Aula 4")+COUNTIF('C122'!G5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 4")+COUNTIF('C112'!G5,"Aula 4")+COUNTIF('C113'!G5,"Aula 4")+COUNTIF('C121'!G5,"Aula 4")+COUNTIF('C122'!G5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 4")+COUNTIF('C112'!F5,"Aula 4")+COUNTIF('C113'!F5,"Aula 4")+COUNTIF('C121'!F5,"Aula 4")+COUNTIF('C122'!F5,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 4")+COUNTIF('C112'!F5,"Aula 4")+COUNTIF('C113'!F5,"Aula 4")+COUNTIF('C121'!F5,"Aula 4")+COUNTIF('C122'!F5,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 4")+COUNTIF('C112'!F5,"Aula 4")+COUNTIF('C113'!F5,"Aula 4")+COUNTIF('C121'!F5,"Aula 4")+COUNTIF('C122'!F5,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="245">
       <c r="C245">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 5")+COUNTIF('C112'!G5,"Aula 5")+COUNTIF('C113'!G5,"Aula 5")+COUNTIF('C121'!G5,"Aula 5")+COUNTIF('C122'!G5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 5")+COUNTIF('C112'!G5,"Aula 5")+COUNTIF('C113'!G5,"Aula 5")+COUNTIF('C121'!G5,"Aula 5")+COUNTIF('C122'!G5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 5")+COUNTIF('C112'!G5,"Aula 5")+COUNTIF('C113'!G5,"Aula 5")+COUNTIF('C121'!G5,"Aula 5")+COUNTIF('C122'!G5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 5")+COUNTIF('C112'!F5,"Aula 5")+COUNTIF('C113'!F5,"Aula 5")+COUNTIF('C121'!F5,"Aula 5")+COUNTIF('C122'!F5,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 5")+COUNTIF('C112'!F5,"Aula 5")+COUNTIF('C113'!F5,"Aula 5")+COUNTIF('C121'!F5,"Aula 5")+COUNTIF('C122'!F5,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 5")+COUNTIF('C112'!F5,"Aula 5")+COUNTIF('C113'!F5,"Aula 5")+COUNTIF('C121'!F5,"Aula 5")+COUNTIF('C122'!F5,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="246">
       <c r="C246">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 6")+COUNTIF('C112'!G5,"Aula 6")+COUNTIF('C113'!G5,"Aula 6")+COUNTIF('C121'!G5,"Aula 6")+COUNTIF('C122'!G5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 6")+COUNTIF('C112'!G5,"Aula 6")+COUNTIF('C113'!G5,"Aula 6")+COUNTIF('C121'!G5,"Aula 6")+COUNTIF('C122'!G5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 6")+COUNTIF('C112'!G5,"Aula 6")+COUNTIF('C113'!G5,"Aula 6")+COUNTIF('C121'!G5,"Aula 6")+COUNTIF('C122'!G5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 6")+COUNTIF('C112'!F5,"Aula 6")+COUNTIF('C113'!F5,"Aula 6")+COUNTIF('C121'!F5,"Aula 6")+COUNTIF('C122'!F5,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 6")+COUNTIF('C112'!F5,"Aula 6")+COUNTIF('C113'!F5,"Aula 6")+COUNTIF('C121'!F5,"Aula 6")+COUNTIF('C122'!F5,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 6")+COUNTIF('C112'!F5,"Aula 6")+COUNTIF('C113'!F5,"Aula 6")+COUNTIF('C121'!F5,"Aula 6")+COUNTIF('C122'!F5,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="247">
       <c r="C247">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 7")+COUNTIF('C112'!G5,"Aula 7")+COUNTIF('C113'!G5,"Aula 7")+COUNTIF('C121'!G5,"Aula 7")+COUNTIF('C122'!G5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 7")+COUNTIF('C112'!G5,"Aula 7")+COUNTIF('C113'!G5,"Aula 7")+COUNTIF('C121'!G5,"Aula 7")+COUNTIF('C122'!G5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 7")+COUNTIF('C112'!G5,"Aula 7")+COUNTIF('C113'!G5,"Aula 7")+COUNTIF('C121'!G5,"Aula 7")+COUNTIF('C122'!G5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 7")+COUNTIF('C112'!F5,"Aula 7")+COUNTIF('C113'!F5,"Aula 7")+COUNTIF('C121'!F5,"Aula 7")+COUNTIF('C122'!F5,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 7")+COUNTIF('C112'!F5,"Aula 7")+COUNTIF('C113'!F5,"Aula 7")+COUNTIF('C121'!F5,"Aula 7")+COUNTIF('C122'!F5,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 7")+COUNTIF('C112'!F5,"Aula 7")+COUNTIF('C113'!F5,"Aula 7")+COUNTIF('C121'!F5,"Aula 7")+COUNTIF('C122'!F5,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="248">
       <c r="C248">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 8")+COUNTIF('C112'!G5,"Aula 8")+COUNTIF('C113'!G5,"Aula 8")+COUNTIF('C121'!G5,"Aula 8")+COUNTIF('C122'!G5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 8")+COUNTIF('C112'!G5,"Aula 8")+COUNTIF('C113'!G5,"Aula 8")+COUNTIF('C121'!G5,"Aula 8")+COUNTIF('C122'!G5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 8")+COUNTIF('C112'!G5,"Aula 8")+COUNTIF('C113'!G5,"Aula 8")+COUNTIF('C121'!G5,"Aula 8")+COUNTIF('C122'!G5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 8")+COUNTIF('C112'!F5,"Aula 8")+COUNTIF('C113'!F5,"Aula 8")+COUNTIF('C121'!F5,"Aula 8")+COUNTIF('C122'!F5,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 8")+COUNTIF('C112'!F5,"Aula 8")+COUNTIF('C113'!F5,"Aula 8")+COUNTIF('C121'!F5,"Aula 8")+COUNTIF('C122'!F5,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 8")+COUNTIF('C112'!F5,"Aula 8")+COUNTIF('C113'!F5,"Aula 8")+COUNTIF('C121'!F5,"Aula 8")+COUNTIF('C122'!F5,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="249">
       <c r="C249">
-        <f>IF((IF((COUNTIF('C111'!G5,"Aula 9")+COUNTIF('C112'!G5,"Aula 9")+COUNTIF('C113'!G5,"Aula 9")+COUNTIF('C121'!G5,"Aula 9")+COUNTIF('C122'!G5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Aula 9")+COUNTIF('C112'!G5,"Aula 9")+COUNTIF('C113'!G5,"Aula 9")+COUNTIF('C121'!G5,"Aula 9")+COUNTIF('C122'!G5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Aula 9")+COUNTIF('C112'!G5,"Aula 9")+COUNTIF('C113'!G5,"Aula 9")+COUNTIF('C121'!G5,"Aula 9")+COUNTIF('C122'!G5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Aula 9")+COUNTIF('C112'!F5,"Aula 9")+COUNTIF('C113'!F5,"Aula 9")+COUNTIF('C121'!F5,"Aula 9")+COUNTIF('C122'!F5,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Aula 9")+COUNTIF('C112'!F5,"Aula 9")+COUNTIF('C113'!F5,"Aula 9")+COUNTIF('C121'!F5,"Aula 9")+COUNTIF('C122'!F5,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Aula 9")+COUNTIF('C112'!F5,"Aula 9")+COUNTIF('C113'!F5,"Aula 9")+COUNTIF('C121'!F5,"Aula 9")+COUNTIF('C122'!F5,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="C250">
-        <f>IF((IF((COUNTIF('C111'!G5,"Lab")+COUNTIF('C112'!G5,"Lab")+COUNTIF('C113'!G5,"Lab")+COUNTIF('C121'!G5,"Lab")+COUNTIF('C122'!G5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G5,"Lab")+COUNTIF('C112'!G5,"Lab")+COUNTIF('C113'!G5,"Lab")+COUNTIF('C121'!G5,"Lab")+COUNTIF('C122'!G5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G5,"Lab")+COUNTIF('C112'!G5,"Lab")+COUNTIF('C113'!G5,"Lab")+COUNTIF('C121'!G5,"Lab")+COUNTIF('C122'!G5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F5,"Lab")+COUNTIF('C112'!F5,"Lab")+COUNTIF('C113'!F5,"Lab")+COUNTIF('C121'!F5,"Lab")+COUNTIF('C122'!F5,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F5,"Lab")+COUNTIF('C112'!F5,"Lab")+COUNTIF('C113'!F5,"Lab")+COUNTIF('C121'!F5,"Lab")+COUNTIF('C122'!F5,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F5,"Lab")+COUNTIF('C112'!F5,"Lab")+COUNTIF('C113'!F5,"Lab")+COUNTIF('C121'!F5,"Lab")+COUNTIF('C122'!F5,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="C251">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 1")+COUNTIF('C112'!G7,"Aula 1")+COUNTIF('C113'!G7,"Aula 1")+COUNTIF('C121'!G7,"Aula 1")+COUNTIF('C122'!G7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 1")+COUNTIF('C112'!G7,"Aula 1")+COUNTIF('C113'!G7,"Aula 1")+COUNTIF('C121'!G7,"Aula 1")+COUNTIF('C122'!G7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 1")+COUNTIF('C112'!G7,"Aula 1")+COUNTIF('C113'!G7,"Aula 1")+COUNTIF('C121'!G7,"Aula 1")+COUNTIF('C122'!G7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 1")+COUNTIF('C112'!F7,"Aula 1")+COUNTIF('C113'!F7,"Aula 1")+COUNTIF('C121'!F7,"Aula 1")+COUNTIF('C122'!F7,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 1")+COUNTIF('C112'!F7,"Aula 1")+COUNTIF('C113'!F7,"Aula 1")+COUNTIF('C121'!F7,"Aula 1")+COUNTIF('C122'!F7,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 1")+COUNTIF('C112'!F7,"Aula 1")+COUNTIF('C113'!F7,"Aula 1")+COUNTIF('C121'!F7,"Aula 1")+COUNTIF('C122'!F7,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="252">
       <c r="C252">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 2")+COUNTIF('C112'!G7,"Aula 2")+COUNTIF('C113'!G7,"Aula 2")+COUNTIF('C121'!G7,"Aula 2")+COUNTIF('C122'!G7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 2")+COUNTIF('C112'!G7,"Aula 2")+COUNTIF('C113'!G7,"Aula 2")+COUNTIF('C121'!G7,"Aula 2")+COUNTIF('C122'!G7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 2")+COUNTIF('C112'!G7,"Aula 2")+COUNTIF('C113'!G7,"Aula 2")+COUNTIF('C121'!G7,"Aula 2")+COUNTIF('C122'!G7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 2")+COUNTIF('C112'!F7,"Aula 2")+COUNTIF('C113'!F7,"Aula 2")+COUNTIF('C121'!F7,"Aula 2")+COUNTIF('C122'!F7,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 2")+COUNTIF('C112'!F7,"Aula 2")+COUNTIF('C113'!F7,"Aula 2")+COUNTIF('C121'!F7,"Aula 2")+COUNTIF('C122'!F7,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 2")+COUNTIF('C112'!F7,"Aula 2")+COUNTIF('C113'!F7,"Aula 2")+COUNTIF('C121'!F7,"Aula 2")+COUNTIF('C122'!F7,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="253">
       <c r="C253">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 3")+COUNTIF('C112'!G7,"Aula 3")+COUNTIF('C113'!G7,"Aula 3")+COUNTIF('C121'!G7,"Aula 3")+COUNTIF('C122'!G7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 3")+COUNTIF('C112'!G7,"Aula 3")+COUNTIF('C113'!G7,"Aula 3")+COUNTIF('C121'!G7,"Aula 3")+COUNTIF('C122'!G7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 3")+COUNTIF('C112'!G7,"Aula 3")+COUNTIF('C113'!G7,"Aula 3")+COUNTIF('C121'!G7,"Aula 3")+COUNTIF('C122'!G7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 3")+COUNTIF('C112'!F7,"Aula 3")+COUNTIF('C113'!F7,"Aula 3")+COUNTIF('C121'!F7,"Aula 3")+COUNTIF('C122'!F7,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 3")+COUNTIF('C112'!F7,"Aula 3")+COUNTIF('C113'!F7,"Aula 3")+COUNTIF('C121'!F7,"Aula 3")+COUNTIF('C122'!F7,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 3")+COUNTIF('C112'!F7,"Aula 3")+COUNTIF('C113'!F7,"Aula 3")+COUNTIF('C121'!F7,"Aula 3")+COUNTIF('C122'!F7,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="254">
       <c r="C254">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 4")+COUNTIF('C112'!G7,"Aula 4")+COUNTIF('C113'!G7,"Aula 4")+COUNTIF('C121'!G7,"Aula 4")+COUNTIF('C122'!G7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 4")+COUNTIF('C112'!G7,"Aula 4")+COUNTIF('C113'!G7,"Aula 4")+COUNTIF('C121'!G7,"Aula 4")+COUNTIF('C122'!G7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 4")+COUNTIF('C112'!G7,"Aula 4")+COUNTIF('C113'!G7,"Aula 4")+COUNTIF('C121'!G7,"Aula 4")+COUNTIF('C122'!G7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 4")+COUNTIF('C112'!F7,"Aula 4")+COUNTIF('C113'!F7,"Aula 4")+COUNTIF('C121'!F7,"Aula 4")+COUNTIF('C122'!F7,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 4")+COUNTIF('C112'!F7,"Aula 4")+COUNTIF('C113'!F7,"Aula 4")+COUNTIF('C121'!F7,"Aula 4")+COUNTIF('C122'!F7,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 4")+COUNTIF('C112'!F7,"Aula 4")+COUNTIF('C113'!F7,"Aula 4")+COUNTIF('C121'!F7,"Aula 4")+COUNTIF('C122'!F7,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="255">
       <c r="C255">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 5")+COUNTIF('C112'!G7,"Aula 5")+COUNTIF('C113'!G7,"Aula 5")+COUNTIF('C121'!G7,"Aula 5")+COUNTIF('C122'!G7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 5")+COUNTIF('C112'!G7,"Aula 5")+COUNTIF('C113'!G7,"Aula 5")+COUNTIF('C121'!G7,"Aula 5")+COUNTIF('C122'!G7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 5")+COUNTIF('C112'!G7,"Aula 5")+COUNTIF('C113'!G7,"Aula 5")+COUNTIF('C121'!G7,"Aula 5")+COUNTIF('C122'!G7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 5")+COUNTIF('C112'!F7,"Aula 5")+COUNTIF('C113'!F7,"Aula 5")+COUNTIF('C121'!F7,"Aula 5")+COUNTIF('C122'!F7,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 5")+COUNTIF('C112'!F7,"Aula 5")+COUNTIF('C113'!F7,"Aula 5")+COUNTIF('C121'!F7,"Aula 5")+COUNTIF('C122'!F7,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 5")+COUNTIF('C112'!F7,"Aula 5")+COUNTIF('C113'!F7,"Aula 5")+COUNTIF('C121'!F7,"Aula 5")+COUNTIF('C122'!F7,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="256">
       <c r="C256">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 6")+COUNTIF('C112'!G7,"Aula 6")+COUNTIF('C113'!G7,"Aula 6")+COUNTIF('C121'!G7,"Aula 6")+COUNTIF('C122'!G7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 6")+COUNTIF('C112'!G7,"Aula 6")+COUNTIF('C113'!G7,"Aula 6")+COUNTIF('C121'!G7,"Aula 6")+COUNTIF('C122'!G7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 6")+COUNTIF('C112'!G7,"Aula 6")+COUNTIF('C113'!G7,"Aula 6")+COUNTIF('C121'!G7,"Aula 6")+COUNTIF('C122'!G7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 6")+COUNTIF('C112'!F7,"Aula 6")+COUNTIF('C113'!F7,"Aula 6")+COUNTIF('C121'!F7,"Aula 6")+COUNTIF('C122'!F7,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 6")+COUNTIF('C112'!F7,"Aula 6")+COUNTIF('C113'!F7,"Aula 6")+COUNTIF('C121'!F7,"Aula 6")+COUNTIF('C122'!F7,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 6")+COUNTIF('C112'!F7,"Aula 6")+COUNTIF('C113'!F7,"Aula 6")+COUNTIF('C121'!F7,"Aula 6")+COUNTIF('C122'!F7,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="257">
       <c r="C257">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 7")+COUNTIF('C112'!G7,"Aula 7")+COUNTIF('C113'!G7,"Aula 7")+COUNTIF('C121'!G7,"Aula 7")+COUNTIF('C122'!G7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 7")+COUNTIF('C112'!G7,"Aula 7")+COUNTIF('C113'!G7,"Aula 7")+COUNTIF('C121'!G7,"Aula 7")+COUNTIF('C122'!G7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 7")+COUNTIF('C112'!G7,"Aula 7")+COUNTIF('C113'!G7,"Aula 7")+COUNTIF('C121'!G7,"Aula 7")+COUNTIF('C122'!G7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 7")+COUNTIF('C112'!F7,"Aula 7")+COUNTIF('C113'!F7,"Aula 7")+COUNTIF('C121'!F7,"Aula 7")+COUNTIF('C122'!F7,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 7")+COUNTIF('C112'!F7,"Aula 7")+COUNTIF('C113'!F7,"Aula 7")+COUNTIF('C121'!F7,"Aula 7")+COUNTIF('C122'!F7,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 7")+COUNTIF('C112'!F7,"Aula 7")+COUNTIF('C113'!F7,"Aula 7")+COUNTIF('C121'!F7,"Aula 7")+COUNTIF('C122'!F7,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="258">
       <c r="C258">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 8")+COUNTIF('C112'!G7,"Aula 8")+COUNTIF('C113'!G7,"Aula 8")+COUNTIF('C121'!G7,"Aula 8")+COUNTIF('C122'!G7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 8")+COUNTIF('C112'!G7,"Aula 8")+COUNTIF('C113'!G7,"Aula 8")+COUNTIF('C121'!G7,"Aula 8")+COUNTIF('C122'!G7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 8")+COUNTIF('C112'!G7,"Aula 8")+COUNTIF('C113'!G7,"Aula 8")+COUNTIF('C121'!G7,"Aula 8")+COUNTIF('C122'!G7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 8")+COUNTIF('C112'!F7,"Aula 8")+COUNTIF('C113'!F7,"Aula 8")+COUNTIF('C121'!F7,"Aula 8")+COUNTIF('C122'!F7,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 8")+COUNTIF('C112'!F7,"Aula 8")+COUNTIF('C113'!F7,"Aula 8")+COUNTIF('C121'!F7,"Aula 8")+COUNTIF('C122'!F7,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 8")+COUNTIF('C112'!F7,"Aula 8")+COUNTIF('C113'!F7,"Aula 8")+COUNTIF('C121'!F7,"Aula 8")+COUNTIF('C122'!F7,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="259">
       <c r="C259">
-        <f>IF((IF((COUNTIF('C111'!G7,"Aula 9")+COUNTIF('C112'!G7,"Aula 9")+COUNTIF('C113'!G7,"Aula 9")+COUNTIF('C121'!G7,"Aula 9")+COUNTIF('C122'!G7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Aula 9")+COUNTIF('C112'!G7,"Aula 9")+COUNTIF('C113'!G7,"Aula 9")+COUNTIF('C121'!G7,"Aula 9")+COUNTIF('C122'!G7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Aula 9")+COUNTIF('C112'!G7,"Aula 9")+COUNTIF('C113'!G7,"Aula 9")+COUNTIF('C121'!G7,"Aula 9")+COUNTIF('C122'!G7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Aula 9")+COUNTIF('C112'!F7,"Aula 9")+COUNTIF('C113'!F7,"Aula 9")+COUNTIF('C121'!F7,"Aula 9")+COUNTIF('C122'!F7,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Aula 9")+COUNTIF('C112'!F7,"Aula 9")+COUNTIF('C113'!F7,"Aula 9")+COUNTIF('C121'!F7,"Aula 9")+COUNTIF('C122'!F7,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Aula 9")+COUNTIF('C112'!F7,"Aula 9")+COUNTIF('C113'!F7,"Aula 9")+COUNTIF('C121'!F7,"Aula 9")+COUNTIF('C122'!F7,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="260">
       <c r="C260">
-        <f>IF((IF((COUNTIF('C111'!G7,"Lab")+COUNTIF('C112'!G7,"Lab")+COUNTIF('C113'!G7,"Lab")+COUNTIF('C121'!G7,"Lab")+COUNTIF('C122'!G7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G7,"Lab")+COUNTIF('C112'!G7,"Lab")+COUNTIF('C113'!G7,"Lab")+COUNTIF('C121'!G7,"Lab")+COUNTIF('C122'!G7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G7,"Lab")+COUNTIF('C112'!G7,"Lab")+COUNTIF('C113'!G7,"Lab")+COUNTIF('C121'!G7,"Lab")+COUNTIF('C122'!G7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F7,"Lab")+COUNTIF('C112'!F7,"Lab")+COUNTIF('C113'!F7,"Lab")+COUNTIF('C121'!F7,"Lab")+COUNTIF('C122'!F7,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F7,"Lab")+COUNTIF('C112'!F7,"Lab")+COUNTIF('C113'!F7,"Lab")+COUNTIF('C121'!F7,"Lab")+COUNTIF('C122'!F7,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F7,"Lab")+COUNTIF('C112'!F7,"Lab")+COUNTIF('C113'!F7,"Lab")+COUNTIF('C121'!F7,"Lab")+COUNTIF('C122'!F7,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="261">
       <c r="C261">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 1")+COUNTIF('C112'!G9,"Aula 1")+COUNTIF('C113'!G9,"Aula 1")+COUNTIF('C121'!G9,"Aula 1")+COUNTIF('C122'!G9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 1")+COUNTIF('C112'!G9,"Aula 1")+COUNTIF('C113'!G9,"Aula 1")+COUNTIF('C121'!G9,"Aula 1")+COUNTIF('C122'!G9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 1")+COUNTIF('C112'!G9,"Aula 1")+COUNTIF('C113'!G9,"Aula 1")+COUNTIF('C121'!G9,"Aula 1")+COUNTIF('C122'!G9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 1")+COUNTIF('C112'!F9,"Aula 1")+COUNTIF('C113'!F9,"Aula 1")+COUNTIF('C121'!F9,"Aula 1")+COUNTIF('C122'!F9,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 1")+COUNTIF('C112'!F9,"Aula 1")+COUNTIF('C113'!F9,"Aula 1")+COUNTIF('C121'!F9,"Aula 1")+COUNTIF('C122'!F9,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 1")+COUNTIF('C112'!F9,"Aula 1")+COUNTIF('C113'!F9,"Aula 1")+COUNTIF('C121'!F9,"Aula 1")+COUNTIF('C122'!F9,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="262">
       <c r="C262">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 2")+COUNTIF('C112'!G9,"Aula 2")+COUNTIF('C113'!G9,"Aula 2")+COUNTIF('C121'!G9,"Aula 2")+COUNTIF('C122'!G9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 2")+COUNTIF('C112'!G9,"Aula 2")+COUNTIF('C113'!G9,"Aula 2")+COUNTIF('C121'!G9,"Aula 2")+COUNTIF('C122'!G9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 2")+COUNTIF('C112'!G9,"Aula 2")+COUNTIF('C113'!G9,"Aula 2")+COUNTIF('C121'!G9,"Aula 2")+COUNTIF('C122'!G9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 2")+COUNTIF('C112'!F9,"Aula 2")+COUNTIF('C113'!F9,"Aula 2")+COUNTIF('C121'!F9,"Aula 2")+COUNTIF('C122'!F9,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 2")+COUNTIF('C112'!F9,"Aula 2")+COUNTIF('C113'!F9,"Aula 2")+COUNTIF('C121'!F9,"Aula 2")+COUNTIF('C122'!F9,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 2")+COUNTIF('C112'!F9,"Aula 2")+COUNTIF('C113'!F9,"Aula 2")+COUNTIF('C121'!F9,"Aula 2")+COUNTIF('C122'!F9,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="263">
       <c r="C263">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 3")+COUNTIF('C112'!G9,"Aula 3")+COUNTIF('C113'!G9,"Aula 3")+COUNTIF('C121'!G9,"Aula 3")+COUNTIF('C122'!G9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 3")+COUNTIF('C112'!G9,"Aula 3")+COUNTIF('C113'!G9,"Aula 3")+COUNTIF('C121'!G9,"Aula 3")+COUNTIF('C122'!G9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 3")+COUNTIF('C112'!G9,"Aula 3")+COUNTIF('C113'!G9,"Aula 3")+COUNTIF('C121'!G9,"Aula 3")+COUNTIF('C122'!G9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 3")+COUNTIF('C112'!F9,"Aula 3")+COUNTIF('C113'!F9,"Aula 3")+COUNTIF('C121'!F9,"Aula 3")+COUNTIF('C122'!F9,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 3")+COUNTIF('C112'!F9,"Aula 3")+COUNTIF('C113'!F9,"Aula 3")+COUNTIF('C121'!F9,"Aula 3")+COUNTIF('C122'!F9,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 3")+COUNTIF('C112'!F9,"Aula 3")+COUNTIF('C113'!F9,"Aula 3")+COUNTIF('C121'!F9,"Aula 3")+COUNTIF('C122'!F9,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="264">
       <c r="C264">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 4")+COUNTIF('C112'!G9,"Aula 4")+COUNTIF('C113'!G9,"Aula 4")+COUNTIF('C121'!G9,"Aula 4")+COUNTIF('C122'!G9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 4")+COUNTIF('C112'!G9,"Aula 4")+COUNTIF('C113'!G9,"Aula 4")+COUNTIF('C121'!G9,"Aula 4")+COUNTIF('C122'!G9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 4")+COUNTIF('C112'!G9,"Aula 4")+COUNTIF('C113'!G9,"Aula 4")+COUNTIF('C121'!G9,"Aula 4")+COUNTIF('C122'!G9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 4")+COUNTIF('C112'!F9,"Aula 4")+COUNTIF('C113'!F9,"Aula 4")+COUNTIF('C121'!F9,"Aula 4")+COUNTIF('C122'!F9,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 4")+COUNTIF('C112'!F9,"Aula 4")+COUNTIF('C113'!F9,"Aula 4")+COUNTIF('C121'!F9,"Aula 4")+COUNTIF('C122'!F9,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 4")+COUNTIF('C112'!F9,"Aula 4")+COUNTIF('C113'!F9,"Aula 4")+COUNTIF('C121'!F9,"Aula 4")+COUNTIF('C122'!F9,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="265">
       <c r="C265">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 5")+COUNTIF('C112'!G9,"Aula 5")+COUNTIF('C113'!G9,"Aula 5")+COUNTIF('C121'!G9,"Aula 5")+COUNTIF('C122'!G9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 5")+COUNTIF('C112'!G9,"Aula 5")+COUNTIF('C113'!G9,"Aula 5")+COUNTIF('C121'!G9,"Aula 5")+COUNTIF('C122'!G9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 5")+COUNTIF('C112'!G9,"Aula 5")+COUNTIF('C113'!G9,"Aula 5")+COUNTIF('C121'!G9,"Aula 5")+COUNTIF('C122'!G9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 5")+COUNTIF('C112'!F9,"Aula 5")+COUNTIF('C113'!F9,"Aula 5")+COUNTIF('C121'!F9,"Aula 5")+COUNTIF('C122'!F9,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 5")+COUNTIF('C112'!F9,"Aula 5")+COUNTIF('C113'!F9,"Aula 5")+COUNTIF('C121'!F9,"Aula 5")+COUNTIF('C122'!F9,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 5")+COUNTIF('C112'!F9,"Aula 5")+COUNTIF('C113'!F9,"Aula 5")+COUNTIF('C121'!F9,"Aula 5")+COUNTIF('C122'!F9,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="C266">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 6")+COUNTIF('C112'!G9,"Aula 6")+COUNTIF('C113'!G9,"Aula 6")+COUNTIF('C121'!G9,"Aula 6")+COUNTIF('C122'!G9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 6")+COUNTIF('C112'!G9,"Aula 6")+COUNTIF('C113'!G9,"Aula 6")+COUNTIF('C121'!G9,"Aula 6")+COUNTIF('C122'!G9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 6")+COUNTIF('C112'!G9,"Aula 6")+COUNTIF('C113'!G9,"Aula 6")+COUNTIF('C121'!G9,"Aula 6")+COUNTIF('C122'!G9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 6")+COUNTIF('C112'!F9,"Aula 6")+COUNTIF('C113'!F9,"Aula 6")+COUNTIF('C121'!F9,"Aula 6")+COUNTIF('C122'!F9,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 6")+COUNTIF('C112'!F9,"Aula 6")+COUNTIF('C113'!F9,"Aula 6")+COUNTIF('C121'!F9,"Aula 6")+COUNTIF('C122'!F9,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 6")+COUNTIF('C112'!F9,"Aula 6")+COUNTIF('C113'!F9,"Aula 6")+COUNTIF('C121'!F9,"Aula 6")+COUNTIF('C122'!F9,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="267">
       <c r="C267">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 7")+COUNTIF('C112'!G9,"Aula 7")+COUNTIF('C113'!G9,"Aula 7")+COUNTIF('C121'!G9,"Aula 7")+COUNTIF('C122'!G9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 7")+COUNTIF('C112'!G9,"Aula 7")+COUNTIF('C113'!G9,"Aula 7")+COUNTIF('C121'!G9,"Aula 7")+COUNTIF('C122'!G9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 7")+COUNTIF('C112'!G9,"Aula 7")+COUNTIF('C113'!G9,"Aula 7")+COUNTIF('C121'!G9,"Aula 7")+COUNTIF('C122'!G9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 7")+COUNTIF('C112'!F9,"Aula 7")+COUNTIF('C113'!F9,"Aula 7")+COUNTIF('C121'!F9,"Aula 7")+COUNTIF('C122'!F9,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 7")+COUNTIF('C112'!F9,"Aula 7")+COUNTIF('C113'!F9,"Aula 7")+COUNTIF('C121'!F9,"Aula 7")+COUNTIF('C122'!F9,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 7")+COUNTIF('C112'!F9,"Aula 7")+COUNTIF('C113'!F9,"Aula 7")+COUNTIF('C121'!F9,"Aula 7")+COUNTIF('C122'!F9,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="268">
       <c r="C268">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 8")+COUNTIF('C112'!G9,"Aula 8")+COUNTIF('C113'!G9,"Aula 8")+COUNTIF('C121'!G9,"Aula 8")+COUNTIF('C122'!G9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 8")+COUNTIF('C112'!G9,"Aula 8")+COUNTIF('C113'!G9,"Aula 8")+COUNTIF('C121'!G9,"Aula 8")+COUNTIF('C122'!G9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 8")+COUNTIF('C112'!G9,"Aula 8")+COUNTIF('C113'!G9,"Aula 8")+COUNTIF('C121'!G9,"Aula 8")+COUNTIF('C122'!G9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 8")+COUNTIF('C112'!F9,"Aula 8")+COUNTIF('C113'!F9,"Aula 8")+COUNTIF('C121'!F9,"Aula 8")+COUNTIF('C122'!F9,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 8")+COUNTIF('C112'!F9,"Aula 8")+COUNTIF('C113'!F9,"Aula 8")+COUNTIF('C121'!F9,"Aula 8")+COUNTIF('C122'!F9,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 8")+COUNTIF('C112'!F9,"Aula 8")+COUNTIF('C113'!F9,"Aula 8")+COUNTIF('C121'!F9,"Aula 8")+COUNTIF('C122'!F9,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="269">
       <c r="C269">
-        <f>IF((IF((COUNTIF('C111'!G9,"Aula 9")+COUNTIF('C112'!G9,"Aula 9")+COUNTIF('C113'!G9,"Aula 9")+COUNTIF('C121'!G9,"Aula 9")+COUNTIF('C122'!G9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Aula 9")+COUNTIF('C112'!G9,"Aula 9")+COUNTIF('C113'!G9,"Aula 9")+COUNTIF('C121'!G9,"Aula 9")+COUNTIF('C122'!G9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Aula 9")+COUNTIF('C112'!G9,"Aula 9")+COUNTIF('C113'!G9,"Aula 9")+COUNTIF('C121'!G9,"Aula 9")+COUNTIF('C122'!G9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Aula 9")+COUNTIF('C112'!F9,"Aula 9")+COUNTIF('C113'!F9,"Aula 9")+COUNTIF('C121'!F9,"Aula 9")+COUNTIF('C122'!F9,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Aula 9")+COUNTIF('C112'!F9,"Aula 9")+COUNTIF('C113'!F9,"Aula 9")+COUNTIF('C121'!F9,"Aula 9")+COUNTIF('C122'!F9,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Aula 9")+COUNTIF('C112'!F9,"Aula 9")+COUNTIF('C113'!F9,"Aula 9")+COUNTIF('C121'!F9,"Aula 9")+COUNTIF('C122'!F9,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="270">
       <c r="C270">
-        <f>IF((IF((COUNTIF('C111'!G9,"Lab")+COUNTIF('C112'!G9,"Lab")+COUNTIF('C113'!G9,"Lab")+COUNTIF('C121'!G9,"Lab")+COUNTIF('C122'!G9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G9,"Lab")+COUNTIF('C112'!G9,"Lab")+COUNTIF('C113'!G9,"Lab")+COUNTIF('C121'!G9,"Lab")+COUNTIF('C122'!G9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G9,"Lab")+COUNTIF('C112'!G9,"Lab")+COUNTIF('C113'!G9,"Lab")+COUNTIF('C121'!G9,"Lab")+COUNTIF('C122'!G9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F9,"Lab")+COUNTIF('C112'!F9,"Lab")+COUNTIF('C113'!F9,"Lab")+COUNTIF('C121'!F9,"Lab")+COUNTIF('C122'!F9,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F9,"Lab")+COUNTIF('C112'!F9,"Lab")+COUNTIF('C113'!F9,"Lab")+COUNTIF('C121'!F9,"Lab")+COUNTIF('C122'!F9,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F9,"Lab")+COUNTIF('C112'!F9,"Lab")+COUNTIF('C113'!F9,"Lab")+COUNTIF('C121'!F9,"Lab")+COUNTIF('C122'!F9,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="271">
       <c r="C271">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 1")+COUNTIF('C112'!G11,"Aula 1")+COUNTIF('C113'!G11,"Aula 1")+COUNTIF('C121'!G11,"Aula 1")+COUNTIF('C122'!G11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 1")+COUNTIF('C112'!G11,"Aula 1")+COUNTIF('C113'!G11,"Aula 1")+COUNTIF('C121'!G11,"Aula 1")+COUNTIF('C122'!G11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 1")+COUNTIF('C112'!G11,"Aula 1")+COUNTIF('C113'!G11,"Aula 1")+COUNTIF('C121'!G11,"Aula 1")+COUNTIF('C122'!G11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 1")+COUNTIF('C112'!F11,"Aula 1")+COUNTIF('C113'!F11,"Aula 1")+COUNTIF('C121'!F11,"Aula 1")+COUNTIF('C122'!F11,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 1")+COUNTIF('C112'!F11,"Aula 1")+COUNTIF('C113'!F11,"Aula 1")+COUNTIF('C121'!F11,"Aula 1")+COUNTIF('C122'!F11,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 1")+COUNTIF('C112'!F11,"Aula 1")+COUNTIF('C113'!F11,"Aula 1")+COUNTIF('C121'!F11,"Aula 1")+COUNTIF('C122'!F11,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="272">
       <c r="C272">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 2")+COUNTIF('C112'!G11,"Aula 2")+COUNTIF('C113'!G11,"Aula 2")+COUNTIF('C121'!G11,"Aula 2")+COUNTIF('C122'!G11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 2")+COUNTIF('C112'!G11,"Aula 2")+COUNTIF('C113'!G11,"Aula 2")+COUNTIF('C121'!G11,"Aula 2")+COUNTIF('C122'!G11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 2")+COUNTIF('C112'!G11,"Aula 2")+COUNTIF('C113'!G11,"Aula 2")+COUNTIF('C121'!G11,"Aula 2")+COUNTIF('C122'!G11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 2")+COUNTIF('C112'!F11,"Aula 2")+COUNTIF('C113'!F11,"Aula 2")+COUNTIF('C121'!F11,"Aula 2")+COUNTIF('C122'!F11,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 2")+COUNTIF('C112'!F11,"Aula 2")+COUNTIF('C113'!F11,"Aula 2")+COUNTIF('C121'!F11,"Aula 2")+COUNTIF('C122'!F11,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 2")+COUNTIF('C112'!F11,"Aula 2")+COUNTIF('C113'!F11,"Aula 2")+COUNTIF('C121'!F11,"Aula 2")+COUNTIF('C122'!F11,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="273">
       <c r="C273">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 3")+COUNTIF('C112'!G11,"Aula 3")+COUNTIF('C113'!G11,"Aula 3")+COUNTIF('C121'!G11,"Aula 3")+COUNTIF('C122'!G11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 3")+COUNTIF('C112'!G11,"Aula 3")+COUNTIF('C113'!G11,"Aula 3")+COUNTIF('C121'!G11,"Aula 3")+COUNTIF('C122'!G11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 3")+COUNTIF('C112'!G11,"Aula 3")+COUNTIF('C113'!G11,"Aula 3")+COUNTIF('C121'!G11,"Aula 3")+COUNTIF('C122'!G11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 3")+COUNTIF('C112'!F11,"Aula 3")+COUNTIF('C113'!F11,"Aula 3")+COUNTIF('C121'!F11,"Aula 3")+COUNTIF('C122'!F11,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 3")+COUNTIF('C112'!F11,"Aula 3")+COUNTIF('C113'!F11,"Aula 3")+COUNTIF('C121'!F11,"Aula 3")+COUNTIF('C122'!F11,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 3")+COUNTIF('C112'!F11,"Aula 3")+COUNTIF('C113'!F11,"Aula 3")+COUNTIF('C121'!F11,"Aula 3")+COUNTIF('C122'!F11,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="274">
       <c r="C274">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 4")+COUNTIF('C112'!G11,"Aula 4")+COUNTIF('C113'!G11,"Aula 4")+COUNTIF('C121'!G11,"Aula 4")+COUNTIF('C122'!G11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 4")+COUNTIF('C112'!G11,"Aula 4")+COUNTIF('C113'!G11,"Aula 4")+COUNTIF('C121'!G11,"Aula 4")+COUNTIF('C122'!G11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 4")+COUNTIF('C112'!G11,"Aula 4")+COUNTIF('C113'!G11,"Aula 4")+COUNTIF('C121'!G11,"Aula 4")+COUNTIF('C122'!G11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 4")+COUNTIF('C112'!F11,"Aula 4")+COUNTIF('C113'!F11,"Aula 4")+COUNTIF('C121'!F11,"Aula 4")+COUNTIF('C122'!F11,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 4")+COUNTIF('C112'!F11,"Aula 4")+COUNTIF('C113'!F11,"Aula 4")+COUNTIF('C121'!F11,"Aula 4")+COUNTIF('C122'!F11,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 4")+COUNTIF('C112'!F11,"Aula 4")+COUNTIF('C113'!F11,"Aula 4")+COUNTIF('C121'!F11,"Aula 4")+COUNTIF('C122'!F11,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="275">
       <c r="C275">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 5")+COUNTIF('C112'!G11,"Aula 5")+COUNTIF('C113'!G11,"Aula 5")+COUNTIF('C121'!G11,"Aula 5")+COUNTIF('C122'!G11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 5")+COUNTIF('C112'!G11,"Aula 5")+COUNTIF('C113'!G11,"Aula 5")+COUNTIF('C121'!G11,"Aula 5")+COUNTIF('C122'!G11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 5")+COUNTIF('C112'!G11,"Aula 5")+COUNTIF('C113'!G11,"Aula 5")+COUNTIF('C121'!G11,"Aula 5")+COUNTIF('C122'!G11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 5")+COUNTIF('C112'!F11,"Aula 5")+COUNTIF('C113'!F11,"Aula 5")+COUNTIF('C121'!F11,"Aula 5")+COUNTIF('C122'!F11,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 5")+COUNTIF('C112'!F11,"Aula 5")+COUNTIF('C113'!F11,"Aula 5")+COUNTIF('C121'!F11,"Aula 5")+COUNTIF('C122'!F11,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 5")+COUNTIF('C112'!F11,"Aula 5")+COUNTIF('C113'!F11,"Aula 5")+COUNTIF('C121'!F11,"Aula 5")+COUNTIF('C122'!F11,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="276">
       <c r="C276">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 6")+COUNTIF('C112'!G11,"Aula 6")+COUNTIF('C113'!G11,"Aula 6")+COUNTIF('C121'!G11,"Aula 6")+COUNTIF('C122'!G11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 6")+COUNTIF('C112'!G11,"Aula 6")+COUNTIF('C113'!G11,"Aula 6")+COUNTIF('C121'!G11,"Aula 6")+COUNTIF('C122'!G11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 6")+COUNTIF('C112'!G11,"Aula 6")+COUNTIF('C113'!G11,"Aula 6")+COUNTIF('C121'!G11,"Aula 6")+COUNTIF('C122'!G11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 6")+COUNTIF('C112'!F11,"Aula 6")+COUNTIF('C113'!F11,"Aula 6")+COUNTIF('C121'!F11,"Aula 6")+COUNTIF('C122'!F11,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 6")+COUNTIF('C112'!F11,"Aula 6")+COUNTIF('C113'!F11,"Aula 6")+COUNTIF('C121'!F11,"Aula 6")+COUNTIF('C122'!F11,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 6")+COUNTIF('C112'!F11,"Aula 6")+COUNTIF('C113'!F11,"Aula 6")+COUNTIF('C121'!F11,"Aula 6")+COUNTIF('C122'!F11,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="277">
       <c r="C277">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 7")+COUNTIF('C112'!G11,"Aula 7")+COUNTIF('C113'!G11,"Aula 7")+COUNTIF('C121'!G11,"Aula 7")+COUNTIF('C122'!G11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 7")+COUNTIF('C112'!G11,"Aula 7")+COUNTIF('C113'!G11,"Aula 7")+COUNTIF('C121'!G11,"Aula 7")+COUNTIF('C122'!G11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 7")+COUNTIF('C112'!G11,"Aula 7")+COUNTIF('C113'!G11,"Aula 7")+COUNTIF('C121'!G11,"Aula 7")+COUNTIF('C122'!G11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 7")+COUNTIF('C112'!F11,"Aula 7")+COUNTIF('C113'!F11,"Aula 7")+COUNTIF('C121'!F11,"Aula 7")+COUNTIF('C122'!F11,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 7")+COUNTIF('C112'!F11,"Aula 7")+COUNTIF('C113'!F11,"Aula 7")+COUNTIF('C121'!F11,"Aula 7")+COUNTIF('C122'!F11,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 7")+COUNTIF('C112'!F11,"Aula 7")+COUNTIF('C113'!F11,"Aula 7")+COUNTIF('C121'!F11,"Aula 7")+COUNTIF('C122'!F11,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="278">
       <c r="C278">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 8")+COUNTIF('C112'!G11,"Aula 8")+COUNTIF('C113'!G11,"Aula 8")+COUNTIF('C121'!G11,"Aula 8")+COUNTIF('C122'!G11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 8")+COUNTIF('C112'!G11,"Aula 8")+COUNTIF('C113'!G11,"Aula 8")+COUNTIF('C121'!G11,"Aula 8")+COUNTIF('C122'!G11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 8")+COUNTIF('C112'!G11,"Aula 8")+COUNTIF('C113'!G11,"Aula 8")+COUNTIF('C121'!G11,"Aula 8")+COUNTIF('C122'!G11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 8")+COUNTIF('C112'!F11,"Aula 8")+COUNTIF('C113'!F11,"Aula 8")+COUNTIF('C121'!F11,"Aula 8")+COUNTIF('C122'!F11,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 8")+COUNTIF('C112'!F11,"Aula 8")+COUNTIF('C113'!F11,"Aula 8")+COUNTIF('C121'!F11,"Aula 8")+COUNTIF('C122'!F11,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 8")+COUNTIF('C112'!F11,"Aula 8")+COUNTIF('C113'!F11,"Aula 8")+COUNTIF('C121'!F11,"Aula 8")+COUNTIF('C122'!F11,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="279">
       <c r="C279">
-        <f>IF((IF((COUNTIF('C111'!G11,"Aula 9")+COUNTIF('C112'!G11,"Aula 9")+COUNTIF('C113'!G11,"Aula 9")+COUNTIF('C121'!G11,"Aula 9")+COUNTIF('C122'!G11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Aula 9")+COUNTIF('C112'!G11,"Aula 9")+COUNTIF('C113'!G11,"Aula 9")+COUNTIF('C121'!G11,"Aula 9")+COUNTIF('C122'!G11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Aula 9")+COUNTIF('C112'!G11,"Aula 9")+COUNTIF('C113'!G11,"Aula 9")+COUNTIF('C121'!G11,"Aula 9")+COUNTIF('C122'!G11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Aula 9")+COUNTIF('C112'!F11,"Aula 9")+COUNTIF('C113'!F11,"Aula 9")+COUNTIF('C121'!F11,"Aula 9")+COUNTIF('C122'!F11,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Aula 9")+COUNTIF('C112'!F11,"Aula 9")+COUNTIF('C113'!F11,"Aula 9")+COUNTIF('C121'!F11,"Aula 9")+COUNTIF('C122'!F11,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Aula 9")+COUNTIF('C112'!F11,"Aula 9")+COUNTIF('C113'!F11,"Aula 9")+COUNTIF('C121'!F11,"Aula 9")+COUNTIF('C122'!F11,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="280">
       <c r="C280">
-        <f>IF((IF((COUNTIF('C111'!G11,"Lab")+COUNTIF('C112'!G11,"Lab")+COUNTIF('C113'!G11,"Lab")+COUNTIF('C121'!G11,"Lab")+COUNTIF('C122'!G11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G11,"Lab")+COUNTIF('C112'!G11,"Lab")+COUNTIF('C113'!G11,"Lab")+COUNTIF('C121'!G11,"Lab")+COUNTIF('C122'!G11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G11,"Lab")+COUNTIF('C112'!G11,"Lab")+COUNTIF('C113'!G11,"Lab")+COUNTIF('C121'!G11,"Lab")+COUNTIF('C122'!G11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F11,"Lab")+COUNTIF('C112'!F11,"Lab")+COUNTIF('C113'!F11,"Lab")+COUNTIF('C121'!F11,"Lab")+COUNTIF('C122'!F11,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F11,"Lab")+COUNTIF('C112'!F11,"Lab")+COUNTIF('C113'!F11,"Lab")+COUNTIF('C121'!F11,"Lab")+COUNTIF('C122'!F11,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F11,"Lab")+COUNTIF('C112'!F11,"Lab")+COUNTIF('C113'!F11,"Lab")+COUNTIF('C121'!F11,"Lab")+COUNTIF('C122'!F11,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="C281">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 1")+COUNTIF('C112'!G13,"Aula 1")+COUNTIF('C113'!G13,"Aula 1")+COUNTIF('C121'!G13,"Aula 1")+COUNTIF('C122'!G13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 1")+COUNTIF('C112'!G13,"Aula 1")+COUNTIF('C113'!G13,"Aula 1")+COUNTIF('C121'!G13,"Aula 1")+COUNTIF('C122'!G13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 1")+COUNTIF('C112'!G13,"Aula 1")+COUNTIF('C113'!G13,"Aula 1")+COUNTIF('C121'!G13,"Aula 1")+COUNTIF('C122'!G13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 1")+COUNTIF('C112'!F13,"Aula 1")+COUNTIF('C113'!F13,"Aula 1")+COUNTIF('C121'!F13,"Aula 1")+COUNTIF('C122'!F13,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 1")+COUNTIF('C112'!F13,"Aula 1")+COUNTIF('C113'!F13,"Aula 1")+COUNTIF('C121'!F13,"Aula 1")+COUNTIF('C122'!F13,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 1")+COUNTIF('C112'!F13,"Aula 1")+COUNTIF('C113'!F13,"Aula 1")+COUNTIF('C121'!F13,"Aula 1")+COUNTIF('C122'!F13,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="282">
       <c r="C282">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 2")+COUNTIF('C112'!G13,"Aula 2")+COUNTIF('C113'!G13,"Aula 2")+COUNTIF('C121'!G13,"Aula 2")+COUNTIF('C122'!G13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 2")+COUNTIF('C112'!G13,"Aula 2")+COUNTIF('C113'!G13,"Aula 2")+COUNTIF('C121'!G13,"Aula 2")+COUNTIF('C122'!G13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 2")+COUNTIF('C112'!G13,"Aula 2")+COUNTIF('C113'!G13,"Aula 2")+COUNTIF('C121'!G13,"Aula 2")+COUNTIF('C122'!G13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 2")+COUNTIF('C112'!F13,"Aula 2")+COUNTIF('C113'!F13,"Aula 2")+COUNTIF('C121'!F13,"Aula 2")+COUNTIF('C122'!F13,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 2")+COUNTIF('C112'!F13,"Aula 2")+COUNTIF('C113'!F13,"Aula 2")+COUNTIF('C121'!F13,"Aula 2")+COUNTIF('C122'!F13,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 2")+COUNTIF('C112'!F13,"Aula 2")+COUNTIF('C113'!F13,"Aula 2")+COUNTIF('C121'!F13,"Aula 2")+COUNTIF('C122'!F13,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="283">
       <c r="C283">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 3")+COUNTIF('C112'!G13,"Aula 3")+COUNTIF('C113'!G13,"Aula 3")+COUNTIF('C121'!G13,"Aula 3")+COUNTIF('C122'!G13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 3")+COUNTIF('C112'!G13,"Aula 3")+COUNTIF('C113'!G13,"Aula 3")+COUNTIF('C121'!G13,"Aula 3")+COUNTIF('C122'!G13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 3")+COUNTIF('C112'!G13,"Aula 3")+COUNTIF('C113'!G13,"Aula 3")+COUNTIF('C121'!G13,"Aula 3")+COUNTIF('C122'!G13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 3")+COUNTIF('C112'!F13,"Aula 3")+COUNTIF('C113'!F13,"Aula 3")+COUNTIF('C121'!F13,"Aula 3")+COUNTIF('C122'!F13,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 3")+COUNTIF('C112'!F13,"Aula 3")+COUNTIF('C113'!F13,"Aula 3")+COUNTIF('C121'!F13,"Aula 3")+COUNTIF('C122'!F13,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 3")+COUNTIF('C112'!F13,"Aula 3")+COUNTIF('C113'!F13,"Aula 3")+COUNTIF('C121'!F13,"Aula 3")+COUNTIF('C122'!F13,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="C284">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 4")+COUNTIF('C112'!G13,"Aula 4")+COUNTIF('C113'!G13,"Aula 4")+COUNTIF('C121'!G13,"Aula 4")+COUNTIF('C122'!G13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 4")+COUNTIF('C112'!G13,"Aula 4")+COUNTIF('C113'!G13,"Aula 4")+COUNTIF('C121'!G13,"Aula 4")+COUNTIF('C122'!G13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 4")+COUNTIF('C112'!G13,"Aula 4")+COUNTIF('C113'!G13,"Aula 4")+COUNTIF('C121'!G13,"Aula 4")+COUNTIF('C122'!G13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 4")+COUNTIF('C112'!F13,"Aula 4")+COUNTIF('C113'!F13,"Aula 4")+COUNTIF('C121'!F13,"Aula 4")+COUNTIF('C122'!F13,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 4")+COUNTIF('C112'!F13,"Aula 4")+COUNTIF('C113'!F13,"Aula 4")+COUNTIF('C121'!F13,"Aula 4")+COUNTIF('C122'!F13,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 4")+COUNTIF('C112'!F13,"Aula 4")+COUNTIF('C113'!F13,"Aula 4")+COUNTIF('C121'!F13,"Aula 4")+COUNTIF('C122'!F13,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="285">
       <c r="C285">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 5")+COUNTIF('C112'!G13,"Aula 5")+COUNTIF('C113'!G13,"Aula 5")+COUNTIF('C121'!G13,"Aula 5")+COUNTIF('C122'!G13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 5")+COUNTIF('C112'!G13,"Aula 5")+COUNTIF('C113'!G13,"Aula 5")+COUNTIF('C121'!G13,"Aula 5")+COUNTIF('C122'!G13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 5")+COUNTIF('C112'!G13,"Aula 5")+COUNTIF('C113'!G13,"Aula 5")+COUNTIF('C121'!G13,"Aula 5")+COUNTIF('C122'!G13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 5")+COUNTIF('C112'!F13,"Aula 5")+COUNTIF('C113'!F13,"Aula 5")+COUNTIF('C121'!F13,"Aula 5")+COUNTIF('C122'!F13,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 5")+COUNTIF('C112'!F13,"Aula 5")+COUNTIF('C113'!F13,"Aula 5")+COUNTIF('C121'!F13,"Aula 5")+COUNTIF('C122'!F13,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 5")+COUNTIF('C112'!F13,"Aula 5")+COUNTIF('C113'!F13,"Aula 5")+COUNTIF('C121'!F13,"Aula 5")+COUNTIF('C122'!F13,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="286">
       <c r="C286">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 6")+COUNTIF('C112'!G13,"Aula 6")+COUNTIF('C113'!G13,"Aula 6")+COUNTIF('C121'!G13,"Aula 6")+COUNTIF('C122'!G13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 6")+COUNTIF('C112'!G13,"Aula 6")+COUNTIF('C113'!G13,"Aula 6")+COUNTIF('C121'!G13,"Aula 6")+COUNTIF('C122'!G13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 6")+COUNTIF('C112'!G13,"Aula 6")+COUNTIF('C113'!G13,"Aula 6")+COUNTIF('C121'!G13,"Aula 6")+COUNTIF('C122'!G13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 6")+COUNTIF('C112'!F13,"Aula 6")+COUNTIF('C113'!F13,"Aula 6")+COUNTIF('C121'!F13,"Aula 6")+COUNTIF('C122'!F13,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 6")+COUNTIF('C112'!F13,"Aula 6")+COUNTIF('C113'!F13,"Aula 6")+COUNTIF('C121'!F13,"Aula 6")+COUNTIF('C122'!F13,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 6")+COUNTIF('C112'!F13,"Aula 6")+COUNTIF('C113'!F13,"Aula 6")+COUNTIF('C121'!F13,"Aula 6")+COUNTIF('C122'!F13,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="287">
       <c r="C287">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 7")+COUNTIF('C112'!G13,"Aula 7")+COUNTIF('C113'!G13,"Aula 7")+COUNTIF('C121'!G13,"Aula 7")+COUNTIF('C122'!G13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 7")+COUNTIF('C112'!G13,"Aula 7")+COUNTIF('C113'!G13,"Aula 7")+COUNTIF('C121'!G13,"Aula 7")+COUNTIF('C122'!G13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 7")+COUNTIF('C112'!G13,"Aula 7")+COUNTIF('C113'!G13,"Aula 7")+COUNTIF('C121'!G13,"Aula 7")+COUNTIF('C122'!G13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 7")+COUNTIF('C112'!F13,"Aula 7")+COUNTIF('C113'!F13,"Aula 7")+COUNTIF('C121'!F13,"Aula 7")+COUNTIF('C122'!F13,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 7")+COUNTIF('C112'!F13,"Aula 7")+COUNTIF('C113'!F13,"Aula 7")+COUNTIF('C121'!F13,"Aula 7")+COUNTIF('C122'!F13,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 7")+COUNTIF('C112'!F13,"Aula 7")+COUNTIF('C113'!F13,"Aula 7")+COUNTIF('C121'!F13,"Aula 7")+COUNTIF('C122'!F13,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="288">
       <c r="C288">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 8")+COUNTIF('C112'!G13,"Aula 8")+COUNTIF('C113'!G13,"Aula 8")+COUNTIF('C121'!G13,"Aula 8")+COUNTIF('C122'!G13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 8")+COUNTIF('C112'!G13,"Aula 8")+COUNTIF('C113'!G13,"Aula 8")+COUNTIF('C121'!G13,"Aula 8")+COUNTIF('C122'!G13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 8")+COUNTIF('C112'!G13,"Aula 8")+COUNTIF('C113'!G13,"Aula 8")+COUNTIF('C121'!G13,"Aula 8")+COUNTIF('C122'!G13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 8")+COUNTIF('C112'!F13,"Aula 8")+COUNTIF('C113'!F13,"Aula 8")+COUNTIF('C121'!F13,"Aula 8")+COUNTIF('C122'!F13,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 8")+COUNTIF('C112'!F13,"Aula 8")+COUNTIF('C113'!F13,"Aula 8")+COUNTIF('C121'!F13,"Aula 8")+COUNTIF('C122'!F13,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 8")+COUNTIF('C112'!F13,"Aula 8")+COUNTIF('C113'!F13,"Aula 8")+COUNTIF('C121'!F13,"Aula 8")+COUNTIF('C122'!F13,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="289">
       <c r="C289">
-        <f>IF((IF((COUNTIF('C111'!G13,"Aula 9")+COUNTIF('C112'!G13,"Aula 9")+COUNTIF('C113'!G13,"Aula 9")+COUNTIF('C121'!G13,"Aula 9")+COUNTIF('C122'!G13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Aula 9")+COUNTIF('C112'!G13,"Aula 9")+COUNTIF('C113'!G13,"Aula 9")+COUNTIF('C121'!G13,"Aula 9")+COUNTIF('C122'!G13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Aula 9")+COUNTIF('C112'!G13,"Aula 9")+COUNTIF('C113'!G13,"Aula 9")+COUNTIF('C121'!G13,"Aula 9")+COUNTIF('C122'!G13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Aula 9")+COUNTIF('C112'!F13,"Aula 9")+COUNTIF('C113'!F13,"Aula 9")+COUNTIF('C121'!F13,"Aula 9")+COUNTIF('C122'!F13,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Aula 9")+COUNTIF('C112'!F13,"Aula 9")+COUNTIF('C113'!F13,"Aula 9")+COUNTIF('C121'!F13,"Aula 9")+COUNTIF('C122'!F13,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Aula 9")+COUNTIF('C112'!F13,"Aula 9")+COUNTIF('C113'!F13,"Aula 9")+COUNTIF('C121'!F13,"Aula 9")+COUNTIF('C122'!F13,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="290">
       <c r="C290">
-        <f>IF((IF((COUNTIF('C111'!G13,"Lab")+COUNTIF('C112'!G13,"Lab")+COUNTIF('C113'!G13,"Lab")+COUNTIF('C121'!G13,"Lab")+COUNTIF('C122'!G13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G13,"Lab")+COUNTIF('C112'!G13,"Lab")+COUNTIF('C113'!G13,"Lab")+COUNTIF('C121'!G13,"Lab")+COUNTIF('C122'!G13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G13,"Lab")+COUNTIF('C112'!G13,"Lab")+COUNTIF('C113'!G13,"Lab")+COUNTIF('C121'!G13,"Lab")+COUNTIF('C122'!G13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F13,"Lab")+COUNTIF('C112'!F13,"Lab")+COUNTIF('C113'!F13,"Lab")+COUNTIF('C121'!F13,"Lab")+COUNTIF('C122'!F13,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F13,"Lab")+COUNTIF('C112'!F13,"Lab")+COUNTIF('C113'!F13,"Lab")+COUNTIF('C121'!F13,"Lab")+COUNTIF('C122'!F13,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F13,"Lab")+COUNTIF('C112'!F13,"Lab")+COUNTIF('C113'!F13,"Lab")+COUNTIF('C121'!F13,"Lab")+COUNTIF('C122'!F13,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="291">
       <c r="C291">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 1")+COUNTIF('C112'!G15,"Aula 1")+COUNTIF('C113'!G15,"Aula 1")+COUNTIF('C121'!G15,"Aula 1")+COUNTIF('C122'!G15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 1")+COUNTIF('C112'!G15,"Aula 1")+COUNTIF('C113'!G15,"Aula 1")+COUNTIF('C121'!G15,"Aula 1")+COUNTIF('C122'!G15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 1")+COUNTIF('C112'!G15,"Aula 1")+COUNTIF('C113'!G15,"Aula 1")+COUNTIF('C121'!G15,"Aula 1")+COUNTIF('C122'!G15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 1")+COUNTIF('C112'!F15,"Aula 1")+COUNTIF('C113'!F15,"Aula 1")+COUNTIF('C121'!F15,"Aula 1")+COUNTIF('C122'!F15,"Aula 1"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 1")+COUNTIF('C112'!F15,"Aula 1")+COUNTIF('C113'!F15,"Aula 1")+COUNTIF('C121'!F15,"Aula 1")+COUNTIF('C122'!F15,"Aula 1"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 1")+COUNTIF('C112'!F15,"Aula 1")+COUNTIF('C113'!F15,"Aula 1")+COUNTIF('C121'!F15,"Aula 1")+COUNTIF('C122'!F15,"Aula 1"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="292">
       <c r="C292">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 2")+COUNTIF('C112'!G15,"Aula 2")+COUNTIF('C113'!G15,"Aula 2")+COUNTIF('C121'!G15,"Aula 2")+COUNTIF('C122'!G15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 2")+COUNTIF('C112'!G15,"Aula 2")+COUNTIF('C113'!G15,"Aula 2")+COUNTIF('C121'!G15,"Aula 2")+COUNTIF('C122'!G15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 2")+COUNTIF('C112'!G15,"Aula 2")+COUNTIF('C113'!G15,"Aula 2")+COUNTIF('C121'!G15,"Aula 2")+COUNTIF('C122'!G15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 2")+COUNTIF('C112'!F15,"Aula 2")+COUNTIF('C113'!F15,"Aula 2")+COUNTIF('C121'!F15,"Aula 2")+COUNTIF('C122'!F15,"Aula 2"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 2")+COUNTIF('C112'!F15,"Aula 2")+COUNTIF('C113'!F15,"Aula 2")+COUNTIF('C121'!F15,"Aula 2")+COUNTIF('C122'!F15,"Aula 2"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 2")+COUNTIF('C112'!F15,"Aula 2")+COUNTIF('C113'!F15,"Aula 2")+COUNTIF('C121'!F15,"Aula 2")+COUNTIF('C122'!F15,"Aula 2"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="293">
       <c r="C293">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 3")+COUNTIF('C112'!G15,"Aula 3")+COUNTIF('C113'!G15,"Aula 3")+COUNTIF('C121'!G15,"Aula 3")+COUNTIF('C122'!G15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 3")+COUNTIF('C112'!G15,"Aula 3")+COUNTIF('C113'!G15,"Aula 3")+COUNTIF('C121'!G15,"Aula 3")+COUNTIF('C122'!G15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 3")+COUNTIF('C112'!G15,"Aula 3")+COUNTIF('C113'!G15,"Aula 3")+COUNTIF('C121'!G15,"Aula 3")+COUNTIF('C122'!G15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 3")+COUNTIF('C112'!F15,"Aula 3")+COUNTIF('C113'!F15,"Aula 3")+COUNTIF('C121'!F15,"Aula 3")+COUNTIF('C122'!F15,"Aula 3"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 3")+COUNTIF('C112'!F15,"Aula 3")+COUNTIF('C113'!F15,"Aula 3")+COUNTIF('C121'!F15,"Aula 3")+COUNTIF('C122'!F15,"Aula 3"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 3")+COUNTIF('C112'!F15,"Aula 3")+COUNTIF('C113'!F15,"Aula 3")+COUNTIF('C121'!F15,"Aula 3")+COUNTIF('C122'!F15,"Aula 3"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="C294">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 4")+COUNTIF('C112'!G15,"Aula 4")+COUNTIF('C113'!G15,"Aula 4")+COUNTIF('C121'!G15,"Aula 4")+COUNTIF('C122'!G15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 4")+COUNTIF('C112'!G15,"Aula 4")+COUNTIF('C113'!G15,"Aula 4")+COUNTIF('C121'!G15,"Aula 4")+COUNTIF('C122'!G15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 4")+COUNTIF('C112'!G15,"Aula 4")+COUNTIF('C113'!G15,"Aula 4")+COUNTIF('C121'!G15,"Aula 4")+COUNTIF('C122'!G15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 4")+COUNTIF('C112'!F15,"Aula 4")+COUNTIF('C113'!F15,"Aula 4")+COUNTIF('C121'!F15,"Aula 4")+COUNTIF('C122'!F15,"Aula 4"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 4")+COUNTIF('C112'!F15,"Aula 4")+COUNTIF('C113'!F15,"Aula 4")+COUNTIF('C121'!F15,"Aula 4")+COUNTIF('C122'!F15,"Aula 4"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 4")+COUNTIF('C112'!F15,"Aula 4")+COUNTIF('C113'!F15,"Aula 4")+COUNTIF('C121'!F15,"Aula 4")+COUNTIF('C122'!F15,"Aula 4"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="295">
       <c r="C295">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 5")+COUNTIF('C112'!G15,"Aula 5")+COUNTIF('C113'!G15,"Aula 5")+COUNTIF('C121'!G15,"Aula 5")+COUNTIF('C122'!G15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 5")+COUNTIF('C112'!G15,"Aula 5")+COUNTIF('C113'!G15,"Aula 5")+COUNTIF('C121'!G15,"Aula 5")+COUNTIF('C122'!G15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 5")+COUNTIF('C112'!G15,"Aula 5")+COUNTIF('C113'!G15,"Aula 5")+COUNTIF('C121'!G15,"Aula 5")+COUNTIF('C122'!G15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 5")+COUNTIF('C112'!F15,"Aula 5")+COUNTIF('C113'!F15,"Aula 5")+COUNTIF('C121'!F15,"Aula 5")+COUNTIF('C122'!F15,"Aula 5"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 5")+COUNTIF('C112'!F15,"Aula 5")+COUNTIF('C113'!F15,"Aula 5")+COUNTIF('C121'!F15,"Aula 5")+COUNTIF('C122'!F15,"Aula 5"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 5")+COUNTIF('C112'!F15,"Aula 5")+COUNTIF('C113'!F15,"Aula 5")+COUNTIF('C121'!F15,"Aula 5")+COUNTIF('C122'!F15,"Aula 5"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="296">
       <c r="C296">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 6")+COUNTIF('C112'!G15,"Aula 6")+COUNTIF('C113'!G15,"Aula 6")+COUNTIF('C121'!G15,"Aula 6")+COUNTIF('C122'!G15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 6")+COUNTIF('C112'!G15,"Aula 6")+COUNTIF('C113'!G15,"Aula 6")+COUNTIF('C121'!G15,"Aula 6")+COUNTIF('C122'!G15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 6")+COUNTIF('C112'!G15,"Aula 6")+COUNTIF('C113'!G15,"Aula 6")+COUNTIF('C121'!G15,"Aula 6")+COUNTIF('C122'!G15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 6")+COUNTIF('C112'!F15,"Aula 6")+COUNTIF('C113'!F15,"Aula 6")+COUNTIF('C121'!F15,"Aula 6")+COUNTIF('C122'!F15,"Aula 6"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 6")+COUNTIF('C112'!F15,"Aula 6")+COUNTIF('C113'!F15,"Aula 6")+COUNTIF('C121'!F15,"Aula 6")+COUNTIF('C122'!F15,"Aula 6"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 6")+COUNTIF('C112'!F15,"Aula 6")+COUNTIF('C113'!F15,"Aula 6")+COUNTIF('C121'!F15,"Aula 6")+COUNTIF('C122'!F15,"Aula 6"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="297">
       <c r="C297">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 7")+COUNTIF('C112'!G15,"Aula 7")+COUNTIF('C113'!G15,"Aula 7")+COUNTIF('C121'!G15,"Aula 7")+COUNTIF('C122'!G15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 7")+COUNTIF('C112'!G15,"Aula 7")+COUNTIF('C113'!G15,"Aula 7")+COUNTIF('C121'!G15,"Aula 7")+COUNTIF('C122'!G15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 7")+COUNTIF('C112'!G15,"Aula 7")+COUNTIF('C113'!G15,"Aula 7")+COUNTIF('C121'!G15,"Aula 7")+COUNTIF('C122'!G15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 7")+COUNTIF('C112'!F15,"Aula 7")+COUNTIF('C113'!F15,"Aula 7")+COUNTIF('C121'!F15,"Aula 7")+COUNTIF('C122'!F15,"Aula 7"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 7")+COUNTIF('C112'!F15,"Aula 7")+COUNTIF('C113'!F15,"Aula 7")+COUNTIF('C121'!F15,"Aula 7")+COUNTIF('C122'!F15,"Aula 7"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 7")+COUNTIF('C112'!F15,"Aula 7")+COUNTIF('C113'!F15,"Aula 7")+COUNTIF('C121'!F15,"Aula 7")+COUNTIF('C122'!F15,"Aula 7"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="298">
       <c r="C298">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 8")+COUNTIF('C112'!G15,"Aula 8")+COUNTIF('C113'!G15,"Aula 8")+COUNTIF('C121'!G15,"Aula 8")+COUNTIF('C122'!G15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 8")+COUNTIF('C112'!G15,"Aula 8")+COUNTIF('C113'!G15,"Aula 8")+COUNTIF('C121'!G15,"Aula 8")+COUNTIF('C122'!G15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 8")+COUNTIF('C112'!G15,"Aula 8")+COUNTIF('C113'!G15,"Aula 8")+COUNTIF('C121'!G15,"Aula 8")+COUNTIF('C122'!G15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 8")+COUNTIF('C112'!F15,"Aula 8")+COUNTIF('C113'!F15,"Aula 8")+COUNTIF('C121'!F15,"Aula 8")+COUNTIF('C122'!F15,"Aula 8"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 8")+COUNTIF('C112'!F15,"Aula 8")+COUNTIF('C113'!F15,"Aula 8")+COUNTIF('C121'!F15,"Aula 8")+COUNTIF('C122'!F15,"Aula 8"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 8")+COUNTIF('C112'!F15,"Aula 8")+COUNTIF('C113'!F15,"Aula 8")+COUNTIF('C121'!F15,"Aula 8")+COUNTIF('C122'!F15,"Aula 8"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="C299">
-        <f>IF((IF((COUNTIF('C111'!G15,"Aula 9")+COUNTIF('C112'!G15,"Aula 9")+COUNTIF('C113'!G15,"Aula 9")+COUNTIF('C121'!G15,"Aula 9")+COUNTIF('C122'!G15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Aula 9")+COUNTIF('C112'!G15,"Aula 9")+COUNTIF('C113'!G15,"Aula 9")+COUNTIF('C121'!G15,"Aula 9")+COUNTIF('C122'!G15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Aula 9")+COUNTIF('C112'!G15,"Aula 9")+COUNTIF('C113'!G15,"Aula 9")+COUNTIF('C121'!G15,"Aula 9")+COUNTIF('C122'!G15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Aula 9")+COUNTIF('C112'!F15,"Aula 9")+COUNTIF('C113'!F15,"Aula 9")+COUNTIF('C121'!F15,"Aula 9")+COUNTIF('C122'!F15,"Aula 9"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Aula 9")+COUNTIF('C112'!F15,"Aula 9")+COUNTIF('C113'!F15,"Aula 9")+COUNTIF('C121'!F15,"Aula 9")+COUNTIF('C122'!F15,"Aula 9"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Aula 9")+COUNTIF('C112'!F15,"Aula 9")+COUNTIF('C113'!F15,"Aula 9")+COUNTIF('C121'!F15,"Aula 9")+COUNTIF('C122'!F15,"Aula 9"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
     <row r="300">
       <c r="C300">
-        <f>IF((IF((COUNTIF('C111'!G15,"Lab")+COUNTIF('C112'!G15,"Lab")+COUNTIF('C113'!G15,"Lab")+COUNTIF('C121'!G15,"Lab")+COUNTIF('C122'!G15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!G15,"Lab")+COUNTIF('C112'!G15,"Lab")+COUNTIF('C113'!G15,"Lab")+COUNTIF('C121'!G15,"Lab")+COUNTIF('C122'!G15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!G15,"Lab")+COUNTIF('C112'!G15,"Lab")+COUNTIF('C113'!G15,"Lab")+COUNTIF('C121'!G15,"Lab")+COUNTIF('C122'!G15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
+        <f>IF((IF((COUNTIF('C111'!F15,"Lab")+COUNTIF('C112'!F15,"Lab")+COUNTIF('C113'!F15,"Lab")+COUNTIF('C121'!F15,"Lab")+COUNTIF('C122'!F15,"Lab"))&gt;0,1,0))=0,"",IF((IF((COUNTIF('C111'!F15,"Lab")+COUNTIF('C112'!F15,"Lab")+COUNTIF('C113'!F15,"Lab")+COUNTIF('C121'!F15,"Lab")+COUNTIF('C122'!F15,"Lab"))&gt;0,1,0))=1,IF((COUNTIF('C111'!F15,"Lab")+COUNTIF('C112'!F15,"Lab")+COUNTIF('C113'!F15,"Lab")+COUNTIF('C121'!F15,"Lab")+COUNTIF('C122'!F15,"Lab"))&gt;0,"C1",""),"MIX"))</f>
         <v/>
       </c>
     </row>
@@ -6444,8 +6714,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6459,505 +6742,586 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Asignadas</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>Faltan</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (Conf)</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L4">
-        <f>COUNTIF(C4:G15,I4)</f>
-        <v/>
-      </c>
-      <c r="M4">
+      <c r="L4" s="18">
+        <f>COUNTIF(B4:F15,I4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="19">
         <f>K4-L4</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (C.P.)</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L5">
-        <f>COUNTIF(C4:G15,I5)</f>
-        <v/>
-      </c>
-      <c r="M5">
+      <c r="L5" s="18">
+        <f>COUNTIF(B4:F15,I5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
         <f>K5-L5</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Programación (Conf)</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L6">
-        <f>COUNTIF(C4:G15,I6)</f>
-        <v/>
-      </c>
-      <c r="M6">
+      <c r="L6" s="18">
+        <f>COUNTIF(B4:F15,I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="19">
         <f>K6-L6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Programación (C.P.)</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L7">
-        <f>COUNTIF(C4:G15,I7)</f>
-        <v/>
-      </c>
-      <c r="M7">
+      <c r="L7" s="18">
+        <f>COUNTIF(B4:F15,I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
         <f>K7-L7</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="F8" s="19" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (Conf)</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L8">
-        <f>COUNTIF(C4:G15,I8)</f>
-        <v/>
-      </c>
-      <c r="M8">
+      <c r="L8" s="18">
+        <f>COUNTIF(B4:F15,I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="19">
         <f>K8-L8</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Aula 2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (C.P.)</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L9">
-        <f>COUNTIF(C4:G15,I9)</f>
-        <v/>
-      </c>
-      <c r="M9">
+      <c r="L9" s="18">
+        <f>COUNTIF(B4:F15,I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
         <f>K9-L9</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Filosofía (Conf)</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L10">
-        <f>COUNTIF(C4:G15,I10)</f>
-        <v/>
-      </c>
-      <c r="M10">
+      <c r="L10" s="18">
+        <f>COUNTIF(B4:F15,I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
         <f>K10-L10</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="I11" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Filosofía (C.P.)</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L11">
-        <f>COUNTIF(C4:G15,I11)</f>
-        <v/>
-      </c>
-      <c r="M11">
+      <c r="L11" s="18">
+        <f>COUNTIF(B4:F15,I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
         <f>K11-L11</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>Lógica (Conf)</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L12">
-        <f>COUNTIF(C4:G15,I12)</f>
-        <v/>
-      </c>
-      <c r="M12">
+      <c r="L12" s="18">
+        <f>COUNTIF(B4:F15,I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
         <f>K12-L12</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="I13" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Lógica (C.P.)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L13">
-        <f>COUNTIF(C4:G15,I13)</f>
-        <v/>
-      </c>
-      <c r="M13">
+      <c r="L13" s="18">
+        <f>COUNTIF(B4:F15,I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
         <f>K13-L13</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Educación Física</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="L14">
-        <f>COUNTIF(C4:G15,I14)</f>
-        <v/>
-      </c>
-      <c r="M14">
+      <c r="L14" s="26">
+        <f>COUNTIF(B4:F15,I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
         <f>K14-L14</f>
         <v/>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Leyenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aula fuera del listado de la facultad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Asignatura fuera de la tabla del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sobre-planificada (asignadas &gt; frecuencia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Frecuencia exacta cumplida</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14">
+  <conditionalFormatting sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(C4&lt;&gt;"",COUNTIF($I$4:$I$14,C4)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15">
+      <formula>AND(B4&lt;&gt;"",COUNTIF($I$4:$I$14,B4)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(C5&lt;&gt;"",COUNTIF(AulasValidas,C5)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L14">
+      <formula>AND(B5&lt;&gt;"",COUNTIF(AulasValidas,B5)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:M14">
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>L4&gt;K4</formula>
+      <formula>$L4&gt;$K4</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>L4=K4</formula>
+      <formula>$L4=$K4</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>AulasValidas</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>$I$4:$I$14</formula1>
     </dataValidation>
   </dataValidations>
@@ -6971,8 +7335,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6986,505 +7363,586 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Asignadas</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>Faltan</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (Conf)</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L4">
-        <f>COUNTIF(C4:G15,I4)</f>
-        <v/>
-      </c>
-      <c r="M4">
+      <c r="L4" s="18">
+        <f>COUNTIF(B4:F15,I4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="19">
         <f>K4-L4</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (C.P.)</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L5">
-        <f>COUNTIF(C4:G15,I5)</f>
-        <v/>
-      </c>
-      <c r="M5">
+      <c r="L5" s="18">
+        <f>COUNTIF(B4:F15,I5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
         <f>K5-L5</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Programación (Conf)</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L6">
-        <f>COUNTIF(C4:G15,I6)</f>
-        <v/>
-      </c>
-      <c r="M6">
+      <c r="L6" s="18">
+        <f>COUNTIF(B4:F15,I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="19">
         <f>K6-L6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Programación (C.P.)</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L7">
-        <f>COUNTIF(C4:G15,I7)</f>
-        <v/>
-      </c>
-      <c r="M7">
+      <c r="L7" s="18">
+        <f>COUNTIF(B4:F15,I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
         <f>K7-L7</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="F8" s="19" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (Conf)</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L8">
-        <f>COUNTIF(C4:G15,I8)</f>
-        <v/>
-      </c>
-      <c r="M8">
+      <c r="L8" s="18">
+        <f>COUNTIF(B4:F15,I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="19">
         <f>K8-L8</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Aula 3</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (C.P.)</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L9">
-        <f>COUNTIF(C4:G15,I9)</f>
-        <v/>
-      </c>
-      <c r="M9">
+      <c r="L9" s="18">
+        <f>COUNTIF(B4:F15,I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
         <f>K9-L9</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Filosofía (Conf)</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L10">
-        <f>COUNTIF(C4:G15,I10)</f>
-        <v/>
-      </c>
-      <c r="M10">
+      <c r="L10" s="18">
+        <f>COUNTIF(B4:F15,I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
         <f>K10-L10</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="I11" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Filosofía (C.P.)</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L11">
-        <f>COUNTIF(C4:G15,I11)</f>
-        <v/>
-      </c>
-      <c r="M11">
+      <c r="L11" s="18">
+        <f>COUNTIF(B4:F15,I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
         <f>K11-L11</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>Lógica (Conf)</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L12">
-        <f>COUNTIF(C4:G15,I12)</f>
-        <v/>
-      </c>
-      <c r="M12">
+      <c r="L12" s="18">
+        <f>COUNTIF(B4:F15,I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
         <f>K12-L12</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="I13" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Lógica (C.P.)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L13">
-        <f>COUNTIF(C4:G15,I13)</f>
-        <v/>
-      </c>
-      <c r="M13">
+      <c r="L13" s="18">
+        <f>COUNTIF(B4:F15,I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
         <f>K13-L13</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Educación Física</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="L14">
-        <f>COUNTIF(C4:G15,I14)</f>
-        <v/>
-      </c>
-      <c r="M14">
+      <c r="L14" s="26">
+        <f>COUNTIF(B4:F15,I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
         <f>K14-L14</f>
         <v/>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Leyenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aula fuera del listado de la facultad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Asignatura fuera de la tabla del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sobre-planificada (asignadas &gt; frecuencia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Frecuencia exacta cumplida</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14">
+  <conditionalFormatting sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(C4&lt;&gt;"",COUNTIF($I$4:$I$14,C4)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15">
+      <formula>AND(B4&lt;&gt;"",COUNTIF($I$4:$I$14,B4)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(C5&lt;&gt;"",COUNTIF(AulasValidas,C5)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L14">
+      <formula>AND(B5&lt;&gt;"",COUNTIF(AulasValidas,B5)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:M14">
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>L4&gt;K4</formula>
+      <formula>$L4&gt;$K4</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>L4=K4</formula>
+      <formula>$L4=$K4</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>AulasValidas</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>$I$4:$I$14</formula1>
     </dataValidation>
   </dataValidations>
@@ -7498,8 +7956,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -7513,505 +7984,586 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Asignadas</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>Faltan</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (Conf)</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L4">
-        <f>COUNTIF(C4:G15,I4)</f>
-        <v/>
-      </c>
-      <c r="M4">
+      <c r="L4" s="18">
+        <f>COUNTIF(B4:F15,I4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="19">
         <f>K4-L4</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (C.P.)</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L5">
-        <f>COUNTIF(C4:G15,I5)</f>
-        <v/>
-      </c>
-      <c r="M5">
+      <c r="L5" s="18">
+        <f>COUNTIF(B4:F15,I5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
         <f>K5-L5</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Programación (Conf)</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L6">
-        <f>COUNTIF(C4:G15,I6)</f>
-        <v/>
-      </c>
-      <c r="M6">
+      <c r="L6" s="18">
+        <f>COUNTIF(B4:F15,I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="19">
         <f>K6-L6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Programación (C.P.)</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L7">
-        <f>COUNTIF(C4:G15,I7)</f>
-        <v/>
-      </c>
-      <c r="M7">
+      <c r="L7" s="18">
+        <f>COUNTIF(B4:F15,I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
         <f>K7-L7</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="F8" s="19" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (Conf)</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L8">
-        <f>COUNTIF(C4:G15,I8)</f>
-        <v/>
-      </c>
-      <c r="M8">
+      <c r="L8" s="18">
+        <f>COUNTIF(B4:F15,I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="19">
         <f>K8-L8</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (C.P.)</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L9">
-        <f>COUNTIF(C4:G15,I9)</f>
-        <v/>
-      </c>
-      <c r="M9">
+      <c r="L9" s="18">
+        <f>COUNTIF(B4:F15,I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
         <f>K9-L9</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Filosofía (Conf)</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L10">
-        <f>COUNTIF(C4:G15,I10)</f>
-        <v/>
-      </c>
-      <c r="M10">
+      <c r="L10" s="18">
+        <f>COUNTIF(B4:F15,I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
         <f>K10-L10</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="I11" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Filosofía (C.P.)</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L11">
-        <f>COUNTIF(C4:G15,I11)</f>
-        <v/>
-      </c>
-      <c r="M11">
+      <c r="L11" s="18">
+        <f>COUNTIF(B4:F15,I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
         <f>K11-L11</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>Lógica (Conf)</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L12">
-        <f>COUNTIF(C4:G15,I12)</f>
-        <v/>
-      </c>
-      <c r="M12">
+      <c r="L12" s="18">
+        <f>COUNTIF(B4:F15,I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
         <f>K12-L12</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="I13" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Lógica (C.P.)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L13">
-        <f>COUNTIF(C4:G15,I13)</f>
-        <v/>
-      </c>
-      <c r="M13">
+      <c r="L13" s="18">
+        <f>COUNTIF(B4:F15,I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
         <f>K13-L13</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Educación Física</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="L14">
-        <f>COUNTIF(C4:G15,I14)</f>
-        <v/>
-      </c>
-      <c r="M14">
+      <c r="L14" s="26">
+        <f>COUNTIF(B4:F15,I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
         <f>K14-L14</f>
         <v/>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Leyenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aula fuera del listado de la facultad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Asignatura fuera de la tabla del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sobre-planificada (asignadas &gt; frecuencia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Frecuencia exacta cumplida</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14">
+  <conditionalFormatting sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(C4&lt;&gt;"",COUNTIF($I$4:$I$14,C4)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15">
+      <formula>AND(B4&lt;&gt;"",COUNTIF($I$4:$I$14,B4)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(C5&lt;&gt;"",COUNTIF(AulasValidas,C5)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L14">
+      <formula>AND(B5&lt;&gt;"",COUNTIF(AulasValidas,B5)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:M14">
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>L4&gt;K4</formula>
+      <formula>$L4&gt;$K4</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>L4=K4</formula>
+      <formula>$L4=$K4</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>AulasValidas</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>$I$4:$I$14</formula1>
     </dataValidation>
   </dataValidations>
@@ -8025,8 +8577,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8040,365 +8605,474 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Asignadas</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>Faltan</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (Conf)</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L4">
-        <f>COUNTIF(C4:G15,I4)</f>
-        <v/>
-      </c>
-      <c r="M4">
+      <c r="L4" s="18">
+        <f>COUNTIF(B4:F15,I4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="19">
         <f>K4-L4</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="I5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (C.P.)</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L5">
-        <f>COUNTIF(C4:G15,I5)</f>
-        <v/>
-      </c>
-      <c r="M5">
+      <c r="L5" s="18">
+        <f>COUNTIF(B4:F15,I5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
         <f>K5-L5</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Programación (Conf)</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L6">
-        <f>COUNTIF(C4:G15,I6)</f>
-        <v/>
-      </c>
-      <c r="M6">
+      <c r="L6" s="18">
+        <f>COUNTIF(B4:F15,I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="19">
         <f>K6-L6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="I7" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Programación (C.P.)</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L7">
-        <f>COUNTIF(C4:G15,I7)</f>
-        <v/>
-      </c>
-      <c r="M7">
+      <c r="L7" s="18">
+        <f>COUNTIF(B4:F15,I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
         <f>K7-L7</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (Conf)</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L8">
-        <f>COUNTIF(C4:G15,I8)</f>
-        <v/>
-      </c>
-      <c r="M8">
+      <c r="L8" s="18">
+        <f>COUNTIF(B4:F15,I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="19">
         <f>K8-L8</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="I9" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (C.P.)</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L9">
-        <f>COUNTIF(C4:G15,I9)</f>
-        <v/>
-      </c>
-      <c r="M9">
+      <c r="L9" s="18">
+        <f>COUNTIF(B4:F15,I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
         <f>K9-L9</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Filosofía (Conf)</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L10">
-        <f>COUNTIF(C4:G15,I10)</f>
-        <v/>
-      </c>
-      <c r="M10">
+      <c r="L10" s="18">
+        <f>COUNTIF(B4:F15,I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
         <f>K10-L10</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="I11" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Filosofía (C.P.)</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L11">
-        <f>COUNTIF(C4:G15,I11)</f>
-        <v/>
-      </c>
-      <c r="M11">
+      <c r="L11" s="18">
+        <f>COUNTIF(B4:F15,I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
         <f>K11-L11</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>Lógica (Conf)</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L12">
-        <f>COUNTIF(C4:G15,I12)</f>
-        <v/>
-      </c>
-      <c r="M12">
+      <c r="L12" s="18">
+        <f>COUNTIF(B4:F15,I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
         <f>K12-L12</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="I13" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Lógica (C.P.)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L13">
-        <f>COUNTIF(C4:G15,I13)</f>
-        <v/>
-      </c>
-      <c r="M13">
+      <c r="L13" s="18">
+        <f>COUNTIF(B4:F15,I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
         <f>K13-L13</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Educación Física</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="L14">
-        <f>COUNTIF(C4:G15,I14)</f>
-        <v/>
-      </c>
-      <c r="M14">
+      <c r="L14" s="26">
+        <f>COUNTIF(B4:F15,I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
         <f>K14-L14</f>
         <v/>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Leyenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aula fuera del listado de la facultad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Asignatura fuera de la tabla del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sobre-planificada (asignadas &gt; frecuencia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Frecuencia exacta cumplida</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14">
+  <conditionalFormatting sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(C4&lt;&gt;"",COUNTIF($I$4:$I$14,C4)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15">
+      <formula>AND(B4&lt;&gt;"",COUNTIF($I$4:$I$14,B4)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(C5&lt;&gt;"",COUNTIF(AulasValidas,C5)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L14">
+      <formula>AND(B5&lt;&gt;"",COUNTIF(AulasValidas,B5)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:M14">
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>L4&gt;K4</formula>
+      <formula>$L4&gt;$K4</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>L4=K4</formula>
+      <formula>$L4=$K4</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>AulasValidas</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>$I$4:$I$14</formula1>
     </dataValidation>
   </dataValidations>
@@ -8412,8 +9086,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8427,365 +9114,474 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Asignadas</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>Faltan</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Turno 1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>AMI-C</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (Conf)</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L4">
-        <f>COUNTIF(C4:G15,I4)</f>
-        <v/>
-      </c>
-      <c r="M4">
+      <c r="L4" s="18">
+        <f>COUNTIF(B4:F15,I4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="19">
         <f>K4-L4</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="I5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>AMI-CP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Análisis Matemático I (C.P.)</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L5">
-        <f>COUNTIF(C4:G15,I5)</f>
-        <v/>
-      </c>
-      <c r="M5">
+      <c r="L5" s="18">
+        <f>COUNTIF(B4:F15,I5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
         <f>K5-L5</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Turno 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Pro-C</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Programación (Conf)</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L6">
-        <f>COUNTIF(C4:G15,I6)</f>
-        <v/>
-      </c>
-      <c r="M6">
+      <c r="L6" s="18">
+        <f>COUNTIF(B4:F15,I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="19">
         <f>K6-L6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="I7" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Pro-CP</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Programación (C.P.)</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L7">
-        <f>COUNTIF(C4:G15,I7)</f>
-        <v/>
-      </c>
-      <c r="M7">
+      <c r="L7" s="18">
+        <f>COUNTIF(B4:F15,I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
         <f>K7-L7</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>A1-C</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (Conf)</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L8">
-        <f>COUNTIF(C4:G15,I8)</f>
-        <v/>
-      </c>
-      <c r="M8">
+      <c r="L8" s="18">
+        <f>COUNTIF(B4:F15,I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="19">
         <f>K8-L8</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="I9" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>A1-CP</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Álgebra I (C.P.)</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L9">
-        <f>COUNTIF(C4:G15,I9)</f>
-        <v/>
-      </c>
-      <c r="M9">
+      <c r="L9" s="18">
+        <f>COUNTIF(B4:F15,I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
         <f>K9-L9</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Turno 4</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>F-C</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Filosofía (Conf)</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L10">
-        <f>COUNTIF(C4:G15,I10)</f>
-        <v/>
-      </c>
-      <c r="M10">
+      <c r="L10" s="18">
+        <f>COUNTIF(B4:F15,I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
         <f>K10-L10</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="I11" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>F-CP</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Filosofía (C.P.)</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L11">
-        <f>COUNTIF(C4:G15,I11)</f>
-        <v/>
-      </c>
-      <c r="M11">
+      <c r="L11" s="18">
+        <f>COUNTIF(B4:F15,I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
         <f>K11-L11</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Turno 5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>L-C</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>Lógica (Conf)</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L12">
-        <f>COUNTIF(C4:G15,I12)</f>
-        <v/>
-      </c>
-      <c r="M12">
+      <c r="L12" s="18">
+        <f>COUNTIF(B4:F15,I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
         <f>K12-L12</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="I13" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>L-CP</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Lógica (C.P.)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L13">
-        <f>COUNTIF(C4:G15,I13)</f>
-        <v/>
-      </c>
-      <c r="M13">
+      <c r="L13" s="18">
+        <f>COUNTIF(B4:F15,I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
         <f>K13-L13</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Turno 6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>EF</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Educación Física</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="L14">
-        <f>COUNTIF(C4:G15,I14)</f>
-        <v/>
-      </c>
-      <c r="M14">
+      <c r="L14" s="26">
+        <f>COUNTIF(B4:F15,I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
         <f>K14-L14</f>
         <v/>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Leyenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aula fuera del listado de la facultad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Asignatura fuera de la tabla del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sobre-planificada (asignadas &gt; frecuencia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Frecuencia exacta cumplida</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14">
+  <conditionalFormatting sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(C4&lt;&gt;"",COUNTIF($I$4:$I$14,C4)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15">
+      <formula>AND(B4&lt;&gt;"",COUNTIF($I$4:$I$14,B4)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(C5&lt;&gt;"",COUNTIF(AulasValidas,C5)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L14">
+      <formula>AND(B5&lt;&gt;"",COUNTIF(AulasValidas,B5)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:M14">
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>L4&gt;K4</formula>
+      <formula>$L4&gt;$K4</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>L4=K4</formula>
+      <formula>$L4=$K4</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G5 C7:G7 C9:G9 C11:G11 C13:G13 C15:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:F5 B7:F7 B9:F9 B11:F11 B13:F13 B15:F15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>AulasValidas</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:G4 C6:G6 C8:G8 C10:G10 C12:G12 C14:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F4 B6:F6 B8:F8 B10:F10 B12:F12 B14:F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="information">
       <formula1>$I$4:$I$14</formula1>
     </dataValidation>
   </dataValidations>
